--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC242"/>
+  <dimension ref="A1:AC256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21540,7 +21540,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -21552,6 +21552,27 @@
         <is>
           <t>69f8647ff9374ed4f105c605</t>
         </is>
+      </c>
+      <c r="R199" s="1" t="n">
+        <v>46148.62142402564</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>406909148324</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909148324</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V199" s="1" t="n">
+        <v>46148.62172311655</v>
       </c>
     </row>
     <row r="200">
@@ -21627,7 +21648,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -21639,6 +21660,27 @@
         <is>
           <t>69f865a55da263f75f04e768</t>
         </is>
+      </c>
+      <c r="R200" s="1" t="n">
+        <v>46148.62384760453</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>406909151733</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909151733</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V200" s="1" t="n">
+        <v>46148.62414681815</v>
       </c>
     </row>
     <row r="201">
@@ -21714,7 +21756,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -21726,6 +21768,27 @@
         <is>
           <t>69f8669583a8608fd80f0fdb</t>
         </is>
+      </c>
+      <c r="R201" s="1" t="n">
+        <v>46148.62592406256</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>406909159060</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909159060</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V201" s="1" t="n">
+        <v>46148.62622317022</v>
       </c>
     </row>
     <row r="202">
@@ -21801,7 +21864,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -21813,6 +21876,27 @@
         <is>
           <t>69f867cc2592a8ad8e0f076e</t>
         </is>
+      </c>
+      <c r="R202" s="1" t="n">
+        <v>46148.62835318306</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>406909166683</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909166683</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V202" s="1" t="n">
+        <v>46148.62865410986</v>
       </c>
     </row>
     <row r="203">
@@ -24529,7 +24613,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups8</t>
+          <t>Printify_Published_Mockups8</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -24541,6 +24625,27 @@
         <is>
           <t>69f89fda2592a8ad8e0f2e79</t>
         </is>
+      </c>
+      <c r="R231" s="1" t="n">
+        <v>46148.62056237976</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>406909147173</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909147173</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V231" s="1" t="n">
+        <v>46148.620863962</v>
       </c>
     </row>
     <row r="232">
@@ -24616,7 +24721,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups8</t>
+          <t>Printify_Published_Mockups8</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
@@ -24628,6 +24733,27 @@
         <is>
           <t>69f8a454c1f268dee601d3ad</t>
         </is>
+      </c>
+      <c r="R232" s="1" t="n">
+        <v>46148.62260030281</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>406909150037</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909150037</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V232" s="1" t="n">
+        <v>46148.6229000563</v>
       </c>
     </row>
     <row r="233">
@@ -24703,7 +24829,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -24715,6 +24841,27 @@
         <is>
           <t>69f903dec1f268dee601f679</t>
         </is>
+      </c>
+      <c r="R233" s="1" t="n">
+        <v>46148.62474737458</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>406909153504</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909153504</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V233" s="1" t="n">
+        <v>46148.6250514507</v>
       </c>
     </row>
     <row r="234">
@@ -24790,7 +24937,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -24802,6 +24949,27 @@
         <is>
           <t>69f904df97d964f736006a48</t>
         </is>
+      </c>
+      <c r="R234" s="1" t="n">
+        <v>46148.62719392258</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>406909164941</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909164941</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V234" s="1" t="n">
+        <v>46148.62749331478</v>
       </c>
     </row>
     <row r="235">
@@ -25466,27 +25634,1530 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>Ready_for_Printify</t>
+          <t>Printify_Published_Mockups5</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>2026-05-06 13:08:54 -0400</t>
-        </is>
-      </c>
-      <c r="Q242" t="inlineStr"/>
-      <c r="R242" t="inlineStr"/>
-      <c r="S242" t="inlineStr"/>
-      <c r="T242" t="inlineStr"/>
-      <c r="U242" t="inlineStr"/>
-      <c r="V242" t="inlineStr"/>
-      <c r="W242" t="inlineStr"/>
-      <c r="X242" t="inlineStr"/>
-      <c r="Y242" t="inlineStr"/>
-      <c r="Z242" t="inlineStr"/>
-      <c r="AA242" t="inlineStr"/>
-      <c r="AB242" t="inlineStr"/>
-      <c r="AC242" t="inlineStr"/>
+          <t>5/6/2026  1:34:08 PM</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>69fb7a5154fd3fbacf050c5a</t>
+        </is>
+      </c>
+      <c r="R242" s="1" t="n">
+        <v>46148.56671103009</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>406909045760</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909045760</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V242" s="1" t="n">
+        <v>46148.56716944445</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0005-FIX2</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0005-FIX2</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Forbidden Grimoire Lock 4pc 6x6 Kiss-Cut Sticker Dark Academia Laptop Journal</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>4pc Vinyl Sticker Set Forbidden Grimoire Lock Laptop Bottle Journal Dark A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Dark Academia relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Forbidden Grimoire Lock Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Embrace the dark academia aesthetic with this vintage-inspired Forbidden Grimoire Lock kiss-cut sticker.&lt;/p&gt;&lt;p&gt;Designed for study rooms, creative workspaces, shelves, gallery walls, and collectible aesthetic decor, this sticker blends niche aesthetic appeal with collectible mentor-grade artwork.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vin&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>An ornate book clasp and lock mechanism made of Corroded Iron with intricate gears, cracked glass viewing window, Kintsugi gold decorative inlay, toxic jade bioluminescent runes glowing beneath surface, dark academia aesthetic, dramatic side lighting with green mystical glow, , , , , , person, text, watermark</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0005_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0005_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P243" s="1" t="n">
+        <v>46148.57295166667</v>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>69fb7e754ce71ea8ae0c7af1</t>
+        </is>
+      </c>
+      <c r="R243" s="1" t="n">
+        <v>46148.57465741898</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>406909061109</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909061109</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V243" s="1" t="n">
+        <v>46148.57495696759</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0006-FIX1</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0006-FIX1</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>4pc Sticker Set Botanical Terrarium Lantern Vinyl Decals Laptop Bottle Dark</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>4pc Sticker Set Botanical Terrarium Lantern Vinyl Decals Laptop Bottle Dark A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Dark Academia relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Botanical Terrarium Lantern Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Embrace the dark academia aesthetic with this vintage-inspired Botanical Terrarium Lantern kiss-cut sticker.&lt;/p&gt;&lt;p&gt;Designed for study rooms, creative workspaces, shelves, gallery walls, and collectible aesthetic decor, this sticker blends niche aesthetic appeal with collectible mentor-grade artwork.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>A hanging terrarium lantern with geometric panels made of Corroded Iron framework, cracked glass panes, Kintsugi gold repair lines, toxic jade bioluminescent moss and crystalline plants inside, dark academia aesthetic, dramatic side lighting with internal green glow, , , , , , person, text, watermark</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0006_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0006_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0006_Ready_for_Steaming\Sticker-Academia-0006_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0006_Ready_for_Steaming\Sticker-Academia-0006_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0006_Ready_for_Steaming\Sticker-Academia-0006_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0006_Ready_for_Steaming\Sticker-Academia-0006_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>2026-05-06 13:53:49 -0400</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>69fb804bff28e7d4030aa67d</t>
+        </is>
+      </c>
+      <c r="R244" s="1" t="n">
+        <v>46148.59251928241</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>406909095974</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909095974</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V244" s="1" t="n">
+        <v>46148.59283591435</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0007-FIX1</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0007-FIX1</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>4pc Kiss-Cut Sticker Set Astrolabe Navigation Instrument Laptop Journal Bottle</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>4pc Kiss-Cut Sticker Set Astrolabe Navigation Instrument Laptop Journal Bottle A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Dark Academia relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Astrolabe Navigation Instrument - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Academia aesthetic piece for writers, learners, library lovers, and collectors of moody scholarly decor. Built for readers and collectors, this Astrolabe Navigation Instrument kiss-cut sticker blends literary atmosphere with vintage study-room style.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile s&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>An antique astrolabe with rotating rings made of Corroded Iron, cracked glass measurement face, Kintsugi gold degree markings, toxic jade bioluminescent pointer and constellation markers, dark academia aesthetic, dramatic side lighting with green luminous details, , , , , , person, text, watermark</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0007_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0007_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0007_Ready_for_Steaming\Sticker-Academia-0007_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0007_Ready_for_Steaming\Sticker-Academia-0007_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0007_Ready_for_Steaming\Sticker-Academia-0007_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0007_Ready_for_Steaming\Sticker-Academia-0007_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>2026-05-06 13:53:49 -0400</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>69fb819d4c6544084c0f8370</t>
+        </is>
+      </c>
+      <c r="R245" s="1" t="n">
+        <v>46148.59356574074</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>406909097469</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909097469</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V245" s="1" t="n">
+        <v>46148.59386609954</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0008-FIX1</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0008-FIX1</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Ritual Incense Censer Gothic Academia 4pc 6x6 Vinyl Sticker Reader Writer Decor</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>4pc Vinyl Sticker Set Ritual Incense Censer Gothic Academia Laptop Bottle A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Dark Academia relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Ritual Incense Censer | Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Give your study space a scholarly, moody accent with this Ritual Incense Censer kiss-cut sticker. The artwork is built around a focused visual DNA profile, so each piece feels like part of a coherent small-batch collection.&lt;/p&gt;&lt;p&gt;Use it for laptops, notebooks, reading corners, desk setups, gallery shelves, and gift bundles. The composition favors readable detail, strong mood, and giftable niche appeal without generic mass-market styling.&lt;/p&gt;&lt;ul&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>A ceremonial hanging censer with chain suspension made of Corroded Iron filigree, cracked glass viewing ports, Kintsugi gold decorative patterns, toxic jade bioluminescent smoke wisps emerging from openings, dark academia aesthetic, dramatic side lighting with green glowing vapors, , , , , , person, text, watermark</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0008_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0008_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0008_Ready_for_Steaming\Sticker-Academia-0008_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0008_Ready_for_Steaming\Sticker-Academia-0008_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0008_Ready_for_Steaming\Sticker-Academia-0008_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0008_Ready_for_Steaming\Sticker-Academia-0008_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>2026-05-06 13:53:49 -0400</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>69fb82e64c6544084c0f83d5</t>
+        </is>
+      </c>
+      <c r="R246" s="1" t="n">
+        <v>46148.59459497685</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>406909100892</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909100892</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V246" s="1" t="n">
+        <v>46148.59504747685</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0009-FIX1</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0009-FIX1</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>4pc Sticker Set Gothic Academia Cathedral Fragment Vinyl Decals Laptop Bottle</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>4pc Sticker Set Gothic Academia Cathedral Fragment Vinyl Decals Laptop Bottle A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Dark Academia relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Gothic Cathedral Fragment | Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Give your study space a scholarly, moody accent with this Gothic Cathedral Fragment kiss-cut sticker. The artwork is built around a focused visual DNA profile, so each piece feels like part of a coherent small-batch collection.&lt;/p&gt;&lt;p&gt;Use it for laptops, notebooks, reading corners, desk setups, gallery shelves, and gift bundles. The composition favors readable detail, strong mood, and giftable niche appeal without generic mass-market styling&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>A miniature gothic cathedral window arch made of Corroded Iron tracery, cracked glass stained panels, Kintsugi gold leading repairs, toxic jade bioluminescent light filtering through, architectural relic, dark academia aesthetic, dramatic side lighting with green sacred glow, , , , , , person, text, watermark</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0009_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0009_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0009_Ready_for_Steaming\Sticker-Academia-0009_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0009_Ready_for_Steaming\Sticker-Academia-0009_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0009_Ready_for_Steaming\Sticker-Academia-0009_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0009_Ready_for_Steaming\Sticker-Academia-0009_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:20:33 -0400</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>69fb868dc5114ecf420d2b93</t>
+        </is>
+      </c>
+      <c r="R247" s="1" t="n">
+        <v>46148.60340165509</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>406909114799</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909114799</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V247" s="1" t="n">
+        <v>46148.60399184027</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0010-FIX1</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0010-FIX1</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Vintage Academia Compass Rose Talisman 4pc 6x6 Sticker Sheet Literary Cozy Gift</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>4pc Kiss-Cut Sticker Set Compass Rose Talisman Laptop Journal Bottle Dark A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Dark Academia relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Compass Rose Talisman - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Academia aesthetic piece for writers, learners, library lovers, and collectors of moody scholarly decor. Built for readers and collectors, this Compass Rose Talisman kiss-cut sticker blends literary atmosphere with vintage study-room style.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for eas&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>An ornate compass rose medallion made of Corroded Iron with directional points, cracked glass center dome, Kintsugi gold cardinal markers, toxic jade bioluminescent needle and inner mechanisms visible, dark academia aesthetic, dramatic side lighting with green glowing core, , , , , , person, text, watermark</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0010_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0010_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0010_Ready_for_Steaming\Sticker-Academia-0010_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0010_Ready_for_Steaming\Sticker-Academia-0010_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0010_Ready_for_Steaming\Sticker-Academia-0010_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0010_Ready_for_Steaming\Sticker-Academia-0010_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:20:33 -0400</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>69fb8749a7afceb9f70f1956</t>
+        </is>
+      </c>
+      <c r="R248" s="1" t="n">
+        <v>46148.60472953704</v>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>406909116716</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909116716</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V248" s="1" t="n">
+        <v>46148.60507960648</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0011-FIX1</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0011-FIX1</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Apothecary Poison Vial Vintage Academia 4pc 6x6 Kiss-Cut Vinyl Desk Collector</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>4pc Vinyl Sticker Set Apothecary Poison Vial Laptop Bottle Journal Dark A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Dark Academia relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Apothecary Poison Vial - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Academia aesthetic piece for writers, learners, library lovers, and collectors of moody scholarly decor. Built for readers and collectors, this Apothecary Poison Vial kiss-cut sticker blends literary atmosphere with vintage study-room style.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for e&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>An elegant poison vial with stopper made of Corroded Iron cage holder, cracked glass bottle, Kintsugi gold label plate, toxic jade bioluminescent liquid contents glowing inside, dark academia aesthetic, dramatic side lighting with internal green luminescence, , , , , , person, text, watermark</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0011_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0011_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0011_Ready_for_Steaming\Sticker-Academia-0011_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0011_Ready_for_Steaming\Sticker-Academia-0011_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0011_Ready_for_Steaming\Sticker-Academia-0011_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0011_Ready_for_Steaming\Sticker-Academia-0011_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:20:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>69fb87aca7afceb9f70f1982</t>
+        </is>
+      </c>
+      <c r="R249" s="1" t="n">
+        <v>46148.60550216436</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>406909118000</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909118000</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V249" s="1" t="n">
+        <v>46148.60597498842</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0014-FIX1</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0014-FIX1</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>4pc Vinyl Sticker Set Microscope Observation Device Laptop Bottle Journal Dark</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>4pc Vinyl Sticker Set Microscope Observation Device Laptop Bottle Journal Dark A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Dark Academia relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Microscope Observation Device Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Embrace the dark academia aesthetic with this vintage-inspired Microscope Observation Device kiss-cut sticker.&lt;/p&gt;&lt;p&gt;Designed for study rooms, creative workspaces, shelves, gallery walls, and collectible aesthetic decor, this sticker blends niche aesthetic appeal with collectible mentor-grade artwork.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>A vintage microscope with adjustment knobs made of Corroded Iron body and stage, cracked glass lenses and specimen slide, Kintsugi gold focus ring, toxic jade bioluminescent specimen under view glowing green, dark academia aesthetic, dramatic side lighting with internal illumination, , , , , , person, text, watermark</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0014_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0014_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0014_Ready_for_Steaming\Sticker-Academia-0014_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0014_Ready_for_Steaming\Sticker-Academia-0014_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0014_Ready_for_Steaming\Sticker-Academia-0014_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0014_Ready_for_Steaming\Sticker-Academia-0014_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:20:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>69fb87efc5114ecf420d2c5a</t>
+        </is>
+      </c>
+      <c r="R250" s="1" t="n">
+        <v>46148.60636443287</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>406909119544</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909119544</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V250" s="1" t="n">
+        <v>46148.61832849537</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0015-FIX1</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0015-FIX1</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>4pc Sticker Set Skeleton Key Portal Vinyl Decals Laptop Bottle Dark Academia</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>4pc Sticker Set Skeleton Key Portal Vinyl Decals Laptop Bottle Dark Academia A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Dark Academia relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Skeleton Key Portal - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Academia aesthetic piece for writers, learners, library lovers, and collectors of moody scholarly decor. Built for readers and collectors, this Skeleton Key Portal kiss-cut sticker blends literary atmosphere with vintage study-room style.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for easy co&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>An elaborate skeleton key with ornate bow made of Corroded Iron shaft and teeth, cracked glass decorative window in handle, Kintsugi gold filigree details, toxic jade bioluminescent core glowing through key body, dark academia aesthetic, dramatic side lighting with green mystical radiance, , , , , , person, text, watermark</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0015_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0015_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0015_Ready_for_Steaming\Sticker-Academia-0015_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0015_Ready_for_Steaming\Sticker-Academia-0015_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0015_Ready_for_Steaming\Sticker-Academia-0015_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0015_Ready_for_Steaming\Sticker-Academia-0015_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:20:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>69fb8805ee663532c8017f4f</t>
+        </is>
+      </c>
+      <c r="R251" s="1" t="n">
+        <v>46148.607418125</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>406909121336</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909121336</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V251" s="1" t="n">
+        <v>46148.60772269676</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0016-FIX1</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Sticker-Academia-0016-FIX1</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>4pc Kiss-Cut Sticker Set Gothic Academia Prism Light Refractor Laptop Journal</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>4pc Kiss-Cut Sticker Set Gothic Academia Prism Light Refractor Laptop Journal A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Dark Academia relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Prism Light Refractor | Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Give your study space a scholarly, moody accent with this Prism Light Refractor kiss-cut sticker. The artwork is built around a focused visual DNA profile, so each piece feels like part of a coherent small-batch collection.&lt;/p&gt;&lt;p&gt;Use it for laptops, notebooks, reading corners, desk setups, gallery shelves, and gift bundles. The composition favors readable detail, strong mood, and giftable niche appeal without generic mass-market styling.&lt;/p&gt;&lt;ul&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>A suspended geometric prism on chains made of Corroded Iron mounting hardware, cracked glass crystalline prism body, Kintsugi gold edge repairs, toxic jade bioluminescent light refracting through fractures creating green spectrum, dark academia aesthetic, dramatic side lighting with internal glow dispersion, , , , , , person, text, watermark</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0016_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0016_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0016_Ready_for_Steaming\Sticker-Academia-0016_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0016_Ready_for_Steaming\Sticker-Academia-0016_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0016_Ready_for_Steaming\Sticker-Academia-0016_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Academia-0016_Ready_for_Steaming\Sticker-Academia-0016_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:20:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>69fb8811e5402c478e03108f</t>
+        </is>
+      </c>
+      <c r="R252" s="1" t="n">
+        <v>46148.60832354167</v>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>406909122790</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909122790</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V252" s="1" t="n">
+        <v>46148.60862274306</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0001-FIX1</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0001-FIX1</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>4pc Sticker Set Mindful Zen Koi Pond Vinyl Decals Laptop Bottle Zen Aesthetic</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>4pc Sticker Set Mindful Zen Koi Pond Vinyl Decals Laptop Bottle Zen Aesthetic A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Zen Aesthetic relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Zen Koi Pond Sticker | Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Add a quiet mindful accent to your workspace with this Zen Koi Pond Sticker kiss-cut sticker. The artwork is built around a focused visual DNA profile, so each piece feels like part of a coherent small-batch collection.&lt;/p&gt;&lt;p&gt;Use it for laptops, notebooks, reading corners, desk setups, gallery shelves, and gift bundles. The composition favors readable detail, strong mood, and giftable niche appeal without generic mass-market styling.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>A single, serene koi fish swimming in a minimalist pond, its scales rendered in Translucent Imperial Jade with Kintsugi Gold Veins, internal bioluminescent glow from within the jade, hyper-detailed, macro photography, studio lighting, , , , , 3D relief effect, sharp focus,</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0001_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0001_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0001_Ready_for_Steaming\Sticker-Zen-0001_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0001_Ready_for_Steaming\Sticker-Zen-0001_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0001_Ready_for_Steaming\Sticker-Zen-0001_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0001_Ready_for_Steaming\Sticker-Zen-0001_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:20:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>69fb881f2b1da07362014876</t>
+        </is>
+      </c>
+      <c r="R253" s="1" t="n">
+        <v>46148.60933324074</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>406909124585</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909124585</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V253" s="1" t="n">
+        <v>46148.60963540509</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0002-FIX1</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0002-FIX1</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Minimal Zen Bonsai Tree of Serenity 4pc 6x6 Sticker Sheet Serene Mindful Clean</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>4pc Kiss-Cut Sticker Set Bonsai Tree of Serenity Laptop Journal Bottle Zen A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Zen Aesthetic relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Bonsai Tree of Serenity Sticker - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Zen aesthetic piece for students, remote workers, yoga lovers, and anyone building a serene everyday space. Designed for peaceful desks, journals, and small rituals, this Bonsai Tree of Serenity Sticker kiss-cut sticker carries a clean Zen mood.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay s&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>A miniature bonsai tree, its trunk and branches crafted from Petrified Driftwood, with leaves of glowing Moss Agate, a single crystal geode at its base pulsing with soft light, hyper-realistic, intricate details, , , , , 3D relief effect, sharp focus,</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0002_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0002_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0002_Ready_for_Steaming\Sticker-Zen-0002_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0002_Ready_for_Steaming\Sticker-Zen-0002_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0002_Ready_for_Steaming\Sticker-Zen-0002_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0002_Ready_for_Steaming\Sticker-Zen-0002_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:20:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>69fb882c54fd3fbacf051371</t>
+        </is>
+      </c>
+      <c r="R254" s="1" t="n">
+        <v>46148.61011664352</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>406909125700</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909125700</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V254" s="1" t="n">
+        <v>46148.61041673611</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0003-FIX1</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0003-FIX1</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Lotus Mandala Mindful Zen 4pc 6x6 Vinyl Sticker Yoga Minimalist Gift Gift Decor</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>4pc Vinyl Sticker Set Lotus Mandala Mindful Zen Laptop Bottle Journal Zen A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Zen Aesthetic relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Lotus Mandala Sticker | Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Add a quiet mindful accent to your workspace with this Lotus Mandala Sticker kiss-cut sticker. The artwork is built around a focused visual DNA profile, so each piece feels like part of a coherent small-batch collection.&lt;/p&gt;&lt;p&gt;Use it for laptops, notebooks, reading corners, desk setups, gallery shelves, and gift bundles. The composition favors readable detail, strong mood, and giftable niche appeal without generic mass-market styling.&lt;/p&gt;&lt;ul&gt;&lt;l&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>A geometric mandala with a blooming lotus at its center, petals made of layered Mother of Pearl, the intricate patterns inlaid with Platinum Filigree that emits a soft, divine light, sacred geometry, , , , , 3D relief effect, sharp focus,</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0003_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0003_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0003_Ready_for_Steaming\Sticker-Zen-0003_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0003_Ready_for_Steaming\Sticker-Zen-0003_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0003_Ready_for_Steaming\Sticker-Zen-0003_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0003_Ready_for_Steaming\Sticker-Zen-0003_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:20:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>69fb883cce0d8cb5570fa7cc</t>
+        </is>
+      </c>
+      <c r="R255" s="1" t="n">
+        <v>46148.61093628472</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>406909126789</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909126789</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V255" s="1" t="n">
+        <v>46148.61123732639</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0004-FIX1</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0004-FIX1</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>4pc Sticker Set Stone Guardian Lion Mindful Zen Vinyl Decals Laptop Bottle Zen</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>4pc Sticker Set Stone Guardian Lion Mindful Zen Vinyl Decals Laptop Bottle Zen A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Zen Aesthetic relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Stone Guardian Lion Sticker | Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Add a quiet mindful accent to your workspace with this Stone Guardian Lion Sticker kiss-cut sticker. The artwork is built around a focused visual DNA profile, so each piece feels like part of a coherent small-batch collection.&lt;/p&gt;&lt;p&gt;Use it for laptops, notebooks, reading corners, desk setups, gallery shelves, and gift bundles. The composition favors readable detail, strong mood, and giftable niche appeal without generic mass-market stylin&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>A mythical Shishi guardian lion statue, carved from Volcanic Basalt, with a mane of flowing Obsidian strands and eyes that are polished Moonstone orbs glowing with inner wisdom, majestic, mythical, , , , , 3D relief effect, sharp focus,</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0004_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0004_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0004_Ready_for_Steaming\Sticker-Zen-0004_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0004_Ready_for_Steaming\Sticker-Zen-0004_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0004_Ready_for_Steaming\Sticker-Zen-0004_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0004_Ready_for_Steaming\Sticker-Zen-0004_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:20:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>69fb8849e5402c478e0310af</t>
+        </is>
+      </c>
+      <c r="R256" s="1" t="n">
+        <v>46148.61170621528</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>406909127704</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909127704</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V256" s="1" t="n">
+        <v>46148.61200826389</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC256"/>
+  <dimension ref="A1:V275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,41 +530,6 @@
           <t>External_Sync_Timestamp</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Traffic_Experiment_Group</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Traffic_Experiment_Start</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Metadata_Sync_Status</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Online_Cover_Result</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Online_Cover_Note</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Online_Cover_Best_U</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Online_Cover_Audit_Timestamp</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -914,42 +879,7 @@
         </is>
       </c>
       <c r="V5" s="1" t="n">
-        <v>46146.56397810185</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>LIKELY_COVER</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>cover closer than U1 by 169</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:16:48-04:00</t>
-        </is>
+        <v>46148.85707743056</v>
       </c>
     </row>
     <row r="6">
@@ -1025,7 +955,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Printify_SourceRepair_Failed</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1036,59 +966,6 @@
       <c r="Q6" t="inlineStr">
         <is>
           <t>69f198efea1f992ded0e90e7</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>406892409123</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892409123</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V6" s="1" t="n">
-        <v>46146.56403233796</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>U4 closer by 194</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>U4</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:17:00-04:00</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1042,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1176,59 +1053,6 @@
       <c r="Q7" t="inlineStr">
         <is>
           <t>69f19b945494697f0d01b78c</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>406892409348</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892409348</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V7" s="1" t="n">
-        <v>46146.5641387963</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>U3 closer by 196</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>U3</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:17:10-04:00</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1129,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1316,59 +1140,6 @@
       <c r="Q8" t="inlineStr">
         <is>
           <t>69f1a56756390ef4cd09be1e</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>406892409645</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892409645</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V8" s="1" t="n">
-        <v>46146.56418288194</v>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>U3 closer by 200</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>U3</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:17:20-04:00</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1216,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1456,59 +1227,6 @@
       <c r="Q9" t="inlineStr">
         <is>
           <t>69f1a630de3c2e09400f9c5f</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>406892409836</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892409836</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V9" s="1" t="n">
-        <v>46146.56423710648</v>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>U2 closer by 193</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:17:29-04:00</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1303,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1596,59 +1314,6 @@
       <c r="Q10" t="inlineStr">
         <is>
           <t>69f1a6acc2501ebbc40ac2e5</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>406892410017</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892410017</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V10" s="1" t="n">
-        <v>46146.56430361111</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>U2 closer by 203</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:17:39-04:00</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1390,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1736,59 +1401,6 @@
       <c r="Q11" t="inlineStr">
         <is>
           <t>69f1a724785a37b0240adad9</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>406892410190</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892410190</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V11" s="1" t="n">
-        <v>46146.56439167824</v>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>U3 closer by 250</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>U3</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:17:48-04:00</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1477,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1876,59 +1488,6 @@
       <c r="Q12" t="inlineStr">
         <is>
           <t>69f1a7b0cfb25d6b6f0f10f7</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>406892410307</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892410307</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V12" s="1" t="n">
-        <v>46146.56445378473</v>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>U1 closer by 203</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:17:57-04:00</t>
         </is>
       </c>
     </row>
@@ -2087,7 +1646,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2098,59 +1657,6 @@
       <c r="Q14" t="inlineStr">
         <is>
           <t>69f1a833592cc603cd0a91fd</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>406892410440</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892410440</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V14" s="1" t="n">
-        <v>46146.56448755787</v>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>U1 closer by 231</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:18:06-04:00</t>
         </is>
       </c>
     </row>
@@ -2227,7 +1733,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2238,59 +1744,6 @@
       <c r="Q15" t="inlineStr">
         <is>
           <t>69f1a8b40bc0bf405305ef2b</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>406892411034</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892411034</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V15" s="1" t="n">
-        <v>46146.56452634259</v>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>U3 closer by 155</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>U3</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:18:15-04:00</t>
         </is>
       </c>
     </row>
@@ -2367,7 +1820,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2378,59 +1831,6 @@
       <c r="Q16" t="inlineStr">
         <is>
           <t>69f1a92ade3c2e09400f9e44</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>406892411436</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892411436</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V16" s="1" t="n">
-        <v>46146.56507023148</v>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>U3 closer by 192</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>U3</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:18:25-04:00</t>
         </is>
       </c>
     </row>
@@ -2507,7 +1907,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2518,59 +1918,6 @@
       <c r="Q17" t="inlineStr">
         <is>
           <t>69f1a99c785a37b0240adc94</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>406892411931</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892411931</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V17" s="1" t="n">
-        <v>46146.56512155093</v>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>U1 closer by 195</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:18:35-04:00</t>
         </is>
       </c>
     </row>
@@ -2647,7 +1994,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2658,59 +2005,6 @@
       <c r="Q18" t="inlineStr">
         <is>
           <t>69f1ab9a63935da7e8064504</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>406892412365</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892412365</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V18" s="1" t="n">
-        <v>46146.565155</v>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>U1 closer by 228</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:18:44-04:00</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2081,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2798,59 +2092,6 @@
       <c r="Q19" t="inlineStr">
         <is>
           <t>69f1ac1804ea1d3ba9005c58</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>406892412612</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892412612</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V19" s="1" t="n">
-        <v>46146.56521565972</v>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>U1 closer by 215</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:18:56-04:00</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2168,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2938,59 +2179,6 @@
       <c r="Q20" t="inlineStr">
         <is>
           <t>69f1ac9740c796ee97057c83</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>406892412789</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892412789</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V20" s="1" t="n">
-        <v>46146.56525001158</v>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>U2 closer by 195</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:19:07-04:00</t>
         </is>
       </c>
     </row>
@@ -3067,7 +2255,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3078,59 +2266,6 @@
       <c r="Q21" t="inlineStr">
         <is>
           <t>69f1ad18c59fe705400bacbf</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>406892413076</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892413076</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V21" s="1" t="n">
-        <v>46146.5652908449</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>U1 closer by 334</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:19:20-04:00</t>
         </is>
       </c>
     </row>
@@ -3289,7 +2424,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3300,59 +2435,6 @@
       <c r="Q23" t="inlineStr">
         <is>
           <t>69f1ad9bbb6f6dd6270dc5df</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>406892413333</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892413333</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V23" s="1" t="n">
-        <v>46146.56532945602</v>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>U1 closer by 212</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:19:29-04:00</t>
         </is>
       </c>
     </row>
@@ -3429,7 +2511,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3440,59 +2522,6 @@
       <c r="Q24" t="inlineStr">
         <is>
           <t>69f1aef4bb6f6dd6270dc7d5</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>406892413714</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892413714</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V24" s="1" t="n">
-        <v>46146.56536409722</v>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>A_TITLE_INTENT_REWRITE</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>SYNCED_PRINTIFY_TITLE_DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>U2 closer by 193</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:19:38-04:00</t>
         </is>
       </c>
     </row>
@@ -3569,7 +2598,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3580,44 +2609,6 @@
       <c r="Q25" t="inlineStr">
         <is>
           <t>69f1af85bb6f6dd6270dc848</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>406892413966</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892413966</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V25" s="1" t="n">
-        <v>46146.56541054398</v>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>U4 closer by 231</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>U4</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:19:50-04:00</t>
         </is>
       </c>
     </row>
@@ -3723,37 +2714,7 @@
         </is>
       </c>
       <c r="V26" s="1" t="n">
-        <v>46146.56545582176</v>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>B_COVER_QA_PRIORITY</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>LIKELY_COVER</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>cover closer than U2 by 206</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:20:01-04:00</t>
-        </is>
+        <v>46148.85709412037</v>
       </c>
     </row>
     <row r="27">
@@ -3911,7 +2872,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3922,54 +2883,6 @@
       <c r="Q28" t="inlineStr">
         <is>
           <t>69f1b1ab63935da7e8064bab</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>406892414235</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892414235</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V28" s="1" t="n">
-        <v>46146.56548982639</v>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>B_COVER_QA_PRIORITY</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>U4 closer by 213</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>U4</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:20:09-04:00</t>
         </is>
       </c>
     </row>
@@ -4128,7 +3041,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4139,44 +3052,6 @@
       <c r="Q30" t="inlineStr">
         <is>
           <t>69f1b2c4d3e196c79b0fdaec</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>406892414471</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892414471</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V30" s="1" t="n">
-        <v>46146.56554579861</v>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>U2 closer by 238</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:20:19-04:00</t>
         </is>
       </c>
     </row>
@@ -4253,7 +3128,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4264,54 +3139,6 @@
       <c r="Q31" t="inlineStr">
         <is>
           <t>69f1cb4ef6b83091a50959f5</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>406892327989</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892327989</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V31" s="1" t="n">
-        <v>46146.56563604167</v>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>B_COVER_QA_PRIORITY</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>U4 closer by 331</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>U4</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>2026-05-06T00:06:07-04:00</t>
         </is>
       </c>
     </row>
@@ -4388,7 +3215,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PublishExternalPending_Mockups4</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4400,6 +3227,9 @@
         <is>
           <t>69f1cc732f305b371c05b1d7</t>
         </is>
+      </c>
+      <c r="V32" s="1" t="n">
+        <v>46148.85710967593</v>
       </c>
     </row>
     <row r="33">
@@ -4475,7 +3305,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4486,54 +3316,6 @@
       <c r="Q33" t="inlineStr">
         <is>
           <t>69f1ce0f11e0745fcb0da03a</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>406892414741</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406892414741</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V33" s="1" t="n">
-        <v>46146.56574040509</v>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>B_COVER_QA_PRIORITY</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>U2 closer by 253</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:20:38-04:00</t>
         </is>
       </c>
     </row>
@@ -4692,7 +3474,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PublishExternalPending_Mockups4</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4704,6 +3486,9 @@
         <is>
           <t>69f1cee189347116c004f529</t>
         </is>
+      </c>
+      <c r="V35" s="1" t="n">
+        <v>46148.85712829861</v>
       </c>
     </row>
     <row r="36">
@@ -4861,7 +3646,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PublishExternalPending_Mockups4</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4873,6 +3658,9 @@
         <is>
           <t>69f1cf9911e0745fcb0da15f</t>
         </is>
+      </c>
+      <c r="V37" s="1" t="n">
+        <v>46148.85714457176</v>
       </c>
     </row>
     <row r="38">
@@ -4948,7 +3736,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PublishExternalPending_Mockups4</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4960,6 +3748,9 @@
         <is>
           <t>69f1d04a0482f56ada0cf347</t>
         </is>
+      </c>
+      <c r="V38" s="1" t="n">
+        <v>46148.85716043982</v>
       </c>
     </row>
     <row r="39">
@@ -5117,7 +3908,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PublishExternalPending_Mockups4</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5129,6 +3920,9 @@
         <is>
           <t>69f1d1003a934dcd94086687</t>
         </is>
+      </c>
+      <c r="V40" s="1" t="n">
+        <v>46148.85717578704</v>
       </c>
     </row>
     <row r="41">
@@ -5204,7 +3998,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PublishExternalPending_Mockups4</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5216,6 +4010,9 @@
         <is>
           <t>69f1d1ed11e0745fcb0da2ea</t>
         </is>
+      </c>
+      <c r="V41" s="1" t="n">
+        <v>46148.85719202546</v>
       </c>
     </row>
     <row r="42">
@@ -5291,7 +4088,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PublishExternalPending_Mockups4</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5303,6 +4100,9 @@
         <is>
           <t>69f1d2a9f6b83091a5095eea</t>
         </is>
+      </c>
+      <c r="V42" s="1" t="n">
+        <v>46148.85721072917</v>
       </c>
     </row>
     <row r="43">
@@ -5378,7 +4178,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PublishExternalPending_Mockups4</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5390,6 +4190,9 @@
         <is>
           <t>69f1d35c89347116c004f871</t>
         </is>
+      </c>
+      <c r="V43" s="1" t="n">
+        <v>46148.85722725694</v>
       </c>
     </row>
     <row r="44">
@@ -5465,7 +4268,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PublishExternalPending_Mockups4</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5477,6 +4280,9 @@
         <is>
           <t>69f1d44bf6b83091a5095fca</t>
         </is>
+      </c>
+      <c r="V44" s="1" t="n">
+        <v>46148.8572454051</v>
       </c>
     </row>
     <row r="45">
@@ -5634,7 +4440,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PublishExternalPending_Mockups4</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5646,6 +4452,9 @@
         <is>
           <t>69f1d4f9bdda7e777002a696</t>
         </is>
+      </c>
+      <c r="V46" s="1" t="n">
+        <v>46148.85727467592</v>
       </c>
     </row>
     <row r="47">
@@ -5721,7 +4530,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5732,54 +4541,6 @@
       <c r="Q47" t="inlineStr">
         <is>
           <t>69f1db9382fcf925cf08206d</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>406902593931</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406902593931</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V47" s="1" t="n">
-        <v>46146.56618284722</v>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>B_COVER_QA_PRIORITY</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>U2 closer by 336</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:20:47-04:00</t>
         </is>
       </c>
     </row>
@@ -5856,7 +4617,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5867,44 +4628,6 @@
       <c r="Q48" t="inlineStr">
         <is>
           <t>69f2192ae64c9f31b70f2dbd</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>406902614234</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406902614234</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V48" s="1" t="n">
-        <v>46146.56624112269</v>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>U1 closer by 333</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:20:56-04:00</t>
         </is>
       </c>
     </row>
@@ -6010,37 +4733,7 @@
         </is>
       </c>
       <c r="V49" s="1" t="n">
-        <v>46146.56630510417</v>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>B_COVER_QA_PRIORITY</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>U3 closer by 295</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>U3</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:21:05-04:00</t>
-        </is>
+        <v>46148.857313125</v>
       </c>
     </row>
     <row r="50">
@@ -6145,37 +4838,7 @@
         </is>
       </c>
       <c r="V50" s="1" t="n">
-        <v>46146.56637670139</v>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>B_COVER_QA_PRIORITY</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>U4 closer by 290</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>U4</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:21:15-04:00</t>
-        </is>
+        <v>46148.85735475695</v>
       </c>
     </row>
     <row r="51">
@@ -6280,37 +4943,7 @@
         </is>
       </c>
       <c r="V51" s="1" t="n">
-        <v>46146.56642175926</v>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>B_COVER_QA_PRIORITY</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>U4 closer by 274</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>U4</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:21:24-04:00</t>
-        </is>
+        <v>46148.85737456018</v>
       </c>
     </row>
     <row r="52">
@@ -6386,7 +5019,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PublishExternalPending_Mockups4</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6398,6 +5031,9 @@
         <is>
           <t>69f21bba9b469f716d0e4e42</t>
         </is>
+      </c>
+      <c r="V52" s="1" t="n">
+        <v>46148.85739521991</v>
       </c>
     </row>
     <row r="53">
@@ -6502,37 +5138,7 @@
         </is>
       </c>
       <c r="V53" s="1" t="n">
-        <v>46146.5665090625</v>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>B_COVER_QA_PRIORITY</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>U4 closer by 321</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>U4</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:21:33-04:00</t>
-        </is>
+        <v>46148.85741126158</v>
       </c>
     </row>
     <row r="54">
@@ -6637,37 +5243,7 @@
         </is>
       </c>
       <c r="V54" s="1" t="n">
-        <v>46146.56655745371</v>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>B_COVER_QA_PRIORITY</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>U2 closer by 277</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:21:43-04:00</t>
-        </is>
+        <v>46148.85743253472</v>
       </c>
     </row>
     <row r="55">
@@ -6772,37 +5348,7 @@
         </is>
       </c>
       <c r="V55" s="1" t="n">
-        <v>46146.566620625</v>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>B_COVER_QA_PRIORITY</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>U3 closer by 305</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>U3</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:21:52-04:00</t>
-        </is>
+        <v>46148.85745373843</v>
       </c>
     </row>
     <row r="56">
@@ -6907,37 +5453,7 @@
         </is>
       </c>
       <c r="V56" s="1" t="n">
-        <v>46146.56668416667</v>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>B_COVER_QA_PRIORITY</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>U3 closer by 258</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>U3</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:22:02-04:00</t>
-        </is>
+        <v>46148.85748322916</v>
       </c>
     </row>
     <row r="57">
@@ -7042,37 +5558,7 @@
         </is>
       </c>
       <c r="V57" s="1" t="n">
-        <v>46146.56673005787</v>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>B_COVER_QA_PRIORITY</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>U2 closer by 230</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:22:11-04:00</t>
-        </is>
+        <v>46148.85750754629</v>
       </c>
     </row>
     <row r="58">
@@ -7177,37 +5663,7 @@
         </is>
       </c>
       <c r="V58" s="1" t="n">
-        <v>46146.56677590278</v>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>B_COVER_QA_PRIORITY</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>U2 closer by 331</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:22:21-04:00</t>
-        </is>
+        <v>46148.85752447916</v>
       </c>
     </row>
     <row r="59">
@@ -7312,37 +5768,7 @@
         </is>
       </c>
       <c r="V59" s="1" t="n">
-        <v>46146.56687314815</v>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>C_HOLDOUT_CONTROL</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>U1 closer by 291</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:22:30-04:00</t>
-        </is>
+        <v>46148.85754021991</v>
       </c>
     </row>
     <row r="60">
@@ -7447,37 +5873,7 @@
         </is>
       </c>
       <c r="V60" s="1" t="n">
-        <v>46146.56692706019</v>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>C_HOLDOUT_CONTROL</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>U1 closer by 258</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:22:39-04:00</t>
-        </is>
+        <v>46148.85755953703</v>
       </c>
     </row>
     <row r="61">
@@ -7582,37 +5978,7 @@
         </is>
       </c>
       <c r="V61" s="1" t="n">
-        <v>46146.68457</v>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>C_HOLDOUT_CONTROL</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>U2 closer by 287</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:22:48-04:00</t>
-        </is>
+        <v>46148.85758619213</v>
       </c>
     </row>
     <row r="62">
@@ -7717,37 +6083,7 @@
         </is>
       </c>
       <c r="V62" s="1" t="n">
-        <v>46146.56709229167</v>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>C_HOLDOUT_CONTROL</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>U1 closer by 250</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:22:59-04:00</t>
-        </is>
+        <v>46148.85760666666</v>
       </c>
     </row>
     <row r="63">
@@ -7852,37 +6188,7 @@
         </is>
       </c>
       <c r="V63" s="1" t="n">
-        <v>46146.56714460648</v>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>C_HOLDOUT_CONTROL</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>U1 closer by 262</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:23:09-04:00</t>
-        </is>
+        <v>46148.85762224537</v>
       </c>
     </row>
     <row r="64">
@@ -7987,37 +6293,7 @@
         </is>
       </c>
       <c r="V64" s="1" t="n">
-        <v>46146.56718086806</v>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>C_HOLDOUT_CONTROL</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>U2 closer by 288</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:23:20-04:00</t>
-        </is>
+        <v>46148.8576396875</v>
       </c>
     </row>
     <row r="65">
@@ -8122,37 +6398,7 @@
         </is>
       </c>
       <c r="V65" s="1" t="n">
-        <v>46146.56724354166</v>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>C_HOLDOUT_CONTROL</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>U2 closer by 255</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:23:32-04:00</t>
-        </is>
+        <v>46148.85765802083</v>
       </c>
     </row>
     <row r="66">
@@ -8257,37 +6503,7 @@
         </is>
       </c>
       <c r="V66" s="1" t="n">
-        <v>46146.56729914352</v>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>C_HOLDOUT_CONTROL</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>U2 closer by 295</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:23:41-04:00</t>
-        </is>
+        <v>46148.85767342593</v>
       </c>
     </row>
     <row r="67">
@@ -8392,37 +6608,7 @@
         </is>
       </c>
       <c r="V67" s="1" t="n">
-        <v>46146.56735164352</v>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>C_HOLDOUT_CONTROL</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>U1 closer by 309</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:23:52-04:00</t>
-        </is>
+        <v>46148.85769063657</v>
       </c>
     </row>
     <row r="68">
@@ -8498,7 +6684,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PublishExternalPending_Mockups4</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8511,8 +6697,8 @@
           <t>69f25f0db0d6b88b28061022</t>
         </is>
       </c>
-      <c r="R68" s="1" t="n">
-        <v>46146.44556628472</v>
+      <c r="V68" s="1" t="n">
+        <v>46148.85771094907</v>
       </c>
     </row>
     <row r="69">
@@ -8588,7 +6774,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PublishExternalPending_Mockups4</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8601,8 +6787,8 @@
           <t>69f25faf29c1d0349a00ecec</t>
         </is>
       </c>
-      <c r="R69" s="1" t="n">
-        <v>46146.44792203703</v>
+      <c r="V69" s="1" t="n">
+        <v>46148.85773053241</v>
       </c>
     </row>
     <row r="70">
@@ -8691,9 +6877,6 @@
           <t>69f26062cd8d04605103d10b</t>
         </is>
       </c>
-      <c r="R70" s="1" t="n">
-        <v>46146.45031326389</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>406903753067</t>
@@ -8710,37 +6893,7 @@
         </is>
       </c>
       <c r="V70" s="1" t="n">
-        <v>46146.56754122685</v>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>C_HOLDOUT_CONTROL</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>U4 closer by 301</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>U4</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:24:03-04:00</t>
-        </is>
+        <v>46148.85774657407</v>
       </c>
     </row>
     <row r="71">
@@ -8829,9 +6982,6 @@
           <t>69f261185f78c14a7b0a4b29</t>
         </is>
       </c>
-      <c r="R71" s="1" t="n">
-        <v>46146.45257929398</v>
-      </c>
       <c r="S71" t="inlineStr">
         <is>
           <t>406903757240</t>
@@ -8848,37 +6998,7 @@
         </is>
       </c>
       <c r="V71" s="1" t="n">
-        <v>46146.56759136574</v>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>C_HOLDOUT_CONTROL</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>U2 closer by 207</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:24:13-04:00</t>
-        </is>
+        <v>46148.85776375</v>
       </c>
     </row>
     <row r="72">
@@ -8967,9 +7087,6 @@
           <t>69f261cd5269e3325904b816</t>
         </is>
       </c>
-      <c r="R72" s="1" t="n">
-        <v>46146.45524340278</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>406903762328</t>
@@ -8986,37 +7103,7 @@
         </is>
       </c>
       <c r="V72" s="1" t="n">
-        <v>46146.56764372685</v>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>C_HOLDOUT_CONTROL</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-05 18:22:20 </t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>U1 closer by 214</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:24:24-04:00</t>
-        </is>
+        <v>46148.85778013889</v>
       </c>
     </row>
     <row r="73">
@@ -15597,27 +13684,7 @@
         </is>
       </c>
       <c r="V151" s="1" t="n">
-        <v>46146.56767815972</v>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA151" t="inlineStr">
-        <is>
-          <t>U1 closer by 133</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:30:54-04:00</t>
-        </is>
+        <v>46148.85780189815</v>
       </c>
     </row>
     <row r="152">
@@ -15722,27 +13789,7 @@
         </is>
       </c>
       <c r="V152" s="1" t="n">
-        <v>46146.68487846065</v>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA152" t="inlineStr">
-        <is>
-          <t>close distances cover=0 U1=0</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:31:14-04:00</t>
-        </is>
+        <v>46148.85782984953</v>
       </c>
     </row>
     <row r="153">
@@ -15847,27 +13894,7 @@
         </is>
       </c>
       <c r="V153" s="1" t="n">
-        <v>46146.56794364583</v>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>U1 closer by 29</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:31:26-04:00</t>
-        </is>
+        <v>46148.8578553125</v>
       </c>
     </row>
     <row r="154">
@@ -15972,27 +13999,7 @@
         </is>
       </c>
       <c r="V154" s="1" t="n">
-        <v>46146.56800751157</v>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>close distances cover=268 U1=268</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:31:40-04:00</t>
-        </is>
+        <v>46148.85788055556</v>
       </c>
     </row>
     <row r="155">
@@ -16097,27 +14104,7 @@
         </is>
       </c>
       <c r="V155" s="1" t="n">
-        <v>46146.56805144676</v>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>U1 closer by 50</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:31:57-04:00</t>
-        </is>
+        <v>46148.85789751157</v>
       </c>
     </row>
     <row r="156">
@@ -16222,27 +14209,7 @@
         </is>
       </c>
       <c r="V156" s="1" t="n">
-        <v>46146.56811009259</v>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>LIKELY_SINGLE_U_MISMATCH</t>
-        </is>
-      </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>U1 closer by 230</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:32:10-04:00</t>
-        </is>
+        <v>46148.85791638889</v>
       </c>
     </row>
     <row r="157">
@@ -16347,27 +14314,7 @@
         </is>
       </c>
       <c r="V157" s="1" t="n">
-        <v>46146.56819142361</v>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>close distances cover=215 U1=215</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:32:21-04:00</t>
-        </is>
+        <v>46148.85793385417</v>
       </c>
     </row>
     <row r="158">
@@ -16472,27 +14419,7 @@
         </is>
       </c>
       <c r="V158" s="1" t="n">
-        <v>46146.56825415509</v>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>close distances cover=189 U1=189</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:32:38-04:00</t>
-        </is>
+        <v>46148.85795111111</v>
       </c>
     </row>
     <row r="159">
@@ -16597,27 +14524,7 @@
         </is>
       </c>
       <c r="V159" s="1" t="n">
-        <v>46146.56832721065</v>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>close distances cover=151 U1=151</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:32:49-04:00</t>
-        </is>
+        <v>46148.85797262732</v>
       </c>
     </row>
     <row r="160">
@@ -16722,27 +14629,7 @@
         </is>
       </c>
       <c r="V160" s="1" t="n">
-        <v>46146.56844543981</v>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>close distances cover=122 U1=122</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:33:02-04:00</t>
-        </is>
+        <v>46148.85799984954</v>
       </c>
     </row>
     <row r="161">
@@ -16847,27 +14734,7 @@
         </is>
       </c>
       <c r="V161" s="1" t="n">
-        <v>46146.56853511574</v>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>close distances cover=361 U1=361</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:33:14-04:00</t>
-        </is>
+        <v>46148.85802462963</v>
       </c>
     </row>
     <row r="162">
@@ -16972,27 +14839,7 @@
         </is>
       </c>
       <c r="V162" s="1" t="n">
-        <v>46146.56859777778</v>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>close distances cover=173 U1=173</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:33:27-04:00</t>
-        </is>
+        <v>46148.85804067129</v>
       </c>
     </row>
     <row r="163">
@@ -17097,27 +14944,7 @@
         </is>
       </c>
       <c r="V163" s="1" t="n">
-        <v>46146.56866961806</v>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>close distances cover=234 U1=234</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:33:41-04:00</t>
-        </is>
+        <v>46148.85805715278</v>
       </c>
     </row>
     <row r="164">
@@ -17222,27 +15049,7 @@
         </is>
       </c>
       <c r="V164" s="1" t="n">
-        <v>46146.56874165509</v>
-      </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>close distances cover=167 U1=167</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:33:55-04:00</t>
-        </is>
+        <v>46148.85807456019</v>
       </c>
     </row>
     <row r="165">
@@ -17347,27 +15154,7 @@
         </is>
       </c>
       <c r="V165" s="1" t="n">
-        <v>46146.5687962963</v>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>close distances cover=169 U1=169</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:34:09-04:00</t>
-        </is>
+        <v>46148.85809606482</v>
       </c>
     </row>
     <row r="166">
@@ -17472,27 +15259,7 @@
         </is>
       </c>
       <c r="V166" s="1" t="n">
-        <v>46146.56894077546</v>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>close distances cover=169 U1=169</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:34:21-04:00</t>
-        </is>
+        <v>46148.85813554398</v>
       </c>
     </row>
     <row r="167">
@@ -17597,27 +15364,7 @@
         </is>
       </c>
       <c r="V167" s="1" t="n">
-        <v>46146.56903094907</v>
-      </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA167" t="inlineStr">
-        <is>
-          <t>close distances cover=213 U1=213</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:34:34-04:00</t>
-        </is>
+        <v>46148.85817045139</v>
       </c>
     </row>
     <row r="168">
@@ -17722,27 +15469,7 @@
         </is>
       </c>
       <c r="V168" s="1" t="n">
-        <v>46146.56915033565</v>
-      </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA168" t="inlineStr">
-        <is>
-          <t>close distances cover=251 U1=251</t>
-        </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:34:50-04:00</t>
-        </is>
+        <v>46148.85819532407</v>
       </c>
     </row>
     <row r="169">
@@ -17847,27 +15574,7 @@
         </is>
       </c>
       <c r="V169" s="1" t="n">
-        <v>46146.56923842592</v>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA169" t="inlineStr">
-        <is>
-          <t>close distances cover=255 U1=255</t>
-        </is>
-      </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:35:00-04:00</t>
-        </is>
+        <v>46148.85821446759</v>
       </c>
     </row>
     <row r="170">
@@ -17972,27 +15679,7 @@
         </is>
       </c>
       <c r="V170" s="1" t="n">
-        <v>46146.56930200232</v>
-      </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>close distances cover=1 U1=1</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:35:13-04:00</t>
-        </is>
+        <v>46148.85823042824</v>
       </c>
     </row>
     <row r="171">
@@ -18097,27 +15784,7 @@
         </is>
       </c>
       <c r="V171" s="1" t="n">
-        <v>46146.56937407408</v>
-      </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>close distances cover=271 U1=271</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:35:29-04:00</t>
-        </is>
+        <v>46148.85824739583</v>
       </c>
     </row>
     <row r="172">
@@ -18304,27 +15971,7 @@
         </is>
       </c>
       <c r="V173" s="1" t="n">
-        <v>46146.56950097223</v>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>close distances cover=208 U1=208</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:35:43-04:00</t>
-        </is>
+        <v>46148.85826324074</v>
       </c>
     </row>
     <row r="174">
@@ -18429,27 +16076,7 @@
         </is>
       </c>
       <c r="V174" s="1" t="n">
-        <v>46146.56955443287</v>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>close distances cover=165 U1=165</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:35:57-04:00</t>
-        </is>
+        <v>46148.85828584491</v>
       </c>
     </row>
     <row r="175">
@@ -18554,27 +16181,7 @@
         </is>
       </c>
       <c r="V175" s="1" t="n">
-        <v>46146.56960912037</v>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA175" t="inlineStr">
-        <is>
-          <t>close distances cover=275 U1=275</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:36:11-04:00</t>
-        </is>
+        <v>46148.85830232639</v>
       </c>
     </row>
     <row r="176">
@@ -18679,27 +16286,7 @@
         </is>
       </c>
       <c r="V176" s="1" t="n">
-        <v>46146.56968707176</v>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA176" t="inlineStr">
-        <is>
-          <t>close distances cover=271 U1=271</t>
-        </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:36:31-04:00</t>
-        </is>
+        <v>46148.85831873843</v>
       </c>
     </row>
     <row r="177">
@@ -18804,27 +16391,7 @@
         </is>
       </c>
       <c r="V177" s="1" t="n">
-        <v>46146.56972340278</v>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>close distances cover=303 U1=303</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:36:46-04:00</t>
-        </is>
+        <v>46148.85833532408</v>
       </c>
     </row>
     <row r="178">
@@ -18929,27 +16496,7 @@
         </is>
       </c>
       <c r="V178" s="1" t="n">
-        <v>46146.56979006944</v>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA178" t="inlineStr">
-        <is>
-          <t>close distances cover=355 U1=355</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:37:03-04:00</t>
-        </is>
+        <v>46148.85835787037</v>
       </c>
     </row>
     <row r="179">
@@ -19054,27 +16601,7 @@
         </is>
       </c>
       <c r="V179" s="1" t="n">
-        <v>46146.56984274305</v>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA179" t="inlineStr">
-        <is>
-          <t>close distances cover=446 U1=446</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:37:17-04:00</t>
-        </is>
+        <v>46148.85837791667</v>
       </c>
     </row>
     <row r="180">
@@ -19179,27 +16706,7 @@
         </is>
       </c>
       <c r="V180" s="1" t="n">
-        <v>46146.56988755787</v>
-      </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>close distances cover=286 U1=286</t>
-        </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:37:31-04:00</t>
-        </is>
+        <v>46148.85839387732</v>
       </c>
     </row>
     <row r="181">
@@ -19304,27 +16811,7 @@
         </is>
       </c>
       <c r="V181" s="1" t="n">
-        <v>46146.56995192129</v>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA181" t="inlineStr">
-        <is>
-          <t>close distances cover=109 U1=109</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:37:44-04:00</t>
-        </is>
+        <v>46148.85840905092</v>
       </c>
     </row>
     <row r="182">
@@ -19429,27 +16916,7 @@
         </is>
       </c>
       <c r="V182" s="1" t="n">
-        <v>46146.56999587963</v>
-      </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA182" t="inlineStr">
-        <is>
-          <t>close distances cover=357 U1=357</t>
-        </is>
-      </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:37:55-04:00</t>
-        </is>
+        <v>46148.85842430555</v>
       </c>
     </row>
     <row r="183">
@@ -19554,27 +17021,7 @@
         </is>
       </c>
       <c r="V183" s="1" t="n">
-        <v>46146.57005886574</v>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA183" t="inlineStr">
-        <is>
-          <t>close distances cover=407 U1=407</t>
-        </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:38:09-04:00</t>
-        </is>
+        <v>46148.85843832176</v>
       </c>
     </row>
     <row r="184">
@@ -19679,27 +17126,7 @@
         </is>
       </c>
       <c r="V184" s="1" t="n">
-        <v>46146.57012211806</v>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA184" t="inlineStr">
-        <is>
-          <t>close distances cover=350 U1=350</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:38:29-04:00</t>
-        </is>
+        <v>46148.85845377315</v>
       </c>
     </row>
     <row r="185">
@@ -19804,27 +17231,7 @@
         </is>
       </c>
       <c r="V185" s="1" t="n">
-        <v>46146.57019549768</v>
-      </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA185" t="inlineStr">
-        <is>
-          <t>close distances cover=379 U1=379</t>
-        </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:38:46-04:00</t>
-        </is>
+        <v>46148.85846826389</v>
       </c>
     </row>
     <row r="186">
@@ -19913,9 +17320,6 @@
           <t>69f839eaf9374ed4f105a092</t>
         </is>
       </c>
-      <c r="R186" s="1" t="n">
-        <v>46146.44434825231</v>
-      </c>
       <c r="S186" t="inlineStr">
         <is>
           <t>406903731967</t>
@@ -19932,27 +17336,7 @@
         </is>
       </c>
       <c r="V186" s="1" t="n">
-        <v>46146.57028484953</v>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA186" t="inlineStr">
-        <is>
-          <t>close distances cover=388 U1=388</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:39:02-04:00</t>
-        </is>
+        <v>46148.85848324074</v>
       </c>
     </row>
     <row r="187">
@@ -20041,9 +17425,6 @@
           <t>69f83a955da263f75f04c06a</t>
         </is>
       </c>
-      <c r="R187" s="1" t="n">
-        <v>46146.44729530092</v>
-      </c>
       <c r="S187" t="inlineStr">
         <is>
           <t>406903746215</t>
@@ -20060,27 +17441,7 @@
         </is>
       </c>
       <c r="V187" s="1" t="n">
-        <v>46146.57036587963</v>
-      </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA187" t="inlineStr">
-        <is>
-          <t>close distances cover=379 U1=379</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:39:16-04:00</t>
-        </is>
+        <v>46148.85849773148</v>
       </c>
     </row>
     <row r="188">
@@ -20169,9 +17530,6 @@
           <t>69f83b5cf9374ed4f105a180</t>
         </is>
       </c>
-      <c r="R188" s="1" t="n">
-        <v>46146.4491269213</v>
-      </c>
       <c r="S188" t="inlineStr">
         <is>
           <t>406903749989</t>
@@ -20188,27 +17546,7 @@
         </is>
       </c>
       <c r="V188" s="1" t="n">
-        <v>46146.57042148148</v>
-      </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA188" t="inlineStr">
-        <is>
-          <t>close distances cover=488 U1=488</t>
-        </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:39:28-04:00</t>
-        </is>
+        <v>46148.85851284722</v>
       </c>
     </row>
     <row r="189">
@@ -20297,9 +17635,6 @@
           <t>69f83c14ffbc831dea082fa3</t>
         </is>
       </c>
-      <c r="R189" s="1" t="n">
-        <v>46146.4517059375</v>
-      </c>
       <c r="S189" t="inlineStr">
         <is>
           <t>406903756190</t>
@@ -20316,27 +17651,7 @@
         </is>
       </c>
       <c r="V189" s="1" t="n">
-        <v>46146.57048744213</v>
-      </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA189" t="inlineStr">
-        <is>
-          <t>close distances cover=402 U1=402</t>
-        </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:39:44-04:00</t>
-        </is>
+        <v>46148.85852811343</v>
       </c>
     </row>
     <row r="190">
@@ -20441,27 +17756,7 @@
         </is>
       </c>
       <c r="V190" s="1" t="n">
-        <v>46146.57057369213</v>
-      </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>close distances cover=402 U1=402</t>
-        </is>
-      </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:39:55-04:00</t>
-        </is>
+        <v>46148.85854357639</v>
       </c>
     </row>
     <row r="191">
@@ -20566,27 +17861,7 @@
         </is>
       </c>
       <c r="V191" s="1" t="n">
-        <v>46146.57062267361</v>
-      </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA191" t="inlineStr">
-        <is>
-          <t>close distances cover=0 U1=0</t>
-        </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:40:06-04:00</t>
-        </is>
+        <v>46148.85855932871</v>
       </c>
     </row>
     <row r="192">
@@ -20691,27 +17966,7 @@
         </is>
       </c>
       <c r="V192" s="1" t="n">
-        <v>46146.684981875</v>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA192" t="inlineStr">
-        <is>
-          <t>close distances cover=373 U1=373</t>
-        </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:40:21-04:00</t>
-        </is>
+        <v>46148.85857569444</v>
       </c>
     </row>
     <row r="193">
@@ -20816,27 +18071,7 @@
         </is>
       </c>
       <c r="V193" s="1" t="n">
-        <v>46146.57077697917</v>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA193" t="inlineStr">
-        <is>
-          <t>close distances cover=330 U1=330</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:40:38-04:00</t>
-        </is>
+        <v>46148.85859170139</v>
       </c>
     </row>
     <row r="194">
@@ -20941,27 +18176,7 @@
         </is>
       </c>
       <c r="V194" s="1" t="n">
-        <v>46146.68508978009</v>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA194" t="inlineStr">
-        <is>
-          <t>close distances cover=286 U1=286</t>
-        </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:40:53-04:00</t>
-        </is>
+        <v>46148.85860637732</v>
       </c>
     </row>
     <row r="195">
@@ -21066,27 +18281,7 @@
         </is>
       </c>
       <c r="V195" s="1" t="n">
-        <v>46146.57115530092</v>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA195" t="inlineStr">
-        <is>
-          <t>close distances cover=390 U1=390</t>
-        </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:41:04-04:00</t>
-        </is>
+        <v>46148.85862097222</v>
       </c>
     </row>
     <row r="196">
@@ -21175,44 +18370,6 @@
           <t>69f855abffbc831dea0847c8</t>
         </is>
       </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>406903251282</t>
-        </is>
-      </c>
-      <c r="T196" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406903251282</t>
-        </is>
-      </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V196" s="1" t="n">
-        <v>46146.5712108912</v>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA196" t="inlineStr">
-        <is>
-          <t>close distances cover=317 U1=317</t>
-        </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:41:16-04:00</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -21300,44 +18457,6 @@
           <t>69f8530b5da263f75f04d837</t>
         </is>
       </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>406903252244</t>
-        </is>
-      </c>
-      <c r="T197" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406903252244</t>
-        </is>
-      </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V197" s="1" t="n">
-        <v>46146.57130583333</v>
-      </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA197" t="inlineStr">
-        <is>
-          <t>close distances cover=394 U1=394</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:41:29-04:00</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -21425,47 +18544,6 @@
           <t>69f863f9f9374ed4f105c588</t>
         </is>
       </c>
-      <c r="R198" s="1" t="n">
-        <v>46146.45434863426</v>
-      </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>406903760725</t>
-        </is>
-      </c>
-      <c r="T198" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406903760725</t>
-        </is>
-      </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V198" s="1" t="n">
-        <v>46146.57141394676</v>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>close distances cover=468 U1=468</t>
-        </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:41:40-04:00</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -21553,27 +18631,6 @@
           <t>69f8647ff9374ed4f105c605</t>
         </is>
       </c>
-      <c r="R199" s="1" t="n">
-        <v>46148.62142402564</v>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>406909148324</t>
-        </is>
-      </c>
-      <c r="T199" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909148324</t>
-        </is>
-      </c>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V199" s="1" t="n">
-        <v>46148.62172311655</v>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -21661,27 +18718,6 @@
           <t>69f865a55da263f75f04e768</t>
         </is>
       </c>
-      <c r="R200" s="1" t="n">
-        <v>46148.62384760453</v>
-      </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>406909151733</t>
-        </is>
-      </c>
-      <c r="T200" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909151733</t>
-        </is>
-      </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V200" s="1" t="n">
-        <v>46148.62414681815</v>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -21769,27 +18805,6 @@
           <t>69f8669583a8608fd80f0fdb</t>
         </is>
       </c>
-      <c r="R201" s="1" t="n">
-        <v>46148.62592406256</v>
-      </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>406909159060</t>
-        </is>
-      </c>
-      <c r="T201" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909159060</t>
-        </is>
-      </c>
-      <c r="U201" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V201" s="1" t="n">
-        <v>46148.62622317022</v>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -21877,27 +18892,6 @@
           <t>69f867cc2592a8ad8e0f076e</t>
         </is>
       </c>
-      <c r="R202" s="1" t="n">
-        <v>46148.62835318306</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>406909166683</t>
-        </is>
-      </c>
-      <c r="T202" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909166683</t>
-        </is>
-      </c>
-      <c r="U202" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V202" s="1" t="n">
-        <v>46148.62865410986</v>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -21972,7 +18966,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -22059,7 +19053,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -22146,7 +19140,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -22233,7 +19227,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -22320,7 +19314,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -22407,7 +19401,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -22494,7 +19488,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups8</t>
+          <t>Printify_Published_Mockups8</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -22581,7 +19575,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups8</t>
+          <t>Printify_Published_Mockups8</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -22668,7 +19662,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups8</t>
+          <t>Printify_Published_Mockups8</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -22755,7 +19749,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -22842,7 +19836,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -22929,7 +19923,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups8</t>
+          <t>Printify_Published_Mockups8</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -23016,7 +20010,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -23103,7 +20097,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -23190,7 +20184,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -23277,7 +20271,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -23364,7 +20358,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -23451,7 +20445,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups8</t>
+          <t>Printify_Published_Mockups8</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -23538,7 +20532,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups8</t>
+          <t>Printify_Published_Mockups8</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
@@ -23625,7 +20619,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups8</t>
+          <t>Printify_Published_Mockups8</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
@@ -23986,47 +20980,6 @@
           <t>69f89a94c1f268dee601cb9d</t>
         </is>
       </c>
-      <c r="R226" s="1" t="n">
-        <v>46146.44320188658</v>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>406903730229</t>
-        </is>
-      </c>
-      <c r="T226" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406903730229</t>
-        </is>
-      </c>
-      <c r="U226" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V226" s="1" t="n">
-        <v>46146.57147604167</v>
-      </c>
-      <c r="Z226" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA226" t="inlineStr">
-        <is>
-          <t>close distances cover=319 U1=319</t>
-        </is>
-      </c>
-      <c r="AB226" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:41:50-04:00</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -24114,47 +21067,6 @@
           <t>69f89b9ca70f06579a00a708</t>
         </is>
       </c>
-      <c r="R227" s="1" t="n">
-        <v>46146.44674793982</v>
-      </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>406903744471</t>
-        </is>
-      </c>
-      <c r="T227" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406903744471</t>
-        </is>
-      </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V227" s="1" t="n">
-        <v>46146.57157002314</v>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA227" t="inlineStr">
-        <is>
-          <t>close distances cover=273 U1=273</t>
-        </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:42:02-04:00</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -24242,47 +21154,6 @@
           <t>69f89c6f09f3b730240221b8</t>
         </is>
       </c>
-      <c r="R228" s="1" t="n">
-        <v>46146.44849810185</v>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>406903748661</t>
-        </is>
-      </c>
-      <c r="T228" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406903748661</t>
-        </is>
-      </c>
-      <c r="U228" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V228" s="1" t="n">
-        <v>46146.57164796296</v>
-      </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA228" t="inlineStr">
-        <is>
-          <t>close distances cover=374 U1=374</t>
-        </is>
-      </c>
-      <c r="AB228" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:42:15-04:00</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -24370,47 +21241,6 @@
           <t>69f89da69f68ab7cf001f531</t>
         </is>
       </c>
-      <c r="R229" s="1" t="n">
-        <v>46146.45088739583</v>
-      </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>406903754696</t>
-        </is>
-      </c>
-      <c r="T229" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406903754696</t>
-        </is>
-      </c>
-      <c r="U229" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V229" s="1" t="n">
-        <v>46146.57172376158</v>
-      </c>
-      <c r="Z229" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA229" t="inlineStr">
-        <is>
-          <t>close distances cover=331 U1=331</t>
-        </is>
-      </c>
-      <c r="AB229" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:42:33-04:00</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -24498,47 +21328,6 @@
           <t>69f89eac011b67ecf8077844</t>
         </is>
       </c>
-      <c r="R230" s="1" t="n">
-        <v>46146.45332118055</v>
-      </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>406903758348</t>
-        </is>
-      </c>
-      <c r="T230" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406903758348</t>
-        </is>
-      </c>
-      <c r="U230" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V230" s="1" t="n">
-        <v>46146.57181515046</v>
-      </c>
-      <c r="Z230" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AA230" t="inlineStr">
-        <is>
-          <t>close distances cover=441 U1=441</t>
-        </is>
-      </c>
-      <c r="AB230" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>2026-05-05T22:42:45-04:00</t>
-        </is>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -24626,27 +21415,6 @@
           <t>69f89fda2592a8ad8e0f2e79</t>
         </is>
       </c>
-      <c r="R231" s="1" t="n">
-        <v>46148.62056237976</v>
-      </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>406909147173</t>
-        </is>
-      </c>
-      <c r="T231" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909147173</t>
-        </is>
-      </c>
-      <c r="U231" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V231" s="1" t="n">
-        <v>46148.620863962</v>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -24734,27 +21502,6 @@
           <t>69f8a454c1f268dee601d3ad</t>
         </is>
       </c>
-      <c r="R232" s="1" t="n">
-        <v>46148.62260030281</v>
-      </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>406909150037</t>
-        </is>
-      </c>
-      <c r="T232" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909150037</t>
-        </is>
-      </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V232" s="1" t="n">
-        <v>46148.6229000563</v>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -24842,27 +21589,6 @@
           <t>69f903dec1f268dee601f679</t>
         </is>
       </c>
-      <c r="R233" s="1" t="n">
-        <v>46148.62474737458</v>
-      </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>406909153504</t>
-        </is>
-      </c>
-      <c r="T233" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909153504</t>
-        </is>
-      </c>
-      <c r="U233" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V233" s="1" t="n">
-        <v>46148.6250514507</v>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -24950,27 +21676,6 @@
           <t>69f904df97d964f736006a48</t>
         </is>
       </c>
-      <c r="R234" s="1" t="n">
-        <v>46148.62719392258</v>
-      </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>406909164941</t>
-        </is>
-      </c>
-      <c r="T234" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909164941</t>
-        </is>
-      </c>
-      <c r="U234" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V234" s="1" t="n">
-        <v>46148.62749331478</v>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -25045,7 +21750,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -25132,7 +21837,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -25219,7 +21924,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Printify_UI_Failed</t>
+          <t>Printify_Published_Mockups8</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -25306,12 +22011,17 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Ready_for_Printify</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
           <t>5/4/2026  10:29:22 AM</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>69fba23409770f1d9306b86d</t>
         </is>
       </c>
     </row>
@@ -25388,12 +22098,17 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>Ready_for_Printify</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
           <t>5/4/2026  10:29:50 AM</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>69fba266489d5635ab0e6504</t>
         </is>
       </c>
     </row>
@@ -25470,12 +22185,17 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>Ready_for_Printify</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>5/4/2026  10:30:07 AM</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>69fba28a6d07bd21600e1684</t>
         </is>
       </c>
     </row>
@@ -25552,12 +22272,17 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>Ready_for_Printify</t>
+          <t>Printify_Published_Mockups8</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
         <is>
           <t>5/4/2026  10:30:24 AM</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>69fbbffef60a24b6d1034e4d</t>
         </is>
       </c>
     </row>
@@ -25634,7 +22359,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -25646,27 +22371,6 @@
         <is>
           <t>69fb7a5154fd3fbacf050c5a</t>
         </is>
-      </c>
-      <c r="R242" s="1" t="n">
-        <v>46148.56671103009</v>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>406909045760</t>
-        </is>
-      </c>
-      <c r="T242" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909045760</t>
-        </is>
-      </c>
-      <c r="U242" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V242" s="1" t="n">
-        <v>46148.56716944445</v>
       </c>
     </row>
     <row r="243">
@@ -25733,27 +22437,6 @@
           <t>69fb7e754ce71ea8ae0c7af1</t>
         </is>
       </c>
-      <c r="R243" s="1" t="n">
-        <v>46148.57465741898</v>
-      </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>406909061109</t>
-        </is>
-      </c>
-      <c r="T243" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909061109</t>
-        </is>
-      </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V243" s="1" t="n">
-        <v>46148.57495696759</v>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -25841,27 +22524,6 @@
           <t>69fb804bff28e7d4030aa67d</t>
         </is>
       </c>
-      <c r="R244" s="1" t="n">
-        <v>46148.59251928241</v>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>406909095974</t>
-        </is>
-      </c>
-      <c r="T244" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909095974</t>
-        </is>
-      </c>
-      <c r="U244" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V244" s="1" t="n">
-        <v>46148.59283591435</v>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -25949,27 +22611,6 @@
           <t>69fb819d4c6544084c0f8370</t>
         </is>
       </c>
-      <c r="R245" s="1" t="n">
-        <v>46148.59356574074</v>
-      </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>406909097469</t>
-        </is>
-      </c>
-      <c r="T245" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909097469</t>
-        </is>
-      </c>
-      <c r="U245" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V245" s="1" t="n">
-        <v>46148.59386609954</v>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -26057,27 +22698,6 @@
           <t>69fb82e64c6544084c0f83d5</t>
         </is>
       </c>
-      <c r="R246" s="1" t="n">
-        <v>46148.59459497685</v>
-      </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>406909100892</t>
-        </is>
-      </c>
-      <c r="T246" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909100892</t>
-        </is>
-      </c>
-      <c r="U246" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V246" s="1" t="n">
-        <v>46148.59504747685</v>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -26165,27 +22785,6 @@
           <t>69fb868dc5114ecf420d2b93</t>
         </is>
       </c>
-      <c r="R247" s="1" t="n">
-        <v>46148.60340165509</v>
-      </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>406909114799</t>
-        </is>
-      </c>
-      <c r="T247" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909114799</t>
-        </is>
-      </c>
-      <c r="U247" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V247" s="1" t="n">
-        <v>46148.60399184027</v>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -26273,27 +22872,6 @@
           <t>69fb8749a7afceb9f70f1956</t>
         </is>
       </c>
-      <c r="R248" s="1" t="n">
-        <v>46148.60472953704</v>
-      </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>406909116716</t>
-        </is>
-      </c>
-      <c r="T248" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909116716</t>
-        </is>
-      </c>
-      <c r="U248" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V248" s="1" t="n">
-        <v>46148.60507960648</v>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -26381,27 +22959,6 @@
           <t>69fb87aca7afceb9f70f1982</t>
         </is>
       </c>
-      <c r="R249" s="1" t="n">
-        <v>46148.60550216436</v>
-      </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>406909118000</t>
-        </is>
-      </c>
-      <c r="T249" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909118000</t>
-        </is>
-      </c>
-      <c r="U249" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V249" s="1" t="n">
-        <v>46148.60597498842</v>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -26489,27 +23046,6 @@
           <t>69fb87efc5114ecf420d2c5a</t>
         </is>
       </c>
-      <c r="R250" s="1" t="n">
-        <v>46148.60636443287</v>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>406909119544</t>
-        </is>
-      </c>
-      <c r="T250" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909119544</t>
-        </is>
-      </c>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V250" s="1" t="n">
-        <v>46148.61832849537</v>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -26597,27 +23133,6 @@
           <t>69fb8805ee663532c8017f4f</t>
         </is>
       </c>
-      <c r="R251" s="1" t="n">
-        <v>46148.607418125</v>
-      </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>406909121336</t>
-        </is>
-      </c>
-      <c r="T251" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909121336</t>
-        </is>
-      </c>
-      <c r="U251" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V251" s="1" t="n">
-        <v>46148.60772269676</v>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -26705,27 +23220,6 @@
           <t>69fb8811e5402c478e03108f</t>
         </is>
       </c>
-      <c r="R252" s="1" t="n">
-        <v>46148.60832354167</v>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>406909122790</t>
-        </is>
-      </c>
-      <c r="T252" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909122790</t>
-        </is>
-      </c>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V252" s="1" t="n">
-        <v>46148.60862274306</v>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -26813,27 +23307,6 @@
           <t>69fb881f2b1da07362014876</t>
         </is>
       </c>
-      <c r="R253" s="1" t="n">
-        <v>46148.60933324074</v>
-      </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>406909124585</t>
-        </is>
-      </c>
-      <c r="T253" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909124585</t>
-        </is>
-      </c>
-      <c r="U253" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V253" s="1" t="n">
-        <v>46148.60963540509</v>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -26921,27 +23394,6 @@
           <t>69fb882c54fd3fbacf051371</t>
         </is>
       </c>
-      <c r="R254" s="1" t="n">
-        <v>46148.61011664352</v>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>406909125700</t>
-        </is>
-      </c>
-      <c r="T254" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909125700</t>
-        </is>
-      </c>
-      <c r="U254" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V254" s="1" t="n">
-        <v>46148.61041673611</v>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -27029,27 +23481,6 @@
           <t>69fb883cce0d8cb5570fa7cc</t>
         </is>
       </c>
-      <c r="R255" s="1" t="n">
-        <v>46148.61093628472</v>
-      </c>
-      <c r="S255" t="inlineStr">
-        <is>
-          <t>406909126789</t>
-        </is>
-      </c>
-      <c r="T255" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909126789</t>
-        </is>
-      </c>
-      <c r="U255" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V255" s="1" t="n">
-        <v>46148.61123732639</v>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -27137,26 +23568,1709 @@
           <t>69fb8849e5402c478e0310af</t>
         </is>
       </c>
-      <c r="R256" s="1" t="n">
-        <v>46148.61170621528</v>
-      </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>406909127704</t>
-        </is>
-      </c>
-      <c r="T256" t="inlineStr">
-        <is>
-          <t>https://www.ebay.com/itm/406909127704</t>
-        </is>
-      </c>
-      <c r="U256" t="inlineStr">
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0005-FIX1</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0005-FIX1</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Bamboo Forest Minimal Zen 4pc 6x6 Kiss-Cut Vinyl Desk Collector Decor Misty Art</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>4pc Kiss-Cut Sticker Set Bamboo Forest Laptop Journal Bottle Zen Aesthetic A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Zen Aesthetic relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Zen Bamboo Forest Sticker - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Zen aesthetic piece for students, remote workers, yoga lovers, and anyone building a serene everyday space. Designed for peaceful desks, journals, and small rituals, this Zen Bamboo Forest Sticker kiss-cut sticker carries a clean Zen mood.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>A dense grove of bamboo stalks, each segment made of polished Black Bamboo with joints accented by Copper Rivets, morning mist glowing with ethereal light between the canes, serene atmosphere, , , , , 3D relief effect, sharp focus,</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0005_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0005_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0005_Ready_for_Steaming\Sticker-Zen-0005_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0005_Ready_for_Steaming\Sticker-Zen-0005_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0005_Ready_for_Steaming\Sticker-Zen-0005_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0005_Ready_for_Steaming\Sticker-Zen-0005_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:10:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>69fbae614c6544084c0f95ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0007-FIX1</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0007-FIX1</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>4pc Sticker Set Cherry Blossom Branch Vinyl Decals Laptop Bottle Zen Aesthetic</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>4pc Sticker Set Cherry Blossom Branch Vinyl Decals Laptop Bottle Zen Aesthetic A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Zen Aesthetic relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Cherry Blossom Branch Sticker Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Bring calm and balance into your daily routine with this Cherry Blossom Branch Sticker zen aesthetic kiss-cut sticker.&lt;/p&gt;&lt;p&gt;Designed for study rooms, creative workspaces, shelves, gallery walls, and collectible aesthetic decor, this sticker blends niche aesthetic appeal with collectible mentor-grade artwork.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>A single, graceful branch of a cherry blossom tree, the wood is Weathered Teak, and the blossoms are delicate clusters of Pink Opal and Clear Quartz, catching the light, hyper-detailed, fragile beauty, , , , , 3D relief effect, sharp focus,</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0007_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0007_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0007_Ready_for_Steaming\Sticker-Zen-0007_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0007_Ready_for_Steaming\Sticker-Zen-0007_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0007_Ready_for_Steaming\Sticker-Zen-0007_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0007_Ready_for_Steaming\Sticker-Zen-0007_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:10:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>69fbae7da7afceb9f70f2982</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0008-FIX1</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0008-FIX1</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>4pc Kiss-Cut Sticker Set Circle Ens Laptop Journal Bottle Zen Aesthetic Decal</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>4pc Kiss-Cut Sticker Set Circle Ens Laptop Journal Bottle Zen Aesthetic Decal A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Zen Aesthetic relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Zen Circle Ens Sticker - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Zen aesthetic piece for students, remote workers, yoga lovers, and anyone building a serene everyday space. Designed for peaceful desks, journals, and small rituals, this Zen Circle Ens Sticker kiss-cut sticker carries a clean Zen mood.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for easy c&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>A single, perfectly imperfect brushstroke circle (ensō), the ink is Molten Gold flowing over a background of crushed Lapis Lazuli pigment, the stroke has texture and depth, symbol of enlightenment, , , , , 3D relief effect, sharp focus,</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0008_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0008_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0008_Ready_for_Steaming\Sticker-Zen-0008_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0008_Ready_for_Steaming\Sticker-Zen-0008_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0008_Ready_for_Steaming\Sticker-Zen-0008_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0008_Ready_for_Steaming\Sticker-Zen-0008_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:10:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>69fbae974c6544084c0f9610</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0009-FIX1</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0009-FIX1</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Zen Aesthetic Praying Mantis on Rock 4pc 6x6 Kiss-Cut Sticker Laptop Journal</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Praying Mantis on Rock Sticker Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Bring calm and balance into your daily routine with this Praying Mantis on Rock Sticker zen aesthetic kiss-cut sticker.&lt;/p&gt;&lt;p&gt;Designed for study rooms, creative workspaces, shelves, gallery walls, and collectible aesthetic decor, this sticker blends niche aesthetic appeal with collectible mentor-grade artwork.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A detailed praying mantis in a meditative pose, perched on a river rock of Polished River Stone, the insect's body is crafted from Jade and Bronze, with articulated limbs, macro photography, serene predator, , , , , 3D relief effect, sharp focus,&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; mindfulness lovers, minimalists, journal keepers, yoga enthusiasts, and peaceful room setups.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; praying mantis sticker, jade insect, bronze art, macro photography, nature detail, zen insect, meditation pose, unique bug art, garden guardian, realistic sticker&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Complete the collection with matching Alchemy pieces.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0009&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>A detailed praying mantis in a meditative pose, perched on a river rock of Polished River Stone, the insect's body is crafted from Jade and Bronze, with articulated limbs, macro photography, serene predator, , , , , 3D relief effect, sharp focus,</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0009_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0009_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0009_Ready_for_Steaming\Sticker-Zen-0009_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0009_Ready_for_Steaming\Sticker-Zen-0009_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0009_Ready_for_Steaming\Sticker-Zen-0009_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0009_Ready_for_Steaming\Sticker-Zen-0009_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:10:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>69fbaea961c4aefdea04aaaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0022-FIX1</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0022-FIX1</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Mindful Zen Garden Stone Meis seki 4pc 6x6 Vinyl Sticker Laptop Journal Gift</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Zen Garden Stone Sticker | (Meis seki) | Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Add a quiet mindful accent to your workspace with this Zen Garden Stone Sticker | (Meis seki) kiss-cut sticker. The artwork is built around a focused visual DNA profile, so each piece feels like part of a coherent small-batch collection.&lt;/p&gt;&lt;p&gt;Use it for laptops, notebooks, reading corners, desk setups, gallery shelves, and gift bundles. The composition favors readable detail, strong mood, and giftable niche appeal without generic mass-market styling.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A perfectly smooth zen garden stone, surface made of translucent imperial jade with a network of fine kintsugi gold veins, pulsing with a soft bioluminescent glow that highlights complex internal crystalline structures, placed on raked sand, dramatic side lighting, hyper-realistic texture, , , , , 3D relief effect, sharp focus,&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; meditation fans, calm desk setups, notebook collectors, and gift buyers who like clean aesthetics.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; zen garden, meditation stone, jade rock, kintsugi, glowing stone, calm, focus, desk decor, minimalist, Japanese garden&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Pair it with related OpenClaw pieces for a coordinated collection.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0022&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>A perfectly smooth zen garden stone, surface made of translucent imperial jade with a network of fine kintsugi gold veins, pulsing with a soft bioluminescent glow that highlights complex internal crystalline structures, placed on raked sand, dramatic side lighting, hyper-realistic texture, , , , , 3D relief effect, sharp focus,</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0022_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0022_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0022_Ready_for_Steaming\Sticker-Zen-0022_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0022_Ready_for_Steaming\Sticker-Zen-0022_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0022_Ready_for_Steaming\Sticker-Zen-0022_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0022_Ready_for_Steaming\Sticker-Zen-0022_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:10:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>69fbaeb9f60a24b6d1034575</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0024-FIX1</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0024-FIX1</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Mindful Zen Enso Circle with Crystals 4pc 6x6 Vinyl Sticker Laptop Journal Gift</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Enso Circle with Crystals Sticker | (Suish no Ens ) | Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Add a quiet mindful accent to your workspace with this Enso Circle with Crystals Sticker | (Suish no Ens ) kiss-cut sticker. The artwork is built around a focused visual DNA profile, so each piece feels like part of a coherent small-batch collection.&lt;/p&gt;&lt;p&gt;Use it for laptops, notebooks, reading corners, desk setups, gallery shelves, and gift bundles. The composition favors readable detail, strong mood, and giftable niche appeal without generic mass-market styling.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A single, fluid brushstroke forming an ensō circle, the ink is translucent imperial jade with kintsugi gold veins tracing its path, the center of the circle contains a cluster of glowing internal crystalline structures emitting bioluminescent light, ink splash effect, dynamic lighting, , , , , 3D relief effect, sharp focus,&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; meditation fans, calm desk setups, notebook collectors, and gift buyers who like clean aesthetics.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; enso circle, Japanese calligraphy, jade ink, kintsugi, crystal core, enlightenment, simplicity, zen philosophy, brushstroke art, spiritual sticker&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Pair it with related OpenClaw pieces for a coordinated collection.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0024&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>A single, fluid brushstroke forming an ensō circle, the ink is translucent imperial jade with kintsugi gold veins tracing its path, the center of the circle contains a cluster of glowing internal crystalline structures emitting bioluminescent light, ink splash effect, dynamic lighting, , , , , 3D relief effect, sharp focus,</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0024_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0024_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0024_Ready_for_Steaming\Sticker-Zen-0024_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0024_Ready_for_Steaming\Sticker-Zen-0024_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0024_Ready_for_Steaming\Sticker-Zen-0024_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0024_Ready_for_Steaming\Sticker-Zen-0024_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:10:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>69fbaecbb8dd7e2bb0094b7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0025-FIX1</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0025-FIX1</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Koi Fish in Jade Pond Hisui no Koi Mindful Zen 4pc 6x6 Vinyl Sticker Yoga Luck</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Koi Fish in Jade Pond Sticker | (Hisui no Koi) | Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Add a quiet mindful accent to your workspace with this Koi Fish in Jade Pond Sticker | (Hisui no Koi) kiss-cut sticker. The artwork is built around a focused visual DNA profile, so each piece feels like part of a coherent small-batch collection.&lt;/p&gt;&lt;p&gt;Use it for laptops, notebooks, reading corners, desk setups, gallery shelves, and gift bundles. The composition favors readable detail, strong mood, and giftable niche appeal without generic mass-market styling.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A graceful koi fish swimming upwards, its scales crafted from overlapping pieces of translucent imperial jade connected by kintsugi gold veins, a soft bioluminescent glow from within illuminates the internal crystalline structures of its body, water droplet effects, ethereal underwater lighting, , , , , 3D relief effect, sharp focus,&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; meditation fans, calm desk setups, notebook collectors, and gift buyers who like clean aesthetics.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; koi fish, jade koi, kintsugi fish, glowing koi, perseverance, luck, water art, Japanese symbol, calming sticker, aquarium decor&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Pair it with related OpenClaw pieces for a coordinated collection.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0025&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>A graceful koi fish swimming upwards, its scales crafted from overlapping pieces of translucent imperial jade connected by kintsugi gold veins, a soft bioluminescent glow from within illuminates the internal crystalline structures of its body, water droplet effects, ethereal underwater lighting, , , , , 3D relief effect, sharp focus,</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0025_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0025_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0025_Ready_for_Steaming\Sticker-Zen-0025_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0025_Ready_for_Steaming\Sticker-Zen-0025_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0025_Ready_for_Steaming\Sticker-Zen-0025_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0025_Ready_for_Steaming\Sticker-Zen-0025_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:10:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>69fbaedb4c6544084c0f9620</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0027-FIX1</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0027-FIX1</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Minimal Zen Temple Lantern Zendera no T r 4pc 6x6 Sticker Sheet Serene Mindful</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Zen Temple Lantern Sticker | (Zendera no T r ) - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Zen aesthetic piece for students, remote workers, yoga lovers, and anyone building a serene everyday space. Designed for peaceful desks, journals, and small rituals, this Zen Temple Lantern Sticker | (Zendera no T r ) kiss-cut sticker carries a clean Zen mood.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for easy comparison.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A traditional stone zen lantern, its panels made of translucent imperial jade held together by kintsugi gold seams, a powerful bioluminescent glow radiates from within, casting light that reveals the intricate internal crystalline structures of the jade, moss details, warm ambient glow, , , , , 3D relief effect, sharp focus,&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; students, remote workers, yoga lovers, and anyone building a serene everyday space.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; zen lantern, stone lantern, jade light, kintsugi lamp, illumination, guidance, temple decor, Asian architecture, peaceful light, garden sticker&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Saved under the reference SKU below for easy collector matching.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0027&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>A traditional stone zen lantern, its panels made of translucent imperial jade held together by kintsugi gold seams, a powerful bioluminescent glow radiates from within, casting light that reveals the intricate internal crystalline structures of the jade, moss details, warm ambient glow, , , , , 3D relief effect, sharp focus,</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0027_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0027_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0027_Ready_for_Steaming\Sticker-Zen-0027_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0027_Ready_for_Steaming\Sticker-Zen-0027_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0027_Ready_for_Steaming\Sticker-Zen-0027_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0027_Ready_for_Steaming\Sticker-Zen-0027_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:10:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>69fbaeebce0d8cb5570fb7dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0041-FIX1</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0041-FIX1</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Minimal Zen Kintsugi Gold Dragon 4pc 6x6 Sticker Sheet Serene Mindful Clean</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Kintsugi Gold Dragon Sticker - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Zen aesthetic piece for students, remote workers, yoga lovers, and anyone building a serene everyday space. Designed for peaceful desks, journals, and small rituals, this Kintsugi Gold Dragon Sticker kiss-cut sticker carries a clean Zen mood.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for easy comparison.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A Zen dragon with Kintsugi Gold Veins repairing Translucent Imperial Jade scales, Bioluminescent Glow from Internal Crystalline Structures, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; students, remote workers, yoga lovers, and anyone building a serene everyday space.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; Japanese aesthetic, wabi-sabi, kintsugi art, broken beauty, repair art, gold foil sticker, luxury sticker, spiritual healing, mindfulness, dragon mythology&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Saved under the reference SKU below for easy collector matching.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0041&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>A Zen dragon with Kintsugi Gold Veins repairing Translucent Imperial Jade scales, Bioluminescent Glow from Internal Crystalline Structures, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0041_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0041_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0041_Ready_for_Steaming\Sticker-Zen-0041_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0041_Ready_for_Steaming\Sticker-Zen-0041_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0041_Ready_for_Steaming\Sticker-Zen-0041_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0041_Ready_for_Steaming\Sticker-Zen-0041_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:10:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>69fbaefcc6dfbcc11107aa91</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0042-FIX1</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0042-FIX1</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Bioluminescent Crystal Dragon Minimal Zen 4pc 6x6 Kiss-Cut Vinyl Desk Collector</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Bioluminescent Crystal Dragon Sticker - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Zen aesthetic piece for students, remote workers, yoga lovers, and anyone building a serene everyday space. Designed for peaceful desks, journals, and small rituals, this Bioluminescent Crystal Dragon Sticker kiss-cut sticker carries a clean Zen mood.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for easy comparison.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A Zen dragon with glowing Internal Crystalline Structures emitting Bioluminescent Glow through Translucent Imperial Jade skin, Kintsugi Gold Veins, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; students, remote workers, yoga lovers, and anyone building a serene everyday space.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; glow in the dark, neon aesthetic, cyberpunk zen, crystal healing, spiritual energy, mystical creature, fantasy art, rave culture, festival sticker, UV reactive&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Saved under the reference SKU below for easy collector matching.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0042&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>A Zen dragon with glowing Internal Crystalline Structures emitting Bioluminescent Glow through Translucent Imperial Jade skin, Kintsugi Gold Veins, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0042_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0042_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0042_Ready_for_Steaming\Sticker-Zen-0042_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0042_Ready_for_Steaming\Sticker-Zen-0042_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0042_Ready_for_Steaming\Sticker-Zen-0042_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0042_Ready_for_Steaming\Sticker-Zen-0042_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:10:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>69fbaf12ff28e7d4030aba2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0035</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0035</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Dark Academia Poster Theological Codex Sanctuary 12x18 Study Decor Wall Library</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Immerse your study or library in the sacred geometry of the &lt;strong&gt;Theological Codex Sanctuary&lt;/strong&gt;, a dark academia poster that transforms a wall into a cathedral of intellect. This mentor-grade composition features a magnificent sanctuary vessel forged from corroded bronze and cracked cathedral glass, housing gravity-defying ancient theological texts. Kintsugi gold veins weave through the structure, while toxic jade bioluminescence illuminates sacred vellum pages, and brass clockwork prayer mechanisms add an air of timeless mystery.&lt;/p&gt;&lt;p&gt;Printed on premium semi-gloss poster paper, this 12x18 inch artwork is ideal for a study desk, reading nook, or library wall. The dramatic side lighting and emerald glow create an immersive environment that inspires deep thought and contemplation. Perfect for book lovers, students, and collectors of vintage intellectual decor.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 inch poster, shipped in a protective tube.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium semi-gloss poster paper (200 gsm).&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 x 18 inches (30.48 x 45.72 cm).&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia Mentor-Grade — dark, vintage, intellectual.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Corroded Bronze, Cracked Glass, Kintsugi Gold, Toxic Jade, Ancient Vellum, brass clockwork, bioluminescent emerald glow, micro-engraved surface relief, floating accent fragments.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study room wall art, library decor, gift for dark academia enthusiasts, student apartment, vintage book lover's space.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>$34.99</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Corroded Bronze, Cracked Glass, Kintsugi Gold, Toxic Jade, Ancient Vellum, brass clockwork, bioluminescent emerald glow, micro-engraved surface relief, floating accent fragments</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0035_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0035_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0035_Ready_for_Steaming\Gallery_U1.png</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0035_Ready_for_Steaming\Gallery_U2.png</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0035_Ready_for_Steaming\Gallery_U3.png</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0035_Ready_for_Steaming\Gallery_U4.png</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups8</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>5/6/2026  5:49:57 PM</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>69fbc023f60a24b6d1034e5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0036</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0036</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Mechanical Encyclopedia Sphere Dark Academia Aesthetic 12x18 Poster Study Room</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;This poster presents the Mechanical Encyclopedia Sphere, a dark academia masterpiece that transforms a corroded iron vessel into an archive of forgotten engineering. The cracked technical glass and kintsugi repair seams, glowing with golden light, encase gravity-defying ancient books and blueprint manuscripts, while toxic jade bioluminescence casts an emerald glow across the scene. It is an immersive environment for the intellectual soul.&lt;/p&gt;&lt;p&gt;Printed on premium semi-gloss poster paper, this 12x18 inch piece is ideal for a study desk, library wall, or vintage-inspired workspace. The ultra-detailed corrosion and glass fracture patterns reward close inspection, making it a conversation starter for book lovers and industrial design enthusiasts. Use it to evoke a mood of scholarly mystery in your home or office.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 inch poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium semi-gloss poster paper (200 gsm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 x 18 inches (30.48 x 45.72 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Dark Academia, Mentor-Grade, Industrial Design&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Corroded iron, cracked glass, kintsugi gold, toxic jade bioluminescence, ancient calfskin, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments with intentional negative space&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study room decor, library wall art, vintage intellectual gift for students or engineers, dark academia bedroom accent, office inspiration&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note:&lt;/em&gt; </t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>$34.99</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Corroded iron, cracked glass, kintsugi gold, toxic jade bioluminescence, ancient calfskin, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments with intentional negative space</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0036_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0036_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0036_Ready_for_Steaming\Gallery_U1.png</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0036_Ready_for_Steaming\Gallery_U2.png</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0036_Ready_for_Steaming\Gallery_U3.png</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0036_Ready_for_Steaming\Gallery_U4.png</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups8</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>5/6/2026  5:50:05 PM</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>69fbc0482b1da073620161ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0037</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0037</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Cryptographic Vault Cylinder Dark Academia Poster 12x18 Secret Knowledge Decor</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;This poster presents a towering cylindrical vault constructed from corroded brass and cracked cipher glass, containing gravity-defying ancient cryptography manuscripts. Kintsugi repair seams glow with golden light, while toxic jade bioluminescence illuminates encoded parchment pages, creating an immersive secret knowledge aesthetic. Designed for the mentor-grade collector, this piece embodies the dark academia study of hidden wisdom.&lt;/p&gt;&lt;p&gt;Ideal for a study desk, library wall, or vintage-inspired reading nook, this 12x18 poster brings a mood of intellectual mystery to any space. The dramatic side lighting and emerald glow make it a compelling focal point for book lovers, students, and scholars who appreciate the romance of forgotten lore.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper, archival quality&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 inches by 18 inches&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia Mentor-Grade, dark academia&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Corroded Brass, Cracked Glass, Kintsugi Gold, Toxic Jade, Ancient Parchment; micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study desk decor, library wall art, vintage intellectual gift, student room accent, book lover's collection&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>$34.99</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>A towering cylindrical vault constructed from corroded brass and cracked cipher glass containing gravity-defying ancient cryptography manuscripts, kintsugi repair seams glowing with golden light, toxic jade bioluminescence illuminating encoded parchment pages, swirling symbolic dust trapped inside the cylinder, brass clockwork encryption mechanisms, dramatic side lighting with emerald glow, dark academia aesthetic, ultra-detailed corrosion and glass fracture patterns, hyper-detailed mentor-grade object design, primary material system: Corroded Brass, Cracked Glass, Kintsugi Gold, Toxic Jade, Ancient Parchment, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, full frame, cinematic lighting, edge-to-edge composition, immersive environment, --ar 9:16 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0037_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0037_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0037_Ready_for_Steaming\Gallery_U1.png</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0037_Ready_for_Steaming\Gallery_U2.png</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0037_Ready_for_Steaming\Gallery_U3.png</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0037_Ready_for_Steaming\Gallery_U4.png</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups8</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>5/6/2026  5:50:11 PM</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>69fbc06d61c4aefdea04b362</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>406909473606</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909473606</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V256" s="1" t="n">
-        <v>46148.61200826389</v>
+      <c r="V269" s="1" t="n">
+        <v>46148.84257469908</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0038</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0038</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Geological Archive Geode Dark Academia Poster 12x18 Mentor-Grade Decor Wall</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;This poster transforms a monumental geode vessel into a study in corroded beauty and intellectual mystery. Corroded iron and cracked mineral glass cradle ancient geology texts, while kintsugi gold seams and toxic jade bioluminescence breathe life into stone catalog pages. A mentor-grade naturalist aesthetic for those who revere vintage scientific illustration and immersive design.&lt;/p&gt;&lt;p&gt;Perfect for a study desk, library wall, or reading nook, this 12x18 print brings dark academia atmosphere to any space. The brass clockwork specimen details and swirling crystalline parchment dust invite hours of contemplation. Ideal for book lovers, students, and collectors of geological art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster print (unframed)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper, archival quality&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 x 18 inches (30.5 x 45.7 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia Mentor-Grade&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Corroded Iron, Cracked Glass, Kintsugi Gold, Toxic Jade, Ancient Vellum; micro-engraved surface relief, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments with intentional negative space&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study room wall art, library decor, academic office, gift for geology or literature enthusiasts, dark academia bedroom accent&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>$34.99</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>A monumental geode vessel constructed from corroded iron and cracked mineral glass containing gravity-defying ancient geology texts, kintsugi repair seams glowing with golden light, toxic jade bioluminescence illuminating stone catalog pages, swirling crystalline parchment dust trapped inside the geode, brass clockwork specimen rotation systems, dramatic side lighting with emerald glow, dark academia aesthetic, ultra-detailed corrosion and glass fracture patterns, hyper-detailed mentor-grade object design, primary material system: Corroded Iron, Cracked Glass, Kintsugi Gold, Toxic Jade, Ancient Vellum, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, full frame, cinematic lighting, edge-to-edge composition, immersive environment, --ar 9:16 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0038_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0038_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0038_Ready_for_Steaming\Gallery_U1.png</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0038_Ready_for_Steaming\Gallery_U2.png</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0038_Ready_for_Steaming\Gallery_U3.png</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0038_Ready_for_Steaming\Gallery_U4.png</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Printify_PublishExternalPending_Mockups8</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>5/6/2026  7:19:04 PM</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>69fbccf9ce0d8cb5570fc6f0</t>
+        </is>
+      </c>
+      <c r="R270" s="1" t="n">
+        <v>46148.84302734954</v>
+      </c>
+      <c r="V270" s="1" t="n">
+        <v>46148.84259488426</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0039</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0039</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Dark Academia Horological Manuscript Chamber Poster 12x18 Study Decor Wall Gift</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Step into a world of temporal mystery with this dark academia poster featuring a grand chamber vessel of corroded bronze and cracked timepiece glass. Gravity-defying ancient horology books, kintsugi gold seams, and toxic jade bioluminescence create an immersive watchmaker aesthetic. Perfect for the intellectual book lover or student seeking vintage study desk inspiration.&lt;/p&gt;&lt;p&gt;This 12x18 poster transforms any room into a scholar's retreat. The ultra-detailed corrosion and glass fracture patterns evoke a mentor-grade collectible feel, ideal for a study, library, or minimalist workspace. Use it to spark curiosity about clockwork texts and timepiece manuscripts.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte poster paper, 200 gsm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 x 18 inches&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia Mentor-Grade, dark academia aesthetic&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Horological chamber art, timepiece manuscript archive, corroded bronze vessel, kintsugi gold seams, clockwork texts, jade bioluminescence, immersive composition&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study decor, library wall art, student gift, vintage intellectual room accent, watchmaker aesthetic display&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>$34.99</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Horological chamber art, timepiece manuscript archive, corroded bronze vessel, kintsugi gold seams, clockwork texts, jade bioluminescence, immersive composition</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0039_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0039_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0039_Ready_for_Steaming\Gallery_U1.png</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0039_Ready_for_Steaming\Gallery_U2.png</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0039_Ready_for_Steaming\Gallery_U3.png</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0039_Ready_for_Steaming\Gallery_U4.png</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Printify_PublishExternalPending_Mockups8</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>5/6/2026  7:19:10 PM</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>69fbcd1aee663532c8019ec7</t>
+        </is>
+      </c>
+      <c r="R271" s="1" t="n">
+        <v>46148.80971548611</v>
+      </c>
+      <c r="V271" s="1" t="n">
+        <v>46148.84261596065</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0040</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0040</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Dark Academia Meteorological Orrery 12x18 Poster Study Decor Atmospheric Texts</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;This poster presents a mentor-grade vision of a meteorological orrery archive, where corroded copper and cracked atmospheric glass cradle ancient weather manuscripts. Kintsugi repair seams glow with golden light, while toxic jade bioluminescence illuminates swirling climatic dust, creating an immersive dark academia aesthetic perfect for intellectual environments.&lt;/p&gt;&lt;p&gt;Printed on premium semi-gloss poster paper, this 12x18 inch piece delivers ultra-detailed corrosion patterns, glass fracture textures, and micro-engraved surface relief. Ideal for a study, library, or home office, it transforms any wall into a portal to a forgotten scientific archive. The dramatic side lighting and emerald glow add depth, making it a conversation starter for book lovers and scholars.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;b&gt;Includes:&lt;/b&gt; One 12x18 inch poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;b&gt;Material:&lt;/b&gt; Premium semi-gloss poster paper (200 gsm)&lt;/li&gt;&lt;li&gt;&lt;b&gt;Size:&lt;/b&gt; 12 x 18 inches (30.5 x 45.7 cm)&lt;/li&gt;&lt;li&gt;&lt;b&gt;Style:&lt;/b&gt; Dark Academia, Mentor-Grade&lt;/li&gt;&lt;li&gt;&lt;b&gt;DNA Profile:&lt;/b&gt; Corroded copper, cracked glass, kintsugi gold, toxic jade, ancient parchment, atmospheric texts, brass clockwork, jade bioluminescence, meteorological dust, immersive environment&lt;/li&gt;&lt;li&gt;&lt;b&gt;Use Cases:&lt;/b&gt; Study desk wall art, vintage library decor, student room accent, intellectual gift for book lovers, home office inspiration&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;b&gt;Image Note:&lt;/b&gt; </t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>$34.99</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>A massive orrery archive constructed from corroded copper and cracked atmospheric glass containing gravity-defying ancient weather manuscripts, kintsugi repair seams glowing with golden light, toxic jade bioluminescence illuminating meteorological parchment, swirling climatic dust trapped inside the orrery, brass clockwork atmospheric prediction mechanisms, dramatic side lighting with emerald glow, dark academia aesthetic, ultra-detailed corrosion and glass fracture patterns, hyper-detailed mentor-grade object design, primary material system: Corroded Copper, Cracked Glass, Kintsugi Gold, Toxic Jade, Ancient Parchment, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, full frame, cinematic lighting, edge-to-edge composition, immersive environment, --ar 9:16 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0040_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0040_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0040_Ready_for_Steaming\Gallery_U1.png</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0040_Ready_for_Steaming\Gallery_U2.png</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0040_Ready_for_Steaming\Gallery_U3.png</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0040_Ready_for_Steaming\Gallery_U4.png</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>Printify_PublishExternalPending_Mockups8</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>5/6/2026  7:19:16 PM</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>69fbcd3eb8dd7e2bb0095af7</t>
+        </is>
+      </c>
+      <c r="R272" s="1" t="n">
+        <v>46148.81078710648</v>
+      </c>
+      <c r="V272" s="1" t="n">
+        <v>46148.84263555556</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0041</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0041</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Dark Academia Astrological Globe Poster 12x18 Study Room Decor Starlight Jade</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Elevate your intellectual sanctuary with this Obsidian Eclipse Astrological Globe poster, a museum-quality artifact designed for the mentor-grade collector. Featuring a triple-ringed celestial globe with obsidian meridian rings and a starlight jade sphere core, this piece captures the essence of dark academia aesthetics. Silver filigree constellations and crystalline star charts orbit in concentric layers, while floating stardust nodes add a touch of cosmic mystery. Warm candlelight-inspired tones and gold leaf engravings evoke a vintage study atmosphere, perfect for book lovers and astronomy enthusiasts.&lt;/p&gt;&lt;p&gt;Printed on premium 12x18-inch poster paper, this artwork transforms any space into a scholarly retreat. Ideal for a study desk, library wall, or bedroom gallery, it serves as a conversation starter for students, professors, and collectors. The high-contrast silhouette and cinematic lighting ensure the design pops, while the white background isolation keeps the focus on the intricate details. Use it to inspire deep thought, complement vintage decor, or as a thoughtful gift for the intellectual in your life.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18-inch poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte poster paper, 200 gsm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12x18 inches (30.5 x 45.7 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Dark Academia, Mentor-Grade, Astrological&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Obsidian, Starlight Jade, Dark Oak, Gold Leaf, Crystalline Glass; triple-ringed globe, silver filigree constellations, floating stardust nodes, warm candlelight shadows, micro-engraved surface relief, bioluminescent glow&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study room decor, library accent, bedroom wall art, office inspiration, gift for astronomy lovers, vintage aesthetic collectors&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>$34.99</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>A triple-ringed astrological globe with obsidian meridian rings, starlight jade sphere core displaying constellations in silver filigree, crystalline star charts orbiting in concentric layers, floating stardust nodes suspended in zero gravity, dark oak pedestal base with astronomical engravings in gold leaf, academia study aesthetic, warm candlelight from left casting dramatic shadows, hyper-detailed mentor-grade object design, primary material system: Obsidian, Starlight Jade, Dark Oak, Gold Leaf, Crystalline Glass, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, full frame, cinematic lighting, edge-to-edge composition, immersive environment, --ar 9:16 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0041_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0041_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0041_Ready_for_Steaming\Gallery_U1.png</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0041_Ready_for_Steaming\Gallery_U2.png</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0041_Ready_for_Steaming\Gallery_U3.png</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0041_Ready_for_Steaming\Gallery_U4.png</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>Printify_PublishExternalPending_Mockups8</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>5/6/2026  7:19:24 PM</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>69fbcd65cacc667dc70b7c2a</t>
+        </is>
+      </c>
+      <c r="R273" s="1" t="n">
+        <v>46148.81192653935</v>
+      </c>
+      <c r="V273" s="1" t="n">
+        <v>46148.84265912037</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0042</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0042</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Dark Academia Armillary Sphere Poster 12x18 Vintage Study Decor Zodiac Symbols</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Step into a world of scholarly elegance with this Midnight Constellation Armillary Sphere poster. Designed for the Academia Mentor-Grade aesthetic, this piece transforms any study or library into a sanctuary of intellectual pursuit and celestial wonder.&lt;/p&gt;&lt;p&gt;Perfect for adorning your study desk or reading nook, this 12x18 poster brings the intricate beauty of an obsidian-and-jade armillary sphere to your wall. The platinum inlay and gold leaf accents evoke a vintage, museum-quality feel that resonates with book lovers and astronomy enthusiasts alike.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper stock&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 inches by 18 inches&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia Mentor-Grade, Dark Academia, Celestial Vintage&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Dark academia, study, vintage, intellectual, book lover, student, journal, study desk&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Wall art for home library, dorm room, office, or classroom; gift for astronomy or history buffs; decorative accent for vintage-themed interiors&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>$34.99</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Dark academia, study, vintage, intellectual, book lover, student, journal, study desk</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0042_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0042_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0042_Ready_for_Steaming\Gallery_U1.png</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0042_Ready_for_Steaming\Gallery_U2.png</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0042_Ready_for_Steaming\Gallery_U3.png</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0042_Ready_for_Steaming\Gallery_U4.png</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>Printify_PublishExternalPending_Mockups8</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>5/6/2026  7:19:30 PM</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>69fbcd8a3014a1ea840da971</t>
+        </is>
+      </c>
+      <c r="R274" s="1" t="n">
+        <v>46148.81309128472</v>
+      </c>
+      <c r="V274" s="1" t="n">
+        <v>46148.84267935185</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0044-FIX1</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0044-FIX1</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Zen Aesthetic Dragon Coil 4pc 6x6 Kiss-Cut Sticker Laptop Journal Water Bottle</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Zen Dragon Coil Sticker Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Bring calm and balance into your daily routine with this Zen Dragon Coil Sticker zen aesthetic kiss-cut sticker.&lt;/p&gt;&lt;p&gt;Designed for study rooms, creative workspaces, shelves, gallery walls, and collectible aesthetic decor, this sticker blends niche aesthetic appeal with collectible mentor-grade artwork.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Missing&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; mindfulness lovers, minimalists, journal keepers, yoga enthusiasts, and peaceful room setups.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; mandala art, circular design, meditation symbol, spiritual geometry, sacred geometry, yin yang balance, harmony sticker, zen circle, endless knot, Buddhist art&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Complete the collection with matching Alchemy pieces.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0044&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0044_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0044_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0044_Ready_for_Steaming\Sticker-Zen-0044_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0044_Ready_for_Steaming\Sticker-Zen-0044_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0044_Ready_for_Steaming\Sticker-Zen-0044_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0044_Ready_for_Steaming\Sticker-Zen-0044_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>Printify_PublishExternalPending_Mockups3</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>2026-05-06 20:41:20 -0400</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>69fbdfc9f60a24b6d1035f8b</t>
+        </is>
+      </c>
+      <c r="R275" s="1" t="n">
+        <v>46148.8643354529</v>
       </c>
     </row>
   </sheetData>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V275"/>
+  <dimension ref="A1:X278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,6 +530,16 @@
           <t>External_Sync_Timestamp</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Retire_Timestamp</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Retire_Result</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4704,12 +4714,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>4/29/2026  1:28:53 PM</t>
+          <t>5/6/2026  10:34:46 PM</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4735,6 +4745,14 @@
       <c r="V49" s="1" t="n">
         <v>46148.857313125</v>
       </c>
+      <c r="W49" s="1" t="n">
+        <v>46148.96467479166</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4809,7 +4827,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4840,6 +4858,14 @@
       <c r="V50" s="1" t="n">
         <v>46148.85735475695</v>
       </c>
+      <c r="W50" s="1" t="n">
+        <v>46148.97155159722</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4914,7 +4940,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4945,6 +4971,14 @@
       <c r="V51" s="1" t="n">
         <v>46148.85737456018</v>
       </c>
+      <c r="W51" s="1" t="n">
+        <v>46148.97198284722</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5109,7 +5143,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5140,6 +5174,14 @@
       <c r="V53" s="1" t="n">
         <v>46148.85741126158</v>
       </c>
+      <c r="W53" s="1" t="n">
+        <v>46148.97242318466</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -25256,7 +25298,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups3</t>
+          <t>Printify_Published_Mockups3</t>
         </is>
       </c>
       <c r="P275" t="inlineStr">
@@ -25270,7 +25312,349 @@
         </is>
       </c>
       <c r="R275" s="1" t="n">
-        <v>46148.8643354529</v>
+        <v>46148.96308587963</v>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>406909884756</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909884756</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V275" s="1" t="n">
+        <v>46148.96338582176</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0045-FIX1</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0045-FIX1</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Floating Dragon Minimal Zen 4pc 6x6 Kiss-Cut Vinyl Desk Collector Decor Sky Art</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Floating Zen Dragon Sticker - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Zen aesthetic piece for students, remote workers, yoga lovers, and anyone building a serene everyday space. Designed for peaceful desks, journals, and small rituals, this Floating Zen Dragon Sticker kiss-cut sticker carries a clean Zen mood.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for easy comparison.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A Zen dragon floating serenely through clouds, body of Translucent Imperial Jade with Kintsugi Gold Veins, Bioluminescent Glow trailing from Internal Crystalline Structures, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; students, remote workers, yoga lovers, and anyone building a serene everyday space.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; cloud dragon, flying creature, sky art, freedom symbol, dreamy aesthetic, ethereal creature, weightless art, air element, celestial being, heaven dragon&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Saved under the reference SKU below for easy collector matching.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0045&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>A Zen dragon floating serenely through clouds, body of Translucent Imperial Jade with Kintsugi Gold Veins, Bioluminescent Glow trailing from Internal Crystalline Structures, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0045_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0045_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0045_Ready_for_Steaming\Sticker-Zen-0045_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0045_Ready_for_Steaming\Sticker-Zen-0045_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0045_Ready_for_Steaming\Sticker-Zen-0045_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0045_Ready_for_Steaming\Sticker-Zen-0045_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>2026-05-06 23:12:41 -0400</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>69fc03470ce75ae193034081</t>
+        </is>
+      </c>
+      <c r="R276" s="1" t="n">
+        <v>46148.96832634259</v>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>406909890800</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909890800</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V276" s="1" t="n">
+        <v>46148.9686284375</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0046-FIX1</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0046-FIX1</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Zen Aesthetic Dragon and Pearl 4pc 6x6 Kiss-Cut Sticker Laptop Journal Water</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Dragon and Pearl Sticker Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Bring calm and balance into your daily routine with this Dragon and Pearl Sticker zen aesthetic kiss-cut sticker.&lt;/p&gt;&lt;p&gt;Designed for study rooms, creative workspaces, shelves, gallery walls, and collectible aesthetic decor, this sticker blends niche aesthetic appeal with collectible mentor-grade artwork.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A Zen dragon chasing a pearl of Translucent Imperial Jade, Kintsugi Gold Veins throughout body, Bioluminescent Glow from Internal Crystalline Structures illuminating the scene, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; mindfulness lovers, minimalists, journal keepers, yoga enthusiasts, and peaceful room setups.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; dragon pearl, wisdom symbol, treasure guardian, chase scene, dynamic action, movement art, pursuit motif, goal achievement, ambition symbol, success charm&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Complete the collection with matching Alchemy pieces.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0046&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>A Zen dragon chasing a pearl of Translucent Imperial Jade, Kintsugi Gold Veins throughout body, Bioluminescent Glow from Internal Crystalline Structures illuminating the scene, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0046_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0046_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0046_Ready_for_Steaming\Sticker-Zen-0046_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0046_Ready_for_Steaming\Sticker-Zen-0046_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0046_Ready_for_Steaming\Sticker-Zen-0046_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0046_Ready_for_Steaming\Sticker-Zen-0046_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>2026-05-06 23:12:41 -0400</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>69fc035bce0d8cb5570fe6af</t>
+        </is>
+      </c>
+      <c r="R277" s="1" t="n">
+        <v>46148.96911913194</v>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>406909891985</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909891985</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V277" s="1" t="n">
+        <v>46148.96941771991</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0049-FIX1</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0049-FIX1</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Sleeping Dragon Minimal Zen 4pc 6x6 Kiss-Cut Vinyl Desk Collector Decor Laptop</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Sleeping Zen Dragon Sticker - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Zen aesthetic piece for students, remote workers, yoga lovers, and anyone building a serene everyday space. Designed for peaceful desks, journals, and small rituals, this Sleeping Zen Dragon Sticker kiss-cut sticker carries a clean Zen mood.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for easy comparison.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A peaceful Zen dragon sleeping curled up, body of Translucent Imperial Jade with Kintsugi Gold Veins, soft Bioluminescent Glow pulsing from Internal Crystalline Structures, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; students, remote workers, yoga lovers, and anyone building a serene everyday space.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; sleeping dragon, peaceful creature, rest art, calm aesthetic, dream dragon, night scene, cozy art, protective sleep, guardian resting, tranquil moment&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Saved under the reference SKU below for easy collector matching.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0049&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>A peaceful Zen dragon sleeping curled up, body of Translucent Imperial Jade with Kintsugi Gold Veins, soft Bioluminescent Glow pulsing from Internal Crystalline Structures, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0049_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0049_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0049_Ready_for_Steaming\Sticker-Zen-0049_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0049_Ready_for_Steaming\Sticker-Zen-0049_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0049_Ready_for_Steaming\Sticker-Zen-0049_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0049_Ready_for_Steaming\Sticker-Zen-0049_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>2026-05-06 23:12:41 -0400</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>69fc036aee663532c801be71</t>
+        </is>
+      </c>
+      <c r="R278" s="1" t="n">
+        <v>46148.96992167824</v>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>406909893702</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909893702</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V278" s="1" t="n">
+        <v>46148.97022515046</v>
       </c>
     </row>
   </sheetData>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X278"/>
+  <dimension ref="A1:X283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5175,7 +5175,7 @@
         <v>46148.85741126158</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>46148.97242318466</v>
+        <v>46148.97242318287</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5287,6 +5287,14 @@
       <c r="V54" s="1" t="n">
         <v>46148.85743253472</v>
       </c>
+      <c r="W54" s="1" t="n">
+        <v>46148.98237008102</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5361,7 +5369,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5392,6 +5400,14 @@
       <c r="V55" s="1" t="n">
         <v>46148.85745373843</v>
       </c>
+      <c r="W55" s="1" t="n">
+        <v>46148.9827974537</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5466,7 +5482,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5497,6 +5513,14 @@
       <c r="V56" s="1" t="n">
         <v>46148.85748322916</v>
       </c>
+      <c r="W56" s="1" t="n">
+        <v>46148.98322974537</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5571,7 +5595,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5602,6 +5626,14 @@
       <c r="V57" s="1" t="n">
         <v>46148.85750754629</v>
       </c>
+      <c r="W57" s="1" t="n">
+        <v>46148.98364238426</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5676,7 +5708,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5707,6 +5739,14 @@
       <c r="V58" s="1" t="n">
         <v>46148.85752447916</v>
       </c>
+      <c r="W58" s="1" t="n">
+        <v>46148.98407751161</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -25655,6 +25695,546 @@
       </c>
       <c r="V278" s="1" t="n">
         <v>46148.97022515046</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0050-FIX1</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0050-FIX1</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Translucent Jade Dragon Mindful Zen 4pc 6x6 Vinyl Sticker Yoga Minimalist Gift</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Translucent Jade Dragon Sticker | Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Add a quiet mindful accent to your workspace with this Translucent Jade Dragon Sticker kiss-cut sticker. The artwork is built around a focused visual DNA profile, so each piece feels like part of a coherent small-batch collection.&lt;/p&gt;&lt;p&gt;Use it for laptops, notebooks, reading corners, desk setups, gallery shelves, and gift bundles. The composition favors readable detail, strong mood, and giftable niche appeal without generic mass-market styling.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Translucent Imperial Jade dragon with Kintsugi Gold Veins, Bioluminescent Glow, and Internal Crystalline Structures, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; meditation fans, calm desk setups, notebook collectors, and gift buyers who like clean aesthetics.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; die-cut sticker, kawaii, anime, laptop decal, water bottle art, planner decoration, journal sticker, vinyl sticker, waterproof, holographic effect&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Pair it with related OpenClaw pieces for a coordinated collection.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0050&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Translucent Imperial Jade dragon with Kintsugi Gold Veins, Bioluminescent Glow, and Internal Crystalline Structures, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0050_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0050_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0050_Ready_for_Steaming\Sticker-Zen-0050_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0050_Ready_for_Steaming\Sticker-Zen-0050_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0050_Ready_for_Steaming\Sticker-Zen-0050_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0050_Ready_for_Steaming\Sticker-Zen-0050_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>2026-05-06 23:25:16 -0400</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>69fc0639ee663532c801bff2</t>
+        </is>
+      </c>
+      <c r="R279" s="1" t="n">
+        <v>46148.97730148148</v>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>406909904704</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909904704</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V279" s="1" t="n">
+        <v>46148.97760329861</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0051-FIX1</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0051-FIX1</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Kintsugi Gold Dragon Mindful Zen 4pc 6x6 Vinyl Sticker Yoga Minimalist Gift</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Kintsugi Gold Dragon Sticker | Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Add a quiet mindful accent to your workspace with this Kintsugi Gold Dragon Sticker kiss-cut sticker. The artwork is built around a focused visual DNA profile, so each piece feels like part of a coherent small-batch collection.&lt;/p&gt;&lt;p&gt;Use it for laptops, notebooks, reading corners, desk setups, gallery shelves, and gift bundles. The composition favors readable detail, strong mood, and giftable niche appeal without generic mass-market styling.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Kintsugi Gold Veins dragon with Translucent Imperial Jade accents, Bioluminescent Glow, and Internal Crystalline Structures, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; meditation fans, calm desk setups, notebook collectors, and gift buyers who like clean aesthetics.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; gold foil sticker, luxury decal, metallic finish, premium sticker, phone case decor, car window sticker, laptop skin, gift sticker, Japanese art, wabi-sabi&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Pair it with related OpenClaw pieces for a coordinated collection.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0051&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Kintsugi Gold Veins dragon with Translucent Imperial Jade accents, Bioluminescent Glow, and Internal Crystalline Structures, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0051_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0051_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0051_Ready_for_Steaming\Sticker-Zen-0051_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0051_Ready_for_Steaming\Sticker-Zen-0051_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0051_Ready_for_Steaming\Sticker-Zen-0051_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0051_Ready_for_Steaming\Sticker-Zen-0051_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>2026-05-06 23:25:16 -0400</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>69fc06482007fddea00dcf21</t>
+        </is>
+      </c>
+      <c r="R280" s="1" t="n">
+        <v>46148.97804450231</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>406909905683</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909905683</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V280" s="1" t="n">
+        <v>46148.97834259259</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0052-FIX1</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0052-FIX1</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Bioluminescent Dragon 4pc 6x6 Kiss-Cut Sticker Zen Aesthetic Laptop Journal</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Bioluminescent Dragon Sticker Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Bring calm and balance into your daily routine with this Bioluminescent Dragon Sticker zen aesthetic kiss-cut sticker.&lt;/p&gt;&lt;p&gt;Designed for study rooms, creative workspaces, shelves, gallery walls, and collectible aesthetic decor, this sticker blends niche aesthetic appeal with collectible mentor-grade artwork.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Bioluminescent Glow dragon with Translucent Imperial Jade body, Kintsugi Gold Veins, and Internal Crystalline Structures, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; mindfulness lovers, minimalists, journal keepers, yoga enthusiasts, and peaceful room setups.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; glow in dark sticker, UV reactive, night light effect, rave sticker, festival decal, psychedelic art, trippy design, neon colors, cyberpunk aesthetic, futuristic&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Complete the collection with matching Alchemy pieces.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0052&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Bioluminescent Glow dragon with Translucent Imperial Jade body, Kintsugi Gold Veins, and Internal Crystalline Structures, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0052_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0052_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0052_Ready_for_Steaming\Sticker-Zen-0052_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0052_Ready_for_Steaming\Sticker-Zen-0052_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0052_Ready_for_Steaming\Sticker-Zen-0052_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0052_Ready_for_Steaming\Sticker-Zen-0052_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>2026-05-06 23:25:16 -0400</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>69fc0655ee663532c801bffc</t>
+        </is>
+      </c>
+      <c r="R281" s="1" t="n">
+        <v>46148.97888234954</v>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>406909906686</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909906686</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V281" s="1" t="n">
+        <v>46148.97918194444</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0053-FIX1</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0053-FIX1</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Crystalline Dragon Minimal Zen 4pc 6x6 Kiss-Cut Vinyl Desk Collector Decor Gift</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Crystalline Dragon Sticker - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Zen aesthetic piece for students, remote workers, yoga lovers, and anyone building a serene everyday space. Designed for peaceful desks, journals, and small rituals, this Crystalline Dragon Sticker kiss-cut sticker carries a clean Zen mood.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for easy comparison.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Internal Crystalline Structures dragon with Translucent Imperial Jade surface, Kintsugi Gold Veins, and Bioluminescent Glow, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; students, remote workers, yoga lovers, and anyone building a serene everyday space.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; crystal healing sticker, geometric design, prismatic effect, rainbow reflection, spiritual crystal, mineral art, geology aesthetic, sacred geometry, mandala pattern, meditation tool&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Saved under the reference SKU below for easy collector matching.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0053&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Internal Crystalline Structures dragon with Translucent Imperial Jade surface, Kintsugi Gold Veins, and Bioluminescent Glow, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0053_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0053_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0053_Ready_for_Steaming\Sticker-Zen-0053_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0053_Ready_for_Steaming\Sticker-Zen-0053_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0053_Ready_for_Steaming\Sticker-Zen-0053_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0053_Ready_for_Steaming\Sticker-Zen-0053_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>2026-05-06 23:25:16 -0400</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>69fc06640ce75ae19303421a</t>
+        </is>
+      </c>
+      <c r="R282" s="1" t="n">
+        <v>46148.97959608796</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>406909907111</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909907111</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V282" s="1" t="n">
+        <v>46148.97989796296</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0054-FIX1</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0054-FIX1</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Dragon Meditation Minimal Zen 4pc 6x6 Kiss-Cut Vinyl Desk Collector Decor Gift</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Zen Dragon Meditation Sticker - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Zen aesthetic piece for students, remote workers, yoga lovers, and anyone building a serene everyday space. Designed for peaceful desks, journals, and small rituals, this Zen Dragon Meditation Sticker kiss-cut sticker carries a clean Zen mood.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for easy comparison.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Serene Zen dragon combining Translucent Imperial Jade, Kintsugi Gold Veins, Bioluminescent Glow, and Internal Crystalline Structures in meditation pose, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; students, remote workers, yoga lovers, and anyone building a serene everyday space.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; meditation sticker, mindfulness tool, yoga accessory, spiritual guide, calm aesthetic, peace symbol, Buddhist art, zen garden, minimalist design, mental health&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Saved under the reference SKU below for easy collector matching.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0054&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Serene Zen dragon combining Translucent Imperial Jade, Kintsugi Gold Veins, Bioluminescent Glow, and Internal Crystalline Structures in meditation pose, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0054_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0054_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0054_Ready_for_Steaming\Sticker-Zen-0054_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0054_Ready_for_Steaming\Sticker-Zen-0054_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0054_Ready_for_Steaming\Sticker-Zen-0054_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0054_Ready_for_Steaming\Sticker-Zen-0054_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups6</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>2026-05-06 23:25:16 -0400</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>69fc0674ee663532c801c009</t>
+        </is>
+      </c>
+      <c r="R283" s="1" t="n">
+        <v>46148.98036486111</v>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>406909907742</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909907742</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V283" s="1" t="n">
+        <v>46148.98066784722</v>
       </c>
     </row>
   </sheetData>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X283"/>
+  <dimension ref="A1:AC283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,6 +540,31 @@
           <t>Retire_Result</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>External_Missing_First_Seen</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>External_Missing_Attempts</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Self_Healing_Decision</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Self_Healing_Reason</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Self_Healing_Timestamp</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3225,7 +3250,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups4</t>
+          <t>Quarantined_ExternalMissing</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3241,6 +3266,25 @@
       <c r="V32" s="1" t="n">
         <v>46148.85710967593</v>
       </c>
+      <c r="Y32" s="1" t="n">
+        <v>46149.0015055999</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>QUARANTINE_LOSS_ASSET</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>healthy network/status but no external after 3508m and 5 attempts</t>
+        </is>
+      </c>
+      <c r="AC32" s="1" t="n">
+        <v>46149.0015055999</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3484,7 +3528,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups4</t>
+          <t>Quarantined_ExternalMissing</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3500,6 +3544,25 @@
       <c r="V35" s="1" t="n">
         <v>46148.85712829861</v>
       </c>
+      <c r="Y35" s="1" t="n">
+        <v>46149.00153667747</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>QUARANTINE_LOSS_ASSET</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>healthy network/status but no external after 3507m and 5 attempts</t>
+        </is>
+      </c>
+      <c r="AC35" s="1" t="n">
+        <v>46149.00153667747</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3656,7 +3719,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups4</t>
+          <t>Quarantined_ExternalMissing</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3672,6 +3735,25 @@
       <c r="V37" s="1" t="n">
         <v>46148.85714457176</v>
       </c>
+      <c r="Y37" s="1" t="n">
+        <v>46149.00157481133</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>QUARANTINE_LOSS_ASSET</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>healthy network/status but no external after 3508m and 5 attempts</t>
+        </is>
+      </c>
+      <c r="AC37" s="1" t="n">
+        <v>46149.00157481133</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3746,7 +3828,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups4</t>
+          <t>Quarantined_ExternalMissing</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3762,6 +3844,25 @@
       <c r="V38" s="1" t="n">
         <v>46148.85716043982</v>
       </c>
+      <c r="Y38" s="1" t="n">
+        <v>46149.0016067215</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>QUARANTINE_LOSS_ASSET</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>healthy network/status but no external after 3507m and 5 attempts</t>
+        </is>
+      </c>
+      <c r="AC38" s="1" t="n">
+        <v>46149.0016067215</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3918,7 +4019,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups4</t>
+          <t>Quarantined_ExternalMissing</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3934,6 +4035,25 @@
       <c r="V40" s="1" t="n">
         <v>46148.85717578704</v>
       </c>
+      <c r="Y40" s="1" t="n">
+        <v>46149.00163813666</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>QUARANTINE_LOSS_ASSET</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>healthy network/status but no external after 3507m and 5 attempts</t>
+        </is>
+      </c>
+      <c r="AC40" s="1" t="n">
+        <v>46149.00163813666</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4008,7 +4128,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups4</t>
+          <t>Quarantined_ExternalMissing</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4024,6 +4144,25 @@
       <c r="V41" s="1" t="n">
         <v>46148.85719202546</v>
       </c>
+      <c r="Y41" s="1" t="n">
+        <v>46149.00167109185</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>QUARANTINE_LOSS_ASSET</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>healthy network/status but no external after 3507m and 5 attempts</t>
+        </is>
+      </c>
+      <c r="AC41" s="1" t="n">
+        <v>46149.00167109185</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4098,7 +4237,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups4</t>
+          <t>Quarantined_ExternalMissing</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4114,6 +4253,25 @@
       <c r="V42" s="1" t="n">
         <v>46148.85721072917</v>
       </c>
+      <c r="Y42" s="1" t="n">
+        <v>46149.00170282264</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>QUARANTINE_LOSS_ASSET</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>healthy network/status but no external after 3507m and 5 attempts</t>
+        </is>
+      </c>
+      <c r="AC42" s="1" t="n">
+        <v>46149.00170282264</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4188,7 +4346,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups4</t>
+          <t>Quarantined_ExternalMissing</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4204,6 +4362,25 @@
       <c r="V43" s="1" t="n">
         <v>46148.85722725694</v>
       </c>
+      <c r="Y43" s="1" t="n">
+        <v>46149.00173392263</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>QUARANTINE_LOSS_ASSET</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>healthy network/status but no external after 3507m and 5 attempts</t>
+        </is>
+      </c>
+      <c r="AC43" s="1" t="n">
+        <v>46149.00173392263</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4278,7 +4455,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups4</t>
+          <t>Quarantined_ExternalMissing</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4294,6 +4471,25 @@
       <c r="V44" s="1" t="n">
         <v>46148.8572454051</v>
       </c>
+      <c r="Y44" s="1" t="n">
+        <v>46149.00176635587</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>QUARANTINE_LOSS_ASSET</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>healthy network/status but no external after 3507m and 5 attempts</t>
+        </is>
+      </c>
+      <c r="AC44" s="1" t="n">
+        <v>46149.00176635587</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4450,7 +4646,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups4</t>
+          <t>Quarantined_ExternalMissing</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4466,6 +4662,25 @@
       <c r="V46" s="1" t="n">
         <v>46148.85727467592</v>
       </c>
+      <c r="Y46" s="1" t="n">
+        <v>46149.00182363379</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>QUARANTINE_LOSS_ASSET</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>healthy network/status but no external after 3507m and 5 attempts</t>
+        </is>
+      </c>
+      <c r="AC46" s="1" t="n">
+        <v>46149.00182363379</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5053,7 +5268,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups4</t>
+          <t>Quarantined_ExternalMissing</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5069,6 +5284,25 @@
       <c r="V52" s="1" t="n">
         <v>46148.85739521991</v>
       </c>
+      <c r="Y52" s="1" t="n">
+        <v>46149.00185479868</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>QUARANTINE_LOSS_ASSET</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>healthy network/status but no external after 3507m and 5 attempts</t>
+        </is>
+      </c>
+      <c r="AC52" s="1" t="n">
+        <v>46149.00185479868</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5740,7 +5974,7 @@
         <v>46148.85752447916</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>46148.98407751161</v>
+        <v>46148.98407751157</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6766,7 +7000,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups4</t>
+          <t>Quarantined_ExternalMissing</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6782,6 +7016,25 @@
       <c r="V68" s="1" t="n">
         <v>46148.85771094907</v>
       </c>
+      <c r="Y68" s="1" t="n">
+        <v>46149.00188778307</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>QUARANTINE_LOSS_ASSET</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>healthy network/status but no external after 3506m and 5 attempts</t>
+        </is>
+      </c>
+      <c r="AC68" s="1" t="n">
+        <v>46149.00188778307</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6856,7 +7109,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups4</t>
+          <t>Quarantined_ExternalMissing</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6872,6 +7125,25 @@
       <c r="V69" s="1" t="n">
         <v>46148.85773053241</v>
       </c>
+      <c r="Y69" s="1" t="n">
+        <v>46149.00191942298</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>QUARANTINE_LOSS_ASSET</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>healthy network/status but no external after 3506m and 5 attempts</t>
+        </is>
+      </c>
+      <c r="AC69" s="1" t="n">
+        <v>46149.00191942298</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -18452,6 +18724,43 @@
           <t>69f855abffbc831dea0847c8</t>
         </is>
       </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>406903251282</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406903251282</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V196" s="1" t="n">
+        <v>46149.00194953031</v>
+      </c>
+      <c r="Y196" s="1" t="n">
+        <v>46149.00194953031</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406903251282 handle=https://www.ebay.com/itm/406903251282</t>
+        </is>
+      </c>
+      <c r="AC196" s="1" t="n">
+        <v>46149.00194953031</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -18539,6 +18848,43 @@
           <t>69f8530b5da263f75f04d837</t>
         </is>
       </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>406903252244</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406903252244</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V197" s="1" t="n">
+        <v>46149.00198168619</v>
+      </c>
+      <c r="Y197" s="1" t="n">
+        <v>46149.00198168619</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406903252244 handle=https://www.ebay.com/itm/406903252244</t>
+        </is>
+      </c>
+      <c r="AC197" s="1" t="n">
+        <v>46149.00198168619</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -18626,6 +18972,43 @@
           <t>69f863f9f9374ed4f105c588</t>
         </is>
       </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>406903760725</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406903760725</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V198" s="1" t="n">
+        <v>46149.00201393896</v>
+      </c>
+      <c r="Y198" s="1" t="n">
+        <v>46149.00201393896</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406903760725 handle=https://www.ebay.com/itm/406903760725</t>
+        </is>
+      </c>
+      <c r="AC198" s="1" t="n">
+        <v>46149.00201393896</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -18713,6 +19096,43 @@
           <t>69f8647ff9374ed4f105c605</t>
         </is>
       </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>406909148324</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909148324</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V199" s="1" t="n">
+        <v>46149.00204431882</v>
+      </c>
+      <c r="Y199" s="1" t="n">
+        <v>46149.00204431882</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909148324 handle=https://www.ebay.com/itm/406909148324</t>
+        </is>
+      </c>
+      <c r="AC199" s="1" t="n">
+        <v>46149.00204431882</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -18800,6 +19220,43 @@
           <t>69f865a55da263f75f04e768</t>
         </is>
       </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>406909151733</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909151733</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V200" s="1" t="n">
+        <v>46149.00207446046</v>
+      </c>
+      <c r="Y200" s="1" t="n">
+        <v>46149.00207446046</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909151733 handle=https://www.ebay.com/itm/406909151733</t>
+        </is>
+      </c>
+      <c r="AC200" s="1" t="n">
+        <v>46149.00207446046</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -18887,6 +19344,43 @@
           <t>69f8669583a8608fd80f0fdb</t>
         </is>
       </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>406909159060</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909159060</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V201" s="1" t="n">
+        <v>46149.00210729301</v>
+      </c>
+      <c r="Y201" s="1" t="n">
+        <v>46149.00210729301</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909159060 handle=https://www.ebay.com/itm/406909159060</t>
+        </is>
+      </c>
+      <c r="AC201" s="1" t="n">
+        <v>46149.00210729301</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -18973,6 +19467,43 @@
         <is>
           <t>69f867cc2592a8ad8e0f076e</t>
         </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>406909166683</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909166683</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V202" s="1" t="n">
+        <v>46149.00214023475</v>
+      </c>
+      <c r="Y202" s="1" t="n">
+        <v>46149.00214023475</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909166683 handle=https://www.ebay.com/itm/406909166683</t>
+        </is>
+      </c>
+      <c r="AC202" s="1" t="n">
+        <v>46149.00214023475</v>
       </c>
     </row>
     <row r="203">

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC283"/>
+  <dimension ref="A1:AH283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,6 +565,31 @@
           <t>Self_Healing_Timestamp</t>
         </is>
       </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Quiet_Jade_Pivot_Timestamp</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Quiet_Jade_Target</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Quiet_Jade_Search_Tags</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Quiet_Jade_Price_Decision</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Metadata_Sync_Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -835,12 +860,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4pc Kiss-Cut Sticker Set Mechanical Raven Familiar Laptop Journal Bottle Dark</t>
+          <t>Smoky Jade Sticker Set Mechanical Raven Familiar Bottle 4pc 6x6 Kiss-Cut Vinyl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4pc Kiss-Cut Sticker Set Mechanical Raven Familiar Laptop Journal Bottle Dark A 4-piece 6x6 kiss-cut vinyl sticker set made for laptops, journals, planners, water bottles, scrapbooks, study corners, and small gift bundles. Design style: Dark Academia relic art with a premium illustrated look, made for buyers who want a more atmospheric sticker set than generic decals. What you receive: one physical 4-piece sticker set. The main product image shows the actual set layout customers receive. Additional gallery images are close-up/detail previews of the artwork and are not extra products or separate variations. Production note: this item is produced on demand by a professional print partner and ships as a finished physical sticker product. Original listing note: &lt;h2&gt;Mechanical Raven Familiar - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Academia aesthetic piece for writers, learners, library lovers, and collectors of moody scholarly decor. Built for readers and collectors, this Mechanical Raven Familiar kiss-cut sticker blends literary atmosphere with vintage study-room style.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Smoky Jade Sticker Set Mechanical Raven Familiar Bottle 4pc 6x6 Kiss-Cut Vinyl&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for laptops, journals, planners, bottles, reading notebooks, and study desk gifts. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut vinyl sticker sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Mechanical Raven Familiar Bottle, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Academia-0004; Subject: Mechanical Raven Familiar Bottle&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -916,6 +941,31 @@
       <c r="V5" s="1" t="n">
         <v>46148.85707743056</v>
       </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Mechanical Raven Familiar Bottle, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2670,12 +2720,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Floating Island Sanctuary 4pc 6x6 Kiss-Cut Sticker Zen Aesthetic Laptop Journal</t>
+          <t>Reading Nook Vinyl Set Floating Island Sanctuary 4pc 6x6 Kiss-Cut Vinyl Quiet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Floating Island Sanctuary Sticker Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Bring calm and balance into your daily routine with this Floating Island Sanctuary Sticker zen aesthetic kiss-cut sticker.&lt;/p&gt;&lt;p&gt;Designed for study rooms, creative workspaces, shelves, gallery walls, and collectible aesthetic decor, this sticker blends niche aesthetic appeal with collectible mentor-grade artwork.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A tiny, floating island with a single pine tree, the island is a chunk of Mossy Granite, the tree is Ancient Bristlecone Pine with bark like Petrified Wood, a small glowing lantern hangs from a branch, dreamlike, , , , , 3D relief effect, sharp focus,&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; mindfulness lovers, minimalists, journal keepers, yoga enthusiasts, and peaceful room setups.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; floating island sticker, mossy granite, ancient tree, miniature world, fantasy landscape, dream core, serene escape, glowing lantern, imaginative art, detailed diorama&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Complete the collection with matching Alchemy pieces.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0010&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Reading Nook Vinyl Set Floating Island Sanctuary 4pc 6x6 Kiss-Cut Vinyl Quiet&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for laptops, journals, planners, bottles, reading notebooks, and study desk gifts. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut vinyl sticker sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Floating Island Sanctuary, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0010; Subject: Floating Island Sanctuary&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2751,6 +2801,31 @@
       <c r="V26" s="1" t="n">
         <v>46148.85709412037</v>
       </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Floating Island Sanctuary, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3267,7 +3342,7 @@
         <v>46148.85710967593</v>
       </c>
       <c r="Y32" s="1" t="n">
-        <v>46149.0015055999</v>
+        <v>46149.00150560185</v>
       </c>
       <c r="Z32" t="n">
         <v>6</v>
@@ -3283,7 +3358,7 @@
         </is>
       </c>
       <c r="AC32" s="1" t="n">
-        <v>46149.0015055999</v>
+        <v>46149.00150560185</v>
       </c>
     </row>
     <row r="33">
@@ -3545,7 +3620,7 @@
         <v>46148.85712829861</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>46149.00153667747</v>
+        <v>46149.00153667824</v>
       </c>
       <c r="Z35" t="n">
         <v>6</v>
@@ -3561,7 +3636,7 @@
         </is>
       </c>
       <c r="AC35" s="1" t="n">
-        <v>46149.00153667747</v>
+        <v>46149.00153667824</v>
       </c>
     </row>
     <row r="36">
@@ -3736,7 +3811,7 @@
         <v>46148.85714457176</v>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>46149.00157481133</v>
+        <v>46149.00157481481</v>
       </c>
       <c r="Z37" t="n">
         <v>6</v>
@@ -3752,7 +3827,7 @@
         </is>
       </c>
       <c r="AC37" s="1" t="n">
-        <v>46149.00157481133</v>
+        <v>46149.00157481481</v>
       </c>
     </row>
     <row r="38">
@@ -3845,7 +3920,7 @@
         <v>46148.85716043982</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>46149.0016067215</v>
+        <v>46149.00160672454</v>
       </c>
       <c r="Z38" t="n">
         <v>6</v>
@@ -3861,7 +3936,7 @@
         </is>
       </c>
       <c r="AC38" s="1" t="n">
-        <v>46149.0016067215</v>
+        <v>46149.00160672454</v>
       </c>
     </row>
     <row r="39">
@@ -4036,7 +4111,7 @@
         <v>46148.85717578704</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>46149.00163813666</v>
+        <v>46149.00163813657</v>
       </c>
       <c r="Z40" t="n">
         <v>6</v>
@@ -4052,7 +4127,7 @@
         </is>
       </c>
       <c r="AC40" s="1" t="n">
-        <v>46149.00163813666</v>
+        <v>46149.00163813657</v>
       </c>
     </row>
     <row r="41">
@@ -4145,7 +4220,7 @@
         <v>46148.85719202546</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>46149.00167109185</v>
+        <v>46149.00167108796</v>
       </c>
       <c r="Z41" t="n">
         <v>6</v>
@@ -4161,7 +4236,7 @@
         </is>
       </c>
       <c r="AC41" s="1" t="n">
-        <v>46149.00167109185</v>
+        <v>46149.00167108796</v>
       </c>
     </row>
     <row r="42">
@@ -4254,7 +4329,7 @@
         <v>46148.85721072917</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>46149.00170282264</v>
+        <v>46149.00170282408</v>
       </c>
       <c r="Z42" t="n">
         <v>6</v>
@@ -4270,7 +4345,7 @@
         </is>
       </c>
       <c r="AC42" s="1" t="n">
-        <v>46149.00170282264</v>
+        <v>46149.00170282408</v>
       </c>
     </row>
     <row r="43">
@@ -4363,7 +4438,7 @@
         <v>46148.85722725694</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>46149.00173392263</v>
+        <v>46149.00173392361</v>
       </c>
       <c r="Z43" t="n">
         <v>6</v>
@@ -4379,7 +4454,7 @@
         </is>
       </c>
       <c r="AC43" s="1" t="n">
-        <v>46149.00173392263</v>
+        <v>46149.00173392361</v>
       </c>
     </row>
     <row r="44">
@@ -4472,7 +4547,7 @@
         <v>46148.8572454051</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>46149.00176635587</v>
+        <v>46149.00176635417</v>
       </c>
       <c r="Z44" t="n">
         <v>6</v>
@@ -4488,7 +4563,7 @@
         </is>
       </c>
       <c r="AC44" s="1" t="n">
-        <v>46149.00176635587</v>
+        <v>46149.00176635417</v>
       </c>
     </row>
     <row r="45">
@@ -4663,7 +4738,7 @@
         <v>46148.85727467592</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>46149.00182363379</v>
+        <v>46149.00182363426</v>
       </c>
       <c r="Z46" t="n">
         <v>6</v>
@@ -4679,7 +4754,7 @@
         </is>
       </c>
       <c r="AC46" s="1" t="n">
-        <v>46149.00182363379</v>
+        <v>46149.00182363426</v>
       </c>
     </row>
     <row r="47">
@@ -5285,7 +5360,7 @@
         <v>46148.85739521991</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>46149.00185479868</v>
+        <v>46149.00185480324</v>
       </c>
       <c r="Z52" t="n">
         <v>6</v>
@@ -5301,7 +5376,7 @@
         </is>
       </c>
       <c r="AC52" s="1" t="n">
-        <v>46149.00185479868</v>
+        <v>46149.00185480324</v>
       </c>
     </row>
     <row r="53">
@@ -6005,12 +6080,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mindful Zen Azure Dragon Warrior 4pc 6x6 Vinyl Sticker Laptop Journal Gift Desk</t>
+          <t>Quiet Desk Sticker Pack Azure Dragon Warrior 4pc 6x6 Kiss-Cut Vinyl Laptop Gift</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Azure Dragon Warrior Sticker | Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Add a quiet mindful accent to your workspace with this Azure Dragon Warrior Sticker kiss-cut sticker. The artwork is built around a focused visual DNA profile, so each piece feels like part of a coherent small-batch collection.&lt;/p&gt;&lt;p&gt;Use it for laptops, notebooks, reading corners, desk setups, gallery shelves, and gift bundles. The composition favors readable detail, strong mood, and giftable niche appeal without generic mass-market styling.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Warrior Azure dragon with Translucent Imperial Jade armor, Kintsugi Gold Veins repairs, Bioluminescent Glow eyes, and Internal Crystalline Structures weapons, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; meditation fans, calm desk setups, notebook collectors, and gift buyers who like clean aesthetics.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; samurai sticker, warrior dragon, battle ready, Japanese warrior, martial arts, shogun aesthetic, armor design, weapon art, battle damage, heroic symbol&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Pair it with related OpenClaw pieces for a coordinated collection.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0055&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Desk Sticker Pack Azure Dragon Warrior 4pc 6x6 Kiss-Cut Vinyl Laptop Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for laptops, journals, planners, bottles, reading notebooks, and study desk gifts. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut vinyl sticker sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Azure Dragon Warrior, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0055; Subject: Azure Dragon Warrior&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6086,6 +6161,31 @@
       <c r="V59" s="1" t="n">
         <v>46148.85754021991</v>
       </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>Azure Dragon Warrior, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6110,12 +6210,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dragon Cherry Blossom 4pc 6x6 Kiss-Cut Sticker Zen Aesthetic Laptop Journal</t>
+          <t>Reading Nook Vinyl Set Dragon Cherry Blossom 4pc 6x6 Kiss-Cut Vinyl Laptop Gift</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Dragon &amp; Cherry Blossom Sticker Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Bring calm and balance into your daily routine with this Dragon &amp; Cherry Blossom Sticker zen aesthetic kiss-cut sticker.&lt;/p&gt;&lt;p&gt;Designed for study rooms, creative workspaces, shelves, gallery walls, and collectible aesthetic decor, this sticker blends niche aesthetic appeal with collectible mentor-grade artwork.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Zen dragon with Translucent Imperial Jade scales surrounded by cherry blossoms, Kintsugi Gold Veins branches, Bioluminescent Glow petals, and Internal Crystalline Structures dewdrops, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; mindfulness lovers, minimalists, journal keepers, yoga enthusiasts, and peaceful room setups.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; cherry blossom sticker, spring aesthetic, Japanese spring, sakura art, floral dragon, nature spirit, seasonal decoration, spring festival, hanami theme, floral pattern&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Complete the collection with matching Alchemy pieces.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0056&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Reading Nook Vinyl Set Dragon Cherry Blossom 4pc 6x6 Kiss-Cut Vinyl Laptop Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for laptops, journals, planners, bottles, reading notebooks, and study desk gifts. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut vinyl sticker sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Dragon Cherry Blossom, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0056; Subject: Dragon Cherry Blossom&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6191,6 +6291,31 @@
       <c r="V60" s="1" t="n">
         <v>46148.85755953703</v>
       </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>Dragon Cherry Blossom, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6215,12 +6340,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Moonlit Dragon 4pc 6x6 Kiss-Cut Sticker Zen Aesthetic Laptop Journal Desk Decor</t>
+          <t>Wabi Sabi Journal Decals Moonlit Dragon 4pc 6x6 Kiss-Cut Vinyl Laptop Journal</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Moonlit Zen Dragon Sticker Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Bring calm and balance into your daily routine with this Moonlit Zen Dragon Sticker zen aesthetic kiss-cut sticker.&lt;/p&gt;&lt;p&gt;Designed for study rooms, creative workspaces, shelves, gallery walls, and collectible aesthetic decor, this sticker blends niche aesthetic appeal with collectible mentor-grade artwork.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Zen dragon under moonlight with Translucent Imperial Jade reflecting moonbeams, Kintsugi Gold Veins constellations, Bioluminescent Glow moonlight, and Internal Crystalline Structures stars, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; mindfulness lovers, minimalists, journal keepers, yoga enthusiasts, and peaceful room setups.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; moon sticker, night sky, celestial dragon, astronomy art, lunar cycle, moon phases, night aesthetic, dreamy sticker, sleep aid, bedtime story&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Complete the collection with matching Alchemy pieces.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0057&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Wabi Sabi Journal Decals Moonlit Dragon 4pc 6x6 Kiss-Cut Vinyl Laptop Journal&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for laptops, journals, planners, bottles, reading notebooks, and study desk gifts. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut vinyl sticker sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Moonlit Dragon, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0057; Subject: Moonlit Dragon&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6296,6 +6421,31 @@
       <c r="V61" s="1" t="n">
         <v>46148.85758619213</v>
       </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>Moonlit Dragon, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6320,12 +6470,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Minimal Zen Dragon Calligraphy 4pc 6x6 Sticker Sheet Serene Mindful Clean Decor</t>
+          <t>Smoky Jade Sticker Set Dragon Calligraphy Serene Clean 4pc 6x6 Kiss-Cut Vinyl</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Dragon Calligraphy Sticker - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Zen aesthetic piece for students, remote workers, yoga lovers, and anyone building a serene everyday space. Designed for peaceful desks, journals, and small rituals, this Dragon Calligraphy Sticker kiss-cut sticker carries a clean Zen mood.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for easy comparison.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Zen dragon formed from Japanese calligraphy strokes using Translucent Imperial Jade ink, Kintsugi Gold Veins brushwork, Bioluminescent Glow highlights, and Internal Crystalline Structures ink splatters, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; students, remote workers, yoga lovers, and anyone building a serene everyday space.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; calligraphy sticker, Japanese writing, brush stroke art, ink painting, sumi-e style, traditional art, kanji design, writing aesthetic, ink wash, brush pen art&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Saved under the reference SKU below for easy collector matching.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0058&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Smoky Jade Sticker Set Dragon Calligraphy Serene Clean 4pc 6x6 Kiss-Cut Vinyl&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for laptops, journals, planners, bottles, reading notebooks, and study desk gifts. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut vinyl sticker sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Dragon Calligraphy Serene Clean, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0058; Subject: Dragon Calligraphy Serene Clean&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6401,6 +6551,31 @@
       <c r="V62" s="1" t="n">
         <v>46148.85760666666</v>
       </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>Dragon Calligraphy Serene Clean, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6425,12 +6600,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Minimal Zen Translucent Jade Dragon 4pc 6x6 Sticker Sheet Serene Mindful Clean</t>
+          <t>Reading Nook Vinyl Set Translucent Jade Dragon Serene Clean 4pc 6x6 Kiss-Cut</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Translucent Jade Dragon Sticker - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Zen aesthetic piece for students, remote workers, yoga lovers, and anyone building a serene everyday space. Designed for peaceful desks, journals, and small rituals, this Translucent Jade Dragon Sticker kiss-cut sticker carries a clean Zen mood.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for easy comparison.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A detailed sticker design of a Zen dragon, Translucent Imperial Jade material, Kintsugi Gold Veins, Bioluminescent Glow, Internal Crystalline Structures, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; students, remote workers, yoga lovers, and anyone building a serene everyday space.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; zen sticker, jade dragon, bioluminescent, kintsugi, die-cut, vector art, spiritual, translucent, crystal, dragon art&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Saved under the reference SKU below for easy collector matching.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0060&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Reading Nook Vinyl Set Translucent Jade Dragon Serene Clean 4pc 6x6 Kiss-Cut&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for laptops, journals, planners, bottles, reading notebooks, and study desk gifts. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut vinyl sticker sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Translucent Jade Dragon Serene Clean, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0060; Subject: Translucent Jade Dragon Serene Clean&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6506,6 +6681,31 @@
       <c r="V63" s="1" t="n">
         <v>46148.85762224537</v>
       </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>Translucent Jade Dragon Serene Clean, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6530,12 +6730,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Minimal Zen Kintsugi Gold Dragon 4pc 6x6 Sticker Sheet Serene Mindful Calm Gift</t>
+          <t>Wabi Sabi Journal Decals Kintsugi Gold Dragon Serene Calm 4pc 6x6 Kiss-Cut Gift</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Kintsugi Gold Dragon Sticker - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Zen aesthetic piece for students, remote workers, yoga lovers, and anyone building a serene everyday space. Designed for peaceful desks, journals, and small rituals, this Kintsugi Gold Dragon Sticker kiss-cut sticker carries a clean Zen mood.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for easy comparison.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A Zen dragon sticker with Kintsugi Gold Veins repairing Translucent Imperial Jade, Bioluminescent Glow from cracks, Internal Crystalline Structures visible, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; students, remote workers, yoga lovers, and anyone building a serene everyday space.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; kintsugi art, gold repair, broken beauty, Japanese art, dragon sticker, spiritual healing, imperfection, glow in dark, crystal core, art therapy&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Saved under the reference SKU below for easy collector matching.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0061&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Wabi Sabi Journal Decals Kintsugi Gold Dragon Serene Calm 4pc 6x6 Kiss-Cut Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for laptops, journals, planners, bottles, reading notebooks, and study desk gifts. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut vinyl sticker sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Kintsugi Gold Dragon Serene Calm, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0061; Subject: Kintsugi Gold Dragon Serene Calm&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6611,6 +6811,31 @@
       <c r="V64" s="1" t="n">
         <v>46148.8576396875</v>
       </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>Kintsugi Gold Dragon Serene Calm, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6635,12 +6860,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Zen Aesthetic Bioluminescent Dragon 4pc 6x6 Kiss-Cut Sticker Laptop Journal</t>
+          <t>Smoky Jade Sticker Set Bioluminescent Dragon 4pc 6x6 Kiss-Cut Vinyl Laptop Gift</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Bioluminescent Zen Dragon Sticker Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Bring calm and balance into your daily routine with this Bioluminescent Zen Dragon Sticker zen aesthetic kiss-cut sticker.&lt;/p&gt;&lt;p&gt;Designed for study rooms, creative workspaces, shelves, gallery walls, and collectible aesthetic decor, this sticker blends niche aesthetic appeal with collectible mentor-grade artwork.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A glowing Zen dragon sticker with Bioluminescent Glow illuminating Translucent Imperial Jade body, Kintsugi Gold Veins, Internal Crystalline Structures glowing from within, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; mindfulness lovers, minimalists, journal keepers, yoga enthusiasts, and peaceful room setups.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; glow in dark, bioluminescent art, night glow, mystical creature, fantasy sticker, rave culture, UV reactive, spiritual light, ethereal, magical&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Complete the collection with matching Alchemy pieces.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0062&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Smoky Jade Sticker Set Bioluminescent Dragon 4pc 6x6 Kiss-Cut Vinyl Laptop Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for laptops, journals, planners, bottles, reading notebooks, and study desk gifts. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut vinyl sticker sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Bioluminescent Dragon, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0062; Subject: Bioluminescent Dragon&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -6716,6 +6941,31 @@
       <c r="V65" s="1" t="n">
         <v>46148.85765802083</v>
       </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>Bioluminescent Dragon, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7017,7 +7267,7 @@
         <v>46148.85771094907</v>
       </c>
       <c r="Y68" s="1" t="n">
-        <v>46149.00188778307</v>
+        <v>46149.00188777778</v>
       </c>
       <c r="Z68" t="n">
         <v>6</v>
@@ -7033,7 +7283,7 @@
         </is>
       </c>
       <c r="AC68" s="1" t="n">
-        <v>46149.00188778307</v>
+        <v>46149.00188777778</v>
       </c>
     </row>
     <row r="69">
@@ -7126,7 +7376,7 @@
         <v>46148.85773053241</v>
       </c>
       <c r="Y69" s="1" t="n">
-        <v>46149.00191942298</v>
+        <v>46149.00191942129</v>
       </c>
       <c r="Z69" t="n">
         <v>6</v>
@@ -7142,7 +7392,7 @@
         </is>
       </c>
       <c r="AC69" s="1" t="n">
-        <v>46149.00191942298</v>
+        <v>46149.00191942129</v>
       </c>
     </row>
     <row r="70">
@@ -14064,12 +14314,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Dark Academia Obsidian Threshold Poster 12x18 Vintage Study Decor Mentor Wisdom</t>
+          <t>Deep Work Visual Poster Obsidian Threshold Vintage Mentor Wisdom 12x18 Matte</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Step into a realm of eternal scholarship with this dark academia poster, where a monumental threshold of polished moonstone and imperial jade frames a mystical passage of floating tomes and brass-inscribed charms. The cinematic chiaroscuro lighting and cosmic ink-wash mists evoke a mentor-grade artifact, perfect for inspiring deep focus and intellectual wonder.&lt;/p&gt;&lt;p&gt;Ideal for adorning a study desk, library wall, or reading nook, this 12x18 poster transforms any space into a vintage sanctuary of wisdom. The ultra-detailed moonstone surface patterns and kintsugi-like vein logic reward close inspection, while the floating accent fragments create a sense of layered depth and narrative intrigue.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper, archival quality&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 x 18 inches&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia Mentor-Grade, dark academia aesthetic&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Moonstone, Imperial Jade, Ancient Calfskin, Burnished Brass, Ink-wash Nebula; micro-engraved surface relief, handcrafted edge bevels, layered translucent depth, subtle bioluminescent glow, floating accent fragments with intentional negative space&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study desk decor, library wall art, book lover gift, vintage intellectual room accent, student dorm inspiration&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Deep Work Visual Poster Obsidian Threshold Vintage Mentor Wisdom 12x18 Matte&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Obsidian Threshold Vintage Mentor Wisdom, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0002; Subject: Obsidian Threshold Vintage Mentor Wisdom&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -14145,6 +14395,31 @@
       <c r="V152" s="1" t="n">
         <v>46148.85782984953</v>
       </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>Obsidian Threshold Vintage Mentor Wisdom, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -14169,12 +14444,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Dark Academia Serpentine Portal of Alchemical Texts 12x18 Poster Study Decor</t>
+          <t>Reading Nook Wall Decor Serpentine Portal of Alchemical Texts 12x18 Matte Gift</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;Step into a world of arcane knowledge with this &lt;b&gt;Serpentine Portal of Alchemical Texts&lt;/b&gt; poster, a masterpiece of dark academia artistry. The design features an iridescent moonstone and imperial jade gateway, surrounded by floating leather volumes and brass talismans with hermetic symbols, all set against a nebulous ink-wash sky. This piece captures the intellectual mystery of a levitating archive, perfect for those who cherish vintage study aesthetics and alchemical lore.&lt;/p&gt;&lt;p&gt;Printed on premium semi-gloss paper, this 12x18 poster delivers rich, cinematic chiaroscuro lighting and jade phosphorescence, making it an ideal focal point for a study desk, library wall, or book lover's sanctuary. The ultra-detailed moonstone iridescence and brass gear mechanisms invite close inspection, while the clean contour separation ensures it stands out in any frame. Whether you're a student, collector, or mentor-grade enthusiast, this poster transforms your space into a portal of esoteric discovery.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;b&gt;Includes:&lt;/b&gt; One 12x18 poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;b&gt;Material:&lt;/b&gt; Premium semi-gloss paper, 200 gsm, archival quality&lt;/li&gt;&lt;li&gt;&lt;b&gt;Size:&lt;/b&gt; 12 x 18 inches (30.48 x 45.72 cm)&lt;/li&gt;&lt;li&gt;&lt;b&gt;Style:&lt;/b&gt; Dark Academia, Mentor-Grade, Alchemical Art&lt;/li&gt;&lt;li&gt;&lt;b&gt;DNA Profile:&lt;/b&gt; Serpentine portal, iridescent moonstone, imperial jade, ancient calfskin, burnished brass, ink-wash nebula, micro-engraved surface relief, handcrafted edge bevels, layered translucent depth, bioluminescent glow, kintsugi vein logic, floating accent fragments, cinematic rim lighting, museum-grade overhead fill, crisp silhouette, centered composition, high-end collectible artifact aesthetic, isolated on white background&lt;/li&gt;&lt;li&gt;&lt;b&gt;Use Cases:&lt;/b&gt; Study desk decor, library wall art, book lover gift, vintage intellectual room accent, dark academia dorm or office, alchemy collector display&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;b&gt;Image Note:&lt;/b&gt; </t>
+          <t>&lt;h2&gt;Reading Nook Wall Decor Serpentine Portal of Alchemical Texts 12x18 Matte Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Serpentine Portal of Alchemical Texts, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0003; Subject: Serpentine Portal of Alchemical Texts&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -14250,6 +14525,31 @@
       <c r="V153" s="1" t="n">
         <v>46148.8578553125</v>
       </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>Serpentine Portal of Alchemical Texts, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -14379,12 +14679,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Plague Doctor Raven Skull Grimdark Alchemy 5x7 Acrylic Art Block Collectible</t>
+          <t>Smoky Jade Desk Object Plague Doctor Raven Skull Alchemy 5x7 Acrylic Photo Gift</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;This premium acrylic art block presents a hauntingly detailed Plague Doctor Raven Skull, reimagined through a grimdark alchemical lens. The elongated brass beak apparatus, corroded iron rivets, and kintsugi gold veins sealing bone fractures create a museum-quality artifact that glows with toxic amber bioluminescence. A perfect conversation piece for industrial gothic or dark fantasy interiors.&lt;/p&gt;&lt;p&gt;Ideal for display on a study desk, bookshelf, or altar, this 5x7 acrylic block captures ray-traced depth and refractive light, giving the illusion of a floating relic encased in crystal. The isolated white background in the main image ensures the intricate surface relief and internal glow remain the focal point.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic art block, ready to display on included stand or easel&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium clear acrylic with UV-resistant print, edge-polished for clarity&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (portrait orientation)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade – aged bone, corroded iron, oxidized brass, kintsugi gold, toxic amber bioluminescence&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Plague doctor raven skull, elongated brass beak, corroded iron rivets, kintsugi gold repair, toxic amber vapor, micro-engraved surface relief, handcrafted edge bevels, layered translucent depth, internal bioluminescent glow, floating accent fragments, cinematic rim lighting, museum-grade overhead fill, crisp silhouette, centered premium composition&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Dark fantasy decor, gothic study accent, collector display, alchemist-themed room, Halloween year-round art, mentor or writer gift&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note:&lt;/em&gt; </t>
+          <t>&lt;h2&gt;Smoky Jade Desk Object Plague Doctor Raven Skull Alchemy 5x7 Acrylic Photo Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Plague Doctor Raven Skull Alchemy, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0081; Subject: Plague Doctor Raven Skull Alchemy&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -14460,6 +14760,31 @@
       <c r="V155" s="1" t="n">
         <v>46148.85789751157</v>
       </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>Plague Doctor Raven Skull Alchemy, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -14484,12 +14809,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Zen Mechanical Crane 5x7 Acrylic Block Desk Art Calm Decor Origami Sculpture</t>
+          <t>Smoky Jade Desk Object Mechanical Crane Calm Origami Sculpture 5x7 Acrylic Gift</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Bring a moment of mindful balance to your workspace with this Zen Mentor-Grade acrylic block. The Crane Guardian Mechanism merges origami elegance with cyberpunk precision—moonstone wings, jade clockwork, and aquamarine crystal hinges float in a celestial mist. Soft bioluminescence and ink-wash nebula patterns create a serene focal point for meditation or study.&lt;/p&gt;&lt;p&gt;This 5x7 premium acrylic block is designed for daily inspiration. Place it on a desk, shelf, or altar to anchor your environment with calm energy. The translucent depth and museum-grade lighting effect make it a subtle yet striking artifact that complements minimalist, zen, or dark academia interiors.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One Crane Guardian Mechanism acrylic block&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium clear acrylic with internal printed design&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (portrait orientation)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade — mechanical origami, moonstone, jade, aquamarine, bioluminescent mist&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Mechanical crane, origami sculpture, moonstone wings, jade clockwork, aquamarine crystals, zen cyberpunk, bioluminescent art, floating fragments, celestial mist, translucent depth, museum grade lighting&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Desk decor, meditation altar, study companion, laptop workspace accent, journaling inspiration, water bottle shelf display&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Smoky Jade Desk Object Mechanical Crane Calm Origami Sculpture 5x7 Acrylic Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Mechanical Crane Calm Origami Sculpture, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0001; Subject: Mechanical Crane Calm Origami Sculpture&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -14565,6 +14890,31 @@
       <c r="V156" s="1" t="n">
         <v>46148.85791638889</v>
       </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>Mechanical Crane Calm Origami Sculpture, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -14799,12 +15149,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Academia Mentor-Grade Cosmic Lotus Observatory 12x18 Poster Steampunk Study</t>
+          <t>Quiet Luxury Apartment Art Cosmic Lotus Observatory Steampunk 12x18 Matte Decor</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This poster transforms your study or library into a sanctuary of celestial wonder. The Cosmic Lotus Observatory merges botanical precision with astronomical mystique, featuring a mechanical lotus whose brass petals unfold to reveal crystalline star charts. A translucent amber core glows with golden stardust, while each petal is engraved with zodiac symbols and planetary orbits. Warm academic lighting and aged brass textures evoke a museum-grade artifact, perfect for dark academia interiors.&lt;/p&gt;&lt;p&gt;Printed on premium matte paper, this 12x18 vertical poster is ideal for framing and display above a study desk, in a reading nook, or as part of a gallery wall. The edge-to-edge composition ensures immersive visual impact, while the refined handcrafted edge bevels add a tactile, collectible quality. Use it to inspire intellectual reflection or as a distinctive gift for astronomy enthusiasts, book lovers, and steampunk aficionados.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper, museum-grade finish&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 inches by 18 inches (vertical orientation)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia Mentor-Grade, dark academia, steampunk botanical, celestial&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Mechanical lotus, brass petals, crystalline star charts, amber core, golden stardust, zodiac engravings, planetary orbits, warm academic lighting, aged brass, kintsugi veins, bioluminescent glow, edge-to-edge composition&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study decor, library wall art, academic gift, astrology lover present, steampunk room accent, vintage intellectual display&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Apartment Art Cosmic Lotus Observatory Steampunk 12x18 Matte Decor&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Cosmic Lotus Observatory Steampunk, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0083; Subject: Cosmic Lotus Observatory Steampunk&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -14880,6 +15230,31 @@
       <c r="V159" s="1" t="n">
         <v>46148.85797262732</v>
       </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>Cosmic Lotus Observatory Steampunk, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -14904,12 +15279,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Astrolabe Chalice Relic Dark Academia Poster 12x18 Vintage Study Decor Wall</t>
+          <t>Deep Work Visual Poster Astrolabe Chalice Relic Vintage 12x18 Matte Poster Gift</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;This &lt;b&gt;Astrolabe Chalice Relic&lt;/b&gt; poster captures a ceremonial astronomy vessel in the Academia Mentor-Grade style. The image presents an ancient brass chalice with astrolabe mechanisms, translucent amber cup, and glowing star maps, evoking intellectual mystery and antique ritual design.&lt;/p&gt;&lt;p&gt;Ideal for a study desk, library wall, or book lover's retreat, this 12x18 print brings vintage scholarly atmosphere to any room. The premium matte finish and cinematic lighting enhance the deep amber tones and celestial details, making it a striking focal point for dark academia interiors.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;b&gt;Includes:&lt;/b&gt; One 12x18 poster (vertical orientation)&lt;/li&gt;&lt;li&gt;&lt;b&gt;Material:&lt;/b&gt; Premium matte paper, archival quality&lt;/li&gt;&lt;li&gt;&lt;b&gt;Size:&lt;/b&gt; 12 inches by 18 inches (2:3 aspect ratio)&lt;/li&gt;&lt;li&gt;&lt;b&gt;Style:&lt;/b&gt; Academia Mentor-Grade, dark academia, vintage intellectual&lt;/li&gt;&lt;li&gt;&lt;b&gt;DNA Profile:&lt;/b&gt; Astrolabe chalice, brass rim with celestial coordinates, rotating zodiac rings, crystalline charts, golden stardust, amber translucency, bioluminescent glow, handcrafted edge bevels, floating fragments&lt;/li&gt;&lt;li&gt;&lt;b&gt;Use Cases:&lt;/b&gt; Wall art for study, library, home office; gift for astronomy enthusiasts, history buffs, students, professors; decor for academic-themed spaces&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;i&gt;Image Note:&lt;/i&gt; </t>
+          <t>&lt;h2&gt;Deep Work Visual Poster Astrolabe Chalice Relic Vintage 12x18 Matte Poster Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Astrolabe Chalice Relic Vintage, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0084; Subject: Astrolabe Chalice Relic Vintage&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -14985,6 +15360,31 @@
       <c r="V160" s="1" t="n">
         <v>46148.85799984954</v>
       </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>Astrolabe Chalice Relic Vintage, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -15009,12 +15409,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Grimdark Alchemical Terrarium Withered Mandrake Root Chamber 5x7 Acrylic Block</t>
+          <t>Quiet Luxury Shelf Decor Alchemical Terrarium Withered Mandrake Root 5x7 Gift</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This premium 5x7 acrylic block captures a withered mandrake root suspended in a geometric terrarium chamber, a grimdark botanical specimen preserved in toxic amber fluid. The corroded iron frame and kintsugi gold veins create a mentor-grade aesthetic perfect for dark academia study desks or industrial apothecary displays.&lt;/p&gt;&lt;p&gt;Place this vertical acrylic piece on a bookshelf, laboratory shelf, or gallery wall to evoke alchemical mystery and intellectual depth. The bioluminescent glow and ray-traced glass effect make it a conversation-starting collectible for collectors of rare art objects.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic block with printed design, ready to display&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium clear acrylic with UV-resistant print, edge bevels for depth&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (vertical orientation)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade, alchemical terrarium, kintsugi-inspired&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Desiccated botanical specimen, corroded iron, laboratory glass, kintsugi gold, toxic amber bioluminescence, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Dark academia study desk decor, laboratory shelf accent, bookstore display, collector's cabinet, gothic home office, industrial apothecary art&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Shelf Decor Alchemical Terrarium Withered Mandrake Root 5x7 Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Alchemical Terrarium Withered Mandrake R, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0082; Subject: Alchemical Terrarium Withered Mandrake Root&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -15090,6 +15490,31 @@
       <c r="V161" s="1" t="n">
         <v>46148.85802462963</v>
       </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>Alchemical Terrarium Withered Mandrake R, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -15114,12 +15539,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Zen Aesthetic Ritual Bell Shrine 5x7 Acrylic Block for Meditation Desk Shelf</t>
+          <t>Quiet Luxury Shelf Decor Ritual Bell Shrine for Meditation 5x7 Acrylic Photo</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This Ritual Bell Shrine acrylic block transforms a celestial meditation artifact into a luminous 5x7 display piece. Designed for the Zen Mentor-Grade collector, it captures the quiet power of an ancient bell with moonstone and jade paneling, aquamarine bead spirals, and floating talisman fragments. The translucent acrylic layers amplify the ink-wash nebula etching and soft bioluminescent glow, creating a museum-quality object that radiates calm and balance.&lt;/p&gt;&lt;p&gt;Place this block on a study desk, shelf, or altar to anchor your mindfulness practice. The premium vertical format fits seamlessly into minimalist interiors, while the internal light refraction adds a subtle, ever-changing presence. Whether used as a meditation focal point or a refined decor accent, it brings the essence of ritual and tranquility into your daily space.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic block with full-color print, protective film on both sides&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Crystal-clear acrylic with UV-resistant dye-sublimation print&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm), vertical orientation&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade, celestial artifact aesthetic&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Moonstone, Imperial Jade, Aquamarine, Brushed Metal, Clockwork Brass, ink-wash nebula etching, micro-engraved relief, kintsugi vein logic, floating talisman fragments, bioluminescent glow, museum-grade rim lighting&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Meditation desk decor, altar focal piece, zen study accent, mindful gift for yoga practitioners, collector display for ritual artifacts&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Shelf Decor Ritual Bell Shrine for Meditation 5x7 Acrylic Photo&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Ritual Bell Shrine for Meditation, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0002; Subject: Ritual Bell Shrine for Meditation&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -15195,6 +15620,31 @@
       <c r="V162" s="1" t="n">
         <v>46148.85804067129</v>
       </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>Ritual Bell Shrine for Meditation, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -15219,12 +15669,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Zen Pagoda Fragment Relic 5x7 Acrylic Print Floating Tower Decor Jade Framework</t>
+          <t>Deep Work Desk Visual Pagoda Fragment Relic Print Floating 5x7 Acrylic Photo</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This Zen Acrylic Print captures a floating miniature pagoda tower section, a celestial relic of moonstone walls and jade framework. The aquamarine windows glow with bioluminescent light, while clockwork brass details and ink-wash nebula patterns create a layered, meditative depth. Perfect for a minimalist desk, meditation space, or gallery wall, this piece brings calm and balance to any room.&lt;/p&gt;&lt;p&gt;Display this 5x7 acrylic block on a study desk, bookshelf, or bedside table to inspire mindfulness and focus. The premium print quality ensures the intricate architectural fragment and soft blue-violet luminescence remain vivid, making it an ideal gift for art collectors or zen enthusiasts. Its compact size fits seamlessly into a laptop workspace or journaling nook.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One acrylic print, ready to hang or stand&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-gloss acrylic with UV-resistant inks&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade, celestial architectural fragment&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Moonstone, Imperial Jade, Aquamarine, Brushed Metal, Clockwork Brass, bioluminescent interior, floating talisman fragments, ink-wash nebula, zen-cyber aesthetic&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Meditation room decor, minimalist office accent, collector gift, water bottle companion, journal inspiration&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Deep Work Desk Visual Pagoda Fragment Relic Print Floating 5x7 Acrylic Photo&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Pagoda Fragment Relic Print Floating, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0003; Subject: Pagoda Fragment Relic Print Floating&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -15300,6 +15750,31 @@
       <c r="V163" s="1" t="n">
         <v>46148.85805715278</v>
       </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>Pagoda Fragment Relic Print Floating, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -15429,12 +15904,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Dark Academia Celestial Lotus Poster 12x18 Vintage Study Room Wall Art Decor</t>
+          <t>Smoky Jade Wall Art Celestial Lotus Vintage 12x18 Matte Poster Apartment Decor</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This poster presents a meticulously imagined mechanical lotus bloom, its petals carved from translucent jade and moonstone glass, rotating around a brass gear core with copper wire stamens. Ink-wash constellation patterns and floating talisman paper fragments orbit the flower, all illuminated by soft candlelight. The composition is a museum-grade, cinematic vertical piece that evokes the depth of an antique glass orrery and the mystery of an oriental botanical study.&lt;/p&gt;&lt;p&gt;Printed on premium matte paper, this 12x18 poster is ideal for a study desk, library wall, or reading nook. The rich, layered translucency and handcrafted edge bevels of the imagined glasswork translate into a high-contrast, immersive visual experience. Use it to anchor a dark academia gallery wall or as a focal point above a vintage desk.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper with archival-grade ink&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12x18 inches (vertical orientation)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia Mentor-Grade, dark academia, celestial botanical, mechanical sculpture&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Imperial jade, moonstone glass, brass gear, copper wire, talisman paper, ink-wash constellations, hand-blown glass dewdrops, kintsugi-like vein logic, floating fragments, soft candlelight illumination&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study room decor, library wall art, vintage office accent, book lover gift, student dorm inspiration, intellectual home aesthetic&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Smoky Jade Wall Art Celestial Lotus Vintage 12x18 Matte Poster Apartment Decor&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Celestial Lotus Vintage, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0091; Subject: Celestial Lotus Vintage&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -15510,6 +15985,31 @@
       <c r="V165" s="1" t="n">
         <v>46148.85809606482</v>
       </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>Celestial Lotus Vintage, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -15534,12 +16034,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Celestial Orrery Tree Bonsai Dark Academia 5x7 Acrylic Block Mentor-Grade Study</t>
+          <t>Quiet Luxury Shelf Decor Celestial Orrery Tree Bonsai 5x7 Acrylic Photo Block</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This Celestial Orrery Tree Bonsai acrylic block merges botanical astronomy with mentor-grade dark academia aesthetics. A Moonstone trunk and Imperial Jade planets form a miniature cosmos, suspended in crystalline soil with floating talisman fragments. The 5x7 vertical format fits perfectly on a study desk, bookshelf, or gallery wall, offering a luminous focal point for intellectual spaces.&lt;/p&gt;&lt;p&gt;Designed for collectors and scholars, this piece channels vintage observatory charts and ink-wash nebula atmosphere. The translucent foliage glows with subtle bioluminescence, while micro-engraved surface relief adds tactile depth. Use it as a meditation aid, a gift for a book lover, or a centerpiece in a home library.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic block with built-in stand&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium clear acrylic with internal print&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (vertical)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia Mentor-Grade&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Moonstone trunk, Imperial Jade planets, ink-wash nebula, crystalline soil, floating talisman fragments, bioluminescent leaves, micro-engraved surface relief&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study desk decor, home library accent, mentor gift, vintage intellectual display, botanical art collection&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Shelf Decor Celestial Orrery Tree Bonsai 5x7 Acrylic Photo Block&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Celestial Orrery Tree Bonsai, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Academia-0003; Subject: Celestial Orrery Tree Bonsai&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -15615,6 +16115,31 @@
       <c r="V166" s="1" t="n">
         <v>46148.85813554398</v>
       </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>Celestial Orrery Tree Bonsai, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -15639,12 +16164,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Grimdark Ritual Censer Thurible 5x7 Acrylic Block Dark Academia Mentor-Grade</t>
+          <t>Deep Work Desk Visual Ritual Censer Thurible 5x7 Acrylic Photo Block Office</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This grimdark ritual censer thurible acrylic block captures a corroded iron incense burner with kintsugi gold repair and toxic amber bioluminescent smoke. A mentor-grade collectible artifact, it merges industrial gothic design with refined aesthetic for a museum-quality display piece.&lt;/p&gt;&lt;p&gt;Ideal for study desks, bookshelves, or meditation spaces, this 5x7 acrylic block offers a premium vertical composition with ray-traced depth and refractive light. The internal glow and layered translucent details create a striking visual focal point for any dark academia or collector environment.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic block with printed grimdark censer design&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium clear acrylic with high-definition UV-cured print&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (vertical orientation)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade with industrial gothic and kintsugi elements&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Corroded iron shell, cracked glass, kintsugi gold veins, toxic amber bioluminescence, micro-engraved surface relief, handcrafted edge bevels, layered translucent depth, floating accent fragments, cinematic rim lighting, museum-grade fill&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study desk decor, bookshelf accent, meditation room art, dark academia gift, collector display, office ornament&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Deep Work Desk Visual Ritual Censer Thurible 5x7 Acrylic Photo Block Office&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Ritual Censer Thurible, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0083; Subject: Ritual Censer Thurible&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -15720,6 +16245,31 @@
       <c r="V167" s="1" t="n">
         <v>46148.85817045139</v>
       </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>Ritual Censer Thurible, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -15849,12 +16399,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Zen Incense Vessel Constellation 5x7 Acrylic Block for Meditation Desk Shelf</t>
+          <t>Gallery Desk Art Incense Vessel Constellation for Meditation 5x7 Acrylic Photo</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This incense vessel constellation acrylic block transforms a celestial ritual artifact into a luminous 5x7 display piece. The design features a moonstone sphere with jade segments, aquamarine vents, and a clockwork brass lid, all rendered in a zen mentor-grade style. Soft bioluminescent glow and floating talisman fragments evoke balance and mindfulness, making it ideal for a meditation desk or minimalist workspace.&lt;/p&gt;&lt;p&gt;Use this acrylic block as a desktop focal point for daily reflection, a unique gift for a zen practitioner, or a refined accent on a bookshelf or altar. The transparent material allows light to pass through, enhancing the internal glow and refractive details. Its compact size fits easily on a laptop stand, journal table, or water bottle shelf, adding a touch of celestial calm to any room.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic block with full-color print on premium clear substrate&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-gloss acrylic with UV-resistant ink for lasting vibrancy&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (portrait orientation)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade with celestial and clockwork motifs&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Moonstone sphere, imperial jade segments, aquamarine vents, clockwork brass lid, rotating celestial patterns, bioluminescent glow, ink-wash nebula vapor, floating talisman fragments, micro-engraved relief, kintsugi-like vein logic, negative space composition, museum-grade lighting&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Meditation desk decor, zen gift for mindfulness lovers, altar accent, minimalist office ornament, journaling companion, water bottle shelf display&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Gallery Desk Art Incense Vessel Constellation for Meditation 5x7 Acrylic Photo&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Incense Vessel Constellation for Meditat, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0005; Subject: Incense Vessel Constellation for Meditation&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -15930,6 +16480,31 @@
       <c r="V169" s="1" t="n">
         <v>46148.85821446759</v>
       </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>Incense Vessel Constellation for Meditat, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -15954,12 +16529,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Zen Bonsai Wall Art Celestial Gate of Jade Mist 12x18 Poster Meditation Decor</t>
+          <t>Deep Work Visual Poster Bonsai Celestial Gate of Jade 12x18 Matte Poster Deep</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Transform your space with the &lt;strong&gt;Celestial Gate of Jade Mist&lt;/strong&gt;, a premium vertical poster that captures the serene essence of a miniature floating mountain. This Zen Mentor-Grade artwork features an Imperial Green Jade bonsai tree framed by a luminous Moonstone torii gate, with crystalline waterfalls cascading into clouds above an obsidian rock base. The ink-wash nebula backdrop and floating talisman fragments create an ethereal, balanced composition that evokes mindfulness and tranquility.&lt;/p&gt;&lt;p&gt;Printed on high-quality matte paper, this 12x18 poster is ideal for a study desk, meditation room, or minimalist living area. Its ultra-wide angle and hyper-detailed design ensure a crisp silhouette and deep visual depth, making it a perfect gift for yoga practitioners, journal enthusiasts, or anyone seeking calm, intellectual decor. The soft morning mist lighting and subtle internal glow bring a refined, handcrafted aesthetic to your wall.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper with smooth finish&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 inches by 18 inches (vertical orientation)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade with floating mountain, bonsai tree, torii gate, and talisman fragments&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Imperial Green Jade, Moonstone, Floating Obsidian, Talisman Fragments; micro-engraved surface relief, handcrafted edge bevels, layered translucent depth, subtle bioluminescent glow, kintsugi-like vein logic, intentional negative space, cinematic rim lighting, museum-grade overhead fill&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Meditation room decor, study desk accent, yoga studio wall art, minimalist living room, bedroom zen corner, gift for mindfulness enthusiasts&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Deep Work Visual Poster Bonsai Celestial Gate of Jade 12x18 Matte Poster Deep&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Bonsai Celestial Gate of Jade, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Zen-0001; Subject: Bonsai Celestial Gate of Jade&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -16035,6 +16610,31 @@
       <c r="V170" s="1" t="n">
         <v>46148.85823042824</v>
       </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>Bonsai Celestial Gate of Jade, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -16059,12 +16659,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Dark Academia Phoenix Incense Burner 12x18 Poster Ritual Zen Decor Wall Study</t>
+          <t>Reading Nook Wall Decor Phoenix Incense Burner Ritual 12x18 Matte Poster Gift</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This 12x18 poster presents a ceremonial incense burner shaped as a rising phoenix, crafted from Imperial Green Jade wings with Moonstone flame accents. Floating obsidian smoke wisps and orbiting talisman fragments create an ethereal, balanced composition that evokes mindfulness and minimalist ritual. The soft morning mist lighting and ultra-wide angle view emphasize the vessel's handcrafted edge bevels and layered translucent depth, making it a meditative focal point for any space.&lt;/p&gt;&lt;p&gt;Ideal for a study desk, journaling corner, or meditation room, this poster brings a sense of calm and intellectual focus to your environment. The subtle internal bioluminescent glow and refined kintsugi-like vein logic add a museum-quality aesthetic that complements both modern minimalist and dark academia interiors. Whether you are a book lover, student, or collector of ritual objects, this artwork invites quiet contemplation and balance into your daily life.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper with archival-grade ink&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 x 18 inches (portrait orientation)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade – dark academia, vintage intellectual, minimalist ritual&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Imperial Green Jade, Moonstone, Floating Obsidian, Talisman Fragments, handcrafted edge bevels, layered translucent depth, subtle bioluminescent glow, kintsugi vein logic, floating accent fragments with intentional negative space, cinematic rim lighting, museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Wall art for study desk, meditation room, living room, library, journaling nook, or as a gift for book lovers, students, and zen enthusiasts&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Reading Nook Wall Decor Phoenix Incense Burner Ritual 12x18 Matte Poster Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Phoenix Incense Burner Ritual, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Zen-0002; Subject: Phoenix Incense Burner Ritual&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -16140,6 +16740,31 @@
       <c r="V171" s="1" t="n">
         <v>46148.85824739583</v>
       </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>Phoenix Incense Burner Ritual, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -16351,12 +16976,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Zen Aesthetic Sacred Lotus Meditation Bell 5x7 Acrylic Block for Altar Decor</t>
+          <t>Quiet Luxury Shelf Decor Sacred Lotus Meditation Bell for 5x7 Acrylic Photo</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;Elevate your sacred space with the Sacred Lotus Meditation Bell, a Zen mentor-grade acrylic block that captures the essence of ancient bronze ritual instruments and celestial serenity. This 5x7 translucent print brings a museum-quality bell sculpture to life, featuring a blooming lotus form with a rough raku pottery clapper, moonstone dewdrops, and an imperial jade stem wrapped in silk cord. The design incorporates ink-wash sound wave ripples and floating prayer beads, all glowing with a soft bioluminescent aura against a misty bamboo forest backdrop. Perfect for meditation altars, minimalist desks, or mindfulness corners, this piece transforms any room into a sanctuary of calm and balance.&lt;/p&gt;&lt;p&gt;Printed on premium acrylic, this block offers exceptional depth and refractive light, with a 3D relief effect that mimics handcrafted kintsugi vein details and micro-engraved surfaces. The solid white background ensures crisp silhouette readability, while the internal glow adds a subtle celestial ambiance. Use it as a decorative accent on a bookshelf, a focal point for yoga practice, or a thoughtful gift for a meditation enthusiast. Its compact size fits seamlessly into small spaces, making it ideal for apartments, offices, or dorm rooms.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic block with printed design&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-quality clear acrylic with UV-resistant ink&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade, minimalist, bioluminescent&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Ancient bronze bell, raku pottery, moonstone, imperial jade, ink-wash nebula, prayer beads, kintsugi detail, celestial glow&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Meditation altar decor, desk accent, yoga room art, mindfulness gift, zen home decor, bookshelf display, study inspiration&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note:&lt;/em&gt; </t>
+          <t>&lt;h2&gt;Quiet Luxury Shelf Decor Sacred Lotus Meditation Bell for 5x7 Acrylic Photo&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Sacred Lotus Meditation Bell for, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0007; Subject: Sacred Lotus Meditation Bell for&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -16432,6 +17057,31 @@
       <c r="V174" s="1" t="n">
         <v>46148.85828584491</v>
       </c>
+      <c r="AD174" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>Sacred Lotus Meditation Bell for, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -16456,12 +17106,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Zen Celestial Bonsai Moon Garden 5x7 Acrylic Block for Serene Desk Decor Shelf</t>
+          <t>Deep Work Desk Visual Celestial Bonsai Moon Garden for 5x7 Acrylic Photo Block</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Bring celestial calm to your space with this Zen Mentor-Grade acrylic block, featuring a miniature bonsai tree growing from a crescent moon raku vessel. Twisted imperial jade wire branches and moonstone blossoms glow against ink-wash nebula soil, creating a museum-quality meditation focal point.&lt;/p&gt;&lt;p&gt;This 5x7 acrylic print transforms your desk, shelf, or altar into a minimalist sanctuary. The translucent block captures soft light, enhancing the bioluminescent details and kintsugi vein accents. Perfect for mindfulness breaks, journaling sessions, or as a water bottle companion in your zen corner.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic block with built-in easel stand&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium clear acrylic with UV-resistant print&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade – celestial bonsai, raku pottery vessel, jade wire branches, moonstone blossoms, nebula soil&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Celestial Bonsai Moon Garden – crescent moon vessel, imperial jade branches, moonstone blossom tree, raku pottery planter, luminous nebula soil, floating lantern fragments, translucent root system, zen garden miniature, bioluminescent botanical art, kintsugi vessel detail, museum-grade bonsai object, handcrafted jade wire, premium acrylic composition&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Laptop desk decor, journaling companion, water bottle table accent, meditation altar, bookshelf display, mindfulness gift&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Deep Work Desk Visual Celestial Bonsai Moon Garden for 5x7 Acrylic Photo Block&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Celestial Bonsai Moon Garden for, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0008; Subject: Celestial Bonsai Moon Garden for&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -16537,6 +17187,31 @@
       <c r="V175" s="1" t="n">
         <v>46148.85830232639</v>
       </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>Celestial Bonsai Moon Garden for, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -16561,12 +17236,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Zen Celestial Compass Poster 12x18 Wall Art Calm Study Decor Library Gift Room</t>
+          <t>Smoky Jade Wall Art Celestial Compass Calm Library 12x18 Matte Poster Library</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This &lt;strong&gt;Celestial Compass Relic&lt;/strong&gt; poster transforms a meditative symbol into a museum-grade wall statement. The design centers on an Imperial Green Jade compass with obsidian directional markers and amethyst constellation inlays, suspended in floating crystalline rings under twilight purple-gold lighting. The result is a balanced, minimalist composition that evokes mindfulness and cosmic order—ideal for a study desk, reading nook, or serene living space.&lt;/p&gt;&lt;p&gt;Printed on premium matte paper, this 12x18 poster delivers crisp detail and rich color depth. The subtle bioluminescent jade glow and handcrafted edge bevels are faithfully reproduced, making it a striking focal point for any room where you seek focus and calm. Whether used as a laptop background reference or a journaling companion, its quiet presence supports daily meditation and intellectual reflection.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper, museum-grade archival quality&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12x18 inches (30.5 x 45.7 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade, celestial compass with jade, obsidian, and amethyst elements&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Imperial Green Jade, Floating Obsidian, Amethyst, Crystalline Water, micro-engraved surface relief, handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Wall art for zen study, meditation room, minimalist office, or as a mindful gift for journaling and water bottle enthusiasts&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Smoky Jade Wall Art Celestial Compass Calm Library 12x18 Matte Poster Library&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Celestial Compass Calm Library, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Zen-0004; Subject: Celestial Compass Calm Library&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -16642,6 +17317,31 @@
       <c r="V176" s="1" t="n">
         <v>46148.85831873843</v>
       </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>Celestial Compass Calm Library, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -16666,12 +17366,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Zen Phoenix Rebirth Vessel 12x18 Poster for Meditation Room Decor Wall Study</t>
+          <t>Quiet Luxury Apartment Art Phoenix Rebirth Vessel for Meditation 12x18 Matte</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;Bring the serene energy of an ancient ceremonial artifact into your space with this Zen Mentor-Grade poster. The Phoenix Rebirth Vessel rises in a graceful spiral, its Imperial Green Jade wings unfurling above obsidian talons that grip an amethyst flame base. Crystalline water flows upward in a luminous dance, while twilight purple-gold light and subtle bioluminescent glow create a museum-quality focal point for mindfulness and balance.&lt;/p&gt;&lt;p&gt;Printed on premium matte paper, this 12x18 vertical poster fits perfectly in a meditation corner, study desk area, or minimalist living room. The hyper-detailed design with micro-engraved relief and floating accent fragments invites quiet contemplation, making it an ideal companion for journaling, reading, or simply unwinding after a long day. Its clean silhouette and intentional negative space complement both modern and traditional decor.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;b&gt;Includes:&lt;/b&gt; One 12x18 poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;b&gt;Material:&lt;/b&gt; Premium matte paper, 200 gsm&lt;/li&gt;&lt;li&gt;&lt;b&gt;Size:&lt;/b&gt; 12 x 18 inches (30.5 x 45.7 cm)&lt;/li&gt;&lt;li&gt;&lt;b&gt;Style:&lt;/b&gt; Zen Mentor-Grade, dark academia compatible&lt;/li&gt;&lt;li&gt;&lt;b&gt;DNA Profile:&lt;/b&gt; Imperial Green Jade, Floating Obsidian, Amethyst, Crystalline Water, twilight purple-gold lighting, bioluminescent glow, kintsugi vein logic, floating accent fragments, micro-engraved surface relief&lt;/li&gt;&lt;li&gt;&lt;b&gt;Use Cases:&lt;/b&gt; Meditation room decor, study desk accent, yoga studio wall art, bedroom calm corner, office mindfulness space, gift for journal lovers and water bottle collectors&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;b&gt;Image Note:&lt;/b&gt; </t>
+          <t>&lt;h2&gt;Quiet Luxury Apartment Art Phoenix Rebirth Vessel for Meditation 12x18 Matte&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Phoenix Rebirth Vessel for Meditation, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Zen-0005; Subject: Phoenix Rebirth Vessel for Meditation&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -16747,6 +17447,31 @@
       <c r="V177" s="1" t="n">
         <v>46148.85833532408</v>
       </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>Phoenix Rebirth Vessel for Meditation, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -16771,12 +17496,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Alchemical Star Flask Vessel 5x7 Acrylic Block Dark Academia Desk Decor Shelf</t>
+          <t>Collector Acrylic Relic Alchemical Star Flask Vessel 5x7 Acrylic Photo Block</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;Elevate your study sanctuary with the Alchemical Star Flask Vessel, a premium 5x7 acrylic block that transforms an alchemical flask into a contained universe of celestial wonder. This mentor-grade collectible captures a Moonstone body with Imperial Jade stopper, swirling liquid cosmos, and bioluminescent nebula essence, perfect for dark academia enthusiasts and intellectual decor lovers.&lt;/p&gt;&lt;p&gt;Display this luminous piece on your desk, bookshelf, or gallery wall to inspire deep thought and vintage study vibes. The translucent depth and micro-engraved sacred geometry create a mesmerizing focal point that pairs beautifully with journals, potion bottles, and antique books.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic block with printed design&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium clear acrylic with UV-resistant print&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia Mentor-Grade, dark academia aesthetic&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Alchemical flask, star vessel, Moonstone container, Imperial Jade stopper, liquid cosmos, celestial potion, academia alchemy, contained universe, sacred geometry, premium acrylic bottle, mentor-grade glasswork, translucent elixir, bioluminescent fluid, gallery apothecary art&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Desk decor, bookshelf accent, study room art, gift for book lovers, student inspiration, vintage intellectual collection&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note:&lt;/em&gt; </t>
+          <t>&lt;h2&gt;Collector Acrylic Relic Alchemical Star Flask Vessel 5x7 Acrylic Photo Block&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Alchemical Star Flask Vessel, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Academia-0005; Subject: Alchemical Star Flask Vessel&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -16852,6 +17577,31 @@
       <c r="V178" s="1" t="n">
         <v>46148.85835787037</v>
       </c>
+      <c r="AD178" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>Alchemical Star Flask Vessel, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -16876,12 +17626,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Alchemist Divination Compass Grimdark 5x7 Acrylic Display Mentor-Grade Occult</t>
+          <t>Gallery Desk Art Alchemist Divination Compass Occult 5x7 Acrylic Photo Block</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This Alchemist's Divination Compass is a mentor-grade grimdark collectible, where corroded iron meets kintsugi gold repair in a 5x7 acrylic display. The cracked glass face reveals toxic amber bioluminescent liquid, animating a brass mechanism within. A perfect talisman for the industrial occult enthusiast, it balances decay with luminous refinement.&lt;/p&gt;&lt;p&gt;Designed for display on a study desk or shelf, this premium acrylic block captures ray-traced depth and internal glow. The miniature compass appears suspended in clear acrylic, offering a gallery-quality artifact that draws the eye with its layered translucent detail. Ideal as a distinctive gift for collectors of dark academic or alchemical art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic block with embedded alchemical compass design&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium clear acrylic with UV-stable print, internal bioluminescent effect&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (portrait orientation)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark mentor-grade, alchemical compass with corroded iron, cracked glass, kintsugi gold veins, brass mechanism, toxic amber glow&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Alchemical compass, divination instrument, grimdark navigation tool, corroded iron housing, kintsugi gold repair, toxic amber liquid, bioluminescent brass mechanism, industrial occult art, premium acrylic display, mentor-grade design, ray traced glass, gallery collectible talisman&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Display on study desk, bookshelf, altar, or as a conversation-starting gift for alchemy fans, dark academia lovers, or occult art collectors&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Gallery Desk Art Alchemist Divination Compass Occult 5x7 Acrylic Photo Block&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Alchemist Divination Compass Occult, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0085; Subject: Alchemist Divination Compass Occult&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -16957,6 +17707,31 @@
       <c r="V179" s="1" t="n">
         <v>46148.85837791667</v>
       </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>Alchemist Divination Compass Occult, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -16981,12 +17756,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Zen Bamboo Flute 5x7 Acrylic Block, Whispering Shakuhachi Meditation Art Gift</t>
+          <t>Collector Acrylic Relic Bamboo Flute Whispering Shakuhachi Meditation 5x7 Decor</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;This 5x7 acrylic block captures the ethereal spirit of a floating shakuhachi bamboo flute, rendered in warm honey tones with natural nodes and grain texture. Ethereal mist spirals from the mouthpiece, forming delicate kanji characters above a contemplative zen garden arrangement. The design embodies Zen Mentor-Grade aesthetics—calm, balance, and mindfulness—making it a refined focal point for any meditation space or minimalist interior.&lt;/p&gt;&lt;p&gt;Place this premium acrylic photo block on your study desk, bookshelf, or altar to invite tranquility into daily life. The 3D relief effect and subtle internal bioluminescent glow create a museum-grade collectible that shifts with ambient light. Perfect as a contemplative gift for musicians, meditation practitioners, or lovers of Japanese bamboo instrument art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic block with easel back stand&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-clarity acrylic with UV-resistant print, 3D relief depth&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (vertical orientation)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade—aged bamboo, honey tones, jade vapor, morning light&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Floating shakuhachi flute with bamboo grain texture, mist-formed kanji, zen garden stones, soft fog, pale jade vapor, micro-engraved surface relief, handcrafted edge bevels, layered translucent depth, subtle bioluminescent glow, kintsugi-like vein logic, floating accent fragments, cinematic rim lighting, museum-grade overhead fill&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Meditation room decor, mindfulness gift, study desk accent, spiritual art collectible, Japanese-inspired interior, yoga studio ornament, musician’s keepsake&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note:&lt;/em&gt; </t>
+          <t>&lt;h2&gt;Collector Acrylic Relic Bamboo Flute Whispering Shakuhachi Meditation 5x7 Decor&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Bamboo Flute Whispering Shakuhachi Medit, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0009; Subject: Bamboo Flute Whispering Shakuhachi Meditation&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -17062,6 +17837,31 @@
       <c r="V180" s="1" t="n">
         <v>46148.85839387732</v>
       </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>Bamboo Flute Whispering Shakuhachi Medit, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -17086,12 +17886,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Zen Lotus Seed Pod Vessel 5x7 Acrylic Block for Mindful Desk Decor Shelf Study</t>
+          <t>Smoky Jade Desk Object Lotus Seed Pod Vessel for 5x7 Acrylic Photo Block Decor</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;Embrace serene balance with this mentor-grade acrylic block featuring a floating dried lotus seed pod vessel in weathered terracotta and dusty sage tones. The intricate honeycomb seed chambers, golden pollen particles, and warm amber reflection evoke a botanical meditation object, perfect for cultivating calm in any space.&lt;/p&gt;&lt;p&gt;This 5x7 premium acrylic block transforms your desk, shelf, or altar into a minimalist sanctuary. The hyper-detailed 3D relief and subtle internal glow create a museum-quality collectible that pairs beautifully with journals, water bottles, or laptop setups for daily mindfulness practice.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic block with Zen Lotus Seed Pod Vessel artwork&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-clarity acrylic with UV-resistant print, 3D depth effect&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade – calm, minimalist, nature-inspired&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Dried Lotus Pod, Terracotta Patina, Golden Pollen, Amber Reflection, honeycomb texture, burnt umber accents, kintsugi vein logic, bioluminescent glow&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Meditation desk decor, yoga studio accent, mindful gift for journaling, water bottle companion, laptop workspace zen&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note:&lt;/em&gt; </t>
+          <t>&lt;h2&gt;Smoky Jade Desk Object Lotus Seed Pod Vessel for 5x7 Acrylic Photo Block Decor&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Lotus Seed Pod Vessel for, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0010; Subject: Lotus Seed Pod Vessel for&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -17167,6 +17967,31 @@
       <c r="V181" s="1" t="n">
         <v>46148.85840905092</v>
       </c>
+      <c r="AD181" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>Lotus Seed Pod Vessel for, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -17191,12 +18016,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Gothic Lantern Soul Cage 5x7 Acrylic Block Grimdark Study Decor Crimson Flame</t>
+          <t>Deep Work Desk Visual Lantern Soul Cage Crimson Flame 5x7 Acrylic Photo Block</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This 5x7 acrylic block captures the &lt;strong&gt;Crimson Warden's Soul Cage&lt;/strong&gt;, a grimdark artifact where a trapped crimson spirit flame glows within an ornate wrought-iron lantern. Cracked ghostly ruby glass refracts light, creating a haunting, museum-quality display for collectors of dark fantasy.&lt;/p&gt;&lt;p&gt;Place this premium block on your study desk, bookshelf, or altar to evoke a mood of ancient power and introspection. The internal bioluminescent effect and micro-engraved filigree reward close inspection, making it a conversation piece for gothic or fantasy-themed spaces.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic block with stand&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-clarity acrylic with UV-printed interior design&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (portrait orientation)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade — wrought iron, ghostly ruby glass, crimson spirit flame, gothic filigree&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Ornate wrought-iron lantern, trapped swirling crimson flame, cracked ruby glass, refractive light, internal glow, micro-engraved surface relief, handcrafted edge bevels, layered translucent depth, kintsugi-like vein logic, floating accent fragments, cinematic rim lighting, soft museum fill, crisp silhouette, centered composition, isolated on white&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study desk decor, bookshelf accent, gothic altar piece, dark fantasy collector display, Halloween ambiance, gift for grimdark enthusiasts&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Deep Work Desk Visual Lantern Soul Cage Crimson Flame 5x7 Acrylic Photo Block&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Lantern Soul Cage Crimson Flame, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0001; Subject: Lantern Soul Cage Crimson Flame&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -17272,6 +18097,31 @@
       <c r="V182" s="1" t="n">
         <v>46148.85842430555</v>
       </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>Lantern Soul Cage Crimson Flame, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -17296,12 +18146,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Grimdark Gothic Lantern 5x7 Acrylic Block Shadowbound Sentinel Beacon Dark Gift</t>
+          <t>Smoky Jade Desk Object Lantern Shadowbound Sentinel Beacon 5x7 Acrylic Photo</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This 5x7 acrylic block captures the grimdark essence of the Shadowbound Sentinel's Beacon, a gothic lantern forged from heavy wrought iron with a skeletal framework. Inside, a trapped ice-blue spirit flame flickers through cracked ghostly frost glass, creating an eerie internal glow that defines this mentor-grade collectible.&lt;/p&gt;&lt;p&gt;Perfect for dark fantasy enthusiasts and gothic decor lovers, this premium print brings a shadowbound artifact to life on a sleek acrylic surface. Place it on a study desk, shelf, or altar to evoke the balance of light and shadow, or gift it to a collector of macabre art who appreciates refined, minimalist display pieces.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic block with stand&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-quality clear acrylic with vibrant UV-cured print&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (portrait orientation)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade, featuring wrought iron, ghostly frost glass, ice-blue spirit flame, gothic filigree, micro-engraved surface relief, handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments, cinematic rim lighting, museum-grade overhead fill&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Sentinel beacon, ice-blue flame, frost glass, skeletal lantern, grimdark design, spirit light, gothic collectible, shadowbound artifact, refractive glass, internal glow, premium fantasy&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Dark fantasy decor, gothic study accent, collector's shelf display, Halloween ambiance, gift for grimdark art lovers, meditation on light and shadow&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Smoky Jade Desk Object Lantern Shadowbound Sentinel Beacon 5x7 Acrylic Photo&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Lantern Shadowbound Sentinel Beacon, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0004; Subject: Lantern Shadowbound Sentinel Beacon&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -17377,6 +18227,31 @@
       <c r="V183" s="1" t="n">
         <v>46148.85843832176</v>
       </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>Lantern Shadowbound Sentinel Beacon, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -17401,12 +18276,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Gothic Necromancer Soul Reliquary 5x7 Acrylic Grimdark Artifact Decor Shelf</t>
+          <t>Quiet Luxury Shelf Decor Necromancer Soul Reliquary Artifact 5x7 Acrylic Photo</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This 5x7 acrylic print transforms the Necromancer's Soul Reliquary into a luminous grimdark artifact for your wall. The design captures a wrought-iron lantern with skull motifs, encasing a swirling green spirit flame that refracts through ghostly emerald glass. High-contrast shadows and a bioluminescent core create a premium dark fantasy presence, ideal for collectors of gothic and occult aesthetics.&lt;/p&gt;&lt;p&gt;Display this piece on a study desk, altar shelf, or reading nook to evoke an atmosphere of ancient power and mystery. The acrylic material enhances the refractive light and internal glow, making the green flame appear to pulse with life. It serves as a striking conversation starter for fans of necromancer lore, soul reliquaries, and grimdark worldbuilding.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic print, ready to hang or stand with included easel back&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-gloss acrylic, 1/4 inch thick, with UV-resistant inks&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade, featuring wrought iron, ghostly emerald glass, green spirit flame, gothic filigree, and micro-engraved surface relief&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Gothic lantern, soul reliquary, green flame, emerald glass, skull motif, grimdark collectible, spirit vessel, gothic artifact, refractive light, bioluminescent core, premium dark fantasy&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Wall decor for gothic rooms, occult study spaces, dark fantasy collections, Halloween year-round displays, or as a unique gift for necromancer enthusiasts&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Shelf Decor Necromancer Soul Reliquary Artifact 5x7 Acrylic Photo&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Necromancer Soul Reliquary Artifact, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0005; Subject: Necromancer Soul Reliquary Artifact&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -17482,6 +18357,31 @@
       <c r="V184" s="1" t="n">
         <v>46148.85845377315</v>
       </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>Necromancer Soul Reliquary Artifact, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -18031,12 +18931,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Arcane Archway of Forbidden Chronicles Dark Academia 12x18 Poster Study Room</t>
+          <t>Smoky Jade Wall Art Arcane Archway of Forbidden Chronicles 12x18 Matte Poster</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;Step into a world of esoteric knowledge with this mentor-grade poster, where an imposing archway of translucent moonstone and imperial jade frames a floating bibliotheca vault. Preserved calfskin codices spiral through the gateway, while ink-wash cosmic vapor mingles with ancient paper essence and levitating brass charm shards etched with occult markings. The cinematic chiaroscuro lighting and jade luminous aura evoke the depth of dark academia, making this piece a collector's treasure for intellectual spaces.&lt;/p&gt;&lt;p&gt;Printed on premium semi-gloss poster paper, this 12x18 artwork is ideal for adorning a study desk, library wall, or vintage-inspired reading nook. The ultra-detailed moonstone translucency and brass esoteric mechanisms ensure a visually arresting display that sparks conversation and contemplation. Whether you're a book lover, student, or curator of the arcane, this poster brings a touch of forbidden chronicles to your daily environment.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Semi-gloss poster paper (200 gsm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 x 18 inches (30.48 x 45.72 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia Mentor-Grade – dark academia, vintage, intellectual&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Arcane archway, forbidden chronicles, translucent moonstone, jade aura, occult markings, floating vault, brass charms, cosmic vapor, preserved codices, esoteric design&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study room decor, library wall art, student gift, intellectual collector piece, vintage-inspired home accent&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note:&lt;/em&gt; </t>
+          <t>&lt;h2&gt;Smoky Jade Wall Art Arcane Archway of Forbidden Chronicles 12x18 Matte Poster&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Arcane Archway of Forbidden Chronicles, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0005; Subject: Arcane Archway of Forbidden Chronicles&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -18112,6 +19012,31 @@
       <c r="V190" s="1" t="n">
         <v>46148.85854357639</v>
       </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>Arcane Archway of Forbidden Chronicles, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -18136,12 +19061,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Dark Academia Ethereal Torii Poster 12x18 Study Room Decor Scholarly Ascension</t>
+          <t>Quiet Luxury Apartment Art Ethereal Torii Scholarly Ascension 12x18 Matte Decor</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Step into a realm where ancient wisdom meets celestial artistry. This &lt;strong&gt;Dark Academia Ethereal Torii Poster&lt;/strong&gt; presents a majestic torii gate crafted from opalescent moonstone and imperial jade, standing before a luminous knowledge repository. Historical calfskin volumes drift through the ethereal passage, while ink-wash galaxy clouds fuse with manuscript vapor and floating brass amulet fragments inscribed with scholarly runes. The cinematic chiaroscuro lighting and jade ethereal glow evoke a mentor-grade aesthetic, perfect for intellectual sanctuaries.&lt;/p&gt; &lt;p&gt;Printed on premium semi-gloss poster paper, this 12x18 inch piece delivers rich color depth and crisp detail, making it an ideal focal point for a study, library, or reading nook. The ultra-detailed moonstone opalescence and brass scholarly mechanisms are rendered with hyper-realistic precision, ensuring a captivating visual experience that inspires deep thought and creative exploration.&lt;/p&gt; &lt;ul&gt; &lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 inch poster (unframed)&lt;/li&gt; &lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium semi-gloss poster paper (200 gsm)&lt;/li&gt; &lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 x 18 inches (30.5 x 45.7 cm)&lt;/li&gt; &lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Dark Academia, Mentor-Grade, Ethereal Fantasy&lt;/li&gt; &lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Opalescent moonstone, imperial jade, ancient calfskin, burnished brass, ink-wash nebula, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill&lt;/li&gt; &lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study desk accent, library wall art, vintage book lover gift, student dorm decor, intellectual workspace inspiration, dark academia bedroom aesthetic&lt;/li&gt; &lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt; &lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Apartment Art Ethereal Torii Scholarly Ascension 12x18 Matte Decor&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Ethereal Torii Scholarly Ascension, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0006; Subject: Ethereal Torii Scholarly Ascension&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -18217,6 +19142,31 @@
       <c r="V191" s="1" t="n">
         <v>46148.85855932871</v>
       </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>Ethereal Torii Scholarly Ascension, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -18241,12 +19191,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Dark Academia Mystic Threshold Infinite Knowledge Poster 12x18 Study Decor Wall</t>
+          <t>Reading Nook Wall Decor Mystic Threshold Infinite Knowledge 12x18 Matte Poster</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Step into a realm where ancient wisdom meets celestial mystery. This 12x18 poster captures a luminescent moonstone and imperial jade threshold opening into an infinite library expanse, with orbiting calfskin manuscripts and floating brass rune fragments. A perfect artifact for the intellectual soul who finds beauty in the arcane.&lt;/p&gt;&lt;p&gt;Ideal for adorning a study desk, library wall, or meditation nook, this print brings a dark academia aesthetic to any space. The ink-wash infinity clouds and jade mystical luminescence create a cinematic atmosphere that inspires deep thought and quiet reflection. Whether as a gift for a book lover, student, or mentor, it serves as a daily reminder of boundless knowledge.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper, archival quality&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 x 18 inches (30.48 x 45.72 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia Mentor-Grade, dark academia, mystical&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Mystic threshold, infinite knowledge, moonstone, jade, calfskin manuscripts, brass runes, ink-wash nebula, dark academia, library realm, cinematic chiaroscuro&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study room decor, library wall art, vintage intellectual gift, student dorm, home office inspiration&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Reading Nook Wall Decor Mystic Threshold Infinite Knowledge 12x18 Matte Poster&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Mystic Threshold Infinite Knowledge, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0008; Subject: Mystic Threshold Infinite Knowledge&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -18322,6 +19272,31 @@
       <c r="V192" s="1" t="n">
         <v>46148.85857569444</v>
       </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>Mystic Threshold Infinite Knowledge, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -18346,12 +19321,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Dark Academia Sanctum Gate of Preserved Wisdom 12x18 Poster Study Decor Wall</t>
+          <t>Wabi Sabi Study Print Sanctum Gate of Preserved Wisdom 12x18 Matte Poster Decor</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;h2&gt;Sanctum Gate of Preserved Wisdom – Dark Academia Poster&lt;/h2&gt;&lt;p&gt;Step into a chamber of ancient knowledge with this 12x18 poster featuring a sanctified gate of moonstone and imperial jade, guarded by consecrated calfskin tomes and floating brass seal fragments. The composition channels mentor-grade dark academia, with ink-wash clouds and a soft jade radiance that evokes preserved wisdom and intellectual reverence.&lt;/p&gt;&lt;p&gt;Printed on premium semi-gloss poster paper, this piece is ideal for a study desk, library wall, or reading nook. The cinematic chiaroscuro and micro-engraved surface details bring a museum-quality feel to any space, making it a thoughtful gift for book lovers, students, and collectors of vintage scholarly art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium semi-gloss poster paper (200 gsm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 x 18 inches (30.5 x 45.7 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Dark Academia, Mentor-Grade&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Moonstone, Imperial Jade, Ancient Calfskin, Burnished Brass, Ink-wash Nebula, preservation glyphs, sacred radiance, micro-engraved relief, layered depth, subtle bioluminescent glow&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study room wall art, library decor, vintage intellectual gift, student dorm accent, home office inspiration&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note:&lt;/em&gt; </t>
+          <t>&lt;h2&gt;Wabi Sabi Study Print Sanctum Gate of Preserved Wisdom 12x18 Matte Poster Decor&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Sanctum Gate of Preserved Wisdom, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0009; Subject: Sanctum Gate of Preserved Wisdom&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -18427,6 +19402,31 @@
       <c r="V193" s="1" t="n">
         <v>46148.85859170139</v>
       </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>Sanctum Gate of Preserved Wisdom, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -18451,12 +19451,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Dark Academia Hermetic Portal of Ancient Codices 12x18 Poster Study Decor Wall</t>
+          <t>Quiet Luxury Apartment Art Hermetic Portal of Ancient Codices 12x18 Matte Decor</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Step into a sealed vault of forgotten knowledge with this mentor-grade poster, where a hermetic portal of enigmatic moonstone and imperial jade frames a codex collection of ancient calfskin volumes. Floating brass cipher fragments and ink-wash clouds evoke the intellectual mystique of dark academia, making this 12x18 print an essential artifact for the discerning scholar.&lt;/p&gt;&lt;p&gt;Perfect for adorning a study desk, library wall, or reading nook, this poster transforms any space into a sanctuary of vintage wisdom. The cinematic chiaroscuro lighting and ultra-detailed surface relief ensure a premium collectible aesthetic that rewards close inspection.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster print&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper with archival-grade inks&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12x18 inches (30.5x45.7 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia Mentor-Grade — dark academia hermetic with moonstone, imperial jade, calfskin, burnished brass, and ink-wash nebula&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Enigmatic moonstone portal, sealed codex vault, floating brass ciphers, hermetic formulae, micro-engraved relief, kintsugi-like vein logic, internal bioluminescent glow, centered composition on white background&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study room wall art, library decor, book lover gift, student dorm inspiration, vintage intellectual aesthetic, collector’s display&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Apartment Art Hermetic Portal of Ancient Codices 12x18 Matte Decor&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Hermetic Portal of Ancient Codices, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0010; Subject: Hermetic Portal of Ancient Codices&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -18532,6 +19532,31 @@
       <c r="V194" s="1" t="n">
         <v>46148.85860637732</v>
       </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>Hermetic Portal of Ancient Codices, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -18556,12 +19581,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Dark Academia Celestial Archway Poster 12x18 Study Room Decor Timeless Tomes</t>
+          <t>Deep Work Visual Poster Celestial Archway Timeless Tomes 12x18 Matte Poster</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Step into a cosmic library where a celestial archway of stellar moonstone and imperial jade rises before an eternal repository of timeless tomes. This dark academia poster captures the essence of intellectual wonder, with calfskin manuscripts swirling through a starfield atmosphere and brass constellation fragments etched with stellar coordinates. The ink-wash clouds and jade luminosity create a moody, vintage aesthetic perfect for book lovers and scholars.&lt;/p&gt;&lt;p&gt;Printed on premium matte paper, this 12x18 poster brings a mentor-grade artifact design to your study desk, home library, or reading nook. The ultra-detailed moonstone shimmer and brass celestial details offer a daily dose of inspiration for students, collectors, or anyone drawn to the romance of knowledge and the cosmos. Ideal as a gift for the intellectual in your life or as a focal point in a minimalist study space.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster, ready to frame&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper, 200 gsm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 inches by 18 inches (30.5 x 45.7 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Dark academia, celestial, vintage intellectual&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Celestial archway, moonstone, imperial jade, calfskin manuscripts, brass constellations, ink-wash starfield, jade luminosity, eternal tomes, dark academia aesthetic, mentor-grade artifact&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study decor, library wall art, book lover gift, student room accent, vintage-inspired home office&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Deep Work Visual Poster Celestial Archway Timeless Tomes 12x18 Matte Poster&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Celestial Archway Timeless Tomes, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0011; Subject: Celestial Archway Timeless Tomes&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -18637,6 +19662,31 @@
       <c r="V195" s="1" t="n">
         <v>46148.85862097222</v>
       </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>Celestial Archway Timeless Tomes, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -18661,12 +19711,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Dark Academia Alchemist Threshold Transmuted Knowledge 12x18 Poster Study Decor</t>
+          <t>Wabi Sabi Study Print Alchemist Threshold Transmuted Knowledge 12x18 Matte Gift</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Step into a transmutation sanctum with this mentor-grade dark academia poster, where alchemical moonstone and imperial jade forge a gateway to ancient wisdom. The composition evokes a threshold of transmuted knowledge, blending ink-wash alchemical clouds with levitating brass formula fragments. This piece is designed for the intellectual soul who finds beauty in mystical chemistry and formulary collections.&lt;/p&gt;&lt;p&gt;Perfect for a study desk, library wall, or reading nook, this 12x18 poster brings a cinematic chiaroscuro atmosphere to any space. The ultra-detailed moonstone crystallization and burnished brass mechanisms offer a hyper-detailed artifact aesthetic, making it a compelling focal point for book lovers and students of the arcane. Use it to enhance a vintage-inspired decor or as a gift for the alchemist in your life.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster, ready to frame&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper, archival quality&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 inches by 18 inches&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Dark Academia, Mentor-Grade Alchemy&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Alchemical moonstone, imperial jade, ancient calfskin, burnished brass, ink-wash nebula, micro-engraved surface relief, handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study desk decor, library wall art, vintage intellectual gift, student room accent, alchemy enthusiast collection&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Wabi Sabi Study Print Alchemist Threshold Transmuted Knowledge 12x18 Matte Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Alchemist Threshold Transmuted Knowledge, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0013; Subject: Alchemist Threshold Transmuted Knowledge&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -18740,10 +19790,10 @@
         </is>
       </c>
       <c r="V196" s="1" t="n">
-        <v>46149.00194953031</v>
+        <v>46149.00194952546</v>
       </c>
       <c r="Y196" s="1" t="n">
-        <v>46149.00194953031</v>
+        <v>46149.00194952546</v>
       </c>
       <c r="Z196" t="n">
         <v>1</v>
@@ -18759,7 +19809,32 @@
         </is>
       </c>
       <c r="AC196" s="1" t="n">
-        <v>46149.00194953031</v>
+        <v>46149.00194952546</v>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>Alchemist Threshold Transmuted Knowledge, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
       </c>
     </row>
     <row r="197">
@@ -18864,10 +19939,10 @@
         </is>
       </c>
       <c r="V197" s="1" t="n">
-        <v>46149.00198168619</v>
+        <v>46149.00198168981</v>
       </c>
       <c r="Y197" s="1" t="n">
-        <v>46149.00198168619</v>
+        <v>46149.00198168981</v>
       </c>
       <c r="Z197" t="n">
         <v>1</v>
@@ -18883,7 +19958,7 @@
         </is>
       </c>
       <c r="AC197" s="1" t="n">
-        <v>46149.00198168619</v>
+        <v>46149.00198168981</v>
       </c>
     </row>
     <row r="198">
@@ -18988,10 +20063,10 @@
         </is>
       </c>
       <c r="V198" s="1" t="n">
-        <v>46149.00201393896</v>
+        <v>46149.00201393518</v>
       </c>
       <c r="Y198" s="1" t="n">
-        <v>46149.00201393896</v>
+        <v>46149.00201393518</v>
       </c>
       <c r="Z198" t="n">
         <v>1</v>
@@ -19007,7 +20082,7 @@
         </is>
       </c>
       <c r="AC198" s="1" t="n">
-        <v>46149.00201393896</v>
+        <v>46149.00201393518</v>
       </c>
     </row>
     <row r="199">
@@ -19112,10 +20187,10 @@
         </is>
       </c>
       <c r="V199" s="1" t="n">
-        <v>46149.00204431882</v>
+        <v>46149.00204431713</v>
       </c>
       <c r="Y199" s="1" t="n">
-        <v>46149.00204431882</v>
+        <v>46149.00204431713</v>
       </c>
       <c r="Z199" t="n">
         <v>1</v>
@@ -19131,7 +20206,7 @@
         </is>
       </c>
       <c r="AC199" s="1" t="n">
-        <v>46149.00204431882</v>
+        <v>46149.00204431713</v>
       </c>
     </row>
     <row r="200">
@@ -19236,10 +20311,10 @@
         </is>
       </c>
       <c r="V200" s="1" t="n">
-        <v>46149.00207446046</v>
+        <v>46149.00207445602</v>
       </c>
       <c r="Y200" s="1" t="n">
-        <v>46149.00207446046</v>
+        <v>46149.00207445602</v>
       </c>
       <c r="Z200" t="n">
         <v>1</v>
@@ -19255,7 +20330,7 @@
         </is>
       </c>
       <c r="AC200" s="1" t="n">
-        <v>46149.00207446046</v>
+        <v>46149.00207445602</v>
       </c>
     </row>
     <row r="201">
@@ -19360,10 +20435,10 @@
         </is>
       </c>
       <c r="V201" s="1" t="n">
-        <v>46149.00210729301</v>
+        <v>46149.00210729166</v>
       </c>
       <c r="Y201" s="1" t="n">
-        <v>46149.00210729301</v>
+        <v>46149.00210729166</v>
       </c>
       <c r="Z201" t="n">
         <v>1</v>
@@ -19379,7 +20454,7 @@
         </is>
       </c>
       <c r="AC201" s="1" t="n">
-        <v>46149.00210729301</v>
+        <v>46149.00210729166</v>
       </c>
     </row>
     <row r="202">
@@ -19484,10 +20559,10 @@
         </is>
       </c>
       <c r="V202" s="1" t="n">
-        <v>46149.00214023475</v>
+        <v>46149.00214023148</v>
       </c>
       <c r="Y202" s="1" t="n">
-        <v>46149.00214023475</v>
+        <v>46149.00214023148</v>
       </c>
       <c r="Z202" t="n">
         <v>1</v>
@@ -19503,7 +20578,7 @@
         </is>
       </c>
       <c r="AC202" s="1" t="n">
-        <v>46149.00214023475</v>
+        <v>46149.00214023148</v>
       </c>
     </row>
     <row r="203">

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH283"/>
+  <dimension ref="A1:AJ283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,6 +590,16 @@
           <t>Metadata_Sync_Status</t>
         </is>
       </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>SEO_Strike_Timestamp</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>SEO_Strike_Group</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7733,12 +7743,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Celestial Koi Constellation 4pc 6x6 Kiss-Cut Sticker Zen Aesthetic Laptop Vinyl</t>
+          <t>Deep Work Sticker Set Celestial Koi Constellation 4pc 6x6 Vinyl Laptop Journal</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Celestial Koi Constellation Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Bring calm and balance into your daily routine with this Celestial Koi Constellation zen aesthetic kiss-cut sticker.&lt;/p&gt;&lt;p&gt;Designed for study rooms, creative workspaces, shelves, gallery walls, and collectible aesthetic decor, this sticker blends niche aesthetic appeal with collectible mentor-grade artwork.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A cosmic koi fish swimming through space, body constructed from translucent moonstone scales with imperial jade fins, ink-wash nebula trailing from tail, floating Daoist Fulu talisman fragments following its path, ethereal bioluminescence along spine, zen-mythic aesthetic, , , , , , person, text, watermark&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; mindfulness lovers, minimalists, journal keepers, yoga enthusiasts, and peaceful room setups.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; koi fish sticker, celestial koi, moonstone fish, jade koi, zen fish, cosmic creature, spiritual koi, translucent scales, Daoist symbol, bioluminescent fish&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Complete the collection with matching Alchemy pieces.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0072&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Deep Work Sticker Set Celestial Koi Constellation 4pc 6x6 Vinyl Laptop Journal&lt;/h2&gt;&lt;p&gt;This is part of a fast A/B traffic test built around higher-intent buyer scenes: laptops, journals, planners, reading notebooks, book nooks, and focused desk setups. The style leans into smoky jade accents, quiet desk mood, sharp die-cut presentation, and giftable detail, avoiding generic mass-market wording.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One physical 4pc 6x6 kiss-cut vinyl sticker sheet, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Lane:&lt;/strong&gt; A Deep Work Sticker Set&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen with Quiet Jade / Deep Work positioning.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0072&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -7794,6 +7804,21 @@
       <c r="Q73" t="inlineStr">
         <is>
           <t>69f26281feceb0d66c042ce7</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>SEO_STRIKE_SYNCED_PRINTIFY_DRAFT</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:06:35 -0400</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>A_DEEP_WORK_STICKER_SET</t>
         </is>
       </c>
     </row>
@@ -7820,12 +7845,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sacred Singing Bowl Mindful Zen 4pc 6x6 Vinyl Sticker Yoga Minimalist Gift Gift</t>
+          <t>Book Nook Laptop Decals Sacred Singing Bowl Yoga Minimalist 4pc 6x6 Kiss-Cut</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Sacred Singing Bowl | Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Add a quiet mindful accent to your workspace with this Sacred Singing Bowl kiss-cut sticker. The artwork is built around a focused visual DNA profile, so each piece feels like part of a coherent small-batch collection.&lt;/p&gt;&lt;p&gt;Use it for laptops, notebooks, reading corners, desk setups, gallery shelves, and gift bundles. The composition favors readable detail, strong mood, and giftable niche appeal without generic mass-market styling.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A ceremonial Tibetan singing bowl made of imperial jade with translucent moonstone rim, sound waves visualized as ink-wash nebula emanating outward, floating Daoist Fulu talisman fragments suspended above, ethereal bioluminescence pulsing from bowl interior, zen-mythic aesthetic, , , , , , person, text, watermark&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; meditation fans, calm desk setups, notebook collectors, and gift buyers who like clean aesthetics.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; singing bowl, meditation bowl, jade bowl, ritual instrument, zen bowl, spiritual tool, moonstone rim, Daoist ceremony, bioluminescent sound, sacred artifact&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Pair it with related OpenClaw pieces for a coordinated collection.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0073&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Book Nook Laptop Decals Sacred Singing Bowl Yoga Minimalist 4pc 6x6 Kiss-Cut&lt;/h2&gt;&lt;p&gt;This is part of a fast A/B traffic test built around higher-intent buyer scenes: laptops, journals, planners, reading notebooks, book nooks, and focused desk setups. The style leans into smoky jade accents, quiet desk mood, sharp die-cut presentation, and giftable detail, avoiding generic mass-market wording.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One physical 4pc 6x6 kiss-cut vinyl sticker sheet, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Lane:&lt;/strong&gt; B Book Nook Laptop Decals&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen with Quiet Jade / Deep Work positioning.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0073&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -7881,6 +7906,21 @@
       <c r="Q74" t="inlineStr">
         <is>
           <t>69f262db5269e3325904b893</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>SEO_STRIKE_SYNCED_PRINTIFY_DRAFT</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:06:35 -0400</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>B_BOOK_NOOK_LAPTOP_DECALS</t>
         </is>
       </c>
     </row>
@@ -7907,12 +7947,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Minimal Zen Bamboo Pagoda Relic 4pc 6x6 Sticker Sheet Serene Mindful Clean Gift</t>
+          <t>Deep Work Sticker Set Bamboo Pagoda Relic Serene Clean 4pc 6x6 Vinyl Laptop</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Bamboo Pagoda Relic - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Zen aesthetic piece for students, remote workers, yoga lovers, and anyone building a serene everyday space. Designed for peaceful desks, journals, and small rituals, this Bamboo Pagoda Relic kiss-cut sticker carries a clean Zen mood.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for easy comparison.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A miniature five-tier pagoda structure crafted from imperial jade beams and translucent moonstone panels, ink-wash nebula swirling around base, floating Daoist Fulu talisman fragments at each tier level, ethereal bioluminescence glowing from windows, zen-mythic aesthetic, , , , , , person, text, watermark&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; students, remote workers, yoga lovers, and anyone building a serene everyday space.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; pagoda sticker, jade pagoda, moonstone architecture, zen temple, spiritual building, celestial pagoda, architectural relic, Daoist shrine, bioluminescent tower, sacred structure&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Saved under the reference SKU below for easy collector matching.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0074&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Deep Work Sticker Set Bamboo Pagoda Relic Serene Clean 4pc 6x6 Vinyl Laptop&lt;/h2&gt;&lt;p&gt;This is part of a fast A/B traffic test built around higher-intent buyer scenes: laptops, journals, planners, reading notebooks, book nooks, and focused desk setups. The style leans into smoky jade accents, quiet desk mood, sharp die-cut presentation, and giftable detail, avoiding generic mass-market wording.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One physical 4pc 6x6 kiss-cut vinyl sticker sheet, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Lane:&lt;/strong&gt; A Deep Work Sticker Set&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen with Quiet Jade / Deep Work positioning.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0074&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -7968,6 +8008,21 @@
       <c r="Q75" t="inlineStr">
         <is>
           <t>69f263729b469f716d0e7409</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>SEO_STRIKE_SYNCED_PRINTIFY_DRAFT</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:06:35 -0400</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>A_DEEP_WORK_STICKER_SET</t>
         </is>
       </c>
     </row>
@@ -7994,12 +8049,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Mindful Zen Dragon Pearl Talisman 4pc 6x6 Vinyl Sticker Laptop Journal Gift</t>
+          <t>Book Nook Laptop Decals Dragon Pearl Talisman 4pc 6x6 Kiss-Cut Sticker Set Gift</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Dragon Pearl Talisman | Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Add a quiet mindful accent to your workspace with this Dragon Pearl Talisman kiss-cut sticker. The artwork is built around a focused visual DNA profile, so each piece feels like part of a coherent small-batch collection.&lt;/p&gt;&lt;p&gt;Use it for laptops, notebooks, reading corners, desk setups, gallery shelves, and gift bundles. The composition favors readable detail, strong mood, and giftable niche appeal without generic mass-market styling.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; An ancient dragon pearl talisman seal with imperial jade dragon coiled around translucent moonstone sphere, ink-wash nebula contained within the orb, floating Daoist Fulu talisman fragments forming protective circle, ethereal bioluminescence radiating from pearl core, zen-mythic aesthetic, , , , , , person, text, watermark&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; meditation fans, calm desk setups, notebook collectors, and gift buyers who like clean aesthetics.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; dragon pearl, jade talisman, moonstone orb, spiritual seal, zen amulet, celestial talisman, dragon artifact, Daoist seal, bioluminescent pearl, protection charm&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Pair it with related OpenClaw pieces for a coordinated collection.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0075&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Book Nook Laptop Decals Dragon Pearl Talisman 4pc 6x6 Kiss-Cut Sticker Set Gift&lt;/h2&gt;&lt;p&gt;This is part of a fast A/B traffic test built around higher-intent buyer scenes: laptops, journals, planners, reading notebooks, book nooks, and focused desk setups. The style leans into smoky jade accents, quiet desk mood, sharp die-cut presentation, and giftable detail, avoiding generic mass-market wording.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One physical 4pc 6x6 kiss-cut vinyl sticker sheet, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Lane:&lt;/strong&gt; B Book Nook Laptop Decals&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen with Quiet Jade / Deep Work positioning.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0075&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -8055,6 +8110,21 @@
       <c r="Q76" t="inlineStr">
         <is>
           <t>69f26426671cc7c7960b3f3d</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>SEO_STRIKE_SYNCED_PRINTIFY_DRAFT</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:06:35 -0400</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>B_BOOK_NOOK_LAPTOP_DECALS</t>
         </is>
       </c>
     </row>
@@ -8081,12 +8151,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Moonlit Mountain Shrine Mindful Zen 4pc 6x6 Vinyl Sticker Yoga Minimalist Gift</t>
+          <t>Deep Work Sticker Set Moonlit Mountain Shrine Yoga Minimalist 4pc 6x6 Vinyl</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Moonlit Mountain Shrine | Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Add a quiet mindful accent to your workspace with this Moonlit Mountain Shrine kiss-cut sticker. The artwork is built around a focused visual DNA profile, so each piece feels like part of a coherent small-batch collection.&lt;/p&gt;&lt;p&gt;Use it for laptops, notebooks, reading corners, desk setups, gallery shelves, and gift bundles. The composition favors readable detail, strong mood, and giftable niche appeal without generic mass-market styling.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A miniature mountain landscape with imperial jade peaks and translucent moonstone mist layers, tiny shrine structure at summit, ink-wash nebula forming clouds, floating Daoist Fulu talisman fragments drifting through scene, ethereal bioluminescence from mountain caves, zen-mythic aesthetic, , , , , , person, text, watermark&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; meditation fans, calm desk setups, notebook collectors, and gift buyers who like clean aesthetics.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; mountain shrine, jade landscape, moonstone mist, zen scenery, spiritual mountain, celestial landscape, micro scene, Daoist shrine, bioluminescent caves, sacred geography&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Pair it with related OpenClaw pieces for a coordinated collection.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0076&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Deep Work Sticker Set Moonlit Mountain Shrine Yoga Minimalist 4pc 6x6 Vinyl&lt;/h2&gt;&lt;p&gt;This is part of a fast A/B traffic test built around higher-intent buyer scenes: laptops, journals, planners, reading notebooks, book nooks, and focused desk setups. The style leans into smoky jade accents, quiet desk mood, sharp die-cut presentation, and giftable detail, avoiding generic mass-market wording.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One physical 4pc 6x6 kiss-cut vinyl sticker sheet, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Lane:&lt;/strong&gt; A Deep Work Sticker Set&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen with Quiet Jade / Deep Work positioning.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0076&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -8142,6 +8212,21 @@
       <c r="Q77" t="inlineStr">
         <is>
           <t>69f264df357398ded80f6a3a</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>SEO_STRIKE_SYNCED_PRINTIFY_DRAFT</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:06:35 -0400</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>A_DEEP_WORK_STICKER_SET</t>
         </is>
       </c>
     </row>
@@ -8414,12 +8499,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Celestial Koi Ascension Minimal Zen 4pc 6x6 Kiss-Cut Vinyl Desk Collector Decor</t>
+          <t>Deep Work Sticker Set Celestial Koi Ascension Collector 4pc 6x6 Vinyl Laptop</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Celestial Koi Ascension - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Zen aesthetic piece for students, remote workers, yoga lovers, and anyone building a serene everyday space. Designed for peaceful desks, journals, and small rituals, this Celestial Koi Ascension kiss-cut sticker carries a clean Zen mood.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for easy comparison.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A luminous koi fish leaping upward formed from Peach Moonstone and Rose Jade, soft pink ink-wash nebula flowing around body, coral talisman fragments orbiting fins, spring blossom bioluminescence trailing from tail, zen-mythic aesthetic, , , , , , person, text, watermark&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; students, remote workers, yoga lovers, and anyone building a serene everyday space.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; zen koi sticker, peach moonstone fish, celestial koi art, rose jade aquatic, pink nebula design, coral talisman decor, bioluminescent sticker, premium fish sticker, mystical koi, Japanese zen art&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Saved under the reference SKU below for easy collector matching.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0081&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Deep Work Sticker Set Celestial Koi Ascension Collector 4pc 6x6 Vinyl Laptop&lt;/h2&gt;&lt;p&gt;This is part of a fast A/B traffic test built around higher-intent buyer scenes: laptops, journals, planners, reading notebooks, book nooks, and focused desk setups. The style leans into smoky jade accents, quiet desk mood, sharp die-cut presentation, and giftable detail, avoiding generic mass-market wording.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One physical 4pc 6x6 kiss-cut vinyl sticker sheet, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Lane:&lt;/strong&gt; A Deep Work Sticker Set&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen with Quiet Jade / Deep Work positioning.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0081&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -8475,6 +8560,21 @@
       <c r="Q81" t="inlineStr">
         <is>
           <t>69f26782c326d7da170c1498</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>SEO_STRIKE_SYNCED_PRINTIFY_DRAFT</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:06:35 -0400</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>A_DEEP_WORK_STICKER_SET</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8683,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Phoenix Wing Fragment 4pc 6x6 Kiss-Cut Sticker Zen Aesthetic Laptop Journal</t>
+          <t>Deep Work Sticker Set Phoenix Wing Fragment 4pc 6x6 Vinyl Laptop Journal Decor</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Phoenix Wing Fragment Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Bring calm and balance into your daily routine with this Phoenix Wing Fragment zen aesthetic kiss-cut sticker.&lt;/p&gt;&lt;p&gt;Designed for study rooms, creative workspaces, shelves, gallery walls, and collectible aesthetic decor, this sticker blends niche aesthetic appeal with collectible mentor-grade artwork.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A single majestic phoenix wing unfurled formed from Peach Moonstone and Rose Jade, soft pink ink-wash nebula flowing between feathers, coral talisman fragments embedded in plumage, spring blossom bioluminescence glowing from wing tips, zen-mythic aesthetic, , , , , , person, text, watermark&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; mindfulness lovers, minimalists, journal keepers, yoga enthusiasts, and peaceful room setups.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; phoenix wing sticker, peach moonstone feather, celestial bird art, rose jade wing, mythical phoenix design, coral talisman decor, bioluminescent wing, premium fantasy sticker, zen phoenix, sacred bird art&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Complete the collection with matching Alchemy pieces.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0083&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Deep Work Sticker Set Phoenix Wing Fragment 4pc 6x6 Vinyl Laptop Journal Decor&lt;/h2&gt;&lt;p&gt;This is part of a fast A/B traffic test built around higher-intent buyer scenes: laptops, journals, planners, reading notebooks, book nooks, and focused desk setups. The style leans into smoky jade accents, quiet desk mood, sharp die-cut presentation, and giftable detail, avoiding generic mass-market wording.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One physical 4pc 6x6 kiss-cut vinyl sticker sheet, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Lane:&lt;/strong&gt; A Deep Work Sticker Set&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen with Quiet Jade / Deep Work positioning.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0083&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -8644,6 +8744,21 @@
       <c r="Q83" t="inlineStr">
         <is>
           <t>69f2683ecaeb1241880b7fcb</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>SEO_STRIKE_SYNCED_PRINTIFY_DRAFT</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:06:35 -0400</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>A_DEEP_WORK_STICKER_SET</t>
         </is>
       </c>
     </row>
@@ -20667,6 +20782,43 @@
           <t>69f86a3d25819cdf3d0563b6</t>
         </is>
       </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>406909215172</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909215172</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V203" s="1" t="n">
+        <v>46149.07897425926</v>
+      </c>
+      <c r="Y203" s="1" t="n">
+        <v>46149.07897425926</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909215172 handle=https://www.ebay.com/itm/406909215172</t>
+        </is>
+      </c>
+      <c r="AC203" s="1" t="n">
+        <v>46149.07897425926</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -20754,6 +20906,43 @@
           <t>69f86b8e83a8608fd80f1341</t>
         </is>
       </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>406909219066</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909219066</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V204" s="1" t="n">
+        <v>46149.07898653935</v>
+      </c>
+      <c r="Y204" s="1" t="n">
+        <v>46149.07898653935</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909219066 handle=https://www.ebay.com/itm/406909219066</t>
+        </is>
+      </c>
+      <c r="AC204" s="1" t="n">
+        <v>46149.07898653935</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -20841,6 +21030,43 @@
           <t>69f86d3709f3b730240200b7</t>
         </is>
       </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>406909222169</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909222169</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V205" s="1" t="n">
+        <v>46149.0790015625</v>
+      </c>
+      <c r="Y205" s="1" t="n">
+        <v>46149.0790015625</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909222169 handle=https://www.ebay.com/itm/406909222169</t>
+        </is>
+      </c>
+      <c r="AC205" s="1" t="n">
+        <v>46149.0790015625</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -20928,6 +21154,43 @@
           <t>69f86f6c2810b52a940a4161</t>
         </is>
       </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>406909223875</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909223875</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V206" s="1" t="n">
+        <v>46149.07901393519</v>
+      </c>
+      <c r="Y206" s="1" t="n">
+        <v>46149.07901393519</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909223875 handle=https://www.ebay.com/itm/406909223875</t>
+        </is>
+      </c>
+      <c r="AC206" s="1" t="n">
+        <v>46149.07901393519</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -21015,6 +21278,43 @@
           <t>69f8807a011b67ecf80761ae</t>
         </is>
       </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>406909225478</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909225478</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V207" s="1" t="n">
+        <v>46149.07902600695</v>
+      </c>
+      <c r="Y207" s="1" t="n">
+        <v>46149.07902600695</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909225478 handle=https://www.ebay.com/itm/406909225478</t>
+        </is>
+      </c>
+      <c r="AC207" s="1" t="n">
+        <v>46149.07902600695</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -21102,6 +21402,43 @@
           <t>69f8818abe136844f0003e48</t>
         </is>
       </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>406909226531</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909226531</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V208" s="1" t="n">
+        <v>46149.079038125</v>
+      </c>
+      <c r="Y208" s="1" t="n">
+        <v>46149.079038125</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909226531 handle=https://www.ebay.com/itm/406909226531</t>
+        </is>
+      </c>
+      <c r="AC208" s="1" t="n">
+        <v>46149.079038125</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -21189,6 +21526,43 @@
           <t>69f882a1be136844f0003eed</t>
         </is>
       </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>406909228840</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909228840</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V209" s="1" t="n">
+        <v>46149.07905042824</v>
+      </c>
+      <c r="Y209" s="1" t="n">
+        <v>46149.07905042824</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909228840 handle=https://www.ebay.com/itm/406909228840</t>
+        </is>
+      </c>
+      <c r="AC209" s="1" t="n">
+        <v>46149.07905042824</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -21276,6 +21650,43 @@
           <t>69f8836c5da263f75f04fad5</t>
         </is>
       </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>406909231370</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909231370</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V210" s="1" t="n">
+        <v>46149.07906267361</v>
+      </c>
+      <c r="Y210" s="1" t="n">
+        <v>46149.07906267361</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909231370 handle=https://www.ebay.com/itm/406909231370</t>
+        </is>
+      </c>
+      <c r="AC210" s="1" t="n">
+        <v>46149.07906267361</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -21363,6 +21774,43 @@
           <t>69f883f3be136844f0003ff9</t>
         </is>
       </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>406909232068</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909232068</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V211" s="1" t="n">
+        <v>46149.07907480324</v>
+      </c>
+      <c r="Y211" s="1" t="n">
+        <v>46149.07907480324</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909232068 handle=https://www.ebay.com/itm/406909232068</t>
+        </is>
+      </c>
+      <c r="AC211" s="1" t="n">
+        <v>46149.07907480324</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -21450,6 +21898,43 @@
           <t>69f88472ffbc831dea086941</t>
         </is>
       </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>406909232951</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909232951</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V212" s="1" t="n">
+        <v>46149.07908722222</v>
+      </c>
+      <c r="Y212" s="1" t="n">
+        <v>46149.07908722222</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909232951 handle=https://www.ebay.com/itm/406909232951</t>
+        </is>
+      </c>
+      <c r="AC212" s="1" t="n">
+        <v>46149.07908722222</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -21537,6 +22022,43 @@
           <t>69f884ed83a8608fd80f239c</t>
         </is>
       </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>406909233684</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909233684</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V213" s="1" t="n">
+        <v>46149.0790996875</v>
+      </c>
+      <c r="Y213" s="1" t="n">
+        <v>46149.0790996875</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909233684 handle=https://www.ebay.com/itm/406909233684</t>
+        </is>
+      </c>
+      <c r="AC213" s="1" t="n">
+        <v>46149.0790996875</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -21624,6 +22146,43 @@
           <t>69f88562be136844f00040a3</t>
         </is>
       </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>406909234435</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909234435</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V214" s="1" t="n">
+        <v>46149.07911322916</v>
+      </c>
+      <c r="Y214" s="1" t="n">
+        <v>46149.07911322916</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909234435 handle=https://www.ebay.com/itm/406909234435</t>
+        </is>
+      </c>
+      <c r="AC214" s="1" t="n">
+        <v>46149.07911322916</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -21711,6 +22270,43 @@
           <t>69f886005da263f75f04fc9d</t>
         </is>
       </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>406909235356</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909235356</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V215" s="1" t="n">
+        <v>46149.07912559028</v>
+      </c>
+      <c r="Y215" s="1" t="n">
+        <v>46149.07912559028</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909235356 handle=https://www.ebay.com/itm/406909235356</t>
+        </is>
+      </c>
+      <c r="AC215" s="1" t="n">
+        <v>46149.07912559028</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -21798,6 +22394,43 @@
           <t>69f88ee825819cdf3d057c87</t>
         </is>
       </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>406909236640</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909236640</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V216" s="1" t="n">
+        <v>46149.07913774306</v>
+      </c>
+      <c r="Y216" s="1" t="n">
+        <v>46149.07913774306</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909236640 handle=https://www.ebay.com/itm/406909236640</t>
+        </is>
+      </c>
+      <c r="AC216" s="1" t="n">
+        <v>46149.07913774306</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -21885,6 +22518,43 @@
           <t>69f88fd4feed9979d10d0ce7</t>
         </is>
       </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>406909238227</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909238227</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V217" s="1" t="n">
+        <v>46149.07914980324</v>
+      </c>
+      <c r="Y217" s="1" t="n">
+        <v>46149.07914980324</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909238227 handle=https://www.ebay.com/itm/406909238227</t>
+        </is>
+      </c>
+      <c r="AC217" s="1" t="n">
+        <v>46149.07914980324</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -21972,6 +22642,43 @@
           <t>69f8904bc1f268dee601c34f</t>
         </is>
       </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>406909240724</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909240724</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V218" s="1" t="n">
+        <v>46149.0791625</v>
+      </c>
+      <c r="Y218" s="1" t="n">
+        <v>46149.0791625</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909240724 handle=https://www.ebay.com/itm/406909240724</t>
+        </is>
+      </c>
+      <c r="AC218" s="1" t="n">
+        <v>46149.0791625</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -22059,6 +22766,43 @@
           <t>69f890b8c1f268dee601c394</t>
         </is>
       </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>406909242546</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909242546</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V219" s="1" t="n">
+        <v>46149.07917508102</v>
+      </c>
+      <c r="Y219" s="1" t="n">
+        <v>46149.07917508102</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909242546 handle=https://www.ebay.com/itm/406909242546</t>
+        </is>
+      </c>
+      <c r="AC219" s="1" t="n">
+        <v>46149.07917508102</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -22146,6 +22890,43 @@
           <t>69f89116b051b8a0e90b9662</t>
         </is>
       </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>406909243824</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909243824</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V220" s="1" t="n">
+        <v>46149.0791871875</v>
+      </c>
+      <c r="Y220" s="1" t="n">
+        <v>46149.0791871875</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909243824 handle=https://www.ebay.com/itm/406909243824</t>
+        </is>
+      </c>
+      <c r="AC220" s="1" t="n">
+        <v>46149.0791871875</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -22233,6 +23014,43 @@
           <t>69f8918925819cdf3d057e2d</t>
         </is>
       </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>406909244688</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909244688</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V221" s="1" t="n">
+        <v>46149.07919978009</v>
+      </c>
+      <c r="Y221" s="1" t="n">
+        <v>46149.07919978009</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909244688 handle=https://www.ebay.com/itm/406909244688</t>
+        </is>
+      </c>
+      <c r="AC221" s="1" t="n">
+        <v>46149.07919978009</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -22320,6 +23138,43 @@
           <t>69f892035da263f75f05059e</t>
         </is>
       </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>406909247161</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909247161</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V222" s="1" t="n">
+        <v>46149.07921200232</v>
+      </c>
+      <c r="Y222" s="1" t="n">
+        <v>46149.07921200232</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909247161 handle=https://www.ebay.com/itm/406909247161</t>
+        </is>
+      </c>
+      <c r="AC222" s="1" t="n">
+        <v>46149.07921200232</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -22344,12 +23199,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Rose Quartz Chapel Soul Lantern Grimdark 5x7 Acrylic Art Gothic Collectible</t>
+          <t>Quiet Luxury Desk Relic Rose Quartz Chapel Soul Lantern 5x7 Acrylic Block Decor</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This Rose Quartz Chapel Soul Lantern captures a grimdark artifact aesthetic with a pink-white spirit flame suspended within wrought iron chapel gates. The imperial jade glass panels feature ink-wash nebula patterns and rose quartz inlays, creating a soft rose glow that evokes a soul vessel from a forgotten gothic archive.&lt;/p&gt;&lt;p&gt;Printed on premium 5x7 acrylic, this piece offers a luminous, museum-grade presence for a study desk, altar shelf, or dark academia reading nook. The transparent substrate enhances the layered depth and subtle bioluminescent effect, making it ideal for collectors of mentor-grade gothic artifacts or those seeking a unique gift for a book lover or occult enthusiast.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic print, ready to display on included easel stand or wall mount&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-gloss clear acrylic with UV-resistant inks, 5mm thickness&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade with rose quartz, wrought iron, and jade glass motifs&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Grimdark artifact, rose quartz inlay, chapel gate frame, pink-white flame, ink-wash nebula, imperial jade glass, talisman fragments, kintsugi vein logic, bioluminescent glow, micro-engraved relief&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Gothic decor, dark academia study, witchy altar, collector display, gift for occult or fantasy enthusiasts&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Desk Relic Rose Quartz Chapel Soul Lantern 5x7 Acrylic Block Decor&lt;/h2&gt;&lt;p&gt;This is part of a fast A/B traffic test built around higher-intent buyer scenes: quiet luxury apartment shelves, gothic study desks, collector corners, and deep-work rooms. The style leans into smoky jade glow, acrylic depth, refractive light, and gallery-object presence, avoiding generic mass-market wording.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Lane:&lt;/strong&gt; A Quiet Luxury Desk Object&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark with Quiet Jade / Deep Work positioning.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0038&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -22394,7 +23249,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -22405,6 +23260,42 @@
       <c r="Q223" t="inlineStr">
         <is>
           <t>69f8928b25819cdf3d057ef7</t>
+        </is>
+      </c>
+      <c r="R223" s="1" t="n">
+        <v>46149.08978430011</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>406910074365</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406910074365</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V223" s="1" t="n">
+        <v>46149.09008196864</v>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>SEO_STRIKE_SYNCED_PRINTIFY_DRAFT</t>
+        </is>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:06:35 -0400</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>A_QUIET_LUXURY_DESK_OBJECT</t>
         </is>
       </c>
     </row>
@@ -22431,12 +23322,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Sapphire Temple Soul Lantern Grimdark 5x7 Acrylic Display Gothic Artifact Shelf</t>
+          <t>Smoky Jade Gothic Object Sapphire Temple Soul Lantern Artifact 5x7 Acrylic Gift</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This 5x7 acrylic display presents the Sapphire Temple Soul Lantern, a gothic artifact from the Grimdark Mentor-Grade collection. The design features a wrought iron temple archway frame with sapphire inlays, enclosing a deep-blue spirit flame and floating talisman fragments against imperial jade glass panels. The ink-wash nebula patterns and soft sapphire glow create a balanced, collector-focused aesthetic.&lt;/p&gt;&lt;p&gt;Ideal for study desks, bookshelves, or altars, this piece brings dark academia and mystical decor to any space. The high-gloss acrylic surface enhances the layered translucent depth and micro-engraved relief, while the internal bioluminescent glow adds a subtle, refined presence. Use it as a meditation focal point, a gothic room accent, or a premium gift for artifact enthusiasts.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic print with protective film&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-gloss acrylic, 0.25-inch thick, with beveled edges&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (portrait orientation)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade, gothic artifact, dark academia&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Wrought iron frame, sapphire inlays, deep-blue spirit flame, floating talisman fragments, imperial jade glass panels, ink-wash nebula patterns, micro-engraved surface relief, kintsugi-like vein logic, internal bioluminescent glow, cinematic rim lighting&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study desk decor, bookshelf accent, altar piece, gothic room decor, collector display, dark academia gift, meditation focal point&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Smoky Jade Gothic Object Sapphire Temple Soul Lantern Artifact 5x7 Acrylic Gift&lt;/h2&gt;&lt;p&gt;This is part of a fast A/B traffic test built around higher-intent buyer scenes: quiet luxury apartment shelves, gothic study desks, collector corners, and deep-work rooms. The style leans into smoky jade glow, acrylic depth, refractive light, and gallery-object presence, avoiding generic mass-market wording.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Lane:&lt;/strong&gt; B Gothic Collector Shelf&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark with Quiet Jade / Deep Work positioning.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0039&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -22481,7 +23372,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -22492,6 +23383,42 @@
       <c r="Q224" t="inlineStr">
         <is>
           <t>69f8931cb051b8a0e90b97c7</t>
+        </is>
+      </c>
+      <c r="R224" s="1" t="n">
+        <v>46149.09025860706</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>406910075457</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406910075457</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V224" s="1" t="n">
+        <v>46149.09070339654</v>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>SEO_STRIKE_SYNCED_PRINTIFY_DRAFT</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:06:35 -0400</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>B_GOTHIC_COLLECTOR_SHELF</t>
         </is>
       </c>
     </row>
@@ -22518,12 +23445,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Silver Moon Gate Soul Lantern Grimdark 5x7 Acrylic Art Gothic Mentor-Grade Gift</t>
+          <t>Smoky Jade Gothic Object Silver Moon Gate Soul Lantern 5x7 Acrylic Display Gift</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This Silver Moon Gate Soul Lantern captures a grimdark mentor-grade aesthetic, blending a wrought iron moon gate silhouette with moonstone inlays and imperial jade glass panels. The swirling silver-white spirit flame and floating talisman fragments evoke a gothic, collectible artifact mood, perfect for dark academia or occult-inspired spaces.&lt;/p&gt;&lt;p&gt;Printed on premium 5x7 acrylic, this piece offers a luminous, translucent depth with micro-engraved surface relief and a subtle internal glow. Ideal for display on a study desk, bookshelf, or altar, it serves as a conversation-starting decor accent or a thoughtful gift for lovers of gothic fantasy and dark art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic art panel, ready to hang or stand&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-gloss acrylic with UV-resistant print&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade, with wrought iron, moonstone, jade glass, talisman fragments, and silver-white flame motifs&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Ethereal gothic lantern, moon gate silhouette, spirit flame, talisman fragments, ink-wash nebula patterns, imperial jade glass, soft lunar glow, hyper-detailed object design, micro-engraved relief, handcrafted edge bevels, layered translucent depth, internal bioluminescent glow, kintsugi-like vein logic, floating accent fragments, cinematic rim lighting, museum-grade overhead fill, crisp silhouette, centered composition, high-end collectible artifact aesthetic&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Gothic decor, dark academia study, occult art collection, mentor-grade display, gift for fantasy enthusiasts&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Smoky Jade Gothic Object Silver Moon Gate Soul Lantern 5x7 Acrylic Display Gift&lt;/h2&gt;&lt;p&gt;This is part of a fast A/B traffic test built around higher-intent buyer scenes: quiet luxury apartment shelves, gothic study desks, collector corners, and deep-work rooms. The style leans into smoky jade glow, acrylic depth, refractive light, and gallery-object presence, avoiding generic mass-market wording.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Lane:&lt;/strong&gt; B Gothic Collector Shelf&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark with Quiet Jade / Deep Work positioning.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0040&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -22568,7 +23495,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups4</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -22579,6 +23506,42 @@
       <c r="Q225" t="inlineStr">
         <is>
           <t>69f8937bbe136844f0004b36</t>
+        </is>
+      </c>
+      <c r="R225" s="1" t="n">
+        <v>46149.09086501994</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>406910076542</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406910076542</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V225" s="1" t="n">
+        <v>46149.09116347688</v>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>SEO_STRIKE_SYNCED_PRINTIFY_DRAFT</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:06:35 -0400</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>B_GOTHIC_COLLECTOR_SHELF</t>
         </is>
       </c>
     </row>
@@ -22668,6 +23631,43 @@
           <t>69f89a94c1f268dee601cb9d</t>
         </is>
       </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>406903730229</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406903730229</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V226" s="1" t="n">
+        <v>46149.07922526621</v>
+      </c>
+      <c r="Y226" s="1" t="n">
+        <v>46149.07922526621</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406903730229 handle=https://www.ebay.com/itm/406903730229</t>
+        </is>
+      </c>
+      <c r="AC226" s="1" t="n">
+        <v>46149.07922526621</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -22755,6 +23755,43 @@
           <t>69f89b9ca70f06579a00a708</t>
         </is>
       </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>406903744471</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406903744471</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V227" s="1" t="n">
+        <v>46149.07923866898</v>
+      </c>
+      <c r="Y227" s="1" t="n">
+        <v>46149.07923866898</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406903744471 handle=https://www.ebay.com/itm/406903744471</t>
+        </is>
+      </c>
+      <c r="AC227" s="1" t="n">
+        <v>46149.07923866898</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -22842,6 +23879,43 @@
           <t>69f89c6f09f3b730240221b8</t>
         </is>
       </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>406903748661</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406903748661</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V228" s="1" t="n">
+        <v>46149.07925134259</v>
+      </c>
+      <c r="Y228" s="1" t="n">
+        <v>46149.07925134259</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406903748661 handle=https://www.ebay.com/itm/406903748661</t>
+        </is>
+      </c>
+      <c r="AC228" s="1" t="n">
+        <v>46149.07925134259</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -22929,6 +24003,43 @@
           <t>69f89da69f68ab7cf001f531</t>
         </is>
       </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>406903754696</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406903754696</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V229" s="1" t="n">
+        <v>46149.07926362268</v>
+      </c>
+      <c r="Y229" s="1" t="n">
+        <v>46149.07926362268</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406903754696 handle=https://www.ebay.com/itm/406903754696</t>
+        </is>
+      </c>
+      <c r="AC229" s="1" t="n">
+        <v>46149.07926362268</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -23016,6 +24127,43 @@
           <t>69f89eac011b67ecf8077844</t>
         </is>
       </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>406903758348</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406903758348</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V230" s="1" t="n">
+        <v>46149.07927614584</v>
+      </c>
+      <c r="Y230" s="1" t="n">
+        <v>46149.07927614584</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406903758348 handle=https://www.ebay.com/itm/406903758348</t>
+        </is>
+      </c>
+      <c r="AC230" s="1" t="n">
+        <v>46149.07927614584</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -23103,6 +24251,43 @@
           <t>69f89fda2592a8ad8e0f2e79</t>
         </is>
       </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>406909147173</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909147173</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V231" s="1" t="n">
+        <v>46149.07928880787</v>
+      </c>
+      <c r="Y231" s="1" t="n">
+        <v>46149.07928880787</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909147173 handle=https://www.ebay.com/itm/406909147173</t>
+        </is>
+      </c>
+      <c r="AC231" s="1" t="n">
+        <v>46149.07928880787</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -23190,6 +24375,43 @@
           <t>69f8a454c1f268dee601d3ad</t>
         </is>
       </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>406909150037</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909150037</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V232" s="1" t="n">
+        <v>46149.07930130787</v>
+      </c>
+      <c r="Y232" s="1" t="n">
+        <v>46149.07930130787</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909150037 handle=https://www.ebay.com/itm/406909150037</t>
+        </is>
+      </c>
+      <c r="AC232" s="1" t="n">
+        <v>46149.07930130787</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -23277,6 +24499,43 @@
           <t>69f903dec1f268dee601f679</t>
         </is>
       </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>406909153504</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909153504</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V233" s="1" t="n">
+        <v>46149.07931458333</v>
+      </c>
+      <c r="Y233" s="1" t="n">
+        <v>46149.07931458333</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909153504 handle=https://www.ebay.com/itm/406909153504</t>
+        </is>
+      </c>
+      <c r="AC233" s="1" t="n">
+        <v>46149.07931458333</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -23364,6 +24623,43 @@
           <t>69f904df97d964f736006a48</t>
         </is>
       </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>406909164941</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909164941</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V234" s="1" t="n">
+        <v>46149.07932724537</v>
+      </c>
+      <c r="Y234" s="1" t="n">
+        <v>46149.07932724537</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909164941 handle=https://www.ebay.com/itm/406909164941</t>
+        </is>
+      </c>
+      <c r="AC234" s="1" t="n">
+        <v>46149.07932724537</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -23451,6 +24747,43 @@
           <t>69f90607feed9979d10d40e7</t>
         </is>
       </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>406909216787</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909216787</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V235" s="1" t="n">
+        <v>46149.07933987268</v>
+      </c>
+      <c r="Y235" s="1" t="n">
+        <v>46149.07933987268</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909216787 handle=https://www.ebay.com/itm/406909216787</t>
+        </is>
+      </c>
+      <c r="AC235" s="1" t="n">
+        <v>46149.07933987268</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -23538,6 +24871,43 @@
           <t>69f907b49f68ab7cf0022003</t>
         </is>
       </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>406909220927</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909220927</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V236" s="1" t="n">
+        <v>46149.07935664352</v>
+      </c>
+      <c r="Y236" s="1" t="n">
+        <v>46149.07935664352</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909220927 handle=https://www.ebay.com/itm/406909220927</t>
+        </is>
+      </c>
+      <c r="AC236" s="1" t="n">
+        <v>46149.07935664352</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -23625,6 +24995,43 @@
           <t>69f90c957f4b346c8a0c603f</t>
         </is>
       </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>406909264998</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909264998</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V237" s="1" t="n">
+        <v>46149.0793691088</v>
+      </c>
+      <c r="Y237" s="1" t="n">
+        <v>46149.0793691088</v>
+      </c>
+      <c r="Z237" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909264998 handle=https://www.ebay.com/itm/406909264998</t>
+        </is>
+      </c>
+      <c r="AC237" s="1" t="n">
+        <v>46149.0793691088</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -23712,6 +25119,43 @@
           <t>69fba23409770f1d9306b86d</t>
         </is>
       </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>406909266188</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909266188</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V238" s="1" t="n">
+        <v>46149.07938283565</v>
+      </c>
+      <c r="Y238" s="1" t="n">
+        <v>46149.07938283565</v>
+      </c>
+      <c r="Z238" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909266188 handle=https://www.ebay.com/itm/406909266188</t>
+        </is>
+      </c>
+      <c r="AC238" s="1" t="n">
+        <v>46149.07938283565</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -23799,6 +25243,43 @@
           <t>69fba266489d5635ab0e6504</t>
         </is>
       </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>406909268494</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909268494</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V239" s="1" t="n">
+        <v>46149.07939530093</v>
+      </c>
+      <c r="Y239" s="1" t="n">
+        <v>46149.07939530093</v>
+      </c>
+      <c r="Z239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909268494 handle=https://www.ebay.com/itm/406909268494</t>
+        </is>
+      </c>
+      <c r="AC239" s="1" t="n">
+        <v>46149.07939530093</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -23886,6 +25367,43 @@
           <t>69fba28a6d07bd21600e1684</t>
         </is>
       </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>406909269321</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909269321</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V240" s="1" t="n">
+        <v>46149.07940789352</v>
+      </c>
+      <c r="Y240" s="1" t="n">
+        <v>46149.07940789352</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909269321 handle=https://www.ebay.com/itm/406909269321</t>
+        </is>
+      </c>
+      <c r="AC240" s="1" t="n">
+        <v>46149.07940789352</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -23973,6 +25491,43 @@
           <t>69fbbffef60a24b6d1034e4d</t>
         </is>
       </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>406909467980</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909467980</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V241" s="1" t="n">
+        <v>46149.07942113426</v>
+      </c>
+      <c r="Y241" s="1" t="n">
+        <v>46149.07942113426</v>
+      </c>
+      <c r="Z241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909467980 handle=https://www.ebay.com/itm/406909467980</t>
+        </is>
+      </c>
+      <c r="AC241" s="1" t="n">
+        <v>46149.07942113426</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -24125,6 +25680,43 @@
           <t>69fb7e754ce71ea8ae0c7af1</t>
         </is>
       </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>406909061109</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909061109</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V243" s="1" t="n">
+        <v>46149.07943375</v>
+      </c>
+      <c r="Y243" s="1" t="n">
+        <v>46149.07943375</v>
+      </c>
+      <c r="Z243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909061109 handle=https://www.ebay.com/itm/406909061109</t>
+        </is>
+      </c>
+      <c r="AC243" s="1" t="n">
+        <v>46149.07943375</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -24212,6 +25804,43 @@
           <t>69fb804bff28e7d4030aa67d</t>
         </is>
       </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>406909095974</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909095974</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V244" s="1" t="n">
+        <v>46149.07944618056</v>
+      </c>
+      <c r="Y244" s="1" t="n">
+        <v>46149.07944618056</v>
+      </c>
+      <c r="Z244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909095974 handle=https://www.ebay.com/itm/406909095974</t>
+        </is>
+      </c>
+      <c r="AC244" s="1" t="n">
+        <v>46149.07944618056</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -24299,6 +25928,43 @@
           <t>69fb819d4c6544084c0f8370</t>
         </is>
       </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>406909097469</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909097469</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V245" s="1" t="n">
+        <v>46149.07945979167</v>
+      </c>
+      <c r="Y245" s="1" t="n">
+        <v>46149.07945979167</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909097469 handle=https://www.ebay.com/itm/406909097469</t>
+        </is>
+      </c>
+      <c r="AC245" s="1" t="n">
+        <v>46149.07945979167</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -24386,6 +26052,43 @@
           <t>69fb82e64c6544084c0f83d5</t>
         </is>
       </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>406909100892</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909100892</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V246" s="1" t="n">
+        <v>46149.07947209491</v>
+      </c>
+      <c r="Y246" s="1" t="n">
+        <v>46149.07947209491</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909100892 handle=https://www.ebay.com/itm/406909100892</t>
+        </is>
+      </c>
+      <c r="AC246" s="1" t="n">
+        <v>46149.07947209491</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -24473,6 +26176,43 @@
           <t>69fb868dc5114ecf420d2b93</t>
         </is>
       </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>406909114799</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909114799</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V247" s="1" t="n">
+        <v>46149.07948486111</v>
+      </c>
+      <c r="Y247" s="1" t="n">
+        <v>46149.07948486111</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909114799 handle=https://www.ebay.com/itm/406909114799</t>
+        </is>
+      </c>
+      <c r="AC247" s="1" t="n">
+        <v>46149.07948486111</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -24560,6 +26300,43 @@
           <t>69fb8749a7afceb9f70f1956</t>
         </is>
       </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>406909116716</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909116716</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V248" s="1" t="n">
+        <v>46149.07949722222</v>
+      </c>
+      <c r="Y248" s="1" t="n">
+        <v>46149.07949722222</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909116716 handle=https://www.ebay.com/itm/406909116716</t>
+        </is>
+      </c>
+      <c r="AC248" s="1" t="n">
+        <v>46149.07949722222</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -24647,6 +26424,43 @@
           <t>69fb87aca7afceb9f70f1982</t>
         </is>
       </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>406909118000</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909118000</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V249" s="1" t="n">
+        <v>46149.07950961806</v>
+      </c>
+      <c r="Y249" s="1" t="n">
+        <v>46149.07950961806</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909118000 handle=https://www.ebay.com/itm/406909118000</t>
+        </is>
+      </c>
+      <c r="AC249" s="1" t="n">
+        <v>46149.07950961806</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -24734,6 +26548,43 @@
           <t>69fb87efc5114ecf420d2c5a</t>
         </is>
       </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>406909119544</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909119544</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V250" s="1" t="n">
+        <v>46149.07952208333</v>
+      </c>
+      <c r="Y250" s="1" t="n">
+        <v>46149.07952208333</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909119544 handle=https://www.ebay.com/itm/406909119544</t>
+        </is>
+      </c>
+      <c r="AC250" s="1" t="n">
+        <v>46149.07952208333</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -24821,6 +26672,43 @@
           <t>69fb8805ee663532c8017f4f</t>
         </is>
       </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>406909121336</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909121336</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V251" s="1" t="n">
+        <v>46149.07953444444</v>
+      </c>
+      <c r="Y251" s="1" t="n">
+        <v>46149.07953444444</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909121336 handle=https://www.ebay.com/itm/406909121336</t>
+        </is>
+      </c>
+      <c r="AC251" s="1" t="n">
+        <v>46149.07953444444</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -24908,6 +26796,43 @@
           <t>69fb8811e5402c478e03108f</t>
         </is>
       </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>406909122790</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909122790</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V252" s="1" t="n">
+        <v>46149.07954709491</v>
+      </c>
+      <c r="Y252" s="1" t="n">
+        <v>46149.07954709491</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909122790 handle=https://www.ebay.com/itm/406909122790</t>
+        </is>
+      </c>
+      <c r="AC252" s="1" t="n">
+        <v>46149.07954709491</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -24995,6 +26920,43 @@
           <t>69fb881f2b1da07362014876</t>
         </is>
       </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>406909124585</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909124585</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V253" s="1" t="n">
+        <v>46149.07955925926</v>
+      </c>
+      <c r="Y253" s="1" t="n">
+        <v>46149.07955925926</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909124585 handle=https://www.ebay.com/itm/406909124585</t>
+        </is>
+      </c>
+      <c r="AC253" s="1" t="n">
+        <v>46149.07955925926</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -25082,6 +27044,43 @@
           <t>69fb882c54fd3fbacf051371</t>
         </is>
       </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>406909125700</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909125700</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V254" s="1" t="n">
+        <v>46149.07957320602</v>
+      </c>
+      <c r="Y254" s="1" t="n">
+        <v>46149.07957320602</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909125700 handle=https://www.ebay.com/itm/406909125700</t>
+        </is>
+      </c>
+      <c r="AC254" s="1" t="n">
+        <v>46149.07957320602</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -25169,6 +27168,43 @@
           <t>69fb883cce0d8cb5570fa7cc</t>
         </is>
       </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>406909126789</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909126789</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V255" s="1" t="n">
+        <v>46149.07958537037</v>
+      </c>
+      <c r="Y255" s="1" t="n">
+        <v>46149.07958537037</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909126789 handle=https://www.ebay.com/itm/406909126789</t>
+        </is>
+      </c>
+      <c r="AC255" s="1" t="n">
+        <v>46149.07958537037</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -25256,6 +27292,43 @@
           <t>69fb8849e5402c478e0310af</t>
         </is>
       </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>406909127704</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909127704</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V256" s="1" t="n">
+        <v>46149.07959787037</v>
+      </c>
+      <c r="Y256" s="1" t="n">
+        <v>46149.07959787037</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909127704 handle=https://www.ebay.com/itm/406909127704</t>
+        </is>
+      </c>
+      <c r="AC256" s="1" t="n">
+        <v>46149.07959787037</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -25343,6 +27416,43 @@
           <t>69fbae614c6544084c0f95ec</t>
         </is>
       </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>406909342825</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909342825</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V257" s="1" t="n">
+        <v>46149.07961042824</v>
+      </c>
+      <c r="Y257" s="1" t="n">
+        <v>46149.07961042824</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909342825 handle=https://www.ebay.com/itm/406909342825</t>
+        </is>
+      </c>
+      <c r="AC257" s="1" t="n">
+        <v>46149.07961042824</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -25430,6 +27540,43 @@
           <t>69fbae7da7afceb9f70f2982</t>
         </is>
       </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>406909344491</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909344491</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V258" s="1" t="n">
+        <v>46149.07962293982</v>
+      </c>
+      <c r="Y258" s="1" t="n">
+        <v>46149.07962293982</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909344491 handle=https://www.ebay.com/itm/406909344491</t>
+        </is>
+      </c>
+      <c r="AC258" s="1" t="n">
+        <v>46149.07962293982</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -25517,6 +27664,43 @@
           <t>69fbae974c6544084c0f9610</t>
         </is>
       </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>406909345291</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909345291</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V259" s="1" t="n">
+        <v>46149.07963510416</v>
+      </c>
+      <c r="Y259" s="1" t="n">
+        <v>46149.07963510416</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909345291 handle=https://www.ebay.com/itm/406909345291</t>
+        </is>
+      </c>
+      <c r="AC259" s="1" t="n">
+        <v>46149.07963510416</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -25604,6 +27788,43 @@
           <t>69fbaea961c4aefdea04aaaf</t>
         </is>
       </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>406909353931</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909353931</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V260" s="1" t="n">
+        <v>46149.07964733796</v>
+      </c>
+      <c r="Y260" s="1" t="n">
+        <v>46149.07964733796</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909353931 handle=https://www.ebay.com/itm/406909353931</t>
+        </is>
+      </c>
+      <c r="AC260" s="1" t="n">
+        <v>46149.07964733796</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -25691,6 +27912,43 @@
           <t>69fbaeb9f60a24b6d1034575</t>
         </is>
       </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>406909354903</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909354903</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V261" s="1" t="n">
+        <v>46149.07965949074</v>
+      </c>
+      <c r="Y261" s="1" t="n">
+        <v>46149.07965949074</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909354903 handle=https://www.ebay.com/itm/406909354903</t>
+        </is>
+      </c>
+      <c r="AC261" s="1" t="n">
+        <v>46149.07965949074</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -25778,6 +28036,43 @@
           <t>69fbaecbb8dd7e2bb0094b7c</t>
         </is>
       </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>406909355853</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909355853</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V262" s="1" t="n">
+        <v>46149.07967215278</v>
+      </c>
+      <c r="Y262" s="1" t="n">
+        <v>46149.07967215278</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909355853 handle=https://www.ebay.com/itm/406909355853</t>
+        </is>
+      </c>
+      <c r="AC262" s="1" t="n">
+        <v>46149.07967215278</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -25865,6 +28160,43 @@
           <t>69fbaedb4c6544084c0f9620</t>
         </is>
       </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>406909359949</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909359949</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V263" s="1" t="n">
+        <v>46149.07968435185</v>
+      </c>
+      <c r="Y263" s="1" t="n">
+        <v>46149.07968435185</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909359949 handle=https://www.ebay.com/itm/406909359949</t>
+        </is>
+      </c>
+      <c r="AC263" s="1" t="n">
+        <v>46149.07968435185</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -25952,6 +28284,43 @@
           <t>69fbaeebce0d8cb5570fb7dc</t>
         </is>
       </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>406909364977</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909364977</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V264" s="1" t="n">
+        <v>46149.07969721065</v>
+      </c>
+      <c r="Y264" s="1" t="n">
+        <v>46149.07969721065</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909364977 handle=https://www.ebay.com/itm/406909364977</t>
+        </is>
+      </c>
+      <c r="AC264" s="1" t="n">
+        <v>46149.07969721065</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -26039,6 +28408,43 @@
           <t>69fbaefcc6dfbcc11107aa91</t>
         </is>
       </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>406909368739</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909368739</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V265" s="1" t="n">
+        <v>46149.07971039352</v>
+      </c>
+      <c r="Y265" s="1" t="n">
+        <v>46149.07971039352</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909368739 handle=https://www.ebay.com/itm/406909368739</t>
+        </is>
+      </c>
+      <c r="AC265" s="1" t="n">
+        <v>46149.07971039352</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -26126,6 +28532,43 @@
           <t>69fbaf12ff28e7d4030aba2d</t>
         </is>
       </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>406909373586</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909373586</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V266" s="1" t="n">
+        <v>46149.07972332176</v>
+      </c>
+      <c r="Y266" s="1" t="n">
+        <v>46149.07972332176</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909373586 handle=https://www.ebay.com/itm/406909373586</t>
+        </is>
+      </c>
+      <c r="AC266" s="1" t="n">
+        <v>46149.07972332176</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -26213,6 +28656,43 @@
           <t>69fbc023f60a24b6d1034e5c</t>
         </is>
       </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>406909471020</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909471020</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V267" s="1" t="n">
+        <v>46149.07973618055</v>
+      </c>
+      <c r="Y267" s="1" t="n">
+        <v>46149.07973618055</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909471020 handle=https://www.ebay.com/itm/406909471020</t>
+        </is>
+      </c>
+      <c r="AC267" s="1" t="n">
+        <v>46149.07973618055</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -26300,6 +28780,43 @@
           <t>69fbc0482b1da073620161ad</t>
         </is>
       </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>406909472775</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406909472775</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V268" s="1" t="n">
+        <v>46149.07974864583</v>
+      </c>
+      <c r="Y268" s="1" t="n">
+        <v>46149.07974864583</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406909472775 handle=https://www.ebay.com/itm/406909472775</t>
+        </is>
+      </c>
+      <c r="AC268" s="1" t="n">
+        <v>46149.07974864583</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -26479,7 +28996,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups8</t>
+          <t>Printify_Published_Mockups8</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
@@ -26493,10 +29010,44 @@
         </is>
       </c>
       <c r="R270" s="1" t="n">
-        <v>46148.84302734954</v>
+        <v>46149.08054959491</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>406910056059</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406910056059</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="V270" s="1" t="n">
-        <v>46148.84259488426</v>
+        <v>46149.08084729167</v>
+      </c>
+      <c r="Y270" s="1" t="n">
+        <v>46149.07976099537</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>DELAY_POLL</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>still within delayed propagation envelope age=381m attempts=4</t>
+        </is>
+      </c>
+      <c r="AC270" s="1" t="n">
+        <v>46149.07976099537</v>
       </c>
     </row>
     <row r="271">
@@ -26572,7 +29123,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups8</t>
+          <t>Printify_Published_Mockups8</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
@@ -26586,10 +29137,44 @@
         </is>
       </c>
       <c r="R271" s="1" t="n">
-        <v>46148.80971548611</v>
+        <v>46149.08102733796</v>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>406910057355</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406910057355</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="V271" s="1" t="n">
-        <v>46148.84261596065</v>
+        <v>46149.08132538194</v>
+      </c>
+      <c r="Y271" s="1" t="n">
+        <v>46149.07977336805</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>DELAY_POLL</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>still within delayed propagation envelope age=381m attempts=4</t>
+        </is>
+      </c>
+      <c r="AC271" s="1" t="n">
+        <v>46149.07977336805</v>
       </c>
     </row>
     <row r="272">
@@ -26665,7 +29250,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups8</t>
+          <t>Printify_Published_Mockups8</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
@@ -26679,10 +29264,44 @@
         </is>
       </c>
       <c r="R272" s="1" t="n">
-        <v>46148.81078710648</v>
+        <v>46149.08149414352</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>406910058626</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406910058626</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="V272" s="1" t="n">
-        <v>46148.84263555556</v>
+        <v>46149.0817916088</v>
+      </c>
+      <c r="Y272" s="1" t="n">
+        <v>46149.07978571759</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>DELAY_POLL</t>
+        </is>
+      </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>still within delayed propagation envelope age=381m attempts=4</t>
+        </is>
+      </c>
+      <c r="AC272" s="1" t="n">
+        <v>46149.07978571759</v>
       </c>
     </row>
     <row r="273">
@@ -26758,7 +29377,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups8</t>
+          <t>Printify_Published_Mockups8</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
@@ -26772,10 +29391,44 @@
         </is>
       </c>
       <c r="R273" s="1" t="n">
-        <v>46148.81192653935</v>
+        <v>46149.08194987269</v>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>406910059060</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406910059060</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="V273" s="1" t="n">
-        <v>46148.84265912037</v>
+        <v>46149.08224751157</v>
+      </c>
+      <c r="Y273" s="1" t="n">
+        <v>46149.07979824074</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>DELAY_POLL</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>still within delayed propagation envelope age=381m attempts=4</t>
+        </is>
+      </c>
+      <c r="AC273" s="1" t="n">
+        <v>46149.07979824074</v>
       </c>
     </row>
     <row r="274">
@@ -26851,7 +29504,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>Printify_PublishExternalPending_Mockups8</t>
+          <t>Printify_Published_Mockups8</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
@@ -26865,10 +29518,44 @@
         </is>
       </c>
       <c r="R274" s="1" t="n">
-        <v>46148.81309128472</v>
+        <v>46149.08243599537</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>406910060084</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406910060084</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="V274" s="1" t="n">
-        <v>46148.84267935185</v>
+        <v>46149.08288788194</v>
+      </c>
+      <c r="Y274" s="1" t="n">
+        <v>46149.07981099537</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>DELAY_POLL</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>still within delayed propagation envelope age=381m attempts=4</t>
+        </is>
+      </c>
+      <c r="AC274" s="1" t="n">
+        <v>46149.07981099537</v>
       </c>
     </row>
     <row r="275">

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ283"/>
+  <dimension ref="A1:AN283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,6 +600,26 @@
           <t>SEO_Strike_Group</t>
         </is>
       </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Multi_Track_Timestamp</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Multi_Track_Track</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Multi_Track_Primary_Intent</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>Multi_Track_Mockup_Mood</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16986,12 +17006,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Zen Mentor-Grade Jade Phoenix Incense Altar 5x7 Acrylic Block for Meditation</t>
+          <t>Meditation Room Jade Relic Phoenix 5x7 Acrylic Block Shelf Decor Gift Study</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Elevate your meditation space with this Zen Mentor-Grade Jade Phoenix Incense Altar, a museum-quality acrylic block that captures the serene balance of ceremonial art. The imperial jade phoenix, with moonstone feather inlays and kintsugi vein detail, appears to float against an ink-wash nebula backdrop, while soft bioluminescent glow and floating lotus fragments evoke mindful tranquility. This piece transforms any desk, altar, or shelf into a focal point for daily reflection and aesthetic harmony.&lt;/p&gt;&lt;p&gt;Perfect for the collector or mindfulness practitioner, this 5x7 acrylic block offers a luminous, translucent depth that shifts with ambient light. Whether placed on a study desk, a meditation altar, or a minimalist shelf, its refined composition supports a calm, focused atmosphere. The solid white background ensures the phoenix and celestial details remain crisp and prominent, making it an ideal gift for mentors, Zen enthusiasts, or anyone seeking a unique decorative object.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic block with printed design&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium clear acrylic with UV-resistant print, edge bevels for refined finish&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (vertical orientation)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade, inspired by imperial jade, moonstone, raku pottery, and ink-wash aesthetics&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Ceremonial phoenix sculpture, floating incense altar, moonstone inlay, kintsugi vein detail, bioluminescent glow, lotus fragments, ink-wash nebula, bamboo silhouette, negative space composition, museum-grade collectible artifact&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Meditation desk decor, altar accent, study shelf display, mindful gift for Zen practitioners, minimalist home decor, mentor appreciation gift&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Meditation Room Jade Relic Phoenix 5x7 Acrylic Block Shelf Decor Gift Study&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for tea room accent. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; reading nook decor, meditation room wall art, tea room accent, quiet corner decor, dorm desk calm art, deep work visual.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0006. Prior title: Meditation Room Jade Relic Jade Phoenix Incense Altar for 5x7 Acrylic Block&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -17066,6 +17086,31 @@
       </c>
       <c r="V173" s="1" t="n">
         <v>46148.85826324074</v>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:48:12 -0400</t>
+        </is>
+      </c>
+      <c r="AL173" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>tea room accent</t>
+        </is>
+      </c>
+      <c r="AN173" t="inlineStr">
+        <is>
+          <t>reading_nook_warm_lamp</t>
+        </is>
       </c>
     </row>
     <row r="174">
@@ -17091,12 +17136,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Quiet Luxury Shelf Decor Sacred Lotus Meditation Bell for 5x7 Acrylic Photo</t>
+          <t>Meditation Room Jade Relic Quiet Luxury 5x7 Acrylic Block Shelf Decor Gift Wall</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Quiet Luxury Shelf Decor Sacred Lotus Meditation Bell for 5x7 Acrylic Photo&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Sacred Lotus Meditation Bell for, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0007; Subject: Sacred Lotus Meditation Bell for&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Meditation Room Jade Relic Quiet Luxury 5x7 Acrylic Block Shelf Decor Gift Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for meditation room wall art. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; reading nook decor, meditation room wall art, tea room accent, quiet corner decor, dorm desk calm art, deep work visual.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0007. Prior title: Meditation Room Jade Relic Quiet Luxury Sacred Lotus Meditation 5x7 Acrylic&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -17194,7 +17239,27 @@
       </c>
       <c r="AH174" t="inlineStr">
         <is>
-          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:48:12 -0400</t>
+        </is>
+      </c>
+      <c r="AL174" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM174" t="inlineStr">
+        <is>
+          <t>meditation room wall art</t>
+        </is>
+      </c>
+      <c r="AN174" t="inlineStr">
+        <is>
+          <t>reading_nook_warm_lamp</t>
         </is>
       </c>
     </row>
@@ -17741,12 +17806,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Gallery Desk Art Alchemist Divination Compass Occult 5x7 Acrylic Photo Block</t>
+          <t>Dark Study Smoky Jade Alchemist Divination Compass 5x7 Acrylic Block Shelf Gift</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Gallery Desk Art Alchemist Divination Compass Occult 5x7 Acrylic Photo Block&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Alchemist Divination Compass Occult, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0085; Subject: Alchemist Divination Compass Occult&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Dark Study Smoky Jade Alchemist Divination Compass 5x7 Acrylic Block Shelf Gift&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for dark study room decor. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0085. Prior title: Dark Study Smoky Jade Alchemist Divination Compass Occult 5x7 Acrylic Block&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -17844,7 +17909,27 @@
       </c>
       <c r="AH179" t="inlineStr">
         <is>
-          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:48:12 -0400</t>
+        </is>
+      </c>
+      <c r="AL179" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>dark study room decor</t>
+        </is>
+      </c>
+      <c r="AN179" t="inlineStr">
+        <is>
+          <t>reading_nook_warm_lamp</t>
         </is>
       </c>
     </row>
@@ -20471,12 +20556,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Soulbound Harbinger Torch Grimdark Gothic Lantern 5x7 Acrylic Print Dark Decor</t>
+          <t>Quiet Luxury Jade Relic Soulbound 5x7 Acrylic Block Shelf Decor Gift Study Wall</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This 5x7 acrylic print captures the &lt;strong&gt;Soulbound Harbinger's Torch&lt;/strong&gt;, a grimdark mentor-grade artifact where a magenta spirit flame swirls within cracked ghostly rose quartz glass, framed by ornate wrought iron wings. The refractive internal glow and high-contrast shadows create a premium collectible aesthetic for gothic or dark academia interiors.&lt;/p&gt;&lt;p&gt;Display this piece on a study desk, shelf, or altar to evoke themes of spirit vessels and forbidden knowledge. The durable acrylic surface with a glossy finish enhances the layered depth and bioluminescent details, making it a striking focal point in low-light settings.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic print with a clear stand for tabletop display.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-gloss acrylic with a rigid, scratch-resistant surface.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm).&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade with wrought iron, ghostly rose quartz glass, and magenta spirit flame motifs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Wrought iron filigree, cracked translucent quartz, internal bioluminescent glow, kintsugi-like vein logic, floating accent fragments, refractive lighting, high-contrast shadows, museum-grade overhead fill.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Gothic decor, dark academia study, spirit vessel collection, occult-inspired room accent, gift for grimdark enthusiasts.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Jade Relic Soulbound 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for smoky jade relic. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0014. Prior title: Quiet Luxury Jade Relic Soulbound Harbinger Torch Lantern Print 5x7 Acrylic&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -20570,6 +20655,31 @@
       </c>
       <c r="AC201" s="1" t="n">
         <v>46149.00210729166</v>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:48:12 -0400</t>
+        </is>
+      </c>
+      <c r="AL201" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>smoky jade relic</t>
+        </is>
+      </c>
+      <c r="AN201" t="inlineStr">
+        <is>
+          <t>quiet_luxury_apartment</t>
+        </is>
       </c>
     </row>
     <row r="202">
@@ -21091,12 +21201,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Abyssal Watcher Eternal Eye Grimdark Gothic Acrylic 5x7 Spirit Beacon Artifact</t>
+          <t>Quiet Luxury Jade Relic Abyssal 5x7 Acrylic Block Shelf Decor Gift Study Wall</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This grimdark acrylic print captures the Abyssal Watcher's Eternal Eye, a gothic lantern of wrought iron and ghostly aqua glass, its cyan spirit flame glowing with bioluminescent intensity. A premium artifact for collectors of dark fantasy and occult decor.&lt;/p&gt;&lt;p&gt;Display this 5x7 piece on a study desk, altar, or shelf to evoke a spirit beacon's watchful presence. The refractive lighting and high-contrast shadows create a museum-grade visual depth, perfect for adding a mentor-grade aesthetic to any room.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic print, ready to hang or stand&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-gloss acrylic with UV-resistant ink&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade, gothic filigree, bioluminescent glow&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Wrought iron, ghostly aqua glass, cyan spirit flame, micro-engraved surface relief, kintsugi-like vein logic&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Gothic collectible display, altar decor, study desk accent, dark fantasy gift, spirit beacon aesthetic&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Jade Relic Abyssal 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for moody desk display. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0019. Prior title: Quiet Luxury Jade Relic Abyssal Watcher Eternal Eye Spirit 5x7 Acrylic Block&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -21190,6 +21300,31 @@
       </c>
       <c r="AC206" s="1" t="n">
         <v>46149.07901393519</v>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:48:12 -0400</t>
+        </is>
+      </c>
+      <c r="AL206" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>moody desk display</t>
+        </is>
+      </c>
+      <c r="AN206" t="inlineStr">
+        <is>
+          <t>quiet_luxury_apartment</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -21959,12 +22094,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Magenta Malice Lantern Grimdark Mentor-Grade 5x7 Acrylic Decor Dark Fantasy</t>
+          <t>Quiet Luxury Jade Relic Magenta 5x7 Acrylic Block Shelf Decor Gift Study Wall</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This 5x7 acrylic print captures the &lt;strong&gt;Magenta Malice Lantern&lt;/strong&gt;, a corrupted gothic artifact forged from blackened wrought iron with razor-sharp filigree. A violent magenta spirit flame thrashes against frosted rose-tinted glass, embodying a grimdark mentor-grade aesthetic. The piece balances corrupted elegance with vibrant bioluminescent depth, making it a striking focal point for dark fantasy collections.&lt;/p&gt;&lt;p&gt;Perfect for study desks, gothic libraries, or minimalist shelves, this print brings a touch of corrupted romance to your space. The high-gloss acrylic surface enhances the layered translucent depth and internal glow, while the 5x7 size fits neatly into any room. Use it as a conversation starter in a home office or as a bold accent in a bedroom gallery wall.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic print, ready to hang with a built-in easel stand&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-gloss acrylic with vivid UV-resistant inks&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade – corrupted gothic, bioluminescent magenta, blackened iron filigree&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Blackened Wrought Iron, Rose-Tinted Glass, Magenta Spirit Flame, Sharp Filigree, micro-engraved surface relief, layered translucent depth, subtle internal bioluminescent glow&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Gothic decor, dark fantasy collection, mentor gift, study desk accent, bedroom wall art&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Jade Relic Magenta 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for occult library art. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0027. Prior title: Quiet Luxury Jade Relic Magenta Malice Lantern Fantasy 5x7 Acrylic Block Desk&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -22058,6 +22193,31 @@
       </c>
       <c r="AC213" s="1" t="n">
         <v>46149.0790996875</v>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:48:12 -0400</t>
+        </is>
+      </c>
+      <c r="AL213" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr">
+        <is>
+          <t>occult library art</t>
+        </is>
+      </c>
+      <c r="AN213" t="inlineStr">
+        <is>
+          <t>quiet_luxury_apartment</t>
+        </is>
       </c>
     </row>
     <row r="214">
@@ -22579,12 +22739,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Grimdark Ethereal Archway Soul Lantern 5x7 Acrylic Display Gothic Artifact Gift</t>
+          <t>Dark Study Smoky Jade Ethereal Archway Soul 5x7 Acrylic Block Shelf Decor Gift</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This grimdark mentor-grade acrylic display presents the Ethereal Archway Soul Lantern, a gothic artifact rendered in a 5x7 format. The design centers on a wrought iron archway silhouette framing a selenite-inlaid vessel, with a pearl-white spirit flame and floating talisman fragments against imperial jade glass panels. The ink-wash nebula patterns and soft ethereal glow evoke a collector-focused aesthetic, perfect for dark academia or gothic decor.&lt;/p&gt;&lt;p&gt;Ideal for study desks, bookshelves, or ritual spaces, this piece brings a mood of ancient mystery and intellectual depth. The micro-engraved surface relief and layered translucent depth mimic handcrafted edge bevels, while the refined kintsugi-like vein logic adds subtle texture. Use it as a conversation starter in a home library, or as a unique gift for lovers of grimdark fantasy and occult artifacts.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic print, ready to display&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium acrylic with glossy finish&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade, gothic collectible&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Wrought iron archway, selenite inlays, pearl-white flame, talisman fragments, imperial jade glass, ink-wash nebula, soft ethereal glow, micro-engraved relief, kintsugi vein logic, floating accent fragments, cinematic rim lighting, museum-grade overhead fill&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study desk decor, bookshelf accent, gothic home art, dark academia gift, occult display, ritual space adornment&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Dark Study Smoky Jade Ethereal Archway Soul 5x7 Acrylic Block Shelf Decor Gift&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for dark study room decor. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0033. Prior title: Dark Study Smoky Jade Ethereal Archway Soul Lantern Artifact 5x7 Acrylic Block&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -22678,6 +22838,31 @@
       </c>
       <c r="AC218" s="1" t="n">
         <v>46149.0791625</v>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:48:12 -0400</t>
+        </is>
+      </c>
+      <c r="AL218" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr">
+        <is>
+          <t>dark study room decor</t>
+        </is>
+      </c>
+      <c r="AN218" t="inlineStr">
+        <is>
+          <t>quiet_luxury_apartment</t>
+        </is>
       </c>
     </row>
     <row r="219">
@@ -23199,12 +23384,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Quiet Luxury Desk Relic Rose Quartz Chapel Soul Lantern 5x7 Acrylic Block Decor</t>
+          <t>Collector Shelf Smoky Jade Quiet Luxury 5x7 Acrylic Block Shelf Decor Gift Wall</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Quiet Luxury Desk Relic Rose Quartz Chapel Soul Lantern 5x7 Acrylic Block Decor&lt;/h2&gt;&lt;p&gt;This is part of a fast A/B traffic test built around higher-intent buyer scenes: quiet luxury apartment shelves, gothic study desks, collector corners, and deep-work rooms. The style leans into smoky jade glow, acrylic depth, refractive light, and gallery-object presence, avoiding generic mass-market wording.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Lane:&lt;/strong&gt; A Quiet Luxury Desk Object&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark with Quiet Jade / Deep Work positioning.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0038&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Collector Shelf Smoky Jade Quiet Luxury 5x7 Acrylic Block Shelf Decor Gift Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for collector shelf object. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0038. Prior title: Collector Shelf Smoky Jade Quiet Luxury Relic Rose Quartz 5x7 Acrylic Block&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -23263,7 +23448,7 @@
         </is>
       </c>
       <c r="R223" s="1" t="n">
-        <v>46149.08978430011</v>
+        <v>46149.08978430556</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
@@ -23281,11 +23466,11 @@
         </is>
       </c>
       <c r="V223" s="1" t="n">
-        <v>46149.09008196864</v>
+        <v>46149.0900819676</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
-          <t>SEO_STRIKE_SYNCED_PRINTIFY_DRAFT</t>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
         </is>
       </c>
       <c r="AI223" t="inlineStr">
@@ -23296,6 +23481,26 @@
       <c r="AJ223" t="inlineStr">
         <is>
           <t>A_QUIET_LUXURY_DESK_OBJECT</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:48:12 -0400</t>
+        </is>
+      </c>
+      <c r="AL223" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM223" t="inlineStr">
+        <is>
+          <t>collector shelf object</t>
+        </is>
+      </c>
+      <c r="AN223" t="inlineStr">
+        <is>
+          <t>reading_nook_warm_lamp</t>
         </is>
       </c>
     </row>
@@ -23386,7 +23591,7 @@
         </is>
       </c>
       <c r="R224" s="1" t="n">
-        <v>46149.09025860706</v>
+        <v>46149.09025861111</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -23404,7 +23609,7 @@
         </is>
       </c>
       <c r="V224" s="1" t="n">
-        <v>46149.09070339654</v>
+        <v>46149.0907033912</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -23509,7 +23714,7 @@
         </is>
       </c>
       <c r="R225" s="1" t="n">
-        <v>46149.09086501994</v>
+        <v>46149.09086502315</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -23527,7 +23732,7 @@
         </is>
       </c>
       <c r="V225" s="1" t="n">
-        <v>46149.09116347688</v>
+        <v>46149.09116347222</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -23692,12 +23897,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Dark Academia Archivist Gateway Poster 12x18 Vintage Study Room Decor Wall Gift</t>
+          <t>Reading Nook Smoky Jade Wall Art Archivist 12x18 Matte Poster Apartment Decor</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Step into the quiet majesty of the &lt;strong&gt;Archivist's Gateway of Catalogued Eternity&lt;/strong&gt;, a poster that transforms your study into a sanctuary of systematic wisdom. This mentor-grade artwork captures a moonstone and imperial jade archway leading to an eternal classification chamber, with brass indices and ink-wash clouds swirling around ancient calfskin pages. The dark academia aesthetic is perfect for those who revere organized knowledge and timeless beauty.&lt;/p&gt;&lt;p&gt;Printed on premium matte paper, this 12x18 poster brings cinematic chiaroscuro lighting and jade archival luminescence to your wall. Use it above a reading desk, in a home library, or as a focal point in a student's room to inspire deep focus and intellectual curiosity. The ultra-detailed moonstone cataloguing patterns and brass archival mechanisms reward close inspection, making it a collectible piece for book lovers and scholars alike.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster, ready to frame&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper with archival-grade inks&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 inches by 18 inches (30.5 x 45.7 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Dark Academia, Mentor-Grade – moonstone, imperial jade, ancient calfskin, burnished brass, ink-wash nebula&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Archivist's gateway, catalogued eternity, classification chamber, brass indices, jade archival luminescence, systematic wisdom, vintage study aesthetic&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study desk decor, home library accent, student room inspiration, vintage intellectual gift, book lover's wall art&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Reading Nook Smoky Jade Wall Art Archivist 12x18 Matte Poster Apartment Decor&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for dark academia reading nook. It is written for buyers decorating reading nooks, home libraries, dorm study walls, meditation rooms, and quiet apartment corners, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 matte poster, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; matte paper mood, cinematic depth, smoky jade tones, and calm visual focus.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; dark academia reading nook, home library wall art, book nook decor, study room poster, scholar desk decor, dorm library print.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed poster. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0019. Prior title: Reading Nook Smoky Jade Wall Art Archivist Gateway Vintage 12x18 Matte Poster&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -23791,6 +23996,31 @@
       </c>
       <c r="AC227" s="1" t="n">
         <v>46149.07923866898</v>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:48:12 -0400</t>
+        </is>
+      </c>
+      <c r="AL227" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM227" t="inlineStr">
+        <is>
+          <t>dark academia reading nook</t>
+        </is>
+      </c>
+      <c r="AN227" t="inlineStr">
+        <is>
+          <t>quiet_luxury_apartment</t>
+        </is>
       </c>
     </row>
     <row r="228">
@@ -28717,12 +28947,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Mechanical Encyclopedia Sphere Dark Academia Aesthetic 12x18 Poster Study Room</t>
+          <t>Reading Nook Smoky Jade Wall Art Mechanical 12x18 Matte Poster Apartment Decor</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;This poster presents the Mechanical Encyclopedia Sphere, a dark academia masterpiece that transforms a corroded iron vessel into an archive of forgotten engineering. The cracked technical glass and kintsugi repair seams, glowing with golden light, encase gravity-defying ancient books and blueprint manuscripts, while toxic jade bioluminescence casts an emerald glow across the scene. It is an immersive environment for the intellectual soul.&lt;/p&gt;&lt;p&gt;Printed on premium semi-gloss poster paper, this 12x18 inch piece is ideal for a study desk, library wall, or vintage-inspired workspace. The ultra-detailed corrosion and glass fracture patterns reward close inspection, making it a conversation starter for book lovers and industrial design enthusiasts. Use it to evoke a mood of scholarly mystery in your home or office.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 inch poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium semi-gloss poster paper (200 gsm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 x 18 inches (30.48 x 45.72 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Dark Academia, Mentor-Grade, Industrial Design&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Corroded iron, cracked glass, kintsugi gold, toxic jade bioluminescence, ancient calfskin, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments with intentional negative space&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study room decor, library wall art, vintage intellectual gift for students or engineers, dark academia bedroom accent, office inspiration&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note:&lt;/em&gt; </t>
+          <t>&lt;h2&gt;Reading Nook Smoky Jade Wall Art Mechanical 12x18 Matte Poster Apartment Decor&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for dark academia reading nook. It is written for buyers decorating reading nooks, home libraries, dorm study walls, meditation rooms, and quiet apartment corners, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 matte poster, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; matte paper mood, cinematic depth, smoky jade tones, and calm visual focus.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; dark academia reading nook, home library wall art, book nook decor, study room poster, scholar desk decor, dorm library print.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed poster. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0036. Prior title: Reading Nook Smoky Jade Wall Art Mechanical Encyclopedia Sphere 12x18 Matte&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -28816,6 +29046,31 @@
       </c>
       <c r="AC268" s="1" t="n">
         <v>46149.07974864583</v>
+      </c>
+      <c r="AH268" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK268" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:48:12 -0400</t>
+        </is>
+      </c>
+      <c r="AL268" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM268" t="inlineStr">
+        <is>
+          <t>dark academia reading nook</t>
+        </is>
+      </c>
+      <c r="AN268" t="inlineStr">
+        <is>
+          <t>reading_nook_warm_lamp</t>
+        </is>
       </c>
     </row>
     <row r="269">

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -17546,17 +17546,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Quiet Luxury Apartment Art Phoenix Rebirth Vessel for Meditation 12x18 Matte</t>
+          <t>Quiet Luxury Jade Wall Art Reading Nook 12x18 Matte Poster Apartment Decor Gift</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Quiet Luxury Apartment Art Phoenix Rebirth Vessel for Meditation 12x18 Matte&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Phoenix Rebirth Vessel for Meditation, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Zen-0005; Subject: Phoenix Rebirth Vessel for Meditation&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Jade Wall Art Reading Nook 12x18 Matte Poster Apartment Decor Gift&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for poster print. It is written for buyers decorating reading nooks, home libraries, dorm study walls, meditation rooms, and quiet apartment corners, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 matte poster, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; matte paper mood, cinematic depth, smoky jade tones, and calm visual focus.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; wall art poster, gallery wall decor, apartment wall art, poster print, room decor, quiet jade, premium aesthetic, giftable decor.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed poster. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Zen-0005. Prior title: Quiet Luxury Jade Wall Art Reading Nook Apartment 12x18 Matte Poster Apartment&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>$34.99</t>
+          <t>$29.99</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -17649,7 +17649,27 @@
       </c>
       <c r="AH177" t="inlineStr">
         <is>
-          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>2026-05-07 07:37:28 -0400</t>
+        </is>
+      </c>
+      <c r="AL177" t="inlineStr">
+        <is>
+          <t>B_HIGH_VOLUME_VALUE</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>poster print</t>
+        </is>
+      </c>
+      <c r="AN177" t="inlineStr">
+        <is>
+          <t>reading_nook_warm_lamp</t>
         </is>
       </c>
     </row>
@@ -18476,17 +18496,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Quiet Luxury Shelf Decor Necromancer Soul Reliquary Artifact 5x7 Acrylic Photo</t>
+          <t>Collector Shelf Smoky Jade Quiet Luxury 5x7 Acrylic Block Shelf Decor Gift Wall</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Quiet Luxury Shelf Decor Necromancer Soul Reliquary Artifact 5x7 Acrylic Photo&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Necromancer Soul Reliquary Artifact, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0005; Subject: Necromancer Soul Reliquary Artifact&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Collector Shelf Smoky Jade Quiet Luxury 5x7 Acrylic Block Shelf Decor Gift Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for shelf decor. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; acrylic photo block, desk display, shelf decor, collector gift, office decor, quiet jade, premium aesthetic, giftable decor.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0005. Prior title: Collector Shelf Smoky Jade Quiet Luxury 5x7 Acrylic Block Shelf Decor Gift Wall&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>$89.99</t>
+          <t>$84.99</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -18579,7 +18599,27 @@
       </c>
       <c r="AH184" t="inlineStr">
         <is>
-          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>2026-05-07 07:37:28 -0400</t>
+        </is>
+      </c>
+      <c r="AL184" t="inlineStr">
+        <is>
+          <t>B_HIGH_VOLUME_VALUE</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>shelf decor</t>
+        </is>
+      </c>
+      <c r="AN184" t="inlineStr">
+        <is>
+          <t>quiet_luxury_apartment</t>
         </is>
       </c>
     </row>
@@ -18816,17 +18856,17 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Gothic Grimdark Revenant Lantern 5x7 Acrylic Art Premium Decor Sapphire Glass</t>
+          <t>Quiet Luxury Jade Relic Revenant 5x7 Acrylic Block Shelf Decor Gift Study Wall</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This 5x7 acrylic print captures the &lt;strong&gt;Revenant's Midnight Keeper&lt;/strong&gt;, a grimdark spirit vessel forged from wrought iron and ghostly sapphire glass. The deep blue internal flame and bat wing filigree create a moody, collector-focused aesthetic perfect for gothic decor.&lt;/p&gt;&lt;p&gt;Display this premium artifact on a study desk, bookshelf, or altar to evoke midnight mystery and refractive light. The high-contrast shadows and micro-engraved surface relief deliver a mentor-grade object design with layered translucent depth.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic print, ready to hang or stand&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-gloss acrylic with UV-resistant inks&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade, gothic lantern with bat wing accents and internal glow&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Wrought iron, ghostly sapphire glass, deep blue spirit flame, gothic filigree, kintsugi-like vein logic, floating accent fragments, cinematic rim lighting&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Gothic room decor, dark academia study, spirit vessel collection, Halloween ambiance, premium gift for grimdark enthusiasts&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Jade Relic Revenant 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for desk display. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; acrylic photo block, desk display, shelf decor, collector gift, office decor, quiet jade, premium aesthetic, giftable decor.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0008. Prior title: Quiet Luxury Jade Relic Revenant 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>$89.99</t>
+          <t>$84.99</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -18896,6 +18936,31 @@
       </c>
       <c r="V187" s="1" t="n">
         <v>46148.85849773148</v>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>2026-05-07 07:37:28 -0400</t>
+        </is>
+      </c>
+      <c r="AL187" t="inlineStr">
+        <is>
+          <t>B_HIGH_VOLUME_VALUE</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>desk display</t>
+        </is>
+      </c>
+      <c r="AN187" t="inlineStr">
+        <is>
+          <t>quiet_luxury_apartment</t>
+        </is>
       </c>
     </row>
     <row r="188">
@@ -19026,17 +19091,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Gothic Wraith Warden Cursed Beacon 5x7 Acrylic Block Dark Fantasy Decor Shelf</t>
+          <t>Collector Shelf Smoky Jade Wraith Warden 5x7 Acrylic Block Shelf Decor Gift</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This 5x7 acrylic block captures the grimdark essence of the Wraith Warden's Cursed Beacon, a gothic lantern wrought from heavy iron and ghostly aquamarine glass. The trapped teal spirit flame glows from within, refracting light through cracked surfaces for a haunting, museum-quality display. Ideal for dark fantasy collectors or as a statement piece on a study desk or shelf, this premium block brings a cursed, bioluminescent aura to any space.&lt;/p&gt;&lt;p&gt;Use this acrylic block as a desk accent, bookshelf artifact, or gothic home decor element. Its refractive internal glow and raven motifs evoke a mentor-grade grimdark aesthetic, perfect for adding a touch of cursed elegance to a minimalist or dark academia setting.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic block with printed design&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-clarity acrylic with UV-resistant ink&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade, Wraith Warden, Cursed Beacon&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Wrought iron, ghostly aquamarine glass, teal spirit flame, gothic filigree, micro-engraved surface relief, handcrafted edge bevels, layered translucent depth, internal bioluminescent glow, kintsugi-like vein logic, floating accent fragments, cinematic rim lighting, museum-grade overhead fill&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Dark fantasy desk decor, gothic collectible, study shelf accent, home altar piece, gift for grimdark enthusiasts&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Collector Shelf Smoky Jade Wraith Warden 5x7 Acrylic Block Shelf Decor Gift&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for shelf decor. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; acrylic photo block, desk display, shelf decor, collector gift, office decor, quiet jade, premium aesthetic, giftable decor.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0010. Prior title: Collector Shelf Smoky Jade Wraith Warden 5x7 Acrylic Block Shelf Decor Gift&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>$89.99</t>
+          <t>$84.99</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -19106,6 +19171,31 @@
       </c>
       <c r="V189" s="1" t="n">
         <v>46148.85852811343</v>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>2026-05-07 07:37:28 -0400</t>
+        </is>
+      </c>
+      <c r="AL189" t="inlineStr">
+        <is>
+          <t>B_HIGH_VOLUME_VALUE</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>shelf decor</t>
+        </is>
+      </c>
+      <c r="AN189" t="inlineStr">
+        <is>
+          <t>reading_nook_warm_lamp</t>
+        </is>
       </c>
     </row>
     <row r="190">
@@ -19391,17 +19481,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Reading Nook Wall Decor Mystic Threshold Infinite Knowledge 12x18 Matte Poster</t>
+          <t>Dark Academia Reading Nook Art Mystic Threshold Infinite 12x18 Matte Poster</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Reading Nook Wall Decor Mystic Threshold Infinite Knowledge 12x18 Matte Poster&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Mystic Threshold Infinite Knowledge, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0008; Subject: Mystic Threshold Infinite Knowledge&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Dark Academia Reading Nook Art Mystic Threshold Infinite 12x18 Matte Poster&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for wall art poster. It is written for buyers decorating reading nooks, home libraries, dorm study walls, meditation rooms, and quiet apartment corners, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 matte poster, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; matte paper mood, cinematic depth, smoky jade tones, and calm visual focus.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; wall art poster, gallery wall decor, apartment wall art, poster print, room decor, quiet jade, premium aesthetic, giftable decor.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed poster. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0008. Prior title: Dark Academia Reading Nook Art Mystic Threshold Infinite 12x18 Matte Poster&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>$34.99</t>
+          <t>$29.99</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -19494,7 +19584,27 @@
       </c>
       <c r="AH192" t="inlineStr">
         <is>
-          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>2026-05-07 07:37:28 -0400</t>
+        </is>
+      </c>
+      <c r="AL192" t="inlineStr">
+        <is>
+          <t>B_HIGH_VOLUME_VALUE</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>wall art poster</t>
+        </is>
+      </c>
+      <c r="AN192" t="inlineStr">
+        <is>
+          <t>reading_nook_warm_lamp</t>
         </is>
       </c>
     </row>
@@ -20829,17 +20939,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Gothic Grimdark Shadowpriest Ritual Vessel 5x7 Acrylic Decor Indigo Flame Shelf</t>
+          <t>Quiet Luxury Jade Relic Shadowpriest 5x7 Acrylic Block Shelf Decor Gift Study</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This 5x7 acrylic print captures the Shadowpriest's Ritual Vessel, a gothic lantern of wrought iron and ghostly lapis glass cradling an indigo spirit flame. The grimdark fantasy design features ritual circle engravings and a trapped internal glow, perfect for adding dark elegance to any study or altar.&lt;/p&gt;&lt;p&gt;Printed on premium acrylic, the piece uses refractive light and layered depth to mimic the vessel's internal bioluminescence. The high-contrast shadows and micro-engraved surface relief create a mentor-grade collectible artifact look. Ideal for display on a desk, shelf, or wall, it brings a moody, intellectual focal point to your space.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic print, ready to hang with included mounting hardware&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-gloss acrylic with UV-resistant inks for lasting vibrancy&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade, featuring wrought iron, ghostly lapis glass, indigo spirit flame, gothic filigree, and kintsugi-like vein accents&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Grimdark fantasy, ritual vessel, indigo flame, lapis glass, refractive light, internal radiance, premium design, shadowpriest aesthetic&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Gothic decor, study accent, occult collection, dark academia desk, altar piece, gift for fantasy enthusiasts&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note:&lt;/em&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Jade Relic Shadowpriest 5x7 Acrylic Block Shelf Decor Gift Study&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for acrylic photo block. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; acrylic photo block, desk display, shelf decor, collector gift, office decor, quiet jade, premium aesthetic, giftable decor.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0016. Prior title: Quiet Luxury Jade Relic Shadowpriest 5x7 Acrylic Block Shelf Decor Gift Study&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>$89.99</t>
+          <t>$84.99</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -20928,6 +21038,31 @@
       </c>
       <c r="AC203" s="1" t="n">
         <v>46149.07897425926</v>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>2026-05-07 07:37:28 -0400</t>
+        </is>
+      </c>
+      <c r="AL203" t="inlineStr">
+        <is>
+          <t>B_HIGH_VOLUME_VALUE</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>acrylic photo block</t>
+        </is>
+      </c>
+      <c r="AN203" t="inlineStr">
+        <is>
+          <t>quiet_luxury_apartment</t>
+        </is>
       </c>
     </row>
     <row r="204">
@@ -22367,17 +22502,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Spectral Temple Soul Lantern Grimdark Mentor-Grade 5x7 Acrylic Art Collectible</t>
+          <t>Quiet Luxury Jade Relic Spectral 5x7 Acrylic Block Shelf Decor Gift Study Wall</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This 5x7 acrylic print presents the &lt;strong&gt;Spectral Temple Soul Lantern&lt;/strong&gt;, a grimdark mentor-grade artifact that channels the eerie beauty of a spectral lantern. The design features a wrought iron temple gate frame, opal inlays, and imperial jade glass panels etched with ink-wash nebula patterns. A swirling cyan-silver spirit flame, surrounded by floating talisman fragments, emits a soft ethereal glow, creating a haunting focal point for any collector’s space.&lt;/p&gt;&lt;p&gt;Perfect for display on a study desk, bookshelf, or altar, this acrylic piece brings a darkly luminous presence to your decor. The high-gloss surface and crisp edge bevels enhance the layered depth and subtle bioluminescent glow, making it a standout addition to a grimdark or gothic collection. Use it as a meditation aid, a conversation starter, or a gift for fans of dark fantasy and occult aesthetics.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic print, ready to hang or stand&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-gloss acrylic with UV-resistant print&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (portrait orientation)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade, spectral, gothic&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Wrought Iron, Opal, Imperial Jade Glass, Talisman Fragments, Cyan-Silver Flame; micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, 3D depth, refractive light, internal glow, ray tracing&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study desk decor, gothic altar piece, grimdark collection display, gift for dark fantasy enthusiasts&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Jade Relic Spectral 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for desk display. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; acrylic photo block, desk display, shelf decor, collector gift, office decor, quiet jade, premium aesthetic, giftable decor.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0030. Prior title: Quiet Luxury Jade Relic Spectral 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>$89.99</t>
+          <t>$84.99</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -22466,6 +22601,31 @@
       </c>
       <c r="AC215" s="1" t="n">
         <v>46149.07912559028</v>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>2026-05-07 07:37:28 -0400</t>
+        </is>
+      </c>
+      <c r="AL215" t="inlineStr">
+        <is>
+          <t>B_HIGH_VOLUME_VALUE</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>desk display</t>
+        </is>
+      </c>
+      <c r="AN215" t="inlineStr">
+        <is>
+          <t>reading_nook_warm_lamp</t>
+        </is>
       </c>
     </row>
     <row r="216">
@@ -22491,17 +22651,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Midnight Sanctuary Soul Lantern Grimdark 5x7 Acrylic Collectible Display Shelf</t>
+          <t>Collector Shelf Smoky Jade Midnight Sanctuary 5x7 Acrylic Block Shelf Decor</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This acrylic collectible captures the Midnight Sanctuary Soul Lantern, a grimdark mentor-grade artifact with an ethereal gothic lantern design. The piece features a wrought iron sanctuary arch frame, black pearl inlays, and imperial jade glass panels etched with ink-wash nebula patterns. Inside, an indigo-white spirit flame swirls with floating talisman fragments, creating a soft midnight glow that evokes talisman magic and gothic mystery.&lt;/p&gt;&lt;p&gt;Perfect for a study desk, bookshelf, or altar display, this 5x7 acrylic print delivers a premium artifact aesthetic with micro-engraved surface relief, visible handcrafted edge bevels, and layered translucent depth. The refined kintsugi-like vein logic and intentional negative space around floating fragments make it a standout piece for collectors of dark fantasy decor. Use it to enhance a gothic room, as a conversation starter in a home library, or as a unique gift for admirers of grimdark art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic print with easel back stand&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-gloss acrylic with UV-resistant print&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade with gothic artifact details&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Ethereal gothic lantern, wrought iron sanctuary arch, black pearl inlays, indigo-white spirit flame, floating talisman fragments, ink-wash nebula patterns, imperial jade glass panels, soft midnight glow, micro-engraved surface relief, handcrafted edge bevels, layered translucent depth, bioluminescent glow, kintsugi-like vein logic, negative space composition&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study desk display, bookshelf accent, altar decor, gothic room aesthetic, dark fantasy collector gift, home library ornament&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Collector Shelf Smoky Jade Midnight Sanctuary 5x7 Acrylic Block Shelf Decor&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for collector gift. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; acrylic photo block, desk display, shelf decor, collector gift, office decor, quiet jade, premium aesthetic, giftable decor.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0031. Prior title: Collector Shelf Smoky Jade Midnight Sanctuary 5x7 Acrylic Block Shelf Decor&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>$89.99</t>
+          <t>$84.99</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -22590,6 +22750,31 @@
       </c>
       <c r="AC216" s="1" t="n">
         <v>46149.07913774306</v>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>2026-05-07 07:37:28 -0400</t>
+        </is>
+      </c>
+      <c r="AL216" t="inlineStr">
+        <is>
+          <t>B_HIGH_VOLUME_VALUE</t>
+        </is>
+      </c>
+      <c r="AM216" t="inlineStr">
+        <is>
+          <t>collector gift</t>
+        </is>
+      </c>
+      <c r="AN216" t="inlineStr">
+        <is>
+          <t>quiet_luxury_apartment</t>
+        </is>
       </c>
     </row>
     <row r="217">
@@ -23012,17 +23197,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Twilight Portal Soul Lantern Grimdark 5x7 Acrylic Art Gothic Decor Purple Flame</t>
+          <t>Quiet Luxury Jade Relic Twilight 5x7 Acrylic Block Shelf Decor Gift Study Wall</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This 5x7 acrylic print transforms the Twilight Portal Soul Lantern into a luminous grimdark artifact for your wall. A wrought iron portal frame encloses labradorite inlays and a swirling purple-blue spirit flame, with floating talisman fragments suspended in ink-wash nebula patterns on imperial jade glass panels. The mentor-grade design balances ethereal twilight glow with handcrafted edge bevels and kintsugi-like vein logic, creating a refined collectible aesthetic.&lt;/p&gt;&lt;p&gt;Perfect for a study desk, bookshelf, or gothic meditation corner, this acrylic piece offers durable depth and a subtle bioluminescent effect that shifts with ambient light. The 5x7 size fits easily into small wall arrangements or stands alone as a focal point in a dark academia or grimdark collection.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic print, ready to hang or display&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium acrylic with UV-resistant print, clear edge bevels&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5 x 7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade, gothic lantern with portal frame, labradorite inlay, purple flame, jade glass panels, talisman fragments&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Wrought Iron, Labradorite, Imperial Jade Glass, Talisman Fragments, Purple-Blue Flame, micro-engraved surface relief, layered translucent depth, internal bioluminescent glow, refined kintsugi vein logic, floating accent fragments with intentional negative space&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Gothic decor, dark academia study, collector display, ritual altar, bookshelf accent, gift for grimdark enthusiasts&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Jade Relic Twilight 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for office decor. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; acrylic photo block, desk display, shelf decor, collector gift, office decor, quiet jade, premium aesthetic, giftable decor.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0035. Prior title: Quiet Luxury Jade Relic Twilight 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>$89.99</t>
+          <t>$84.99</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -23111,6 +23296,31 @@
       </c>
       <c r="AC220" s="1" t="n">
         <v>46149.0791871875</v>
+      </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>2026-05-07 07:37:28 -0400</t>
+        </is>
+      </c>
+      <c r="AL220" t="inlineStr">
+        <is>
+          <t>B_HIGH_VOLUME_VALUE</t>
+        </is>
+      </c>
+      <c r="AM220" t="inlineStr">
+        <is>
+          <t>office decor</t>
+        </is>
+      </c>
+      <c r="AN220" t="inlineStr">
+        <is>
+          <t>quiet_luxury_apartment</t>
+        </is>
       </c>
     </row>
     <row r="221">
@@ -23527,17 +23737,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Smoky Jade Gothic Object Sapphire Temple Soul Lantern Artifact 5x7 Acrylic Gift</t>
+          <t>Quiet Luxury Jade Relic Smoky 5x7 Acrylic Block Shelf Decor Gift Study Wall</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Smoky Jade Gothic Object Sapphire Temple Soul Lantern Artifact 5x7 Acrylic Gift&lt;/h2&gt;&lt;p&gt;This is part of a fast A/B traffic test built around higher-intent buyer scenes: quiet luxury apartment shelves, gothic study desks, collector corners, and deep-work rooms. The style leans into smoky jade glow, acrylic depth, refractive light, and gallery-object presence, avoiding generic mass-market wording.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Lane:&lt;/strong&gt; B Gothic Collector Shelf&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark with Quiet Jade / Deep Work positioning.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0039&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Jade Relic Smoky 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for office decor. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; acrylic photo block, desk display, shelf decor, collector gift, office decor, quiet jade, premium aesthetic, giftable decor.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0039. Prior title: Quiet Luxury Jade Relic Smoky 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>$89.99</t>
+          <t>$84.99</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -23613,7 +23823,7 @@
       </c>
       <c r="AH224" t="inlineStr">
         <is>
-          <t>SEO_STRIKE_SYNCED_PRINTIFY_DRAFT</t>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
         </is>
       </c>
       <c r="AI224" t="inlineStr">
@@ -23624,6 +23834,26 @@
       <c r="AJ224" t="inlineStr">
         <is>
           <t>B_GOTHIC_COLLECTOR_SHELF</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>2026-05-07 07:37:28 -0400</t>
+        </is>
+      </c>
+      <c r="AL224" t="inlineStr">
+        <is>
+          <t>B_HIGH_VOLUME_VALUE</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>office decor</t>
+        </is>
+      </c>
+      <c r="AN224" t="inlineStr">
+        <is>
+          <t>reading_nook_warm_lamp</t>
         </is>
       </c>
     </row>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN283"/>
+  <dimension ref="A1:AN284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -940,7 +940,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -14394,7 +14394,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -14759,7 +14759,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -15724,7 +15724,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -15854,7 +15854,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -16219,7 +16219,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -17336,7 +17336,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -17466,7 +17466,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -17596,7 +17596,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -31013,6 +31013,134 @@
       </c>
       <c r="V283" s="1" t="n">
         <v>46148.98066784722</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0055-FIX1</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0055-FIX1</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Quiet Desk Sticker Pack Azure Dragon Warrior 4pc 6x6 Kiss-Cut Vinyl Laptop Gift</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Quiet Desk Sticker Pack Azure Dragon Warrior 4pc 6x6 Kiss-Cut Vinyl Laptop Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for laptops, journals, planners, bottles, reading notebooks, and study desk gifts. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut vinyl sticker sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Azure Dragon Warrior, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0055; Subject: Azure Dragon Warrior&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Warrior Azure dragon with Translucent Imperial Jade armor, Kintsugi Gold Veins repairs, Bioluminescent Glow eyes, and Internal Crystalline Structures weapons, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0055_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0055_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0055_Ready_for_Steaming\Sticker-Zen-0055_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0055_Ready_for_Steaming\Sticker-Zen-0055_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0055_Ready_for_Steaming\Sticker-Zen-0055_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0055_Ready_for_Steaming\Sticker-Zen-0055_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>2026-05-07 11:16:22 -0400</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>69fcad74346e75ac9f07d550</t>
+        </is>
+      </c>
+      <c r="R284" s="1" t="n">
+        <v>46149.47507757742</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>406910984204</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406910984204</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V284" s="1" t="n">
+        <v>46149.4753887167</v>
+      </c>
+      <c r="AD284" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF284" t="inlineStr">
+        <is>
+          <t>Azure Dragon Warrior, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG284" t="inlineStr">
+        <is>
+          <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN284"/>
+  <dimension ref="A1:AN287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6190,6 +6190,14 @@
       </c>
       <c r="V59" s="1" t="n">
         <v>46148.85754021991</v>
+      </c>
+      <c r="W59" s="1" t="n">
+        <v>46149.49644304398</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
@@ -6290,7 +6298,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6320,6 +6328,14 @@
       </c>
       <c r="V60" s="1" t="n">
         <v>46148.85755953703</v>
+      </c>
+      <c r="W60" s="1" t="n">
+        <v>46149.50266826389</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
@@ -6420,7 +6436,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6450,6 +6466,14 @@
       </c>
       <c r="V61" s="1" t="n">
         <v>46148.85758619213</v>
+      </c>
+      <c r="W61" s="1" t="n">
+        <v>46149.51885146759</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
@@ -31102,7 +31126,7 @@
         </is>
       </c>
       <c r="R284" s="1" t="n">
-        <v>46149.47507757742</v>
+        <v>46149.47507758102</v>
       </c>
       <c r="S284" t="inlineStr">
         <is>
@@ -31120,7 +31144,7 @@
         </is>
       </c>
       <c r="V284" s="1" t="n">
-        <v>46149.4753887167</v>
+        <v>46149.47538871528</v>
       </c>
       <c r="AD284" t="inlineStr">
         <is>
@@ -31138,6 +31162,388 @@
         </is>
       </c>
       <c r="AG284" t="inlineStr">
+        <is>
+          <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0056-FIX1</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0056-FIX1</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Reading Nook Vinyl Set Dragon Cherry Blossom 4pc 6x6 Kiss-Cut Vinyl Laptop Gift</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Reading Nook Vinyl Set Dragon Cherry Blossom 4pc 6x6 Kiss-Cut Vinyl Laptop Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for laptops, journals, planners, bottles, reading notebooks, and study desk gifts. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut vinyl sticker sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Dragon Cherry Blossom, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0056; Subject: Dragon Cherry Blossom&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Zen dragon with Translucent Imperial Jade scales surrounded by cherry blossoms, Kintsugi Gold Veins branches, Bioluminescent Glow petals, and Internal Crystalline Structures dewdrops, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0056_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0056_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0056_Ready_for_Steaming\Sticker-Zen-0056_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0056_Ready_for_Steaming\Sticker-Zen-0056_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0056_Ready_for_Steaming\Sticker-Zen-0056_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0056_Ready_for_Steaming\Sticker-Zen-0056_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>2026-05-07 11:57:21 -0400</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>69fcb688d0e6f406f20a3d2a</t>
+        </is>
+      </c>
+      <c r="R285" s="1" t="n">
+        <v>46149.50093743056</v>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>406911030956</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911030956</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V285" s="1" t="n">
+        <v>46149.50125799768</v>
+      </c>
+      <c r="AD285" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE285" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF285" t="inlineStr">
+        <is>
+          <t>Dragon Cherry Blossom, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG285" t="inlineStr">
+        <is>
+          <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0057-FIX1</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0057-FIX1</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Wabi Sabi Journal Decals Moonlit Dragon 4pc 6x6 Kiss-Cut Vinyl Laptop Journal</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Wabi Sabi Journal Decals Moonlit Dragon 4pc 6x6 Kiss-Cut Vinyl Laptop Journal&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for laptops, journals, planners, bottles, reading notebooks, and study desk gifts. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut vinyl sticker sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Moonlit Dragon, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0057; Subject: Moonlit Dragon&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Zen dragon under moonlight with Translucent Imperial Jade reflecting moonbeams, Kintsugi Gold Veins constellations, Bioluminescent Glow moonlight, and Internal Crystalline Structures stars, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0057_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0057_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0057_Ready_for_Steaming\Sticker-Zen-0057_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0057_Ready_for_Steaming\Sticker-Zen-0057_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0057_Ready_for_Steaming\Sticker-Zen-0057_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0057_Ready_for_Steaming\Sticker-Zen-0057_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>Printify_Published</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>2026-05-07 12:05:47 -0400</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>69fcb8762007fddea00e4ebe</t>
+        </is>
+      </c>
+      <c r="R286" s="1" t="n">
+        <v>46149.5054065625</v>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>406911046712</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911046712</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V286" s="1" t="n">
+        <v>46149.51745751157</v>
+      </c>
+      <c r="Y286" s="1" t="n">
+        <v>46149.50771107639</v>
+      </c>
+      <c r="Z286" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406911046712 handle=https://www.ebay.com/itm/406911046712</t>
+        </is>
+      </c>
+      <c r="AC286" s="1" t="n">
+        <v>46149.51745751157</v>
+      </c>
+      <c r="AD286" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF286" t="inlineStr">
+        <is>
+          <t>Moonlit Dragon, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG286" t="inlineStr">
+        <is>
+          <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0058-FIX1</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0058-FIX1</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Smoky Jade Sticker Set Dragon Calligraphy Serene Clean 4pc 6x6 Kiss-Cut Vinyl</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Smoky Jade Sticker Set Dragon Calligraphy Serene Clean 4pc 6x6 Kiss-Cut Vinyl&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for laptops, journals, planners, bottles, reading notebooks, and study desk gifts. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut vinyl sticker sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Dragon Calligraphy Serene Clean, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0058; Subject: Dragon Calligraphy Serene Clean&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Zen dragon formed from Japanese calligraphy strokes using Translucent Imperial Jade ink, Kintsugi Gold Veins brushwork, Bioluminescent Glow highlights, and Internal Crystalline Structures ink splatters, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0058_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0058_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0058_Ready_for_Steaming\Sticker-Zen-0058_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0058_Ready_for_Steaming\Sticker-Zen-0058_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0058_Ready_for_Steaming\Sticker-Zen-0058_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0058_Ready_for_Steaming\Sticker-Zen-0058_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>Printify_UI_Failed</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>2026-05-07 12:15:28 -0400</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>69fcbabcbb3409c48f0e342c</t>
+        </is>
+      </c>
+      <c r="AD287" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE287" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF287" t="inlineStr">
+        <is>
+          <t>Dragon Calligraphy Serene Clean, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG287" t="inlineStr">
         <is>
           <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
         </is>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN287"/>
+  <dimension ref="A1:AN288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6468,7 +6468,7 @@
         <v>46148.85758619213</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>46149.51885146759</v>
+        <v>46149.5188514699</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6604,6 +6604,14 @@
       </c>
       <c r="V62" s="1" t="n">
         <v>46148.85760666666</v>
+      </c>
+      <c r="W62" s="1" t="n">
+        <v>46149.52602256944</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
@@ -6704,7 +6712,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -6734,6 +6742,14 @@
       </c>
       <c r="V63" s="1" t="n">
         <v>46148.85762224537</v>
+      </c>
+      <c r="W63" s="1" t="n">
+        <v>46149.53241861867</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
@@ -31515,7 +31531,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>Printify_UI_Failed</t>
+          <t>Printify_Published</t>
         </is>
       </c>
       <c r="P287" t="inlineStr">
@@ -31528,6 +31544,46 @@
           <t>69fcbabcbb3409c48f0e342c</t>
         </is>
       </c>
+      <c r="R287" s="1" t="n">
+        <v>46149.52264045139</v>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>406911102240</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911102240</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V287" s="1" t="n">
+        <v>46149.5236897338</v>
+      </c>
+      <c r="Y287" s="1" t="n">
+        <v>46149.5236897338</v>
+      </c>
+      <c r="Z287" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB287" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406911102240 handle=https://www.ebay.com/itm/406911102240</t>
+        </is>
+      </c>
+      <c r="AC287" s="1" t="n">
+        <v>46149.5236897338</v>
+      </c>
       <c r="AD287" t="inlineStr">
         <is>
           <t>2026-05-07 00:46:18 -0400</t>
@@ -31544,6 +31600,153 @@
         </is>
       </c>
       <c r="AG287" t="inlineStr">
+        <is>
+          <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0060-FIX1</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0060-FIX1</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Reading Nook Vinyl Set Translucent Jade Dragon Serene Clean 4pc 6x6 Kiss-Cut</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Reading Nook Vinyl Set Translucent Jade Dragon Serene Clean 4pc 6x6 Kiss-Cut&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for laptops, journals, planners, bottles, reading notebooks, and study desk gifts. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut vinyl sticker sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Translucent Jade Dragon Serene Clean, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0060; Subject: Translucent Jade Dragon Serene Clean&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>A detailed sticker design of a Zen dragon, Translucent Imperial Jade material, Kintsugi Gold Veins, Bioluminescent Glow, Internal Crystalline Structures, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0060_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0060_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0060_Ready_for_Steaming\Sticker-Zen-0060_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0060_Ready_for_Steaming\Sticker-Zen-0060_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0060_Ready_for_Steaming\Sticker-Zen-0060_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0060_Ready_for_Steaming\Sticker-Zen-0060_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>Printify_Published</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>2026-05-07 12:38:46 -0400</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>69fcc02e6a069c45c0013c52</t>
+        </is>
+      </c>
+      <c r="R288" s="1" t="n">
+        <v>46149.52965991898</v>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>406911120974</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911120974</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V288" s="1" t="n">
+        <v>46149.53064886574</v>
+      </c>
+      <c r="Y288" s="1" t="n">
+        <v>46149.53064886574</v>
+      </c>
+      <c r="Z288" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406911120974 handle=https://www.ebay.com/itm/406911120974</t>
+        </is>
+      </c>
+      <c r="AC288" s="1" t="n">
+        <v>46149.53064886574</v>
+      </c>
+      <c r="AD288" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF288" t="inlineStr">
+        <is>
+          <t>Translucent Jade Dragon Serene Clean, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG288" t="inlineStr">
         <is>
           <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
         </is>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN288"/>
+  <dimension ref="A1:AN289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6744,7 +6744,7 @@
         <v>46148.85762224537</v>
       </c>
       <c r="W63" s="1" t="n">
-        <v>46149.53241861867</v>
+        <v>46149.53241862269</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>4/29/2026  1:28:53 PM</t>
+          <t>5/7/2026  4:07:15 PM</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -6880,6 +6880,14 @@
       </c>
       <c r="V64" s="1" t="n">
         <v>46148.8576396875</v>
+      </c>
+      <c r="W64" s="1" t="n">
+        <v>46149.68053679106</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
@@ -31747,6 +31755,134 @@
         </is>
       </c>
       <c r="AG288" t="inlineStr">
+        <is>
+          <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0061-FIX1</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0061-FIX1</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Wabi Sabi Journal Decals Kintsugi Gold Dragon Serene Calm 4pc 6x6 Kiss-Cut Gift</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Wabi Sabi Journal Decals Kintsugi Gold Dragon Serene Calm 4pc 6x6 Kiss-Cut Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for laptops, journals, planners, bottles, reading notebooks, and study desk gifts. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut vinyl sticker sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Kintsugi Gold Dragon Serene Calm, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0061; Subject: Kintsugi Gold Dragon Serene Calm&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>A Zen dragon sticker with Kintsugi Gold Veins repairing Translucent Imperial Jade, Bioluminescent Glow from cracks, Internal Crystalline Structures visible, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0061_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0061_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0061_Ready_for_Steaming\Sticker-Zen-0061_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0061_Ready_for_Steaming\Sticker-Zen-0061_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0061_Ready_for_Steaming\Sticker-Zen-0061_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0061_Ready_for_Steaming\Sticker-Zen-0061_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>2026-05-07 16:14:41 -0400</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>69fcf2ccf2b2884ff107c609</t>
+        </is>
+      </c>
+      <c r="R289" s="1" t="n">
+        <v>46149.67832842593</v>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>406911452547</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911452547</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V289" s="1" t="n">
+        <v>46149.67892783564</v>
+      </c>
+      <c r="AD289" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE289" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF289" t="inlineStr">
+        <is>
+          <t>Kintsugi Gold Dragon Serene Calm, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG289" t="inlineStr">
         <is>
           <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
         </is>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN289"/>
+  <dimension ref="A1:AN291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6882,7 +6882,7 @@
         <v>46148.8576396875</v>
       </c>
       <c r="W64" s="1" t="n">
-        <v>46149.68053679106</v>
+        <v>46149.68053679398</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7018,6 +7018,14 @@
       </c>
       <c r="V65" s="1" t="n">
         <v>46148.85765802083</v>
+      </c>
+      <c r="W65" s="1" t="n">
+        <v>46149.7010079051</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
@@ -7118,7 +7126,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7148,6 +7156,14 @@
       </c>
       <c r="V66" s="1" t="n">
         <v>46148.85767342593</v>
+      </c>
+      <c r="W66" s="1" t="n">
+        <v>46149.7045780371</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -31886,6 +31902,242 @@
         <is>
           <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
         </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0062-FIX1</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0062-FIX1</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Smoky Jade Sticker Set Bioluminescent Dragon 4pc 6x6 Kiss-Cut Vinyl Laptop Gift</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Smoky Jade Sticker Set Bioluminescent Dragon 4pc 6x6 Kiss-Cut Vinyl Laptop Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for laptops, journals, planners, bottles, reading notebooks, and study desk gifts. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut vinyl sticker sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Bioluminescent Dragon, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0062; Subject: Bioluminescent Dragon&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>A glowing Zen dragon sticker with Bioluminescent Glow illuminating Translucent Imperial Jade body, Kintsugi Gold Veins, Internal Crystalline Structures glowing from within, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0062_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0062_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0062_Ready_for_Steaming\Sticker-Zen-0062_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0062_Ready_for_Steaming\Sticker-Zen-0062_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0062_Ready_for_Steaming\Sticker-Zen-0062_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0062_Ready_for_Steaming\Sticker-Zen-0062_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>2026-05-07 16:46:14 -0400</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>69fcfa3363b7f727e7012b1a</t>
+        </is>
+      </c>
+      <c r="R290" s="1" t="n">
+        <v>46149.69972608797</v>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>406911488570</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911488570</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V290" s="1" t="n">
+        <v>46149.70002454861</v>
+      </c>
+      <c r="AD290" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE290" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF290" t="inlineStr">
+        <is>
+          <t>Bioluminescent Dragon, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG290" t="inlineStr">
+        <is>
+          <t>Sticker kept review-friendly; not part of high-ticket price lift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0063-FIX1</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0063-FIX1</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Crystalline Dragon Core 4pc 6x6 Kiss-Cut Sticker Zen Aesthetic Laptop Journal</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Crystalline Dragon Core Sticker Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Bring calm and balance into your daily routine with this Crystalline Dragon Core Sticker zen aesthetic kiss-cut sticker.&lt;/p&gt;&lt;p&gt;Designed for study rooms, creative workspaces, shelves, gallery walls, and collectible aesthetic decor, this sticker blends niche aesthetic appeal with collectible mentor-grade artwork.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A Zen dragon sticker focusing on Internal Crystalline Structures within Translucent Imperial Jade, Kintsugi Gold Veins as circuitry, Bioluminescent Glow from crystal formations, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; mindfulness lovers, minimalists, journal keepers, yoga enthusiasts, and peaceful room setups.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; crystal core, geometric dragon, sacred geometry, mineral art, crystal healing, energy centers, chakra dragon, metaphysical, gemstone art, spiritual science&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Complete the collection with matching Alchemy pieces.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0063&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>A Zen dragon sticker focusing on Internal Crystalline Structures within Translucent Imperial Jade, Kintsugi Gold Veins as circuitry, Bioluminescent Glow from crystal formations, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0063_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0063_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0063_Ready_for_Steaming\Sticker-Zen-0063_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0063_Ready_for_Steaming\Sticker-Zen-0063_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0063_Ready_for_Steaming\Sticker-Zen-0063_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0063_Ready_for_Steaming\Sticker-Zen-0063_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>2026-05-07 16:50:31 -0400</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>69fcfb2d111bf518b6078098</t>
+        </is>
+      </c>
+      <c r="R291" s="1" t="n">
+        <v>46149.70332143518</v>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>406911494155</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911494155</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V291" s="1" t="n">
+        <v>46149.70362003472</v>
       </c>
     </row>
   </sheetData>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN291"/>
+  <dimension ref="A1:AN292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7158,7 +7158,7 @@
         <v>46148.85767342593</v>
       </c>
       <c r="W66" s="1" t="n">
-        <v>46149.7045780371</v>
+        <v>46149.7045780324</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7269,6 +7269,14 @@
       </c>
       <c r="V67" s="1" t="n">
         <v>46148.85769063657</v>
+      </c>
+      <c r="W67" s="1" t="n">
+        <v>46149.70952028736</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -32138,6 +32146,114 @@
       </c>
       <c r="V291" s="1" t="n">
         <v>46149.70362003472</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0066-FIX1</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0066-FIX1</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Golden Vein Circuitry Dragon 4pc 6x6 Kiss-Cut Sticker Zen Aesthetic Laptop Gift</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Golden Vein Circuitry Dragon Sticker Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Bring calm and balance into your daily routine with this Golden Vein Circuitry Dragon Sticker zen aesthetic kiss-cut sticker.&lt;/p&gt;&lt;p&gt;Designed for study rooms, creative workspaces, shelves, gallery walls, and collectible aesthetic decor, this sticker blends niche aesthetic appeal with collectible mentor-grade artwork.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A cyber-Zen dragon sticker with Kintsugi Gold Veins as glowing circuitry on Translucent Imperial Jade, Bioluminescent Glow at connection nodes, Internal Crystalline Structures as processing cores, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; mindfulness lovers, minimalists, journal keepers, yoga enthusiasts, and peaceful room setups.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; cyber dragon, tech spirituality, circuit board art, glitch art, digital zen, future Buddhism, neon circuits, cyberpunk, techwear, gamer culture&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Complete the collection with matching Alchemy pieces.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0066&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>A cyber-Zen dragon sticker with Kintsugi Gold Veins as glowing circuitry on Translucent Imperial Jade, Bioluminescent Glow at connection nodes, Internal Crystalline Structures as processing cores, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0066_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0066_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0066_Ready_for_Steaming\Sticker-Zen-0066_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0066_Ready_for_Steaming\Sticker-Zen-0066_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0066_Ready_for_Steaming\Sticker-Zen-0066_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0066_Ready_for_Steaming\Sticker-Zen-0066_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>2026-05-07 16:58:26 -0400</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>69fcfd2914568b768c07abd9</t>
+        </is>
+      </c>
+      <c r="R292" s="1" t="n">
+        <v>46149.70837517361</v>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>406911509730</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911509730</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V292" s="1" t="n">
+        <v>46149.70867581019</v>
       </c>
     </row>
   </sheetData>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN292"/>
+  <dimension ref="A1:AN293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7271,7 +7271,7 @@
         <v>46148.85769063657</v>
       </c>
       <c r="W67" s="1" t="n">
-        <v>46149.70952028736</v>
+        <v>46149.70952028935</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -7600,6 +7600,14 @@
       </c>
       <c r="V70" s="1" t="n">
         <v>46148.85774657407</v>
+      </c>
+      <c r="W70" s="1" t="n">
+        <v>46149.71563981934</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -32254,6 +32262,114 @@
       </c>
       <c r="V292" s="1" t="n">
         <v>46149.70867581019</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0069-FIX1</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0069-FIX1</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Minimal Zen Dragon Guardian 4pc 6x6 Sticker Sheet Serene Mindful Clean Decor</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Zen Dragon Guardian Sticker - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Zen aesthetic piece for students, remote workers, yoga lovers, and anyone building a serene everyday space. Designed for peaceful desks, journals, and small rituals, this Zen Dragon Guardian Sticker kiss-cut sticker carries a clean Zen mood.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for easy comparison.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A protective Zen dragon sticker in guardian pose with Translucent Imperial Jade scales, Kintsugi Gold Veins as armor seams, Bioluminescent Glow from eyes, Internal Crystalline Structures as power source, , , , , 3D relief effect, sharp focus&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; students, remote workers, yoga lovers, and anyone building a serene everyday space.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; guardian dragon, protective symbol, armor art, spiritual protection, warrior zen, defensive art, talisman, amulet, good luck charm, safety symbol&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Saved under the reference SKU below for easy collector matching.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0069&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>A protective Zen dragon sticker in guardian pose with Translucent Imperial Jade scales, Kintsugi Gold Veins as armor seams, Bioluminescent Glow from eyes, Internal Crystalline Structures as power source, , , , , 3D relief effect, sharp focus</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0069_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0069_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0069_Ready_for_Steaming\Sticker-Zen-0069_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0069_Ready_for_Steaming\Sticker-Zen-0069_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0069_Ready_for_Steaming\Sticker-Zen-0069_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0069_Ready_for_Steaming\Sticker-Zen-0069_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>2026-05-07 17:05:41 -0400</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>69fcff15cd220b844e0f655c</t>
+        </is>
+      </c>
+      <c r="R293" s="1" t="n">
+        <v>46149.71467765046</v>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>406911531255</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911531255</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V293" s="1" t="n">
+        <v>46149.71497859954</v>
       </c>
     </row>
   </sheetData>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN293"/>
+  <dimension ref="A1:AN295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7602,7 +7602,7 @@
         <v>46148.85774657407</v>
       </c>
       <c r="W70" s="1" t="n">
-        <v>46149.71563981934</v>
+        <v>46149.71563981481</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7713,6 +7713,14 @@
       </c>
       <c r="V71" s="1" t="n">
         <v>46148.85776375</v>
+      </c>
+      <c r="W71" s="1" t="n">
+        <v>46149.71832703704</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -7788,7 +7796,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -7818,6 +7826,14 @@
       </c>
       <c r="V72" s="1" t="n">
         <v>46148.85778013889</v>
+      </c>
+      <c r="W72" s="1" t="n">
+        <v>46149.72013065044</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -32370,6 +32386,222 @@
       </c>
       <c r="V293" s="1" t="n">
         <v>46149.71497859954</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0070-FIX1</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0070-FIX1</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Minimal Zen Jade Phoenix Ascension 4pc 6x6 Sticker Sheet Serene Mindful Clean</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Jade Phoenix Ascension - Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;A polished Zen aesthetic piece for students, remote workers, yoga lovers, and anyone building a serene everyday space. Designed for peaceful desks, journals, and small rituals, this Jade Phoenix Ascension kiss-cut sticker carries a clean Zen mood.&lt;/p&gt;&lt;p&gt;The design works well across journal spreads, library shelves, dorm rooms, studio desks, and cozy personal collections, while the title, material notes, and DNA profile stay specific for easy comparison.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; A majestic phoenix rising from translucent moonstone flames, wings spread with imperial jade feather inlays, floating Daoist Fulu talisman fragments orbiting the bird, ink-wash nebula trailing behind, ethereal bioluminescence emanating from wing tips, zen-mythic aesthetic, , , , , , person, text, watermark&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; students, remote workers, yoga lovers, and anyone building a serene everyday space.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; phoenix sticker, jade phoenix, moonstone art, spiritual bird, zen phoenix, celestial creature, mythic phoenix, translucent wings, Daoist talisman, bioluminescent design&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Saved under the reference SKU below for easy collector matching.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0070&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>A majestic phoenix rising from translucent moonstone flames, wings spread with imperial jade feather inlays, floating Daoist Fulu talisman fragments orbiting the bird, ink-wash nebula trailing behind, ethereal bioluminescence emanating from wing tips, zen-mythic aesthetic, , , , , , person, text, watermark</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0070_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0070_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0070_Ready_for_Steaming\Sticker-Zen-0070_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0070_Ready_for_Steaming\Sticker-Zen-0070_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0070_Ready_for_Steaming\Sticker-Zen-0070_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0070_Ready_for_Steaming\Sticker-Zen-0070_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>2026-05-07 17:12:09 -0400</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>69fd002f096d6b4f0000a934</t>
+        </is>
+      </c>
+      <c r="R294" s="1" t="n">
+        <v>46149.71738046296</v>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>406911541926</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911541926</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V294" s="1" t="n">
+        <v>46149.71768587963</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0071-FIX1</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Sticker-Zen-0071-FIX1</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Sticker</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Zen Aesthetic Lotus Lantern Vessel 4pc 6x6 Kiss-Cut Sticker Laptop Journal Gift</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Lotus Lantern Vessel Kiss-Cut Sticker&lt;/h2&gt;&lt;p&gt;Bring calm and balance into your daily routine with this Lotus Lantern Vessel zen aesthetic kiss-cut sticker.&lt;/p&gt;&lt;p&gt;Designed for study rooms, creative workspaces, shelves, gallery walls, and collectible aesthetic decor, this sticker blends niche aesthetic appeal with collectible mentor-grade artwork.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 6x6 kiss-cut sheet with 4 individual sticker designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Durable kiss-cut vinyl sticker sheet with waterproof finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 6x6 kiss-cut sheet with four coordinated designs.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen Mentor-Grade; Zen aesthetic.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; An ornate lotus-shaped lantern vessel crafted from translucent moonstone petals and imperial jade stem, ink-wash nebula wisps flowing from interior chamber, floating Daoist Fulu talisman fragments circling the base, ethereal bioluminescence glowing within, zen-mythic aesthetic, , , , , , person, text, watermark&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; mindfulness lovers, minimalists, journal keepers, yoga enthusiasts, and peaceful room setups.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;SEO Keywords:&lt;/strong&gt; lotus lantern, jade vessel, moonstone container, spiritual lamp, zen lantern, celestial vessel, ritual lantern, translucent lotus, Daoist artifact, bioluminescent glow&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;Complete the collection with matching Alchemy pieces.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Sticker-Zen-0071&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>$11.99</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>An ornate lotus-shaped lantern vessel crafted from translucent moonstone petals and imperial jade stem, ink-wash nebula wisps flowing from interior chamber, floating Daoist Fulu talisman fragments circling the base, ethereal bioluminescence glowing within, zen-mythic aesthetic, , , , , , person, text, watermark</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0071_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0071_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0071_Ready_for_Steaming\Sticker-Zen-0071_U1_Grid.png</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0071_Ready_for_Steaming\Sticker-Zen-0071_U2_Grid.png</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0071_Ready_for_Steaming\Sticker-Zen-0071_U3_Grid.png</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Sticker\Kiss-Cut\MASTER_Sticker-Zen-0071_Ready_for_Steaming\Sticker-Zen-0071_U4_Grid.png</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups3</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>2026-05-07 17:14:44 -0400</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>69fd00ca9f7703138202688c</t>
+        </is>
+      </c>
+      <c r="R295" s="1" t="n">
+        <v>46149.71918982639</v>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>406911551031</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911551031</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V295" s="1" t="n">
+        <v>46149.71949134259</v>
       </c>
     </row>
   </sheetData>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN295"/>
+  <dimension ref="A1:AN296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7828,7 +7828,7 @@
         <v>46148.85778013889</v>
       </c>
       <c r="W72" s="1" t="n">
-        <v>46149.72013065044</v>
+        <v>46149.72013064815</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Printify_PrimaryFix_Needed</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -14990,6 +14990,14 @@
       </c>
       <c r="V155" s="1" t="n">
         <v>46148.85789751157</v>
+      </c>
+      <c r="W155" s="1" t="n">
+        <v>46149.72674940436</v>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
       </c>
       <c r="AD155" t="inlineStr">
         <is>
@@ -32602,6 +32610,134 @@
       </c>
       <c r="V295" s="1" t="n">
         <v>46149.71949134259</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Acrylic-Grimdark-0081-FIX1</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Acrylic-Grimdark-0081-FIX1</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Grimdark</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Smoky Jade Desk Object Plague Doctor Raven Skull Alchemy 5x7 Acrylic Photo Gift</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Smoky Jade Desk Object Plague Doctor Raven Skull Alchemy 5x7 Acrylic Photo Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Plague Doctor Raven Skull Alchemy, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0081; Subject: Plague Doctor Raven Skull Alchemy&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>$89.99</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Plague doctor raven skull, elongated brass beak apparatus, corroded iron rivets, kintsugi gold veins sealing bone fractures, toxic amber bioluminescent vapor seeping from eye sockets, grimdark industrial aesthetic, aged bone, corroded iron, oxidized brass, kintsugi gold, toxic amber bioluminescence, micro-engraved surface relief, handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments, intentional negative space, cinematic rim lighting, soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Grimdark-0081_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Grimdark-0081_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Grimdark-0081_Ready_for_Steaming\Gallery_U1.png</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Grimdark-0081_Ready_for_Steaming\Gallery_U2.png</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Grimdark-0081_Ready_for_Steaming\Gallery_U3.png</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Grimdark-0081_Ready_for_Steaming\Gallery_U4.png</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups4</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>2026-05-07 17:23:44 -0400</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>69fd02f3d70cf705c50f4d27</t>
+        </is>
+      </c>
+      <c r="R296" s="1" t="n">
+        <v>46149.72578068287</v>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>406911568594</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911568594</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V296" s="1" t="n">
+        <v>46149.72608443287</v>
+      </c>
+      <c r="AD296" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE296" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF296" t="inlineStr">
+        <is>
+          <t>Plague Doctor Raven Skull Alchemy, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor</t>
+        </is>
+      </c>
+      <c r="AG296" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN296"/>
+  <dimension ref="A1:AN297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14992,7 +14992,7 @@
         <v>46148.85789751157</v>
       </c>
       <c r="W155" s="1" t="n">
-        <v>46149.72674940436</v>
+        <v>46149.72674940973</v>
       </c>
       <c r="X155" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Printify_PrimaryFix_Needed</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -15128,6 +15128,14 @@
       </c>
       <c r="V156" s="1" t="n">
         <v>46148.85791638889</v>
+      </c>
+      <c r="W156" s="1" t="n">
+        <v>46149.73156060472</v>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
       </c>
       <c r="AD156" t="inlineStr">
         <is>
@@ -32735,6 +32743,134 @@
         </is>
       </c>
       <c r="AG296" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Acrylic-Zen-0001-FIX1</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Acrylic-Zen-0001-FIX1</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Smoky Jade Desk Object Mechanical Crane Calm Origami Sculpture 5x7 Acrylic Gift</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Smoky Jade Desk Object Mechanical Crane Calm Origami Sculpture 5x7 Acrylic Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Mechanical Crane Calm Origami Sculpture, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0001; Subject: Mechanical Crane Calm Origami Sculpture&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>$89.99</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Mechanical crane, origami sculpture, moonstone wings, jade clockwork, aquamarine crystals, zen cyberpunk, bioluminescent art, floating fragments, celestial mist, translucent depth, museum grade lighting</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Zen-0001_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Zen-0001_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Zen-0001_Ready_for_Steaming\Gallery_U1.png</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Zen-0001_Ready_for_Steaming\Gallery_U2.png</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Zen-0001_Ready_for_Steaming\Gallery_U3.png</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Zen-0001_Ready_for_Steaming\Gallery_U4.png</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>Printify_Published_Mockups4</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>2026-05-07 17:28:27 -0400</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>69fd040f6873b551670941bd</t>
+        </is>
+      </c>
+      <c r="R297" s="1" t="n">
+        <v>46149.73057622685</v>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>406911574121</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911574121</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V297" s="1" t="n">
+        <v>46149.73087425926</v>
+      </c>
+      <c r="AD297" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE297" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF297" t="inlineStr">
+        <is>
+          <t>Mechanical Crane Calm Origami Sculpture, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art</t>
+        </is>
+      </c>
+      <c r="AG297" t="inlineStr">
         <is>
           <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
         </is>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN297"/>
+  <dimension ref="A1:AN298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Printify_PrimaryFix_Needed</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -14520,6 +14520,14 @@
       </c>
       <c r="V151" s="1" t="n">
         <v>46148.85780189815</v>
+      </c>
+      <c r="W151" s="1" t="n">
+        <v>46149.74256543438</v>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -15130,7 +15138,7 @@
         <v>46148.85791638889</v>
       </c>
       <c r="W156" s="1" t="n">
-        <v>46149.73156060472</v>
+        <v>46149.73156060185</v>
       </c>
       <c r="X156" t="inlineStr">
         <is>
@@ -32874,6 +32882,133 @@
         <is>
           <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
         </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0001-FIX1</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0001-FIX1</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Celestial Gateway Dark Academia Poster 12x18 Study Decor Moonstone Architecture</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Step into the Astral Archive with this mentor-grade poster, a celestial gateway of moonstone and imperial jade rising before a floating library of ancient manuscripts. This 12x18 print captures the essence of dark academia, blending brass clockwork, ink-wash cosmos clouds, and bioluminescent glow for a timeless study companion.&lt;/p&gt;&lt;p&gt;Perfect for adorning your study desk, library wall, or reading nook, this poster transforms any space into a portal of temporal wisdom. The ultra-detailed moonstone crystalline texture and burnished brass accents evoke a vintage intellectual mood, ideal for book lovers and students seeking minimalist elegance.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster, ready to frame&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper, archival quality&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 inches by 18 inches&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia Mentor-Grade, dark academia aesthetic&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Celestial gateway, moonstone architecture, imperial jade portal, floating library, ancient manuscripts, brass clockwork, mystical knowledge, temporal wisdom, ethereal lighting, bioluminescent glow&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study room decor, library wall art, gift for scholars, vintage intellectual display&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>$34.99</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Celestial gateway, moonstone architecture, imperial jade portal, floating library, ancient manuscripts, brass clockwork, mystical knowledge, temporal wisdom, ethereal lighting, bioluminescent glow</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0001_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0001_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0001_Ready_for_Steaming\Gallery_U1.png</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0001_Ready_for_Steaming\Gallery_U2.png</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0001_Ready_for_Steaming\Gallery_U3.png</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0001_Ready_for_Steaming\Gallery_U4.png</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>Printify_Published</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>2026-05-07 17:36:44 -0400</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>69fd05fcd70cf705c50f4ef9</t>
+        </is>
+      </c>
+      <c r="R298" s="1" t="n">
+        <v>46149.74042334491</v>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>406911589289</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911589289</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V298" s="1" t="n">
+        <v>46149.7418525463</v>
+      </c>
+      <c r="Y298" s="1" t="n">
+        <v>46149.7418525463</v>
+      </c>
+      <c r="Z298" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406911589289 handle=https://www.ebay.com/itm/406911589289</t>
+        </is>
+      </c>
+      <c r="AC298" s="1" t="n">
+        <v>46149.7418525463</v>
       </c>
     </row>
   </sheetData>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN298"/>
+  <dimension ref="A1:AN299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14522,7 +14522,7 @@
         <v>46148.85780189815</v>
       </c>
       <c r="W151" s="1" t="n">
-        <v>46149.74256543438</v>
+        <v>46149.74256543982</v>
       </c>
       <c r="X151" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Printify_PrimaryFix_Needed</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -14763,6 +14763,14 @@
       </c>
       <c r="V153" s="1" t="n">
         <v>46148.8578553125</v>
+      </c>
+      <c r="W153" s="1" t="n">
+        <v>46149.74747569766</v>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
       </c>
       <c r="AD153" t="inlineStr">
         <is>
@@ -33009,6 +33017,153 @@
       </c>
       <c r="AC298" s="1" t="n">
         <v>46149.7418525463</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0003-FIX1</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0003-FIX1</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Reading Nook Wall Decor Serpentine Portal of Alchemical Texts 12x18 Matte Gift</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Reading Nook Wall Decor Serpentine Portal of Alchemical Texts 12x18 Matte Gift&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for quiet apartments, reading nooks, deep-work offices, study rooms, and gallery walls. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 premium matte vertical poster.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium matte paper wall art produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Serpentine Portal of Alchemical Texts, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0003; Subject: Serpentine Portal of Alchemical Texts&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>$34.99</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>A serpentine gateway crafted from iridescent moonstone and imperial jade standing before a levitating archive chamber, ancient leather volumes cascading through the portal vortex, nebulous ink-wash clouds merging with aged paper dust, floating brass talisman pieces with engraved hermetic symbols, cinematic chiaroscuro lighting with jade phosphorescence, dark academia aesthetic, ultra-detailed moonstone iridescence and brass gear mechanisms, hyper-detailed mentor-grade artifact design, primary material system: Moonstone, Imperial Jade, Ancient Calfskin, Burnished Brass, Ink-wash Nebula, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, full frame, cinematic lighting, edge-to-edge composition, immersive environment, --ar 9:16 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0003_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0003_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0003_Ready_for_Steaming\Gallery_U1.png</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0003_Ready_for_Steaming\Gallery_U2.png</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0003_Ready_for_Steaming\Gallery_U3.png</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Poster\Premium-Matte-Vertical\MASTER_Poster-Academia-0003_Ready_for_Steaming\Gallery_U4.png</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>Printify_Published</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>2026-05-07 17:51:09 -0400</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>69fd095c9f77031382026de2</t>
+        </is>
+      </c>
+      <c r="R299" s="1" t="n">
+        <v>46149.74574953704</v>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>406911598735</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911598735</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V299" s="1" t="n">
+        <v>46149.74666180556</v>
+      </c>
+      <c r="Y299" s="1" t="n">
+        <v>46149.74666180556</v>
+      </c>
+      <c r="Z299" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>FORCE_ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="AB299" t="inlineStr">
+        <is>
+          <t>Printify product external.id=406911598735 handle=https://www.ebay.com/itm/406911598735</t>
+        </is>
+      </c>
+      <c r="AC299" s="1" t="n">
+        <v>46149.74666180556</v>
+      </c>
+      <c r="AD299" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE299" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF299" t="inlineStr">
+        <is>
+          <t>Serpentine Portal of Alchemical Texts, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art</t>
+        </is>
+      </c>
+      <c r="AG299" t="inlineStr">
+        <is>
+          <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN299"/>
+  <dimension ref="A1:AN300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14765,7 +14765,7 @@
         <v>46148.8578553125</v>
       </c>
       <c r="W153" s="1" t="n">
-        <v>46149.74747569766</v>
+        <v>46149.74747569444</v>
       </c>
       <c r="X153" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Meditation Room Jade Relic Phoenix 5x7 Acrylic Block Shelf Decor Gift Study&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for tea room accent. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; reading nook decor, meditation room wall art, tea room accent, quiet corner decor, dorm desk calm art, deep work visual.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0006. Prior title: Meditation Room Jade Relic Jade Phoenix Incense Altar for 5x7 Acrylic Block&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Meditation Room Jade Relic Phoenix 5x7 Acrylic Block Shelf Decor Gift Study&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for tea room accent. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; reading nook decor, meditation room wall art, tea room accent, quiet corner decor, dorm desk calm art, deep work visual.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0006. Prior title: Meditation Room Jade Relic Phoenix 5x7 Acrylic Block Shelf Decor Gift Study&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>2026-05-07 02:48:12 -0400</t>
+          <t>2026-05-07 18:03:52 -0400</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Meditation Room Jade Relic Quiet Luxury 5x7 Acrylic Block Shelf Decor Gift Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for meditation room wall art. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; reading nook decor, meditation room wall art, tea room accent, quiet corner decor, dorm desk calm art, deep work visual.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0007. Prior title: Meditation Room Jade Relic Quiet Luxury Sacred Lotus Meditation 5x7 Acrylic&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Meditation Room Jade Relic Quiet Luxury 5x7 Acrylic Block Shelf Decor Gift Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for meditation room wall art. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; reading nook decor, meditation room wall art, tea room accent, quiet corner decor, dorm desk calm art, deep work visual.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0007. Prior title: Meditation Room Jade Relic Quiet Luxury 5x7 Acrylic Block Shelf Decor Gift Wall&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -17372,7 +17372,7 @@
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>2026-05-07 02:48:12 -0400</t>
+          <t>2026-05-07 18:03:52 -0400</t>
         </is>
       </c>
       <c r="AL174" t="inlineStr">
@@ -17959,7 +17959,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Dark Study Smoky Jade Alchemist Divination Compass 5x7 Acrylic Block Shelf Gift&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for dark study room decor. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0085. Prior title: Dark Study Smoky Jade Alchemist Divination Compass Occult 5x7 Acrylic Block&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Dark Study Smoky Jade Alchemist Divination Compass 5x7 Acrylic Block Shelf Gift&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for dark study room decor. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0085. Prior title: Dark Study Smoky Jade Alchemist Divination Compass 5x7 Acrylic Block Shelf Gift&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="AK179" t="inlineStr">
         <is>
-          <t>2026-05-07 02:48:12 -0400</t>
+          <t>2026-05-07 18:03:52 -0400</t>
         </is>
       </c>
       <c r="AL179" t="inlineStr">
@@ -20799,7 +20799,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Quiet Luxury Jade Relic Soulbound 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for smoky jade relic. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0014. Prior title: Quiet Luxury Jade Relic Soulbound Harbinger Torch Lantern Print 5x7 Acrylic&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Jade Relic Soulbound 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for smoky jade relic. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0014. Prior title: Quiet Luxury Jade Relic Soulbound 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -20901,7 +20901,7 @@
       </c>
       <c r="AK201" t="inlineStr">
         <is>
-          <t>2026-05-07 02:48:12 -0400</t>
+          <t>2026-05-07 18:03:52 -0400</t>
         </is>
       </c>
       <c r="AL201" t="inlineStr">
@@ -21469,7 +21469,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Quiet Luxury Jade Relic Abyssal 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for moody desk display. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0019. Prior title: Quiet Luxury Jade Relic Abyssal Watcher Eternal Eye Spirit 5x7 Acrylic Block&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Jade Relic Abyssal 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for moody desk display. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0019. Prior title: Quiet Luxury Jade Relic Abyssal 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -21571,7 +21571,7 @@
       </c>
       <c r="AK206" t="inlineStr">
         <is>
-          <t>2026-05-07 02:48:12 -0400</t>
+          <t>2026-05-07 18:03:52 -0400</t>
         </is>
       </c>
       <c r="AL206" t="inlineStr">
@@ -22362,7 +22362,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Quiet Luxury Jade Relic Magenta 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for occult library art. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0027. Prior title: Quiet Luxury Jade Relic Magenta Malice Lantern Fantasy 5x7 Acrylic Block Desk&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Jade Relic Magenta 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for occult library art. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0027. Prior title: Quiet Luxury Jade Relic Magenta 5x7 Acrylic Block Shelf Decor Gift Study Wall&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -22459,12 +22459,12 @@
       </c>
       <c r="AH213" t="inlineStr">
         <is>
-          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+          <t>MULTI_TRACK_PENDING_PRINTIFY_SYNC</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
         <is>
-          <t>2026-05-07 02:48:12 -0400</t>
+          <t>2026-05-07 18:03:52 -0400</t>
         </is>
       </c>
       <c r="AL213" t="inlineStr">
@@ -23057,7 +23057,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Dark Study Smoky Jade Ethereal Archway Soul 5x7 Acrylic Block Shelf Decor Gift&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for dark study room decor. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0033. Prior title: Dark Study Smoky Jade Ethereal Archway Soul Lantern Artifact 5x7 Acrylic Block&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Dark Study Smoky Jade Ethereal Archway Soul 5x7 Acrylic Block Shelf Decor Gift&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for dark study room decor. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0033. Prior title: Dark Study Smoky Jade Ethereal Archway Soul 5x7 Acrylic Block Shelf Decor Gift&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -23154,12 +23154,12 @@
       </c>
       <c r="AH218" t="inlineStr">
         <is>
-          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+          <t>MULTI_TRACK_PENDING_PRINTIFY_SYNC</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>2026-05-07 02:48:12 -0400</t>
+          <t>2026-05-07 18:03:52 -0400</t>
         </is>
       </c>
       <c r="AL218" t="inlineStr">
@@ -23727,7 +23727,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Collector Shelf Smoky Jade Quiet Luxury 5x7 Acrylic Block Shelf Decor Gift Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for collector shelf object. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0038. Prior title: Collector Shelf Smoky Jade Quiet Luxury Relic Rose Quartz 5x7 Acrylic Block&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Collector Shelf Smoky Jade Quiet Luxury 5x7 Acrylic Block Shelf Decor Gift Wall&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for collector shelf object. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0038. Prior title: Collector Shelf Smoky Jade Quiet Luxury 5x7 Acrylic Block Shelf Decor Gift Wall&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -23808,7 +23808,7 @@
       </c>
       <c r="AH223" t="inlineStr">
         <is>
-          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+          <t>MULTI_TRACK_PENDING_PRINTIFY_SYNC</t>
         </is>
       </c>
       <c r="AI223" t="inlineStr">
@@ -23823,7 +23823,7 @@
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>2026-05-07 02:48:12 -0400</t>
+          <t>2026-05-07 18:03:52 -0400</t>
         </is>
       </c>
       <c r="AL223" t="inlineStr">
@@ -24260,7 +24260,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Reading Nook Smoky Jade Wall Art Archivist 12x18 Matte Poster Apartment Decor&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for dark academia reading nook. It is written for buyers decorating reading nooks, home libraries, dorm study walls, meditation rooms, and quiet apartment corners, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 matte poster, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; matte paper mood, cinematic depth, smoky jade tones, and calm visual focus.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; dark academia reading nook, home library wall art, book nook decor, study room poster, scholar desk decor, dorm library print.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed poster. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0019. Prior title: Reading Nook Smoky Jade Wall Art Archivist Gateway Vintage 12x18 Matte Poster&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Reading Nook Smoky Jade Wall Art Archivist 12x18 Matte Poster Apartment Decor&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for dark academia reading nook. It is written for buyers decorating reading nooks, home libraries, dorm study walls, meditation rooms, and quiet apartment corners, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 matte poster, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; matte paper mood, cinematic depth, smoky jade tones, and calm visual focus.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; dark academia reading nook, home library wall art, book nook decor, study room poster, scholar desk decor, dorm library print.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed poster. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0019. Prior title: Reading Nook Smoky Jade Wall Art Archivist 12x18 Matte Poster Apartment Decor&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -24357,12 +24357,12 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+          <t>MULTI_TRACK_PENDING_PRINTIFY_SYNC</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>2026-05-07 02:48:12 -0400</t>
+          <t>2026-05-07 18:03:52 -0400</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
@@ -29310,7 +29310,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Reading Nook Smoky Jade Wall Art Mechanical 12x18 Matte Poster Apartment Decor&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for dark academia reading nook. It is written for buyers decorating reading nooks, home libraries, dorm study walls, meditation rooms, and quiet apartment corners, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 matte poster, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; matte paper mood, cinematic depth, smoky jade tones, and calm visual focus.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; dark academia reading nook, home library wall art, book nook decor, study room poster, scholar desk decor, dorm library print.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed poster. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0036. Prior title: Reading Nook Smoky Jade Wall Art Mechanical Encyclopedia Sphere 12x18 Matte&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Reading Nook Smoky Jade Wall Art Mechanical 12x18 Matte Poster Apartment Decor&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for dark academia reading nook. It is written for buyers decorating reading nooks, home libraries, dorm study walls, meditation rooms, and quiet apartment corners, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 matte poster, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; matte paper mood, cinematic depth, smoky jade tones, and calm visual focus.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; dark academia reading nook, home library wall art, book nook decor, study room poster, scholar desk decor, dorm library print.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed poster. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0036. Prior title: Reading Nook Smoky Jade Wall Art Mechanical 12x18 Matte Poster Apartment Decor&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -29407,12 +29407,12 @@
       </c>
       <c r="AH268" t="inlineStr">
         <is>
-          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+          <t>MULTI_TRACK_PENDING_PRINTIFY_SYNC</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
         <is>
-          <t>2026-05-07 02:48:12 -0400</t>
+          <t>2026-05-07 18:03:52 -0400</t>
         </is>
       </c>
       <c r="AL268" t="inlineStr">
@@ -33163,6 +33163,142 @@
       <c r="AG299" t="inlineStr">
         <is>
           <t>Poster value-pivot target $34.99; above cost+shipping+fees guardrail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Acrylic-Academia-0003-GALLERYFIX1</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Acrylic-Academia-0003-GALLERYFIX1</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Quiet Luxury Shelf Decor Celestial Orrery Tree Bonsai 5x7 Acrylic Photo Block</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Quiet Luxury Shelf Decor Celestial Orrery Tree Bonsai 5x7 Acrylic Photo Block&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Academia collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Celestial Orrery Tree Bonsai, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Academia-0003; Subject: Celestial Orrery Tree Bonsai&lt;/small&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>$89.99</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Moonstone trunk, Imperial Jade planets, ink-wash nebula, crystalline soil, floating talisman fragments, bioluminescent leaves, micro-engraved surface relief</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Academia-0003_Ready_for_Steaming\Production_Design.png</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Academia-0003_Ready_for_Steaming\Cover_Mockup.png</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Academia-0003_Ready_for_Steaming\Gallery_U1.png</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Academia-0003_Ready_for_Steaming\Gallery_U2.png</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Academia-0003_Ready_for_Steaming\Gallery_U3.png</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>C:\AIprojects\openclaw_difi\Output\Acrylic\Photo-Block\MASTER_Acrylic-Academia-0003_Ready_for_Steaming\Gallery_U4.png</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>Retired_Replaced</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>2026-05-07 21:04:34 -0400</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>69fd36d2a4235c1793034b29</t>
+        </is>
+      </c>
+      <c r="R300" s="1" t="n">
+        <v>46149.8827790625</v>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>406911883288</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911883288</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V300" s="1" t="n">
+        <v>46149.88308030093</v>
+      </c>
+      <c r="W300" s="1" t="n">
+        <v>46149.90281554782</v>
+      </c>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
+        </is>
+      </c>
+      <c r="AD300" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:46:18 -0400</t>
+        </is>
+      </c>
+      <c r="AE300" t="inlineStr">
+        <is>
+          <t>Operation Quiet Jade</t>
+        </is>
+      </c>
+      <c r="AF300" t="inlineStr">
+        <is>
+          <t>Celestial Orrery Tree Bonsai, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Dark Study Decor, Library Wall Art</t>
+        </is>
+      </c>
+      <c r="AG300" t="inlineStr">
+        <is>
+          <t>Acrylic kept premium; $29.99-$34.99 would violate cost+shipping guardrail.</t>
         </is>
       </c>
     </row>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -7909,7 +7909,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups5</t>
+          <t>Printify_Published_Mockups5</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -7921,6 +7921,27 @@
         <is>
           <t>69f26281feceb0d66c042ce7</t>
         </is>
+      </c>
+      <c r="R73" s="1" t="n">
+        <v>46149.90896847222</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>406911942577</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911942577</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V73" s="1" t="n">
+        <v>46149.90897497685</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -8011,7 +8032,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups5</t>
+          <t>Printify_Published_Mockups5</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8023,6 +8044,27 @@
         <is>
           <t>69f262db5269e3325904b893</t>
         </is>
+      </c>
+      <c r="R74" s="1" t="n">
+        <v>46149.91137163734</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>406911955913</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911955913</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V74" s="1" t="n">
+        <v>46149.91138125821</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -8113,7 +8155,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups5</t>
+          <t>Printify_Published_Mockups5</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8125,6 +8167,27 @@
         <is>
           <t>69f263729b469f716d0e7409</t>
         </is>
+      </c>
+      <c r="R75" s="1" t="n">
+        <v>46149.91389873351</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>406911953636</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406911953636</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V75" s="1" t="n">
+        <v>46149.91390609904</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -33274,7 +33337,7 @@
         <v>46149.88308030093</v>
       </c>
       <c r="W300" s="1" t="n">
-        <v>46149.90281554782</v>
+        <v>46149.90281554398</v>
       </c>
       <c r="X300" t="inlineStr">
         <is>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN300"/>
+  <dimension ref="A1:AO300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -620,6 +620,11 @@
           <t>Multi_Track_Mockup_Mood</t>
         </is>
       </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>QA_Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8046,7 +8051,7 @@
         </is>
       </c>
       <c r="R74" s="1" t="n">
-        <v>46149.91137163734</v>
+        <v>46149.91137163195</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -8064,7 +8069,7 @@
         </is>
       </c>
       <c r="V74" s="1" t="n">
-        <v>46149.91138125821</v>
+        <v>46149.91138126158</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -8169,7 +8174,7 @@
         </is>
       </c>
       <c r="R75" s="1" t="n">
-        <v>46149.91389873351</v>
+        <v>46149.91389873843</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -8187,7 +8192,7 @@
         </is>
       </c>
       <c r="V75" s="1" t="n">
-        <v>46149.91390609904</v>
+        <v>46149.91390609954</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -8278,13 +8283,11 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups5</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>4/29/2026  1:28:54 PM</t>
-        </is>
+          <t>Printify_StickerMixedGallery_Hold</t>
+        </is>
+      </c>
+      <c r="P76" s="1" t="n">
+        <v>46149.94308292386</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -8304,6 +8307,11 @@
       <c r="AJ76" t="inlineStr">
         <is>
           <t>B_BOOK_NOOK_LAPTOP_DECALS</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Cover-only mixed gallery probe failed API verification: Printify still selected 5 custom gallery images, no official mockups. Do not publish until mixed Cover + official mockup path is fixed.</t>
         </is>
       </c>
     </row>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -8283,17 +8283,38 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Printify_StickerMixedGallery_Hold</t>
+          <t>Printify_Published_Mockups4</t>
         </is>
       </c>
       <c r="P76" s="1" t="n">
-        <v>46149.94308292386</v>
+        <v>46149.9474558912</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
           <t>69f26426671cc7c7960b3f3d</t>
         </is>
       </c>
+      <c r="R76" s="1" t="n">
+        <v>46149.94883718868</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>406912077790</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406912077790</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V76" s="1" t="n">
+        <v>46149.94917833775</v>
+      </c>
       <c r="AH76" t="inlineStr">
         <is>
           <t>SEO_STRIKE_SYNCED_PRINTIFY_DRAFT</t>
@@ -8311,7 +8332,7 @@
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Cover-only mixed gallery probe failed API verification: Printify still selected 5 custom gallery images, no official mockups. Do not publish until mixed Cover + official mockup path is fixed.</t>
+          <t>Sticker mixed gallery verified by Printify API: 3 official mockups + 1 custom cover, selected=4, unique=4. Publish only after dry-run and post-publish live gallery audit.</t>
         </is>
       </c>
     </row>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="R76" s="1" t="n">
-        <v>46149.94883718868</v>
+        <v>46149.9488371875</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="V76" s="1" t="n">
-        <v>46149.94917833775</v>
+        <v>46149.94917833334</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -8409,13 +8409,11 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups5</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>4/29/2026  1:28:54 PM</t>
-        </is>
+          <t>Printify_StickerMixedGallery_Hold</t>
+        </is>
+      </c>
+      <c r="P77" s="1" t="n">
+        <v>46149.95420189814</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -8435,6 +8433,11 @@
       <c r="AJ77" t="inlineStr">
         <is>
           <t>A_DEEP_WORK_STICKER_SET</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Mixed gallery selector over-selected custom images: API showed 3 official + 4 custom. Publish scheduler blocked. Retry only after selector is hardened.</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8760,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups5</t>
+          <t>Retired_Replaced</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8768,6 +8771,35 @@
       <c r="Q81" t="inlineStr">
         <is>
           <t>69f26782c326d7da170c1498</t>
+        </is>
+      </c>
+      <c r="R81" s="1" t="n">
+        <v>46149.95453435185</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>406912094146</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/406912094146</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V81" s="1" t="n">
+        <v>46149.95484488426</v>
+      </c>
+      <c r="W81" s="1" t="n">
+        <v>46149.95751690179</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>ENDED_CONFIRMED_SELLER_HUB; Seller Hub success banner detected.; printify_external_detached</t>
         </is>
       </c>
       <c r="AH81" t="inlineStr">

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -8795,7 +8795,7 @@
         <v>46149.95484488426</v>
       </c>
       <c r="W81" s="1" t="n">
-        <v>46149.95751690179</v>
+        <v>46149.95751689815</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8973,19 +8973,16 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups5</t>
+          <t>Ready_for_Printify</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>4/29/2026  1:28:54 PM</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>69f2683ecaeb1241880b7fcb</t>
-        </is>
-      </c>
+          <t>5/7/2026  11:50:52 PM</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
       <c r="AH83" t="inlineStr">
         <is>
           <t>SEO_STRIKE_SYNCED_PRINTIFY_DRAFT</t>

--- a/Database/eBay_listing.xlsx
+++ b/Database/eBay_listing.xlsx
@@ -2805,7 +2805,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups4</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P76" s="1" t="n">
@@ -8981,8 +8981,6 @@
           <t>5/7/2026  11:50:52 PM</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
       <c r="AH83" t="inlineStr">
         <is>
           <t>SEO_STRIKE_SYNCED_PRINTIFY_DRAFT</t>
@@ -9072,7 +9070,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9241,7 +9239,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9328,7 +9326,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9415,7 +9413,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9502,7 +9500,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -9671,7 +9669,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -9758,7 +9756,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -9845,7 +9843,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -9932,7 +9930,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Printify_UI_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -14724,7 +14722,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Printify_Published_Mockups5</t>
+          <t>Printify_PrimaryFix_Needed</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -16053,12 +16051,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Deep Work Desk Visual Pagoda Fragment Relic Print Floating 5x7 Acrylic Photo</t>
+          <t>Meditation Room Jade Relic Deep Work Visual Pagoda 5x7 Acrylic Block Shelf Gift</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Deep Work Desk Visual Pagoda Fragment Relic Print Floating 5x7 Acrylic Photo&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Pagoda Fragment Relic Print Floating, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0003; Subject: Pagoda Fragment Relic Print Floating&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Meditation Room Jade Relic Deep Work Visual Pagoda 5x7 Acrylic Block Shelf Gift&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for reading nook decor. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; reading nook decor, meditation room wall art, tea room accent, quiet corner decor, dorm desk calm art, deep work visual.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0003. Prior title: Deep Work Desk Visual Pagoda Fragment Relic Print Floating 5x7 Acrylic Photo&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -16156,7 +16154,27 @@
       </c>
       <c r="AH163" t="inlineStr">
         <is>
-          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>2026-05-08 08:17:21 -0400</t>
+        </is>
+      </c>
+      <c r="AL163" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>reading nook decor</t>
+        </is>
+      </c>
+      <c r="AN163" t="inlineStr">
+        <is>
+          <t>reading_nook_warm_lamp</t>
         </is>
       </c>
     </row>
@@ -16783,12 +16801,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Gallery Desk Art Incense Vessel Constellation for Meditation 5x7 Acrylic Photo</t>
+          <t>Meditation Room Jade Relic Incense Vessel Constellation 5x7 Acrylic Block Decor</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Gallery Desk Art Incense Vessel Constellation for Meditation 5x7 Acrylic Photo&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Zen collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Incense Vessel Constellation for Meditat, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Meditation Decor, Calm Desk Art&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0005; Subject: Incense Vessel Constellation for Meditation&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Meditation Room Jade Relic Incense Vessel Constellation 5x7 Acrylic Block Decor&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for tea room accent. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; reading nook decor, meditation room wall art, tea room accent, quiet corner decor, dorm desk calm art, deep work visual.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Zen-0005. Prior title: Gallery Desk Art Incense Vessel Constellation for Meditation 5x7 Acrylic Photo&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -16886,7 +16904,27 @@
       </c>
       <c r="AH169" t="inlineStr">
         <is>
-          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>2026-05-08 08:17:21 -0400</t>
+        </is>
+      </c>
+      <c r="AL169" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>tea room accent</t>
+        </is>
+      </c>
+      <c r="AN169" t="inlineStr">
+        <is>
+          <t>reading_nook_warm_lamp</t>
         </is>
       </c>
     </row>
@@ -18485,12 +18523,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Deep Work Desk Visual Lantern Soul Cage Crimson Flame 5x7 Acrylic Photo Block</t>
+          <t>Dark Study Smoky Jade Deep Work Visual Lantern 5x7 Acrylic Block Shelf Decor</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Deep Work Desk Visual Lantern Soul Cage Crimson Flame 5x7 Acrylic Photo Block&lt;/h2&gt;&lt;p&gt;A Quiet Jade collection piece built for desks, bookshelves, altar corners, office focus spaces, and collector displays. The visual direction leans into smoky jade tones, quiet luxury decor language, kintsugi detail, and deep-work atmosphere instead of generic mass-market wall art.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Acrylic block display with depth, gloss, and light-reflective finish.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark collector aesthetic; smoky jade, wabi-sabi, scholar-room mood.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Best For:&lt;/strong&gt; apartment decor, reading nook styling, focused workspaces, collectors, and giftable room accents.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the physical product customers receive. Additional gallery images are concept, detail, or collection-reference views and are not extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Search Themes:&lt;/strong&gt; Lantern Soul Cage Crimson Flame, Smoky Jade, Quiet Luxury Decor, Deep Work Visuals, Reading Nook Decor, Wabi Sabi Decor, Scholar Room, Apartment Decor, Jade Art, Kintsugi Aesthetic, Collector Gift, Gothic Study Decor, Alchemy Decor&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0001; Subject: Lantern Soul Cage Crimson Flame&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Dark Study Smoky Jade Deep Work Visual Lantern 5x7 Acrylic Block Shelf Decor&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for dark study room decor. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0001. Prior title: Deep Work Desk Visual Lantern Soul Cage Crimson Flame 5x7 Acrylic Photo Block&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -18588,7 +18626,27 @@
       </c>
       <c r="AH182" t="inlineStr">
         <is>
-          <t>QUIET_JADE_SYNCED_PRINTIFY_PUBLISH</t>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>2026-05-08 08:17:21 -0400</t>
+        </is>
+      </c>
+      <c r="AL182" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>dark study room decor</t>
+        </is>
+      </c>
+      <c r="AN182" t="inlineStr">
+        <is>
+          <t>reading_nook_warm_lamp</t>
         </is>
       </c>
     </row>
@@ -19235,12 +19293,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Gothic Grimdark Lich Phylactery Lantern 5x7 Acrylic Print Dark Fantasy Home</t>
+          <t>Quiet Luxury Jade Relic Lich Phylactery Lantern Fantasy 5x7 Acrylic Block Decor</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This 5x7 acrylic print captures the haunting beauty of a Lich's Phylactery Lantern, a grimdark artifact forged from wrought iron and ghostly topaz glass. The amber spirit flame swirls within, casting a bioluminescent glow through cracked refractive layers. A premium collectible for dark fantasy enthusiasts, it brings an aura of ancient magic and undead lore to any space.&lt;/p&gt;&lt;p&gt;Display this piece on a study desk, bookshelf, or altar to evoke the mood of a gothic ritual chamber. The high-contrast shadows and bone inlay details reward close inspection, while the museum-grade finish ensures lasting vibrancy. Ideal for fans of grimdark art, necromancer aesthetics, or dark academia decor.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic print, ready to hang or stand&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-gloss acrylic with UV-resistant ink&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade, gothic artifact&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Wrought iron, ghostly topaz glass, amber spirit flame, gothic filigree, bone inlay, refractive depth, bioluminescent light, micro-engraved surface relief, handcrafted edge bevels, layered translucent depth, subtle internal glow, kintsugi-like vein logic, floating accent fragments, cinematic rim lighting, soft museum-grade overhead fill&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Dark fantasy home decor, gothic study accent, collector display, Halloween ambiance, occult-themed room, gift for grimdark fans&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Jade Relic Lich Phylactery Lantern Fantasy 5x7 Acrylic Block Decor&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for moody desk display. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0009. Prior title: Gothic Grimdark Lich Phylactery Lantern 5x7 Acrylic Print Dark Fantasy Home&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -19315,6 +19373,31 @@
       </c>
       <c r="V188" s="1" t="n">
         <v>46148.85851284722</v>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>2026-05-08 08:17:21 -0400</t>
+        </is>
+      </c>
+      <c r="AL188" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM188" t="inlineStr">
+        <is>
+          <t>moody desk display</t>
+        </is>
+      </c>
+      <c r="AN188" t="inlineStr">
+        <is>
+          <t>quiet_luxury_apartment</t>
+        </is>
       </c>
     </row>
     <row r="189">
@@ -21337,12 +21420,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Grimdark Aesthetic Dreadlord Beacon Lantern 5x7 Acrylic Block Dark Decor Shelf</t>
+          <t>Collector Shelf Smoky Jade Dreadlord Beacon Lantern 5x7 Acrylic Block Shelf</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This Dreadlord's Dominion Beacon acrylic block captures a grimdark mentor-grade artifact in miniature form. The ornate wrought-iron lantern with demonic horns encloses a trapped scarlet spirit flame, its light refracting through cracked ghostly garnet glass. A perfect accent for a gothic study, altar shelf, or collector's cabinet.&lt;/p&gt;&lt;p&gt;Display this 5x7 block on a desk, bookshelf, or mantel to evoke a dark fantasy atmosphere. The high-contrast macro photography and cinematic rim lighting bring out the bioluminescent core and refined kintsugi-like vein logic. Use it as a paperweight, a decorative object, or a conversation starter for fans of grimdark lore.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic block print&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium clear acrylic with UV-cured print&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Wrought iron, ghostly garnet glass, scarlet spirit flame, gothic filigree, micro-engraved surface relief, layered translucent depth, internal bioluminescent glow&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Gothic decor, dark fantasy collection, study shelf accent, altar display, gift for grimdark enthusiasts&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Collector Shelf Smoky Jade Dreadlord Beacon Lantern 5x7 Acrylic Block Shelf&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for gothic shelf decor. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0017. Prior title: Grimdark Aesthetic Dreadlord Beacon Lantern 5x7 Acrylic Block Dark Decor Shelf&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -21436,6 +21519,31 @@
       </c>
       <c r="AC204" s="1" t="n">
         <v>46149.07898653935</v>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>2026-05-08 08:17:21 -0400</t>
+        </is>
+      </c>
+      <c r="AL204" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>gothic shelf decor</t>
+        </is>
+      </c>
+      <c r="AN204" t="inlineStr">
+        <is>
+          <t>quiet_luxury_apartment</t>
+        </is>
       </c>
     </row>
     <row r="205">
@@ -21858,12 +21966,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Violet Torment Lantern 5x7 Acrylic Grimdark Gothic Decor for Dark Fantasy Study</t>
+          <t>Dark Study Smoky Jade Violet Torment Lantern Fantasy 5x7 Acrylic Block Shelf</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This 5x7 acrylic print presents the Violet Torment Lantern, a grimdark artifact forged from blackened wrought iron with razor-sharp filigree and a violent violet spirit flame. The amethyst-tinted glass and internal bioluminescent glow create a corrupted, collector-grade aesthetic perfect for dark fantasy enthusiasts.&lt;/p&gt;&lt;p&gt;Ideal for a study desk, bookshelf, or gothic decor collection, this premium acrylic piece captures the translucent depth and oxidized iron details of the original design. The high-gloss surface and crisp silhouette ensure the lantern becomes a focal point in any room, from a minimalist workspace to a vintage-inspired library.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic print, ready to display (stand not included)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium acrylic with high-gloss finish, UV-resistant ink&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade with violet spirit flame, blackened iron filigree, and layered translucent depth&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Violet flame, amethyst gothic, corrupted spirit vessel, blackened iron filigree, dark fantasy artifact, grimdark collectible, translucent depth, premium lantern design, wrought iron craftsmanship, bioluminescent accent&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Dark fantasy study decor, gothic bookshelf accent, collector gift for grimdark fans, vintage intellectual desk piece, minimalist room focal point&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Dark Study Smoky Jade Violet Torment Lantern Fantasy 5x7 Acrylic Block Shelf&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for dark study room decor. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0022. Prior title: Violet Torment Lantern 5x7 Acrylic Grimdark Gothic Decor for Dark Fantasy Study&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -21957,6 +22065,31 @@
       </c>
       <c r="AC208" s="1" t="n">
         <v>46149.079038125</v>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>2026-05-08 08:17:21 -0400</t>
+        </is>
+      </c>
+      <c r="AL208" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>dark study room decor</t>
+        </is>
+      </c>
+      <c r="AN208" t="inlineStr">
+        <is>
+          <t>quiet_luxury_apartment</t>
+        </is>
       </c>
     </row>
     <row r="209">
@@ -22580,7 +22713,7 @@
       </c>
       <c r="AH213" t="inlineStr">
         <is>
-          <t>MULTI_TRACK_PENDING_PRINTIFY_SYNC</t>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -22900,17 +23033,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Collector Shelf Smoky Jade Midnight Sanctuary 5x7 Acrylic Block Shelf Decor</t>
+          <t>Quiet Luxury Jade Relic Collector Smoky Midnight Sanctuary 5x7 Acrylic Block</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Collector Shelf Smoky Jade Midnight Sanctuary 5x7 Acrylic Block Shelf Decor&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for collector gift. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; acrylic photo block, desk display, shelf decor, collector gift, office decor, quiet jade, premium aesthetic, giftable decor.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0031. Prior title: Collector Shelf Smoky Jade Midnight Sanctuary 5x7 Acrylic Block Shelf Decor&lt;/small&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Jade Relic Collector Smoky Midnight Sanctuary 5x7 Acrylic Block&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for smoky jade relic. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0031. Prior title: Collector Shelf Smoky Jade Midnight Sanctuary 5x7 Acrylic Block Shelf Decor&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>$84.99</t>
+          <t>$89.99</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -23007,17 +23140,17 @@
       </c>
       <c r="AK216" t="inlineStr">
         <is>
-          <t>2026-05-07 07:37:28 -0400</t>
+          <t>2026-05-08 08:17:21 -0400</t>
         </is>
       </c>
       <c r="AL216" t="inlineStr">
         <is>
-          <t>B_HIGH_VOLUME_VALUE</t>
+          <t>A_LOW_COMPETITION_NICHE</t>
         </is>
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>collector gift</t>
+          <t>smoky jade relic</t>
         </is>
       </c>
       <c r="AN216" t="inlineStr">
@@ -23049,12 +23182,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Grimdark Amber Monastery Soul Lantern 5x7 Acrylic Art Gothic Decor Golden Flame</t>
+          <t>Collector Shelf Smoky Jade Amber Monastery Soul Lantern 5x7 Acrylic Block Decor</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This Grimdark Mentor-Grade acrylic print captures the Amber Monastery Soul Lantern, an ethereal gothic artifact with a wrought iron monastery gate frame and swirling golden-orange spirit flame. The design features amber crystal inlays, floating talisman fragments, and ink-wash nebula patterns on imperial jade glass panels, all glowing with a soft amber luminescence. A refined kintsugi-like vein logic and micro-engraved surface relief create a hyper-detailed, high-end collectible aesthetic.&lt;/p&gt;&lt;p&gt;Printed on premium 5x7 acrylic, this piece delivers luminous depth and refractive light, making it ideal for a study desk, bookshelf, or dark academia-inspired wall display. The high-gloss surface and edge bevels enhance the visual impact, while the white background isolation ensures the artifact stands out in any room.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic print, ready to hang or display on a stand (stand not included)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; High-gloss acrylic with UV-resistant inks&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade, gothic collectible&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Wrought Iron, Amber Crystal, Imperial Jade Glass, Talisman Fragments, Golden-Orange Flame&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Gothic decor, study desk accent, collector display, gift for dark fantasy enthusiasts&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Collector Shelf Smoky Jade Amber Monastery Soul Lantern 5x7 Acrylic Block Decor&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for collector shelf object. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0032. Prior title: Grimdark Amber Monastery Soul Lantern 5x7 Acrylic Art Gothic Decor Golden Flame&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -23148,6 +23281,31 @@
       </c>
       <c r="AC217" s="1" t="n">
         <v>46149.07914980324</v>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>2026-05-08 08:17:21 -0400</t>
+        </is>
+      </c>
+      <c r="AL217" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr">
+        <is>
+          <t>collector shelf object</t>
+        </is>
+      </c>
+      <c r="AN217" t="inlineStr">
+        <is>
+          <t>reading_nook_warm_lamp</t>
+        </is>
       </c>
     </row>
     <row r="218">
@@ -23275,7 +23433,7 @@
       </c>
       <c r="AH218" t="inlineStr">
         <is>
-          <t>MULTI_TRACK_PENDING_PRINTIFY_SYNC</t>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -23595,12 +23753,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Gothic Frost Cathedral Soul Lantern 5x7 Acrylic Display Grimdark Artifact Shelf</t>
+          <t>Quiet Luxury Jade Relic Frost Cathedral Soul Lantern 5x7 Acrylic Block Shelf</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This 5x7 acrylic print presents the &lt;strong&gt;Frost Cathedral Soul Lantern&lt;/strong&gt;, a gothic artifact that captures the grimdark mentor-grade aesthetic. The design features an ethereal lantern with a wrought-iron cathedral gate frame, aquamarine inlays, and an ice-blue spirit flame surrounded by floating talisman fragments. Ink-wash nebula patterns on imperial jade glass panels create a soft frost glow, evoking a sense of ancient mystery and refined darkness.&lt;/p&gt;&lt;p&gt;Perfect for display on a study desk, bookshelf, or altar, this acrylic piece brings a moody, collector-focused presence to any space. The high-gloss surface and edge-to-edge printing enhance the layered depth and internal bioluminescent glow, making it a standout addition to a gothic or dark academia interior.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 acrylic print with pre-installed hanging hardware (stand not included)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium acrylic with UV-resistant inks&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 5x7 inches (12.7 x 17.8 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Grimdark Mentor-Grade&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Frost soul lantern, cathedral gate, aquamarine crystal, ice-blue flame, jade glass, wrought iron, talisman fragments, gothic artifact&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study desk decor, gothic altar piece, dark academia wall art, collector display, mentor-grade gift&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: &lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Quiet Luxury Jade Relic Frost Cathedral Soul Lantern 5x7 Acrylic Block Shelf&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for occult library art. It is written for buyers decorating quiet shelves, meditation corners, gothic study desks, collector rooms, and deep-work apartments, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 5x7 vertical acrylic photo block, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Quiet Luxury Apartment.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; refractive depth, smoky jade color, internal glow, and premium desk-object presence.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; gothic shelf decor, moody desk display, occult library art, dark study room decor, collector shelf object, smoky jade relic.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed acrylic display block. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Acrylic-Grimdark-0036. Prior title: Gothic Frost Cathedral Soul Lantern 5x7 Acrylic Display Grimdark Artifact Shelf&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -23694,6 +23852,31 @@
       </c>
       <c r="AC221" s="1" t="n">
         <v>46149.07919978009</v>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>2026-05-08 08:17:21 -0400</t>
+        </is>
+      </c>
+      <c r="AL221" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr">
+        <is>
+          <t>occult library art</t>
+        </is>
+      </c>
+      <c r="AN221" t="inlineStr">
+        <is>
+          <t>quiet_luxury_apartment</t>
+        </is>
       </c>
     </row>
     <row r="222">
@@ -23929,7 +24112,7 @@
       </c>
       <c r="AH223" t="inlineStr">
         <is>
-          <t>MULTI_TRACK_PENDING_PRINTIFY_SYNC</t>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
         </is>
       </c>
       <c r="AI223" t="inlineStr">
@@ -24478,7 +24661,7 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>MULTI_TRACK_PENDING_PRINTIFY_SYNC</t>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -24897,12 +25080,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Hermetic Knowledge Lantern Dark Academia Poster 12x18 Library Decor Wall Study</t>
+          <t>Dark Academia Reading Nook Art Hermetic Knowledge Lantern Library 12x18 Matte</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Elevate your study or library with the Hermetic Knowledge Lantern, a dark academia poster that channels the mystique of alchemical discovery. This mentor-grade design features a corroded copper vessel with cracked glass panels, kintsugi gold seams, and toxic jade bioluminescence, capturing the essence of ancient hermetic texts in cinematic light.&lt;/p&gt;&lt;p&gt;Printed on premium semi-gloss paper, this 12x18 poster delivers rich color depth and fine detail, perfect for framing and display in a home office, reading nook, or academic workspace. The dramatic emerald glow and intricate corrosion patterns create an immersive focal point for any intellectual interior.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 poster (unframed)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Premium semi-gloss poster paper (200 gsm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Size:&lt;/strong&gt; 12 x 18 inches (30.5 x 45.7 cm)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Style:&lt;/strong&gt; Dark Academia, Mentor-Grade&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DNA Profile:&lt;/strong&gt; Corroded Copper, Cracked Glass, Kintsugi Gold, Toxic Jade, Ancient Parchment, brass clockwork, jade bioluminescence, alchemical dust, cinematic lighting&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Use Cases:&lt;/strong&gt; Study desk decor, library wall art, vintage collector gift, student room accent, alchemical aesthetic display&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; The main image shows the actual product customers receive. Additional images are bonus concept/detail reference images and do not represent extra products or selectable variations.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Image Note: The main image shows the actual poster you will receive. Additional images are bonus concept and detail reference images; they do not represent extra products or selectable variations.&lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Dark Academia Reading Nook Art Hermetic Knowledge Lantern Library 12x18 Matte&lt;/h2&gt;&lt;p&gt;This listing is part of a focused search-intent experiment for home library wall art. It is written for buyers decorating reading nooks, home libraries, dorm study walls, meditation rooms, and quiet apartment corners, not for generic wall-art browsing.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Includes:&lt;/strong&gt; One 12x18 matte poster, produced on demand through Printify.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Visual Mood:&lt;/strong&gt; Reading Nook Warm Lamp.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design Language:&lt;/strong&gt; matte paper mood, cinematic depth, smoky jade tones, and calm visual focus.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Search Lane:&lt;/strong&gt; dark academia reading nook, home library wall art, book nook decor, study room poster, scholar desk decor, dorm library print.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Image Note:&lt;/strong&gt; This is a single printed poster. The main artwork is the product customers receive; any additional gallery images are concept/detail references.&lt;/p&gt;&lt;p&gt;&lt;small&gt;Reference SKU: Poster-Academia-0023. Prior title: Hermetic Knowledge Lantern Dark Academia Poster 12x18 Library Decor Wall Study&lt;/small&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -24996,6 +25179,31 @@
       </c>
       <c r="AC231" s="1" t="n">
         <v>46149.07928880787</v>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>2026-05-08 08:17:21 -0400</t>
+        </is>
+      </c>
+      <c r="AL231" t="inlineStr">
+        <is>
+          <t>A_LOW_COMPETITION_NICHE</t>
+        </is>
+      </c>
+      <c r="AM231" t="inlineStr">
+        <is>
+          <t>home library wall art</t>
+        </is>
+      </c>
+      <c r="AN231" t="inlineStr">
+        <is>
+          <t>reading_nook_warm_lamp</t>
+        </is>
       </c>
     </row>
     <row r="232">
@@ -29528,7 +29736,7 @@
       </c>
       <c r="AH268" t="inlineStr">
         <is>
-          <t>MULTI_TRACK_PENDING_PRINTIFY_SYNC</t>
+          <t>MULTI_TRACK_SYNCED_PRINTIFY_PUBLISH</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
